--- a/web/EXCEL_TEMPLATE/KHNV/KHNV_DK01A.xlsx
+++ b/web/EXCEL_TEMPLATE/KHNV/KHNV_DK01A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\GIT\IMS_REPORTS\web\EXCEL_TEMPLATE\KHNV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5426CED5-39A1-4753-B57B-92CC6A369A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09EAEAC2-96F6-4ADA-BE0B-F4698C0FA684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11280" xr2:uid="{FEA2E927-87FC-4F8F-B922-B59702A7794E}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="DK_01A" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">DK_01A!$A$1:$G$87</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">DK_01A!$A$1:$G$101</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">DK_01A!$8:$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -140,7 +140,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -198,17 +198,6 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val=".VnTime"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -225,12 +214,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="9"/>
-        <bgColor indexed="64"/>
+        <fgColor indexed="22"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -331,37 +319,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -378,90 +340,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -480,6 +364,23 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="9" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -510,6 +411,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -518,9 +422,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -839,14 +740,15 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <dimension ref="A1:J117"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="17" style="1" customWidth="1"/>
     <col min="3" max="3" width="80.140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" style="1" customWidth="1"/>
     <col min="7" max="7" width="14.28515625" style="2" customWidth="1"/>
     <col min="8" max="257" width="9.140625" style="2"/>
     <col min="258" max="258" width="6.42578125" style="2" customWidth="1"/>
@@ -1166,130 +1068,130 @@
     <col min="16136" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="F1" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="41"/>
-    </row>
-    <row r="2" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="F1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="20"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
-      <c r="F2" s="50" t="s">
+      <c r="F2" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="50"/>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="G2" s="30"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="51" t="s">
+      <c r="D3" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="51" t="s">
+      <c r="D4" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-    </row>
-    <row r="5" spans="1:10" ht="18.75">
-      <c r="A5" s="52" t="s">
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+    </row>
+    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-    </row>
-    <row r="6" spans="1:10" ht="15">
-      <c r="A6" s="53" t="s">
+      <c r="B5" s="32"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+    </row>
+    <row r="6" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="1:10">
-      <c r="E7" s="40" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E7" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="40"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="40"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="42" t="s">
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="42" t="s">
+      <c r="C8" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="42" t="s">
+      <c r="D8" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="42"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="44" t="s">
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="21"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="47" t="s">
+      <c r="F9" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="48"/>
-    </row>
-    <row r="10" spans="1:10" ht="12.75">
-      <c r="A10" s="42"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="49" t="s">
+      <c r="G9" s="27"/>
+    </row>
+    <row r="10" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="49" t="s">
+      <c r="G10" s="28" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="12.75">
-      <c r="A11" s="42"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="49"/>
-    </row>
-    <row r="12" spans="1:10" ht="12.75">
+    <row r="11" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="21"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+    </row>
+    <row r="12" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>1</v>
       </c>
@@ -1310,734 +1212,1364 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="10" customFormat="1">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="9"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="12"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="15"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="15"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="12"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="12"/>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="12"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="12"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="12"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="12"/>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="12"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="11"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="12"/>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="12"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="11"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="12"/>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="12"/>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="11"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="12"/>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="11"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="12"/>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="11"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="12"/>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="11"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="12"/>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="12"/>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="12"/>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="21"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="12"/>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="12"/>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="11"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="20"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="12"/>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" s="11"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="17"/>
-      <c r="G37" s="12"/>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="11"/>
-      <c r="B38" s="11"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="12"/>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="11"/>
-      <c r="B39" s="11"/>
-      <c r="C39" s="21"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="12"/>
-    </row>
-    <row r="40" spans="1:7" s="26" customFormat="1">
-      <c r="A40" s="24"/>
-      <c r="B40" s="24"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="15"/>
-    </row>
-    <row r="41" spans="1:7" s="26" customFormat="1">
-      <c r="A41" s="27"/>
-      <c r="B41" s="27"/>
-      <c r="C41" s="25"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="17"/>
-      <c r="G41" s="15"/>
-    </row>
-    <row r="42" spans="1:7" s="26" customFormat="1">
-      <c r="A42" s="27"/>
-      <c r="B42" s="27"/>
+    <row r="13" spans="1:10" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="17">
+        <f>D13+F13</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="18"/>
+      <c r="G13" s="17">
+        <f>IFERROR(F13/D13*100,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+      <c r="A14" s="15"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="17">
+        <f t="shared" ref="E14:E77" si="0">D14+F14</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="18"/>
+      <c r="G14" s="17">
+        <f t="shared" ref="G14:G77" si="1">IFERROR(F14/D14*100,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+      <c r="A15" s="15"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="18"/>
+      <c r="G15" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="18"/>
+      <c r="G16" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="18"/>
+      <c r="G17" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A18" s="15"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="18"/>
+      <c r="G18" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="18"/>
+      <c r="G19" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A20" s="15"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="18"/>
+      <c r="G20" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A21" s="15"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="18"/>
+      <c r="G21" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F22" s="18"/>
+      <c r="G22" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A23" s="15"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F23" s="18"/>
+      <c r="G23" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A24" s="15"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F24" s="18"/>
+      <c r="G24" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A25" s="15"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F25" s="18"/>
+      <c r="G25" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A26" s="15"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F26" s="18"/>
+      <c r="G26" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F27" s="18"/>
+      <c r="G27" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F28" s="18"/>
+      <c r="G28" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A29" s="15"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="18"/>
+      <c r="G29" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A30" s="15"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F30" s="18"/>
+      <c r="G30" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A31" s="15"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F31" s="18"/>
+      <c r="G31" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A32" s="15"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F32" s="18"/>
+      <c r="G32" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A33" s="15"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F33" s="18"/>
+      <c r="G33" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A34" s="15"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F34" s="18"/>
+      <c r="G34" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A35" s="15"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F35" s="18"/>
+      <c r="G35" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A36" s="15"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F36" s="18"/>
+      <c r="G36" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A37" s="15"/>
+      <c r="B37" s="15"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F37" s="18"/>
+      <c r="G37" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A38" s="15"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F38" s="18"/>
+      <c r="G38" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A39" s="15"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F39" s="18"/>
+      <c r="G39" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A40" s="15"/>
+      <c r="B40" s="15"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="18"/>
+      <c r="G40" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A41" s="15"/>
+      <c r="B41" s="15"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F41" s="18"/>
+      <c r="G41" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A42" s="15"/>
+      <c r="B42" s="15"/>
       <c r="C42" s="14"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="15"/>
-    </row>
-    <row r="43" spans="1:7" s="26" customFormat="1">
-      <c r="A43" s="27"/>
-      <c r="B43" s="27"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F42" s="18"/>
+      <c r="G42" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A43" s="15"/>
+      <c r="B43" s="15"/>
       <c r="C43" s="14"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="17"/>
-      <c r="G43" s="15"/>
-    </row>
-    <row r="44" spans="1:7" s="26" customFormat="1">
-      <c r="A44" s="27"/>
-      <c r="B44" s="27"/>
-      <c r="C44" s="28"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="17"/>
-      <c r="G44" s="15"/>
-    </row>
-    <row r="45" spans="1:7" s="26" customFormat="1">
-      <c r="A45" s="27"/>
-      <c r="B45" s="27"/>
-      <c r="C45" s="28"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="17"/>
-      <c r="G45" s="15"/>
-    </row>
-    <row r="46" spans="1:7" s="26" customFormat="1">
-      <c r="A46" s="29"/>
-      <c r="B46" s="29"/>
-      <c r="C46" s="28"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="17"/>
-      <c r="G46" s="15"/>
-    </row>
-    <row r="47" spans="1:7" s="26" customFormat="1">
-      <c r="A47" s="11"/>
-      <c r="B47" s="11"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="17"/>
-      <c r="G47" s="15"/>
-    </row>
-    <row r="48" spans="1:7" s="10" customFormat="1">
-      <c r="A48" s="6"/>
-      <c r="B48" s="6"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="11"/>
-      <c r="G48" s="9"/>
-    </row>
-    <row r="49" spans="1:7" s="10" customFormat="1">
-      <c r="A49" s="11"/>
-      <c r="B49" s="11"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="9"/>
-    </row>
-    <row r="50" spans="1:7" s="10" customFormat="1">
-      <c r="A50" s="11"/>
-      <c r="B50" s="11"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="9"/>
-    </row>
-    <row r="51" spans="1:7" s="10" customFormat="1">
-      <c r="A51" s="11"/>
-      <c r="B51" s="11"/>
-      <c r="C51" s="16"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="9"/>
-    </row>
-    <row r="52" spans="1:7" s="10" customFormat="1">
-      <c r="A52" s="11"/>
-      <c r="B52" s="11"/>
-      <c r="C52" s="16"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="9"/>
-    </row>
-    <row r="53" spans="1:7" s="10" customFormat="1">
-      <c r="A53" s="11"/>
-      <c r="B53" s="11"/>
-      <c r="C53" s="8"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="11"/>
-      <c r="G53" s="9"/>
-    </row>
-    <row r="54" spans="1:7" s="10" customFormat="1">
-      <c r="A54" s="11"/>
-      <c r="B54" s="11"/>
-      <c r="C54" s="16"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="9"/>
-    </row>
-    <row r="55" spans="1:7" s="10" customFormat="1">
-      <c r="A55" s="17"/>
-      <c r="B55" s="17"/>
-      <c r="C55" s="18"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="11"/>
-      <c r="G55" s="9"/>
-    </row>
-    <row r="56" spans="1:7" s="10" customFormat="1">
-      <c r="A56" s="11"/>
-      <c r="B56" s="11"/>
-      <c r="C56" s="16"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="9"/>
-    </row>
-    <row r="57" spans="1:7" s="10" customFormat="1">
-      <c r="A57" s="11"/>
-      <c r="B57" s="11"/>
-      <c r="C57" s="16"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="9"/>
-    </row>
-    <row r="58" spans="1:7" s="10" customFormat="1">
-      <c r="A58" s="11"/>
-      <c r="B58" s="11"/>
-      <c r="C58" s="16"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="9"/>
-    </row>
-    <row r="59" spans="1:7" s="10" customFormat="1">
-      <c r="A59" s="11"/>
-      <c r="B59" s="11"/>
-      <c r="C59" s="16"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="9"/>
-    </row>
-    <row r="60" spans="1:7" s="10" customFormat="1">
-      <c r="A60" s="11"/>
-      <c r="B60" s="11"/>
-      <c r="C60" s="16"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="11"/>
-      <c r="G60" s="9"/>
-    </row>
-    <row r="61" spans="1:7" s="10" customFormat="1">
-      <c r="A61" s="11"/>
-      <c r="B61" s="11"/>
-      <c r="C61" s="16"/>
-      <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="9"/>
-    </row>
-    <row r="62" spans="1:7" s="10" customFormat="1">
-      <c r="A62" s="11"/>
-      <c r="B62" s="11"/>
-      <c r="C62" s="16"/>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="11"/>
-      <c r="G62" s="9"/>
-    </row>
-    <row r="63" spans="1:7" s="10" customFormat="1">
-      <c r="A63" s="11"/>
-      <c r="B63" s="11"/>
-      <c r="C63" s="16"/>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="11"/>
-      <c r="G63" s="9"/>
-    </row>
-    <row r="64" spans="1:7" s="10" customFormat="1">
-      <c r="A64" s="11"/>
-      <c r="B64" s="11"/>
-      <c r="C64" s="16"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="11"/>
-      <c r="G64" s="9"/>
-    </row>
-    <row r="65" spans="1:7" s="10" customFormat="1">
-      <c r="A65" s="11"/>
-      <c r="B65" s="11"/>
-      <c r="C65" s="16"/>
-      <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="11"/>
-      <c r="G65" s="9"/>
-    </row>
-    <row r="66" spans="1:7">
-      <c r="A66" s="11"/>
-      <c r="B66" s="11"/>
-      <c r="C66" s="16"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="8"/>
-      <c r="G66" s="12"/>
-    </row>
-    <row r="67" spans="1:7">
-      <c r="A67" s="11"/>
-      <c r="B67" s="11"/>
-      <c r="C67" s="16"/>
-      <c r="D67" s="8"/>
-      <c r="E67" s="8"/>
-      <c r="F67" s="8"/>
-      <c r="G67" s="12"/>
-    </row>
-    <row r="68" spans="1:7">
-      <c r="A68" s="11"/>
-      <c r="B68" s="11"/>
-      <c r="C68" s="20"/>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
-      <c r="G68" s="12"/>
-    </row>
-    <row r="69" spans="1:7">
-      <c r="A69" s="11"/>
-      <c r="B69" s="11"/>
-      <c r="C69" s="20"/>
-      <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
-      <c r="F69" s="8"/>
-      <c r="G69" s="12"/>
-    </row>
-    <row r="70" spans="1:7">
-      <c r="A70" s="11"/>
-      <c r="B70" s="11"/>
-      <c r="C70" s="20"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="8"/>
-      <c r="G70" s="12"/>
-    </row>
-    <row r="71" spans="1:7">
-      <c r="A71" s="11"/>
-      <c r="B71" s="11"/>
-      <c r="C71" s="20"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
-      <c r="G71" s="12"/>
-    </row>
-    <row r="72" spans="1:7">
-      <c r="A72" s="11"/>
-      <c r="B72" s="11"/>
-      <c r="C72" s="20"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="8"/>
-      <c r="G72" s="12"/>
-    </row>
-    <row r="73" spans="1:7">
-      <c r="A73" s="11"/>
-      <c r="B73" s="11"/>
-      <c r="C73" s="20"/>
-      <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="8"/>
-      <c r="G73" s="12"/>
-    </row>
-    <row r="74" spans="1:7">
-      <c r="A74" s="11"/>
-      <c r="B74" s="11"/>
-      <c r="C74" s="20"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="8"/>
-      <c r="G74" s="12"/>
-    </row>
-    <row r="75" spans="1:7">
-      <c r="A75" s="11"/>
-      <c r="B75" s="11"/>
-      <c r="C75" s="20"/>
-      <c r="D75" s="8"/>
-      <c r="E75" s="8"/>
-      <c r="F75" s="8"/>
-      <c r="G75" s="12"/>
-    </row>
-    <row r="76" spans="1:7">
-      <c r="A76" s="11"/>
-      <c r="B76" s="11"/>
-      <c r="C76" s="21"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="17"/>
-      <c r="G76" s="12"/>
-    </row>
-    <row r="77" spans="1:7">
-      <c r="A77" s="11"/>
-      <c r="B77" s="11"/>
-      <c r="C77" s="22"/>
-      <c r="D77" s="23"/>
-      <c r="E77" s="8"/>
-      <c r="F77" s="17"/>
-      <c r="G77" s="12"/>
-    </row>
-    <row r="78" spans="1:7">
-      <c r="A78" s="11"/>
-      <c r="B78" s="11"/>
-      <c r="C78" s="20"/>
-      <c r="D78" s="8"/>
-      <c r="E78" s="8"/>
-      <c r="F78" s="17"/>
-      <c r="G78" s="12"/>
-    </row>
-    <row r="79" spans="1:7">
-      <c r="A79" s="11"/>
-      <c r="B79" s="11"/>
-      <c r="C79" s="20"/>
-      <c r="D79" s="8"/>
-      <c r="E79" s="8"/>
-      <c r="F79" s="17"/>
-      <c r="G79" s="12"/>
-    </row>
-    <row r="80" spans="1:7">
-      <c r="A80" s="11"/>
-      <c r="B80" s="11"/>
-      <c r="C80" s="20"/>
-      <c r="D80" s="8"/>
-      <c r="E80" s="8"/>
-      <c r="F80" s="17"/>
-      <c r="G80" s="12"/>
-    </row>
-    <row r="81" spans="1:10">
-      <c r="A81" s="30"/>
-      <c r="B81" s="30"/>
-      <c r="C81" s="31"/>
-      <c r="D81" s="31"/>
-      <c r="E81" s="31"/>
-      <c r="F81" s="31"/>
-      <c r="G81" s="32"/>
-    </row>
-    <row r="82" spans="1:10">
-      <c r="A82" s="33"/>
-      <c r="B82" s="33"/>
-      <c r="C82" s="8"/>
-      <c r="D82" s="8"/>
-      <c r="E82" s="8"/>
-      <c r="F82" s="8"/>
-      <c r="G82" s="9"/>
-    </row>
-    <row r="83" spans="1:10">
-      <c r="A83" s="34"/>
-      <c r="B83" s="34"/>
-      <c r="C83" s="35"/>
-      <c r="G83" s="10"/>
-    </row>
-    <row r="84" spans="1:10">
-      <c r="A84" s="34"/>
-      <c r="B84" s="34"/>
-      <c r="C84" s="1" t="s">
+      <c r="D43" s="16"/>
+      <c r="E43" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F43" s="18"/>
+      <c r="G43" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A44" s="15"/>
+      <c r="B44" s="15"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F44" s="18"/>
+      <c r="G44" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A45" s="15"/>
+      <c r="B45" s="15"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F45" s="18"/>
+      <c r="G45" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A46" s="15"/>
+      <c r="B46" s="15"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="16"/>
+      <c r="E46" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F46" s="18"/>
+      <c r="G46" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A47" s="15"/>
+      <c r="B47" s="15"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F47" s="18"/>
+      <c r="G47" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A48" s="15"/>
+      <c r="B48" s="15"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F48" s="18"/>
+      <c r="G48" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A49" s="15"/>
+      <c r="B49" s="15"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="16"/>
+      <c r="E49" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F49" s="18"/>
+      <c r="G49" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A50" s="15"/>
+      <c r="B50" s="15"/>
+      <c r="C50" s="14"/>
+      <c r="D50" s="16"/>
+      <c r="E50" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F50" s="18"/>
+      <c r="G50" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A51" s="15"/>
+      <c r="B51" s="15"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F51" s="18"/>
+      <c r="G51" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A52" s="15"/>
+      <c r="B52" s="15"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F52" s="18"/>
+      <c r="G52" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A53" s="15"/>
+      <c r="B53" s="15"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="16"/>
+      <c r="E53" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F53" s="18"/>
+      <c r="G53" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A54" s="15"/>
+      <c r="B54" s="15"/>
+      <c r="C54" s="14"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F54" s="18"/>
+      <c r="G54" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A55" s="15"/>
+      <c r="B55" s="15"/>
+      <c r="C55" s="14"/>
+      <c r="D55" s="16"/>
+      <c r="E55" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F55" s="18"/>
+      <c r="G55" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A56" s="15"/>
+      <c r="B56" s="15"/>
+      <c r="C56" s="14"/>
+      <c r="D56" s="16"/>
+      <c r="E56" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F56" s="18"/>
+      <c r="G56" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A57" s="15"/>
+      <c r="B57" s="15"/>
+      <c r="C57" s="14"/>
+      <c r="D57" s="16"/>
+      <c r="E57" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F57" s="18"/>
+      <c r="G57" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A58" s="15"/>
+      <c r="B58" s="15"/>
+      <c r="C58" s="14"/>
+      <c r="D58" s="16"/>
+      <c r="E58" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F58" s="18"/>
+      <c r="G58" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A59" s="15"/>
+      <c r="B59" s="15"/>
+      <c r="C59" s="14"/>
+      <c r="D59" s="16"/>
+      <c r="E59" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F59" s="18"/>
+      <c r="G59" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A60" s="15"/>
+      <c r="B60" s="15"/>
+      <c r="C60" s="14"/>
+      <c r="D60" s="16"/>
+      <c r="E60" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F60" s="18"/>
+      <c r="G60" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A61" s="15"/>
+      <c r="B61" s="15"/>
+      <c r="C61" s="14"/>
+      <c r="D61" s="16"/>
+      <c r="E61" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F61" s="18"/>
+      <c r="G61" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A62" s="15"/>
+      <c r="B62" s="15"/>
+      <c r="C62" s="14"/>
+      <c r="D62" s="16"/>
+      <c r="E62" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F62" s="18"/>
+      <c r="G62" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A63" s="15"/>
+      <c r="B63" s="15"/>
+      <c r="C63" s="14"/>
+      <c r="D63" s="16"/>
+      <c r="E63" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F63" s="18"/>
+      <c r="G63" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A64" s="15"/>
+      <c r="B64" s="15"/>
+      <c r="C64" s="14"/>
+      <c r="D64" s="16"/>
+      <c r="E64" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F64" s="18"/>
+      <c r="G64" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A65" s="15"/>
+      <c r="B65" s="15"/>
+      <c r="C65" s="14"/>
+      <c r="D65" s="16"/>
+      <c r="E65" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F65" s="18"/>
+      <c r="G65" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A66" s="15"/>
+      <c r="B66" s="15"/>
+      <c r="C66" s="14"/>
+      <c r="D66" s="16"/>
+      <c r="E66" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F66" s="18"/>
+      <c r="G66" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A67" s="15"/>
+      <c r="B67" s="15"/>
+      <c r="C67" s="14"/>
+      <c r="D67" s="16"/>
+      <c r="E67" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F67" s="18"/>
+      <c r="G67" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A68" s="15"/>
+      <c r="B68" s="15"/>
+      <c r="C68" s="14"/>
+      <c r="D68" s="16"/>
+      <c r="E68" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F68" s="18"/>
+      <c r="G68" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A69" s="15"/>
+      <c r="B69" s="15"/>
+      <c r="C69" s="14"/>
+      <c r="D69" s="16"/>
+      <c r="E69" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F69" s="18"/>
+      <c r="G69" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A70" s="15"/>
+      <c r="B70" s="15"/>
+      <c r="C70" s="14"/>
+      <c r="D70" s="16"/>
+      <c r="E70" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F70" s="18"/>
+      <c r="G70" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A71" s="15"/>
+      <c r="B71" s="15"/>
+      <c r="C71" s="14"/>
+      <c r="D71" s="16"/>
+      <c r="E71" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F71" s="18"/>
+      <c r="G71" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A72" s="15"/>
+      <c r="B72" s="15"/>
+      <c r="C72" s="14"/>
+      <c r="D72" s="16"/>
+      <c r="E72" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F72" s="18"/>
+      <c r="G72" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A73" s="15"/>
+      <c r="B73" s="15"/>
+      <c r="C73" s="14"/>
+      <c r="D73" s="16"/>
+      <c r="E73" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F73" s="18"/>
+      <c r="G73" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A74" s="15"/>
+      <c r="B74" s="15"/>
+      <c r="C74" s="14"/>
+      <c r="D74" s="16"/>
+      <c r="E74" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F74" s="18"/>
+      <c r="G74" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A75" s="15"/>
+      <c r="B75" s="15"/>
+      <c r="C75" s="14"/>
+      <c r="D75" s="16"/>
+      <c r="E75" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F75" s="18"/>
+      <c r="G75" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A76" s="15"/>
+      <c r="B76" s="15"/>
+      <c r="C76" s="14"/>
+      <c r="D76" s="16"/>
+      <c r="E76" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F76" s="18"/>
+      <c r="G76" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A77" s="15"/>
+      <c r="B77" s="15"/>
+      <c r="C77" s="14"/>
+      <c r="D77" s="16"/>
+      <c r="E77" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F77" s="18"/>
+      <c r="G77" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A78" s="15"/>
+      <c r="B78" s="15"/>
+      <c r="C78" s="14"/>
+      <c r="D78" s="16"/>
+      <c r="E78" s="17">
+        <f t="shared" ref="E78:E96" si="2">D78+F78</f>
+        <v>0</v>
+      </c>
+      <c r="F78" s="18"/>
+      <c r="G78" s="17">
+        <f t="shared" ref="G78:G96" si="3">IFERROR(F78/D78*100,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A79" s="15"/>
+      <c r="B79" s="15"/>
+      <c r="C79" s="14"/>
+      <c r="D79" s="16"/>
+      <c r="E79" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F79" s="18"/>
+      <c r="G79" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A80" s="15"/>
+      <c r="B80" s="15"/>
+      <c r="C80" s="14"/>
+      <c r="D80" s="16"/>
+      <c r="E80" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F80" s="18"/>
+      <c r="G80" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A81" s="15"/>
+      <c r="B81" s="15"/>
+      <c r="C81" s="14"/>
+      <c r="D81" s="16"/>
+      <c r="E81" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F81" s="18"/>
+      <c r="G81" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A82" s="15"/>
+      <c r="B82" s="15"/>
+      <c r="C82" s="14"/>
+      <c r="D82" s="16"/>
+      <c r="E82" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F82" s="18"/>
+      <c r="G82" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A83" s="15"/>
+      <c r="B83" s="15"/>
+      <c r="C83" s="14"/>
+      <c r="D83" s="16"/>
+      <c r="E83" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F83" s="18"/>
+      <c r="G83" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A84" s="15"/>
+      <c r="B84" s="15"/>
+      <c r="C84" s="14"/>
+      <c r="D84" s="16"/>
+      <c r="E84" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F84" s="18"/>
+      <c r="G84" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A85" s="15"/>
+      <c r="B85" s="15"/>
+      <c r="C85" s="14"/>
+      <c r="D85" s="16"/>
+      <c r="E85" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F85" s="18"/>
+      <c r="G85" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A86" s="15"/>
+      <c r="B86" s="15"/>
+      <c r="C86" s="14"/>
+      <c r="D86" s="16"/>
+      <c r="E86" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F86" s="18"/>
+      <c r="G86" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A87" s="15"/>
+      <c r="B87" s="15"/>
+      <c r="C87" s="14"/>
+      <c r="D87" s="16"/>
+      <c r="E87" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F87" s="18"/>
+      <c r="G87" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A88" s="15"/>
+      <c r="B88" s="15"/>
+      <c r="C88" s="14"/>
+      <c r="D88" s="16"/>
+      <c r="E88" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F88" s="18"/>
+      <c r="G88" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A89" s="15"/>
+      <c r="B89" s="15"/>
+      <c r="C89" s="14"/>
+      <c r="D89" s="16"/>
+      <c r="E89" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F89" s="18"/>
+      <c r="G89" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A90" s="15"/>
+      <c r="B90" s="15"/>
+      <c r="C90" s="14"/>
+      <c r="D90" s="16"/>
+      <c r="E90" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F90" s="18"/>
+      <c r="G90" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A91" s="15"/>
+      <c r="B91" s="15"/>
+      <c r="C91" s="14"/>
+      <c r="D91" s="16"/>
+      <c r="E91" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F91" s="18"/>
+      <c r="G91" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A92" s="15"/>
+      <c r="B92" s="15"/>
+      <c r="C92" s="14"/>
+      <c r="D92" s="16"/>
+      <c r="E92" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F92" s="18"/>
+      <c r="G92" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A93" s="15"/>
+      <c r="B93" s="15"/>
+      <c r="C93" s="14"/>
+      <c r="D93" s="16"/>
+      <c r="E93" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F93" s="18"/>
+      <c r="G93" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A94" s="15"/>
+      <c r="B94" s="15"/>
+      <c r="C94" s="14"/>
+      <c r="D94" s="16"/>
+      <c r="E94" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F94" s="18"/>
+      <c r="G94" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A95" s="15"/>
+      <c r="B95" s="15"/>
+      <c r="C95" s="14"/>
+      <c r="D95" s="16"/>
+      <c r="E95" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F95" s="18"/>
+      <c r="G95" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A96" s="15"/>
+      <c r="B96" s="15"/>
+      <c r="C96" s="14"/>
+      <c r="D96" s="16"/>
+      <c r="E96" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F96" s="18"/>
+      <c r="G96" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A97" s="8"/>
+      <c r="B97" s="8"/>
+      <c r="C97" s="9"/>
+      <c r="G97" s="6"/>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A98" s="8"/>
+      <c r="B98" s="8"/>
+      <c r="C98" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G84" s="10"/>
-    </row>
-    <row r="85" spans="1:10">
-      <c r="A85" s="36"/>
-      <c r="B85" s="36"/>
-      <c r="C85" s="36"/>
-      <c r="D85" s="40" t="s">
+      <c r="G98" s="6"/>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A99" s="10"/>
+      <c r="B99" s="10"/>
+      <c r="C99" s="10"/>
+      <c r="D99" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E85" s="40"/>
-      <c r="F85" s="40"/>
-      <c r="G85" s="40"/>
-    </row>
-    <row r="86" spans="1:10">
-      <c r="A86" s="37"/>
-      <c r="B86" s="37"/>
-      <c r="C86" s="38" t="s">
+      <c r="E99" s="19"/>
+      <c r="F99" s="19"/>
+      <c r="G99" s="19"/>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A100" s="11"/>
+      <c r="B100" s="11"/>
+      <c r="C100" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D86" s="41"/>
-      <c r="E86" s="41"/>
-      <c r="F86" s="41"/>
-      <c r="G86" s="41"/>
-      <c r="H86" s="37"/>
-      <c r="I86" s="37"/>
-      <c r="J86" s="37"/>
-    </row>
-    <row r="87" spans="1:10">
-      <c r="A87" s="35"/>
-      <c r="B87" s="35"/>
-      <c r="C87" s="34" t="s">
+      <c r="D100" s="20"/>
+      <c r="E100" s="20"/>
+      <c r="F100" s="20"/>
+      <c r="G100" s="20"/>
+      <c r="H100" s="11"/>
+      <c r="I100" s="11"/>
+      <c r="J100" s="11"/>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A101" s="9"/>
+      <c r="B101" s="9"/>
+      <c r="C101" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D87" s="40"/>
-      <c r="E87" s="40"/>
-      <c r="F87" s="40"/>
-      <c r="G87" s="40"/>
-      <c r="H87" s="39"/>
-      <c r="I87" s="39"/>
-      <c r="J87" s="39"/>
-    </row>
-    <row r="88" spans="1:10" ht="12.75">
-      <c r="A88" s="2"/>
-      <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
-    </row>
-    <row r="93" spans="1:10">
-      <c r="C93" s="37" t="s">
+      <c r="D101" s="19"/>
+      <c r="E101" s="19"/>
+      <c r="F101" s="19"/>
+      <c r="G101" s="19"/>
+      <c r="H101" s="13"/>
+      <c r="I101" s="13"/>
+      <c r="J101" s="13"/>
+    </row>
+    <row r="102" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A102" s="2"/>
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="2"/>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C107" s="11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="94" spans="1:10">
-      <c r="C94" s="1" t="s">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C108" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="95" spans="1:10">
-      <c r="C95" s="1" t="s">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C109" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="96" spans="1:10">
-      <c r="C96" s="1" t="s">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C110" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="97" spans="3:3">
-      <c r="C97" s="1" t="s">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C111" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="98" spans="3:3">
-      <c r="C98" s="1" t="s">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C112" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="100" spans="3:3">
-      <c r="C100" s="1" t="s">
+    <row r="114" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C114" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="103" spans="3:3">
-      <c r="C103" s="37"/>
+    <row r="117" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C117" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -2048,9 +2580,9 @@
     <mergeCell ref="D3:G3"/>
     <mergeCell ref="D4:G4"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="D85:G85"/>
-    <mergeCell ref="D86:G86"/>
-    <mergeCell ref="D87:G87"/>
+    <mergeCell ref="D99:G99"/>
+    <mergeCell ref="D100:G100"/>
+    <mergeCell ref="D101:G101"/>
     <mergeCell ref="E7:H7"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="C8:C11"/>

--- a/web/EXCEL_TEMPLATE/KHNV/KHNV_DK01A.xlsx
+++ b/web/EXCEL_TEMPLATE/KHNV/KHNV_DK01A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\GIT\IMS_REPORTS\build\web\EXCEL_TEMPLATE\KHNV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09EAEAC2-96F6-4ADA-BE0B-F4698C0FA684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB7FE30E-B530-4D3A-890C-693F0DB5BC1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11280" xr2:uid="{FEA2E927-87FC-4F8F-B922-B59702A7794E}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="DK_01A" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">DK_01A!$A$1:$G$101</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">DK_01A!$A$1:$G$171</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">DK_01A!$8:$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -381,14 +381,26 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -409,18 +421,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -740,7 +740,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J117"/>
+  <dimension ref="A1:J187"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" customWidth="1"/>
@@ -1069,127 +1069,127 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="F1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="20"/>
+      <c r="F1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="21"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="30"/>
+      <c r="G2" s="22"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
     </row>
     <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="32"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
     </row>
     <row r="6" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="21"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="23" t="s">
+      <c r="A9" s="20"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="26" t="s">
+      <c r="F9" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="27"/>
+      <c r="G9" s="31"/>
     </row>
     <row r="10" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="21"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="28" t="s">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="28" t="s">
+      <c r="G10" s="32" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="21"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
     </row>
     <row r="12" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
@@ -1233,12 +1233,12 @@
       <c r="C14" s="14"/>
       <c r="D14" s="16"/>
       <c r="E14" s="17">
-        <f t="shared" ref="E14:E77" si="0">D14+F14</f>
+        <f t="shared" ref="E14:E134" si="0">D14+F14</f>
         <v>0</v>
       </c>
       <c r="F14" s="18"/>
       <c r="G14" s="17">
-        <f t="shared" ref="G14:G77" si="1">IFERROR(F14/D14*100,0)</f>
+        <f t="shared" ref="G14:G134" si="1">IFERROR(F14/D14*100,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1617,11 +1617,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A40" s="15"/>
       <c r="B40" s="15"/>
       <c r="C40" s="14"/>
-      <c r="D40" s="16"/>
+      <c r="D40" s="18"/>
       <c r="E40" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1632,11 +1632,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A41" s="15"/>
       <c r="B41" s="15"/>
       <c r="C41" s="14"/>
-      <c r="D41" s="16"/>
+      <c r="D41" s="18"/>
       <c r="E41" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1647,11 +1647,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A42" s="15"/>
       <c r="B42" s="15"/>
       <c r="C42" s="14"/>
-      <c r="D42" s="16"/>
+      <c r="D42" s="18"/>
       <c r="E42" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1662,11 +1662,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="15"/>
       <c r="B43" s="15"/>
       <c r="C43" s="14"/>
-      <c r="D43" s="16"/>
+      <c r="D43" s="18"/>
       <c r="E43" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1677,11 +1677,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="15"/>
       <c r="B44" s="15"/>
       <c r="C44" s="14"/>
-      <c r="D44" s="16"/>
+      <c r="D44" s="18"/>
       <c r="E44" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1692,11 +1692,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A45" s="15"/>
       <c r="B45" s="15"/>
       <c r="C45" s="14"/>
-      <c r="D45" s="16"/>
+      <c r="D45" s="18"/>
       <c r="E45" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1707,11 +1707,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="15"/>
       <c r="B46" s="15"/>
       <c r="C46" s="14"/>
-      <c r="D46" s="16"/>
+      <c r="D46" s="18"/>
       <c r="E46" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1722,11 +1722,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A47" s="15"/>
       <c r="B47" s="15"/>
       <c r="C47" s="14"/>
-      <c r="D47" s="16"/>
+      <c r="D47" s="18"/>
       <c r="E47" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1737,11 +1737,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A48" s="15"/>
       <c r="B48" s="15"/>
       <c r="C48" s="14"/>
-      <c r="D48" s="16"/>
+      <c r="D48" s="18"/>
       <c r="E48" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1752,11 +1752,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A49" s="15"/>
       <c r="B49" s="15"/>
       <c r="C49" s="14"/>
-      <c r="D49" s="16"/>
+      <c r="D49" s="18"/>
       <c r="E49" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1767,11 +1767,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A50" s="15"/>
       <c r="B50" s="15"/>
       <c r="C50" s="14"/>
-      <c r="D50" s="16"/>
+      <c r="D50" s="18"/>
       <c r="E50" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1782,11 +1782,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A51" s="15"/>
       <c r="B51" s="15"/>
       <c r="C51" s="14"/>
-      <c r="D51" s="16"/>
+      <c r="D51" s="18"/>
       <c r="E51" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1797,11 +1797,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A52" s="15"/>
       <c r="B52" s="15"/>
       <c r="C52" s="14"/>
-      <c r="D52" s="16"/>
+      <c r="D52" s="18"/>
       <c r="E52" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1812,11 +1812,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A53" s="15"/>
       <c r="B53" s="15"/>
       <c r="C53" s="14"/>
-      <c r="D53" s="16"/>
+      <c r="D53" s="18"/>
       <c r="E53" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1827,11 +1827,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A54" s="15"/>
       <c r="B54" s="15"/>
       <c r="C54" s="14"/>
-      <c r="D54" s="16"/>
+      <c r="D54" s="18"/>
       <c r="E54" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1842,11 +1842,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A55" s="15"/>
       <c r="B55" s="15"/>
       <c r="C55" s="14"/>
-      <c r="D55" s="16"/>
+      <c r="D55" s="18"/>
       <c r="E55" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1857,11 +1857,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A56" s="15"/>
       <c r="B56" s="15"/>
       <c r="C56" s="14"/>
-      <c r="D56" s="16"/>
+      <c r="D56" s="18"/>
       <c r="E56" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1872,11 +1872,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A57" s="15"/>
       <c r="B57" s="15"/>
       <c r="C57" s="14"/>
-      <c r="D57" s="16"/>
+      <c r="D57" s="18"/>
       <c r="E57" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1887,11 +1887,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A58" s="15"/>
       <c r="B58" s="15"/>
       <c r="C58" s="14"/>
-      <c r="D58" s="16"/>
+      <c r="D58" s="18"/>
       <c r="E58" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1902,11 +1902,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A59" s="15"/>
       <c r="B59" s="15"/>
       <c r="C59" s="14"/>
-      <c r="D59" s="16"/>
+      <c r="D59" s="18"/>
       <c r="E59" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1917,11 +1917,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A60" s="15"/>
       <c r="B60" s="15"/>
       <c r="C60" s="14"/>
-      <c r="D60" s="16"/>
+      <c r="D60" s="18"/>
       <c r="E60" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1932,11 +1932,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A61" s="15"/>
       <c r="B61" s="15"/>
       <c r="C61" s="14"/>
-      <c r="D61" s="16"/>
+      <c r="D61" s="18"/>
       <c r="E61" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1947,11 +1947,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A62" s="15"/>
       <c r="B62" s="15"/>
       <c r="C62" s="14"/>
-      <c r="D62" s="16"/>
+      <c r="D62" s="18"/>
       <c r="E62" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1962,11 +1962,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A63" s="15"/>
       <c r="B63" s="15"/>
       <c r="C63" s="14"/>
-      <c r="D63" s="16"/>
+      <c r="D63" s="18"/>
       <c r="E63" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1977,11 +1977,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A64" s="15"/>
       <c r="B64" s="15"/>
       <c r="C64" s="14"/>
-      <c r="D64" s="16"/>
+      <c r="D64" s="18"/>
       <c r="E64" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1992,11 +1992,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A65" s="15"/>
       <c r="B65" s="15"/>
       <c r="C65" s="14"/>
-      <c r="D65" s="16"/>
+      <c r="D65" s="18"/>
       <c r="E65" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2007,11 +2007,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A66" s="15"/>
       <c r="B66" s="15"/>
       <c r="C66" s="14"/>
-      <c r="D66" s="16"/>
+      <c r="D66" s="18"/>
       <c r="E66" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2022,11 +2022,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A67" s="15"/>
       <c r="B67" s="15"/>
       <c r="C67" s="14"/>
-      <c r="D67" s="16"/>
+      <c r="D67" s="18"/>
       <c r="E67" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2037,11 +2037,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A68" s="15"/>
       <c r="B68" s="15"/>
       <c r="C68" s="14"/>
-      <c r="D68" s="16"/>
+      <c r="D68" s="18"/>
       <c r="E68" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2052,11 +2052,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A69" s="15"/>
       <c r="B69" s="15"/>
       <c r="C69" s="14"/>
-      <c r="D69" s="16"/>
+      <c r="D69" s="18"/>
       <c r="E69" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2067,11 +2067,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A70" s="15"/>
       <c r="B70" s="15"/>
       <c r="C70" s="14"/>
-      <c r="D70" s="16"/>
+      <c r="D70" s="18"/>
       <c r="E70" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2082,11 +2082,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A71" s="15"/>
       <c r="B71" s="15"/>
       <c r="C71" s="14"/>
-      <c r="D71" s="16"/>
+      <c r="D71" s="18"/>
       <c r="E71" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2097,11 +2097,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A72" s="15"/>
       <c r="B72" s="15"/>
       <c r="C72" s="14"/>
-      <c r="D72" s="16"/>
+      <c r="D72" s="18"/>
       <c r="E72" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2112,11 +2112,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A73" s="15"/>
       <c r="B73" s="15"/>
       <c r="C73" s="14"/>
-      <c r="D73" s="16"/>
+      <c r="D73" s="18"/>
       <c r="E73" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2127,11 +2127,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A74" s="15"/>
       <c r="B74" s="15"/>
       <c r="C74" s="14"/>
-      <c r="D74" s="16"/>
+      <c r="D74" s="18"/>
       <c r="E74" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2142,11 +2142,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A75" s="15"/>
       <c r="B75" s="15"/>
       <c r="C75" s="14"/>
-      <c r="D75" s="16"/>
+      <c r="D75" s="18"/>
       <c r="E75" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2157,11 +2157,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A76" s="15"/>
       <c r="B76" s="15"/>
       <c r="C76" s="14"/>
-      <c r="D76" s="16"/>
+      <c r="D76" s="18"/>
       <c r="E76" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2172,11 +2172,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A77" s="15"/>
       <c r="B77" s="15"/>
       <c r="C77" s="14"/>
-      <c r="D77" s="16"/>
+      <c r="D77" s="18"/>
       <c r="E77" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2187,108 +2187,108 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A78" s="15"/>
       <c r="B78" s="15"/>
       <c r="C78" s="14"/>
-      <c r="D78" s="16"/>
+      <c r="D78" s="18"/>
       <c r="E78" s="17">
-        <f t="shared" ref="E78:E96" si="2">D78+F78</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F78" s="18"/>
       <c r="G78" s="17">
-        <f t="shared" ref="G78:G96" si="3">IFERROR(F78/D78*100,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A79" s="15"/>
       <c r="B79" s="15"/>
       <c r="C79" s="14"/>
-      <c r="D79" s="16"/>
+      <c r="D79" s="18"/>
       <c r="E79" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F79" s="18"/>
       <c r="G79" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A80" s="15"/>
       <c r="B80" s="15"/>
       <c r="C80" s="14"/>
-      <c r="D80" s="16"/>
+      <c r="D80" s="18"/>
       <c r="E80" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F80" s="18"/>
       <c r="G80" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A81" s="15"/>
       <c r="B81" s="15"/>
       <c r="C81" s="14"/>
-      <c r="D81" s="16"/>
+      <c r="D81" s="18"/>
       <c r="E81" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F81" s="18"/>
       <c r="G81" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A82" s="15"/>
       <c r="B82" s="15"/>
       <c r="C82" s="14"/>
-      <c r="D82" s="16"/>
+      <c r="D82" s="18"/>
       <c r="E82" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F82" s="18"/>
       <c r="G82" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A83" s="15"/>
       <c r="B83" s="15"/>
       <c r="C83" s="14"/>
-      <c r="D83" s="16"/>
+      <c r="D83" s="18"/>
       <c r="E83" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F83" s="18"/>
       <c r="G83" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A84" s="15"/>
       <c r="B84" s="15"/>
       <c r="C84" s="14"/>
-      <c r="D84" s="16"/>
+      <c r="D84" s="18"/>
       <c r="E84" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F84" s="18"/>
       <c r="G84" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2296,14 +2296,14 @@
       <c r="A85" s="15"/>
       <c r="B85" s="15"/>
       <c r="C85" s="14"/>
-      <c r="D85" s="16"/>
+      <c r="D85" s="18"/>
       <c r="E85" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F85" s="18"/>
       <c r="G85" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2311,14 +2311,14 @@
       <c r="A86" s="15"/>
       <c r="B86" s="15"/>
       <c r="C86" s="14"/>
-      <c r="D86" s="16"/>
+      <c r="D86" s="18"/>
       <c r="E86" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F86" s="18"/>
       <c r="G86" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2326,14 +2326,14 @@
       <c r="A87" s="15"/>
       <c r="B87" s="15"/>
       <c r="C87" s="14"/>
-      <c r="D87" s="16"/>
+      <c r="D87" s="18"/>
       <c r="E87" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F87" s="18"/>
       <c r="G87" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2341,14 +2341,14 @@
       <c r="A88" s="15"/>
       <c r="B88" s="15"/>
       <c r="C88" s="14"/>
-      <c r="D88" s="16"/>
+      <c r="D88" s="18"/>
       <c r="E88" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F88" s="18"/>
       <c r="G88" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2356,14 +2356,14 @@
       <c r="A89" s="15"/>
       <c r="B89" s="15"/>
       <c r="C89" s="14"/>
-      <c r="D89" s="16"/>
+      <c r="D89" s="18"/>
       <c r="E89" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F89" s="18"/>
       <c r="G89" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2371,14 +2371,14 @@
       <c r="A90" s="15"/>
       <c r="B90" s="15"/>
       <c r="C90" s="14"/>
-      <c r="D90" s="16"/>
+      <c r="D90" s="18"/>
       <c r="E90" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F90" s="18"/>
       <c r="G90" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2386,14 +2386,14 @@
       <c r="A91" s="15"/>
       <c r="B91" s="15"/>
       <c r="C91" s="14"/>
-      <c r="D91" s="16"/>
+      <c r="D91" s="18"/>
       <c r="E91" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F91" s="18"/>
       <c r="G91" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2401,14 +2401,14 @@
       <c r="A92" s="15"/>
       <c r="B92" s="15"/>
       <c r="C92" s="14"/>
-      <c r="D92" s="16"/>
+      <c r="D92" s="18"/>
       <c r="E92" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F92" s="18"/>
       <c r="G92" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2416,14 +2416,14 @@
       <c r="A93" s="15"/>
       <c r="B93" s="15"/>
       <c r="C93" s="14"/>
-      <c r="D93" s="16"/>
+      <c r="D93" s="18"/>
       <c r="E93" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F93" s="18"/>
       <c r="G93" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2431,14 +2431,14 @@
       <c r="A94" s="15"/>
       <c r="B94" s="15"/>
       <c r="C94" s="14"/>
-      <c r="D94" s="16"/>
+      <c r="D94" s="18"/>
       <c r="E94" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F94" s="18"/>
       <c r="G94" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2446,14 +2446,14 @@
       <c r="A95" s="15"/>
       <c r="B95" s="15"/>
       <c r="C95" s="14"/>
-      <c r="D95" s="16"/>
+      <c r="D95" s="18"/>
       <c r="E95" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F95" s="18"/>
       <c r="G95" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2461,128 +2461,1171 @@
       <c r="A96" s="15"/>
       <c r="B96" s="15"/>
       <c r="C96" s="14"/>
-      <c r="D96" s="16"/>
+      <c r="D96" s="18"/>
       <c r="E96" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F96" s="18"/>
       <c r="G96" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A97" s="15"/>
+      <c r="B97" s="15"/>
+      <c r="C97" s="14"/>
+      <c r="D97" s="16"/>
+      <c r="E97" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F97" s="18"/>
+      <c r="G97" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A98" s="15"/>
+      <c r="B98" s="15"/>
+      <c r="C98" s="14"/>
+      <c r="D98" s="16"/>
+      <c r="E98" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F98" s="18"/>
+      <c r="G98" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A99" s="15"/>
+      <c r="B99" s="15"/>
+      <c r="C99" s="14"/>
+      <c r="D99" s="16"/>
+      <c r="E99" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F99" s="18"/>
+      <c r="G99" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A100" s="15"/>
+      <c r="B100" s="15"/>
+      <c r="C100" s="14"/>
+      <c r="D100" s="16"/>
+      <c r="E100" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F100" s="18"/>
+      <c r="G100" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A101" s="15"/>
+      <c r="B101" s="15"/>
+      <c r="C101" s="14"/>
+      <c r="D101" s="16"/>
+      <c r="E101" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F101" s="18"/>
+      <c r="G101" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A102" s="15"/>
+      <c r="B102" s="15"/>
+      <c r="C102" s="14"/>
+      <c r="D102" s="16"/>
+      <c r="E102" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F102" s="18"/>
+      <c r="G102" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A103" s="15"/>
+      <c r="B103" s="15"/>
+      <c r="C103" s="14"/>
+      <c r="D103" s="16"/>
+      <c r="E103" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F103" s="18"/>
+      <c r="G103" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A104" s="15"/>
+      <c r="B104" s="15"/>
+      <c r="C104" s="14"/>
+      <c r="D104" s="16"/>
+      <c r="E104" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F104" s="18"/>
+      <c r="G104" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A105" s="15"/>
+      <c r="B105" s="15"/>
+      <c r="C105" s="14"/>
+      <c r="D105" s="16"/>
+      <c r="E105" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F105" s="18"/>
+      <c r="G105" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A106" s="15"/>
+      <c r="B106" s="15"/>
+      <c r="C106" s="14"/>
+      <c r="D106" s="16"/>
+      <c r="E106" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F106" s="18"/>
+      <c r="G106" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A107" s="15"/>
+      <c r="B107" s="15"/>
+      <c r="C107" s="14"/>
+      <c r="D107" s="16"/>
+      <c r="E107" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F107" s="18"/>
+      <c r="G107" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A108" s="15"/>
+      <c r="B108" s="15"/>
+      <c r="C108" s="14"/>
+      <c r="D108" s="16"/>
+      <c r="E108" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F108" s="18"/>
+      <c r="G108" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A109" s="15"/>
+      <c r="B109" s="15"/>
+      <c r="C109" s="14"/>
+      <c r="D109" s="16"/>
+      <c r="E109" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F109" s="18"/>
+      <c r="G109" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A110" s="15"/>
+      <c r="B110" s="15"/>
+      <c r="C110" s="14"/>
+      <c r="D110" s="16"/>
+      <c r="E110" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F110" s="18"/>
+      <c r="G110" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A111" s="15"/>
+      <c r="B111" s="15"/>
+      <c r="C111" s="14"/>
+      <c r="D111" s="16"/>
+      <c r="E111" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F111" s="18"/>
+      <c r="G111" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A112" s="15"/>
+      <c r="B112" s="15"/>
+      <c r="C112" s="14"/>
+      <c r="D112" s="16"/>
+      <c r="E112" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F112" s="18"/>
+      <c r="G112" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A113" s="15"/>
+      <c r="B113" s="15"/>
+      <c r="C113" s="14"/>
+      <c r="D113" s="16"/>
+      <c r="E113" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F113" s="18"/>
+      <c r="G113" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A114" s="15"/>
+      <c r="B114" s="15"/>
+      <c r="C114" s="14"/>
+      <c r="D114" s="16"/>
+      <c r="E114" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F114" s="18"/>
+      <c r="G114" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A115" s="15"/>
+      <c r="B115" s="15"/>
+      <c r="C115" s="14"/>
+      <c r="D115" s="16"/>
+      <c r="E115" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F115" s="18"/>
+      <c r="G115" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A116" s="15"/>
+      <c r="B116" s="15"/>
+      <c r="C116" s="14"/>
+      <c r="D116" s="16"/>
+      <c r="E116" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F116" s="18"/>
+      <c r="G116" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A117" s="15"/>
+      <c r="B117" s="15"/>
+      <c r="C117" s="14"/>
+      <c r="D117" s="16"/>
+      <c r="E117" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F117" s="18"/>
+      <c r="G117" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A118" s="15"/>
+      <c r="B118" s="15"/>
+      <c r="C118" s="14"/>
+      <c r="D118" s="16"/>
+      <c r="E118" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F118" s="18"/>
+      <c r="G118" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A119" s="15"/>
+      <c r="B119" s="15"/>
+      <c r="C119" s="14"/>
+      <c r="D119" s="16"/>
+      <c r="E119" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F119" s="18"/>
+      <c r="G119" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A120" s="15"/>
+      <c r="B120" s="15"/>
+      <c r="C120" s="14"/>
+      <c r="D120" s="16"/>
+      <c r="E120" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F120" s="18"/>
+      <c r="G120" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A121" s="15"/>
+      <c r="B121" s="15"/>
+      <c r="C121" s="14"/>
+      <c r="D121" s="16"/>
+      <c r="E121" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F121" s="18"/>
+      <c r="G121" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A122" s="15"/>
+      <c r="B122" s="15"/>
+      <c r="C122" s="14"/>
+      <c r="D122" s="16"/>
+      <c r="E122" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F122" s="18"/>
+      <c r="G122" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A123" s="15"/>
+      <c r="B123" s="15"/>
+      <c r="C123" s="14"/>
+      <c r="D123" s="16"/>
+      <c r="E123" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F123" s="18"/>
+      <c r="G123" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A124" s="15"/>
+      <c r="B124" s="15"/>
+      <c r="C124" s="14"/>
+      <c r="D124" s="16"/>
+      <c r="E124" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F124" s="18"/>
+      <c r="G124" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A125" s="15"/>
+      <c r="B125" s="15"/>
+      <c r="C125" s="14"/>
+      <c r="D125" s="16"/>
+      <c r="E125" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F125" s="18"/>
+      <c r="G125" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A126" s="15"/>
+      <c r="B126" s="15"/>
+      <c r="C126" s="14"/>
+      <c r="D126" s="16"/>
+      <c r="E126" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F126" s="18"/>
+      <c r="G126" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A127" s="15"/>
+      <c r="B127" s="15"/>
+      <c r="C127" s="14"/>
+      <c r="D127" s="16"/>
+      <c r="E127" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F127" s="18"/>
+      <c r="G127" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A128" s="15"/>
+      <c r="B128" s="15"/>
+      <c r="C128" s="14"/>
+      <c r="D128" s="16"/>
+      <c r="E128" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F128" s="18"/>
+      <c r="G128" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A129" s="15"/>
+      <c r="B129" s="15"/>
+      <c r="C129" s="14"/>
+      <c r="D129" s="16"/>
+      <c r="E129" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F129" s="18"/>
+      <c r="G129" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A130" s="15"/>
+      <c r="B130" s="15"/>
+      <c r="C130" s="14"/>
+      <c r="D130" s="16"/>
+      <c r="E130" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F130" s="18"/>
+      <c r="G130" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A131" s="15"/>
+      <c r="B131" s="15"/>
+      <c r="C131" s="14"/>
+      <c r="D131" s="16"/>
+      <c r="E131" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F131" s="18"/>
+      <c r="G131" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A132" s="15"/>
+      <c r="B132" s="15"/>
+      <c r="C132" s="14"/>
+      <c r="D132" s="16"/>
+      <c r="E132" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F132" s="18"/>
+      <c r="G132" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A133" s="15"/>
+      <c r="B133" s="15"/>
+      <c r="C133" s="14"/>
+      <c r="D133" s="16"/>
+      <c r="E133" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F133" s="18"/>
+      <c r="G133" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A134" s="15"/>
+      <c r="B134" s="15"/>
+      <c r="C134" s="14"/>
+      <c r="D134" s="16"/>
+      <c r="E134" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F134" s="18"/>
+      <c r="G134" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A135" s="15"/>
+      <c r="B135" s="15"/>
+      <c r="C135" s="14"/>
+      <c r="D135" s="16"/>
+      <c r="E135" s="17">
+        <f t="shared" ref="E135:E166" si="2">D135+F135</f>
+        <v>0</v>
+      </c>
+      <c r="F135" s="18"/>
+      <c r="G135" s="17">
+        <f t="shared" ref="G135:G166" si="3">IFERROR(F135/D135*100,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A136" s="15"/>
+      <c r="B136" s="15"/>
+      <c r="C136" s="14"/>
+      <c r="D136" s="16"/>
+      <c r="E136" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F136" s="18"/>
+      <c r="G136" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A97" s="8"/>
-      <c r="B97" s="8"/>
-      <c r="C97" s="9"/>
-      <c r="G97" s="6"/>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A98" s="8"/>
-      <c r="B98" s="8"/>
-      <c r="C98" s="1" t="s">
+    <row r="137" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A137" s="15"/>
+      <c r="B137" s="15"/>
+      <c r="C137" s="14"/>
+      <c r="D137" s="16"/>
+      <c r="E137" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F137" s="18"/>
+      <c r="G137" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A138" s="15"/>
+      <c r="B138" s="15"/>
+      <c r="C138" s="14"/>
+      <c r="D138" s="16"/>
+      <c r="E138" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F138" s="18"/>
+      <c r="G138" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A139" s="15"/>
+      <c r="B139" s="15"/>
+      <c r="C139" s="14"/>
+      <c r="D139" s="16"/>
+      <c r="E139" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F139" s="18"/>
+      <c r="G139" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A140" s="15"/>
+      <c r="B140" s="15"/>
+      <c r="C140" s="14"/>
+      <c r="D140" s="16"/>
+      <c r="E140" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F140" s="18"/>
+      <c r="G140" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A141" s="15"/>
+      <c r="B141" s="15"/>
+      <c r="C141" s="14"/>
+      <c r="D141" s="18"/>
+      <c r="E141" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F141" s="18"/>
+      <c r="G141" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A142" s="15"/>
+      <c r="B142" s="15"/>
+      <c r="C142" s="14"/>
+      <c r="D142" s="18"/>
+      <c r="E142" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F142" s="18"/>
+      <c r="G142" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A143" s="15"/>
+      <c r="B143" s="15"/>
+      <c r="C143" s="14"/>
+      <c r="D143" s="18"/>
+      <c r="E143" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F143" s="18"/>
+      <c r="G143" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A144" s="15"/>
+      <c r="B144" s="15"/>
+      <c r="C144" s="14"/>
+      <c r="D144" s="18"/>
+      <c r="E144" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F144" s="18"/>
+      <c r="G144" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A145" s="15"/>
+      <c r="B145" s="15"/>
+      <c r="C145" s="14"/>
+      <c r="D145" s="18"/>
+      <c r="E145" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F145" s="18"/>
+      <c r="G145" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A146" s="15"/>
+      <c r="B146" s="15"/>
+      <c r="C146" s="14"/>
+      <c r="D146" s="18"/>
+      <c r="E146" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F146" s="18"/>
+      <c r="G146" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A147" s="15"/>
+      <c r="B147" s="15"/>
+      <c r="C147" s="14"/>
+      <c r="D147" s="18"/>
+      <c r="E147" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F147" s="18"/>
+      <c r="G147" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A148" s="15"/>
+      <c r="B148" s="15"/>
+      <c r="C148" s="14"/>
+      <c r="D148" s="18"/>
+      <c r="E148" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F148" s="18"/>
+      <c r="G148" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A149" s="15"/>
+      <c r="B149" s="15"/>
+      <c r="C149" s="14"/>
+      <c r="D149" s="18"/>
+      <c r="E149" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F149" s="18"/>
+      <c r="G149" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A150" s="15"/>
+      <c r="B150" s="15"/>
+      <c r="C150" s="14"/>
+      <c r="D150" s="18"/>
+      <c r="E150" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F150" s="18"/>
+      <c r="G150" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A151" s="15"/>
+      <c r="B151" s="15"/>
+      <c r="C151" s="14"/>
+      <c r="D151" s="18"/>
+      <c r="E151" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F151" s="18"/>
+      <c r="G151" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A152" s="15"/>
+      <c r="B152" s="15"/>
+      <c r="C152" s="14"/>
+      <c r="D152" s="18"/>
+      <c r="E152" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F152" s="18"/>
+      <c r="G152" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A153" s="15"/>
+      <c r="B153" s="15"/>
+      <c r="C153" s="14"/>
+      <c r="D153" s="18"/>
+      <c r="E153" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F153" s="18"/>
+      <c r="G153" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A154" s="15"/>
+      <c r="B154" s="15"/>
+      <c r="C154" s="14"/>
+      <c r="D154" s="16"/>
+      <c r="E154" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F154" s="18"/>
+      <c r="G154" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A155" s="15"/>
+      <c r="B155" s="15"/>
+      <c r="C155" s="14"/>
+      <c r="D155" s="16"/>
+      <c r="E155" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F155" s="18"/>
+      <c r="G155" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A156" s="15"/>
+      <c r="B156" s="15"/>
+      <c r="C156" s="14"/>
+      <c r="D156" s="16"/>
+      <c r="E156" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F156" s="18"/>
+      <c r="G156" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A157" s="15"/>
+      <c r="B157" s="15"/>
+      <c r="C157" s="14"/>
+      <c r="D157" s="16"/>
+      <c r="E157" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F157" s="18"/>
+      <c r="G157" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A158" s="15"/>
+      <c r="B158" s="15"/>
+      <c r="C158" s="14"/>
+      <c r="D158" s="16"/>
+      <c r="E158" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F158" s="18"/>
+      <c r="G158" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A159" s="15"/>
+      <c r="B159" s="15"/>
+      <c r="C159" s="14"/>
+      <c r="D159" s="16"/>
+      <c r="E159" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F159" s="18"/>
+      <c r="G159" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A160" s="15"/>
+      <c r="B160" s="15"/>
+      <c r="C160" s="14"/>
+      <c r="D160" s="16"/>
+      <c r="E160" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F160" s="18"/>
+      <c r="G160" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+      <c r="A161" s="15"/>
+      <c r="B161" s="15"/>
+      <c r="C161" s="14"/>
+      <c r="D161" s="16"/>
+      <c r="E161" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F161" s="18"/>
+      <c r="G161" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+      <c r="A162" s="15"/>
+      <c r="B162" s="15"/>
+      <c r="C162" s="14"/>
+      <c r="D162" s="16"/>
+      <c r="E162" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F162" s="18"/>
+      <c r="G162" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+      <c r="A163" s="15"/>
+      <c r="B163" s="15"/>
+      <c r="C163" s="14"/>
+      <c r="D163" s="16"/>
+      <c r="E163" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F163" s="18"/>
+      <c r="G163" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+      <c r="A164" s="15"/>
+      <c r="B164" s="15"/>
+      <c r="C164" s="14"/>
+      <c r="D164" s="16"/>
+      <c r="E164" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F164" s="18"/>
+      <c r="G164" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+      <c r="A165" s="15"/>
+      <c r="B165" s="15"/>
+      <c r="C165" s="14"/>
+      <c r="D165" s="16"/>
+      <c r="E165" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F165" s="18"/>
+      <c r="G165" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+      <c r="A166" s="15"/>
+      <c r="B166" s="15"/>
+      <c r="C166" s="14"/>
+      <c r="D166" s="16"/>
+      <c r="E166" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F166" s="18"/>
+      <c r="G166" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A167" s="8"/>
+      <c r="B167" s="8"/>
+      <c r="C167" s="9"/>
+      <c r="G167" s="6"/>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A168" s="8"/>
+      <c r="B168" s="8"/>
+      <c r="C168" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G98" s="6"/>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A99" s="10"/>
-      <c r="B99" s="10"/>
-      <c r="C99" s="10"/>
-      <c r="D99" s="19" t="s">
+      <c r="G168" s="6"/>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A169" s="10"/>
+      <c r="B169" s="10"/>
+      <c r="C169" s="10"/>
+      <c r="D169" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="E99" s="19"/>
-      <c r="F99" s="19"/>
-      <c r="G99" s="19"/>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A100" s="11"/>
-      <c r="B100" s="11"/>
-      <c r="C100" s="12" t="s">
+      <c r="E169" s="25"/>
+      <c r="F169" s="25"/>
+      <c r="G169" s="25"/>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A170" s="11"/>
+      <c r="B170" s="11"/>
+      <c r="C170" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D100" s="20"/>
-      <c r="E100" s="20"/>
-      <c r="F100" s="20"/>
-      <c r="G100" s="20"/>
-      <c r="H100" s="11"/>
-      <c r="I100" s="11"/>
-      <c r="J100" s="11"/>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A101" s="9"/>
-      <c r="B101" s="9"/>
-      <c r="C101" s="8" t="s">
+      <c r="D170" s="21"/>
+      <c r="E170" s="21"/>
+      <c r="F170" s="21"/>
+      <c r="G170" s="21"/>
+      <c r="H170" s="11"/>
+      <c r="I170" s="11"/>
+      <c r="J170" s="11"/>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A171" s="9"/>
+      <c r="B171" s="9"/>
+      <c r="C171" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D101" s="19"/>
-      <c r="E101" s="19"/>
-      <c r="F101" s="19"/>
-      <c r="G101" s="19"/>
-      <c r="H101" s="13"/>
-      <c r="I101" s="13"/>
-      <c r="J101" s="13"/>
-    </row>
-    <row r="102" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A102" s="2"/>
-      <c r="B102" s="2"/>
-      <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
-      <c r="F102" s="2"/>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="C107" s="11" t="s">
+      <c r="D171" s="25"/>
+      <c r="E171" s="25"/>
+      <c r="F171" s="25"/>
+      <c r="G171" s="25"/>
+      <c r="H171" s="13"/>
+      <c r="I171" s="13"/>
+      <c r="J171" s="13"/>
+    </row>
+    <row r="172" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A172" s="2"/>
+      <c r="B172" s="2"/>
+      <c r="C172" s="2"/>
+      <c r="D172" s="2"/>
+      <c r="E172" s="2"/>
+      <c r="F172" s="2"/>
+    </row>
+    <row r="177" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C177" s="11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="C108" s="1" t="s">
+    <row r="178" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C178" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="C109" s="1" t="s">
+    <row r="179" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C179" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="C110" s="1" t="s">
+    <row r="180" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C180" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="C111" s="1" t="s">
+    <row r="181" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C181" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="C112" s="1" t="s">
+    <row r="182" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C182" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="114" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C114" s="1" t="s">
+    <row r="184" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C184" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="117" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C117" s="11"/>
+    <row r="187" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C187" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="D4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="D99:G99"/>
-    <mergeCell ref="D100:G100"/>
-    <mergeCell ref="D101:G101"/>
+    <mergeCell ref="D169:G169"/>
+    <mergeCell ref="D170:G170"/>
+    <mergeCell ref="D171:G171"/>
     <mergeCell ref="E7:H7"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="C8:C11"/>
@@ -2592,6 +3635,13 @@
     <mergeCell ref="F9:G9"/>
     <mergeCell ref="F10:F11"/>
     <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="3.937007874015748E-2" right="3.937007874015748E-2" top="0.19685039370078741" bottom="3.937007874015748E-2" header="3.937007874015748E-2" footer="3.937007874015748E-2"/>

--- a/web/EXCEL_TEMPLATE/KHNV/KHNV_DK01A.xlsx
+++ b/web/EXCEL_TEMPLATE/KHNV/KHNV_DK01A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\GIT\IMS_REPORTS\build\web\EXCEL_TEMPLATE\KHNV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\khnv_01a_thang5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB7FE30E-B530-4D3A-890C-693F0DB5BC1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A05635F-CBEA-4704-813B-E0F296286168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11280" xr2:uid="{FEA2E927-87FC-4F8F-B922-B59702A7794E}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="256">
   <si>
     <t>Biểu số 01a/NHCS-KH</t>
   </si>
@@ -64,9 +64,6 @@
     </r>
   </si>
   <si>
-    <t>NHU CẦU VAY VỐN TÍN DỤNG CHÍNH SÁCH NĂM 2022</t>
-  </si>
-  <si>
     <t>Đơn vị: triệu đồng, %, hộ, người</t>
   </si>
   <si>
@@ -76,18 +73,9 @@
     <t>CHỈ TIÊU</t>
   </si>
   <si>
-    <t>Ước dư nợ đến 31/12/2021</t>
-  </si>
-  <si>
-    <t>Nhu cầu vốn năm 2022</t>
-  </si>
-  <si>
     <t>Tổng số</t>
   </si>
   <si>
-    <t>Tăng, giảm so với 31/12/2021</t>
-  </si>
-  <si>
     <t>Số tuyệt đối (+/-)</t>
   </si>
   <si>
@@ -130,17 +118,713 @@
     <t>Số liệu trên biểu số 01a/NHCS-KH sẽ làm cơ sở để tổng hợp lên biểu số 01/NHCS-KH và 02/NHCS-KH</t>
   </si>
   <si>
-    <t>THÔN: ………………………… XÃ/PHƯỜNG/THỊ TRẤN: ……………………………………</t>
-  </si>
-  <si>
     <t>MÃ CHỈ TIÊU</t>
+  </si>
+  <si>
+    <t>NHU CẦU VAY VỐN TÍN DỤNG CHÍNH SÁCH NĂM 2021</t>
+  </si>
+  <si>
+    <t>Ước dư nợ đến 31/12/2020</t>
+  </si>
+  <si>
+    <t>Nhu cầu vốn năm 2021</t>
+  </si>
+  <si>
+    <t>Tăng, giảm so với 31/12/2020</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>XD00001</t>
+  </si>
+  <si>
+    <t>TỔNG CỘNG (A+B)</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>XD00002</t>
+  </si>
+  <si>
+    <t>NHU CẦU VAY NGUỒN VỐN TRUNG ƯƠNG</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>XD00003</t>
+  </si>
+  <si>
+    <t>Cho vay hộ nghèo theo Nghị định số 78/2002/NĐ-CP</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>XD00004</t>
+  </si>
+  <si>
+    <t>Cho vay hộ cận nghèo theo QĐ 15/2013/QĐ-TTg</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>XD00005</t>
+  </si>
+  <si>
+    <t>Cho vay hộ mới thoát nghèo theo Quyết định số 28/2015/QĐ-TTg</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>XD00006</t>
+  </si>
+  <si>
+    <t>Cho vay học sinh, sinh viên theo QĐ 157/2007/QĐ-TTg</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>XD00007</t>
+  </si>
+  <si>
+    <t>Cho vay vốn Quỹ quốc gia về việc làm theo Nghị định 61/2015/NĐ-CP</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>XD00008</t>
+  </si>
+  <si>
+    <t>Cho vay người lao động đi làm việc ở nước ngoài theo Quyết định số 365/QĐ-NHNN,  Quyết định số 1465/QĐ-TTg, Quyết định số 63/2015/QĐ-TTg và Nghị định số 61/2015/NĐ-CP</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>XD00009</t>
+  </si>
+  <si>
+    <t>Cho vay để ký quỹ đối với người lao động đi làm việc tại Hàn Quốc</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>XD00010</t>
+  </si>
+  <si>
+    <t>Cho vay xuất khẩu lao động tại huyện nghèo theo QĐ 71/2009/QĐ-TTg</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>XD00011</t>
+  </si>
+  <si>
+    <t>Cho vay Chương trình NS-VSMT NT theo QĐ 62/2004/QĐ-TTg</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>XD00012</t>
+  </si>
+  <si>
+    <t>Cho vay hộ gia đình SXKD tại VKK theo QĐ 31/2007/QĐ-TTg</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>XD00013</t>
+  </si>
+  <si>
+    <t>Cho vay mua trả chậm nhà ở vùng ĐBSCL và Tây Nguyên</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>XD00014</t>
+  </si>
+  <si>
+    <t>Cho vay xây dựng cụm tuyến dân cư và nhà ở vùng ngập lũ ĐBSCL giai đoạn 2018-2020 (QĐ 714/QĐ-TTg)</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>XD00015</t>
+  </si>
+  <si>
+    <t>Cho vay hộ đồng bào DTTS ĐBKK theo QĐ 54/2012/QĐ-TTg (QĐ 32/2007/QĐ-TTg)</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>XD00016</t>
+  </si>
+  <si>
+    <t>Cho vay đồng bào DTTS vùng ĐBSCL theo (QĐ 29/2013/QĐ-TTg) (QĐ 74/2008/QĐ-TTg)</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>XD00017</t>
+  </si>
+  <si>
+    <t>Cho vay đồng bào DTTS theo QĐ 755/QĐ-TTg</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>XD00018</t>
+  </si>
+  <si>
+    <t>Cho vay hỗ trợ hộ nghèo về nhà ở theo QĐ 167/2008/QĐ-TTg</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>XD00019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cho vay hỗ trợ hộ nghèo về nhà ở theo QĐ 33/2015/QĐ-TTg </t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>XD00020</t>
+  </si>
+  <si>
+    <t>Cho vay thương nhân tại VKK theo QĐ 92/2009/QĐ-TTg</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>XD00021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cho vay hỗ trợ hộ nghèo xây dựng nhà ở phòng, tránh bão, lụt khu vực miền Trung theo QĐ 48/2014/QĐ-TTg </t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>XD00022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cho vay đối với hộ gia đình và người nhiễm HIV, người sau cai nghiện ma túy, người điều trị nghiện các chất dạng thuốc phiện bằng thuốc thay thế, người bán dâm hoàn lương theo Quyết định số 29/2014/QĐ-TTg </t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>XD00023</t>
+  </si>
+  <si>
+    <t>Cho vay nhà ở xã hội theo NĐ 100/2015/NĐ-CP</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>XD00024</t>
+  </si>
+  <si>
+    <t>Trong đó: nhà ở công nhân trong khu công nghiệp</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>XD00025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cho vay trồng rừng sản xuất, phát triển chăn nuôi theo NĐ 75/2015/NĐ-CP </t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>XD00026</t>
+  </si>
+  <si>
+    <t>Cho vay hỗ trợ phát triển kinh tế - xã hội vùng dân tộc thiểu số và miền núi giai đoạn 2017 - 2020 theo Quyết định số 2085/QĐ-TTg</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>XD00027</t>
+  </si>
+  <si>
+    <t>Cho vay thanh niên xung phong cơ sở ở miền Nam tham gia kháng chiến giai đoạn 1965-1975</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>XD00028</t>
+  </si>
+  <si>
+    <t>Cho vay một số dự án vốn nước ngoài khác</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>XD00029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Cho vay dự án IFAD </t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>XD00030</t>
+  </si>
+  <si>
+    <t>- Cho vay dự án RIDP</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>XD00031</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Cho vay Phát triển DN vừa và nhỏ (Dự án KFW)</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>XD00032</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Cho vay Phát triển ngành Lâm nghiệp (Dự án FSDP)</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>XD00033</t>
+  </si>
+  <si>
+    <t>- Cho vay dự án HIV/AIDS</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>XD00034</t>
+  </si>
+  <si>
+    <t>- Cho vay dự án NIPPON (Mở rộng tài chính cho người khuyết tật)</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>XD00035</t>
+  </si>
+  <si>
+    <t>- Cho vay dự án CWPD</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>XD00036</t>
+  </si>
+  <si>
+    <t>Cho vay các đối tượng chính sách khác</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>XD00037</t>
+  </si>
+  <si>
+    <t>NHU CẦU VAY NGUỒN VỐN ĐỊA PHƯƠNG</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>XD00038</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>XD00039</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>XD00040</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>XD00041</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>XD00042</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>XD00043</t>
+  </si>
+  <si>
+    <t>Cho vay người lao động đi làm việc ở nước ngoài theo Quyết định số 365/QĐ-NHNN, Quyết định số 1465/QĐ-TTg, Quyết định số 63/2015/QĐ-TTg và Nghị định số 61/2015/NĐ-CP</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>XD00044</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>XD00045</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>XD00046</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>XD00047</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>XD00048</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>XD00049</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>XD00050</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>XD00051</t>
+  </si>
+  <si>
+    <t>Cho vay đồng bào DTTS vùng ĐBSCL theo QĐ 29/2013/QĐ-TTg (QĐ 74/2008/QĐ-TTg)</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>XD00052</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>XD00053</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>XD00054</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>XD00055</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>XD00056</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>XD00057</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>XD00058</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>XD00059</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>XD00060</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>XD00061</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>XD00062</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>XD00063</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>XD00064</t>
+  </si>
+  <si>
+    <t>THUYẾT MINH MỘT SỐ CHỈ TIÊU (Dự kiến năm kế hoạch)</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>XD00065</t>
+  </si>
+  <si>
+    <t>Số hộ dân cư trú trên địa bàn</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>XD00066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số hộ dân là hộ đồng bào dân tộc thiểu số </t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>XD00067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số hộ nghèo theo chuẩn hộ nghèo (giai đoạn 2021-2025) </t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>XD00068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số hộ nghèo đang còn dư nợ NHCSXH </t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>XD00069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số hộ nghèo đủ điều kiện vay vốn nhưng chưa được vay vốn NHCSXH </t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>XD00070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số hộ cận nghèo theo chuẩn hộ cận nghèo (giai đoạn 2021-2025) </t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>XD00071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số hộ cận nghèo đang còn dư nợ NHCSXH </t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>XD00072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số hộ cận nghèo đủ điều kiện vay vốn nhưng chưa được vay vốn NHCSXH </t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>XD00073</t>
+  </si>
+  <si>
+    <t>Số hộ mới thoát nghèo (giai đoạn 2019-2021)</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>XD00074</t>
+  </si>
+  <si>
+    <t>Số hộ gia đình sản xuất kinh doanh vùng khó khăn trên địa bàn</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>XD00075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số hộ gia đình SXKD đang còn dư nợ NHCSXH </t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>XD00076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số hộ gia đình SXKD đủ điều kiện vay vốn nhưng chưa được vay vốn NHCSXH </t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>XD00077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số thương nhân hoạt động thương mại tại vùng khó khăn </t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>XD00078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tổng số HSSV theo học các Trường ĐH, CĐ, THCN và dạy nghề </t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>XD00079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số HSSV đang còn dư nợ NHCSXH </t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>XD00080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số lao động có nhu cầu vay vốn giải quyết việc làm </t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>XD00081</t>
+  </si>
+  <si>
+    <t>Số lao động được vay vốn giải quyết việc làm trong năm</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>XD00082</t>
+  </si>
+  <si>
+    <t>Số lao động dự kiến được thu hút từ vay vốn giải quyết việc làm</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>XD00083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tổng số lao động có nhu cầu vay vốn đi lao động có thời hạn ở nước ngoài </t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>XD00084</t>
+  </si>
+  <si>
+    <t>Số công trình NS-VSMT NT dự kiến được xây dựng từ nguồn vốn vay NHCSXH</t>
+  </si>
+  <si>
+    <t>THÔN: ... XÃ/PHƯỜNG/THỊ TRẤN: …</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -196,13 +880,6 @@
       <sz val="11"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -323,7 +1000,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -381,7 +1058,17 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -422,6 +1109,12 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1069,127 +1762,127 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="F1" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="21"/>
+      <c r="F1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="24"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="22"/>
+      <c r="G2" s="25"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
     </row>
     <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-    </row>
-    <row r="6" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
+      <c r="A5" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+    </row>
+    <row r="6" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A6" s="22" t="s">
+        <v>255</v>
+      </c>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="20" t="s">
+      <c r="B8" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="20" t="s">
+      <c r="D8" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="23"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="F9" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="34"/>
+    </row>
+    <row r="10" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="23"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="G10" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="20"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="31"/>
-    </row>
-    <row r="10" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="20"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="32" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="11" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
+      <c r="A11" s="23"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
     </row>
     <row r="12" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
@@ -1203,7 +1896,7 @@
         <v>3</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F12" s="5">
         <v>5</v>
@@ -1213,39 +1906,57 @@
       </c>
     </row>
     <row r="13" spans="1:10" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A13" s="15"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="17">
+      <c r="A13" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="20"/>
+      <c r="E13" s="21">
         <f>D13+F13</f>
         <v>0</v>
       </c>
-      <c r="F13" s="18"/>
-      <c r="G13" s="17">
+      <c r="F13" s="20"/>
+      <c r="G13" s="21">
         <f>IFERROR(F13/D13*100,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A14" s="15"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="17">
+    <row r="14" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A14" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="20"/>
+      <c r="E14" s="21">
         <f t="shared" ref="E14:E134" si="0">D14+F14</f>
         <v>0</v>
       </c>
-      <c r="F14" s="18"/>
-      <c r="G14" s="17">
+      <c r="F14" s="20"/>
+      <c r="G14" s="21">
         <f t="shared" ref="G14:G134" si="1">IFERROR(F14/D14*100,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A15" s="15"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="14"/>
+      <c r="A15" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="37" t="s">
+        <v>35</v>
+      </c>
       <c r="D15" s="16"/>
       <c r="E15" s="17">
         <f t="shared" si="0"/>
@@ -1258,9 +1969,15 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="14"/>
+      <c r="A16" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="37" t="s">
+        <v>38</v>
+      </c>
       <c r="D16" s="16"/>
       <c r="E16" s="17">
         <f t="shared" si="0"/>
@@ -1273,9 +1990,15 @@
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A17" s="15"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="14"/>
+      <c r="A17" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="37" t="s">
+        <v>41</v>
+      </c>
       <c r="D17" s="16"/>
       <c r="E17" s="17">
         <f t="shared" si="0"/>
@@ -1288,9 +2011,15 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A18" s="15"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="14"/>
+      <c r="A18" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="37" t="s">
+        <v>44</v>
+      </c>
       <c r="D18" s="16"/>
       <c r="E18" s="17">
         <f t="shared" si="0"/>
@@ -1303,9 +2032,15 @@
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A19" s="15"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="14"/>
+      <c r="A19" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="37" t="s">
+        <v>47</v>
+      </c>
       <c r="D19" s="16"/>
       <c r="E19" s="17">
         <f t="shared" si="0"/>
@@ -1317,10 +2052,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="14"/>
+    <row r="20" spans="1:7" ht="45" x14ac:dyDescent="0.2">
+      <c r="A20" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="37" t="s">
+        <v>50</v>
+      </c>
       <c r="D20" s="16"/>
       <c r="E20" s="17">
         <f t="shared" si="0"/>
@@ -1333,9 +2074,15 @@
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A21" s="15"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="14"/>
+      <c r="A21" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="37" t="s">
+        <v>53</v>
+      </c>
       <c r="D21" s="16"/>
       <c r="E21" s="17">
         <f t="shared" si="0"/>
@@ -1348,9 +2095,15 @@
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A22" s="15"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="14"/>
+      <c r="A22" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="37" t="s">
+        <v>56</v>
+      </c>
       <c r="D22" s="16"/>
       <c r="E22" s="17">
         <f t="shared" si="0"/>
@@ -1363,9 +2116,15 @@
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A23" s="15"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="14"/>
+      <c r="A23" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" s="37" t="s">
+        <v>59</v>
+      </c>
       <c r="D23" s="16"/>
       <c r="E23" s="17">
         <f t="shared" si="0"/>
@@ -1378,9 +2137,15 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A24" s="15"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="14"/>
+      <c r="A24" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="37" t="s">
+        <v>62</v>
+      </c>
       <c r="D24" s="16"/>
       <c r="E24" s="17">
         <f t="shared" si="0"/>
@@ -1393,9 +2158,15 @@
       </c>
     </row>
     <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A25" s="15"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="14"/>
+      <c r="A25" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="37" t="s">
+        <v>65</v>
+      </c>
       <c r="D25" s="16"/>
       <c r="E25" s="17">
         <f t="shared" si="0"/>
@@ -1407,10 +2178,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A26" s="15"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="14"/>
+    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+      <c r="A26" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="37" t="s">
+        <v>68</v>
+      </c>
       <c r="D26" s="16"/>
       <c r="E26" s="17">
         <f t="shared" si="0"/>
@@ -1423,9 +2200,15 @@
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A27" s="15"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="14"/>
+      <c r="A27" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="37" t="s">
+        <v>71</v>
+      </c>
       <c r="D27" s="16"/>
       <c r="E27" s="17">
         <f t="shared" si="0"/>
@@ -1437,10 +2220,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A28" s="15"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="14"/>
+    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+      <c r="A28" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" s="37" t="s">
+        <v>74</v>
+      </c>
       <c r="D28" s="16"/>
       <c r="E28" s="17">
         <f t="shared" si="0"/>
@@ -1453,9 +2242,15 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A29" s="15"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="14"/>
+      <c r="A29" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" s="37" t="s">
+        <v>77</v>
+      </c>
       <c r="D29" s="16"/>
       <c r="E29" s="17">
         <f t="shared" si="0"/>
@@ -1468,9 +2263,15 @@
       </c>
     </row>
     <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A30" s="15"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="14"/>
+      <c r="A30" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" s="37" t="s">
+        <v>80</v>
+      </c>
       <c r="D30" s="16"/>
       <c r="E30" s="17">
         <f t="shared" si="0"/>
@@ -1483,9 +2284,15 @@
       </c>
     </row>
     <row r="31" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A31" s="15"/>
-      <c r="B31" s="15"/>
-      <c r="C31" s="14"/>
+      <c r="A31" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C31" s="37" t="s">
+        <v>83</v>
+      </c>
       <c r="D31" s="16"/>
       <c r="E31" s="17">
         <f t="shared" si="0"/>
@@ -1498,9 +2305,15 @@
       </c>
     </row>
     <row r="32" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A32" s="15"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="14"/>
+      <c r="A32" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32" s="37" t="s">
+        <v>86</v>
+      </c>
       <c r="D32" s="16"/>
       <c r="E32" s="17">
         <f t="shared" si="0"/>
@@ -1512,10 +2325,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A33" s="15"/>
-      <c r="B33" s="15"/>
-      <c r="C33" s="14"/>
+    <row r="33" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+      <c r="A33" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C33" s="37" t="s">
+        <v>89</v>
+      </c>
       <c r="D33" s="16"/>
       <c r="E33" s="17">
         <f t="shared" si="0"/>
@@ -1527,10 +2346,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A34" s="15"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="14"/>
+    <row r="34" spans="1:7" ht="45" x14ac:dyDescent="0.2">
+      <c r="A34" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C34" s="37" t="s">
+        <v>92</v>
+      </c>
       <c r="D34" s="16"/>
       <c r="E34" s="17">
         <f t="shared" si="0"/>
@@ -1543,9 +2368,15 @@
       </c>
     </row>
     <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A35" s="15"/>
-      <c r="B35" s="15"/>
-      <c r="C35" s="14"/>
+      <c r="A35" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="C35" s="37" t="s">
+        <v>95</v>
+      </c>
       <c r="D35" s="16"/>
       <c r="E35" s="17">
         <f t="shared" si="0"/>
@@ -1558,9 +2389,15 @@
       </c>
     </row>
     <row r="36" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A36" s="15"/>
-      <c r="B36" s="15"/>
-      <c r="C36" s="14"/>
+      <c r="A36" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="C36" s="37" t="s">
+        <v>98</v>
+      </c>
       <c r="D36" s="16"/>
       <c r="E36" s="17">
         <f t="shared" si="0"/>
@@ -1573,9 +2410,15 @@
       </c>
     </row>
     <row r="37" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A37" s="15"/>
-      <c r="B37" s="15"/>
-      <c r="C37" s="14"/>
+      <c r="A37" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="C37" s="37" t="s">
+        <v>101</v>
+      </c>
       <c r="D37" s="16"/>
       <c r="E37" s="17">
         <f t="shared" si="0"/>
@@ -1587,10 +2430,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A38" s="15"/>
-      <c r="B38" s="15"/>
-      <c r="C38" s="14"/>
+    <row r="38" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+      <c r="A38" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C38" s="37" t="s">
+        <v>104</v>
+      </c>
       <c r="D38" s="16"/>
       <c r="E38" s="17">
         <f t="shared" si="0"/>
@@ -1602,10 +2451,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A39" s="15"/>
-      <c r="B39" s="15"/>
-      <c r="C39" s="14"/>
+    <row r="39" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+      <c r="A39" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39" s="37" t="s">
+        <v>107</v>
+      </c>
       <c r="D39" s="16"/>
       <c r="E39" s="17">
         <f t="shared" si="0"/>
@@ -1618,9 +2473,15 @@
       </c>
     </row>
     <row r="40" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A40" s="15"/>
-      <c r="B40" s="15"/>
-      <c r="C40" s="14"/>
+      <c r="A40" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C40" s="37" t="s">
+        <v>110</v>
+      </c>
       <c r="D40" s="18"/>
       <c r="E40" s="17">
         <f t="shared" si="0"/>
@@ -1633,9 +2494,15 @@
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A41" s="15"/>
-      <c r="B41" s="15"/>
-      <c r="C41" s="14"/>
+      <c r="A41" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C41" s="37" t="s">
+        <v>113</v>
+      </c>
       <c r="D41" s="18"/>
       <c r="E41" s="17">
         <f t="shared" si="0"/>
@@ -1648,9 +2515,15 @@
       </c>
     </row>
     <row r="42" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A42" s="15"/>
-      <c r="B42" s="15"/>
-      <c r="C42" s="14"/>
+      <c r="A42" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="C42" s="37" t="s">
+        <v>116</v>
+      </c>
       <c r="D42" s="18"/>
       <c r="E42" s="17">
         <f t="shared" si="0"/>
@@ -1663,9 +2536,15 @@
       </c>
     </row>
     <row r="43" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A43" s="15"/>
-      <c r="B43" s="15"/>
-      <c r="C43" s="14"/>
+      <c r="A43" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="C43" s="37" t="s">
+        <v>119</v>
+      </c>
       <c r="D43" s="18"/>
       <c r="E43" s="17">
         <f t="shared" si="0"/>
@@ -1678,9 +2557,15 @@
       </c>
     </row>
     <row r="44" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A44" s="15"/>
-      <c r="B44" s="15"/>
-      <c r="C44" s="14"/>
+      <c r="A44" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C44" s="37" t="s">
+        <v>122</v>
+      </c>
       <c r="D44" s="18"/>
       <c r="E44" s="17">
         <f t="shared" si="0"/>
@@ -1693,9 +2578,15 @@
       </c>
     </row>
     <row r="45" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A45" s="15"/>
-      <c r="B45" s="15"/>
-      <c r="C45" s="14"/>
+      <c r="A45" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="C45" s="37" t="s">
+        <v>125</v>
+      </c>
       <c r="D45" s="18"/>
       <c r="E45" s="17">
         <f t="shared" si="0"/>
@@ -1708,9 +2599,15 @@
       </c>
     </row>
     <row r="46" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A46" s="15"/>
-      <c r="B46" s="15"/>
-      <c r="C46" s="14"/>
+      <c r="A46" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="C46" s="37" t="s">
+        <v>128</v>
+      </c>
       <c r="D46" s="18"/>
       <c r="E46" s="17">
         <f t="shared" si="0"/>
@@ -1723,9 +2620,15 @@
       </c>
     </row>
     <row r="47" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A47" s="15"/>
-      <c r="B47" s="15"/>
-      <c r="C47" s="14"/>
+      <c r="A47" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="C47" s="37" t="s">
+        <v>131</v>
+      </c>
       <c r="D47" s="18"/>
       <c r="E47" s="17">
         <f t="shared" si="0"/>
@@ -1738,9 +2641,15 @@
       </c>
     </row>
     <row r="48" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A48" s="15"/>
-      <c r="B48" s="15"/>
-      <c r="C48" s="14"/>
+      <c r="A48" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="B48" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="C48" s="37" t="s">
+        <v>134</v>
+      </c>
       <c r="D48" s="18"/>
       <c r="E48" s="17">
         <f t="shared" si="0"/>
@@ -1752,25 +2661,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A49" s="15"/>
-      <c r="B49" s="15"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="18"/>
-      <c r="E49" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F49" s="18"/>
-      <c r="G49" s="17">
+    <row r="49" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A49" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="B49" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="C49" s="36" t="s">
+        <v>137</v>
+      </c>
+      <c r="D49" s="20"/>
+      <c r="E49" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F49" s="20"/>
+      <c r="G49" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A50" s="15"/>
-      <c r="B50" s="15"/>
-      <c r="C50" s="14"/>
+      <c r="A50" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="C50" s="37" t="s">
+        <v>35</v>
+      </c>
       <c r="D50" s="18"/>
       <c r="E50" s="17">
         <f t="shared" si="0"/>
@@ -1783,9 +2704,15 @@
       </c>
     </row>
     <row r="51" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A51" s="15"/>
-      <c r="B51" s="15"/>
-      <c r="C51" s="14"/>
+      <c r="A51" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="C51" s="37" t="s">
+        <v>38</v>
+      </c>
       <c r="D51" s="18"/>
       <c r="E51" s="17">
         <f t="shared" si="0"/>
@@ -1798,9 +2725,15 @@
       </c>
     </row>
     <row r="52" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A52" s="15"/>
-      <c r="B52" s="15"/>
-      <c r="C52" s="14"/>
+      <c r="A52" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="C52" s="37" t="s">
+        <v>41</v>
+      </c>
       <c r="D52" s="18"/>
       <c r="E52" s="17">
         <f t="shared" si="0"/>
@@ -1813,9 +2746,15 @@
       </c>
     </row>
     <row r="53" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A53" s="15"/>
-      <c r="B53" s="15"/>
-      <c r="C53" s="14"/>
+      <c r="A53" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="C53" s="37" t="s">
+        <v>44</v>
+      </c>
       <c r="D53" s="18"/>
       <c r="E53" s="17">
         <f t="shared" si="0"/>
@@ -1828,9 +2767,15 @@
       </c>
     </row>
     <row r="54" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A54" s="15"/>
-      <c r="B54" s="15"/>
-      <c r="C54" s="14"/>
+      <c r="A54" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="C54" s="37" t="s">
+        <v>47</v>
+      </c>
       <c r="D54" s="18"/>
       <c r="E54" s="17">
         <f t="shared" si="0"/>
@@ -1842,10 +2787,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A55" s="15"/>
-      <c r="B55" s="15"/>
-      <c r="C55" s="14"/>
+    <row r="55" spans="1:7" ht="45" x14ac:dyDescent="0.2">
+      <c r="A55" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="C55" s="37" t="s">
+        <v>150</v>
+      </c>
       <c r="D55" s="18"/>
       <c r="E55" s="17">
         <f t="shared" si="0"/>
@@ -1858,9 +2809,15 @@
       </c>
     </row>
     <row r="56" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A56" s="15"/>
-      <c r="B56" s="15"/>
-      <c r="C56" s="14"/>
+      <c r="A56" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="B56" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="C56" s="37" t="s">
+        <v>53</v>
+      </c>
       <c r="D56" s="18"/>
       <c r="E56" s="17">
         <f t="shared" si="0"/>
@@ -1873,9 +2830,15 @@
       </c>
     </row>
     <row r="57" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A57" s="15"/>
-      <c r="B57" s="15"/>
-      <c r="C57" s="14"/>
+      <c r="A57" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="B57" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="C57" s="37" t="s">
+        <v>56</v>
+      </c>
       <c r="D57" s="18"/>
       <c r="E57" s="17">
         <f t="shared" si="0"/>
@@ -1888,9 +2851,15 @@
       </c>
     </row>
     <row r="58" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A58" s="15"/>
-      <c r="B58" s="15"/>
-      <c r="C58" s="14"/>
+      <c r="A58" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="B58" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="C58" s="37" t="s">
+        <v>59</v>
+      </c>
       <c r="D58" s="18"/>
       <c r="E58" s="17">
         <f t="shared" si="0"/>
@@ -1903,9 +2872,15 @@
       </c>
     </row>
     <row r="59" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A59" s="15"/>
-      <c r="B59" s="15"/>
-      <c r="C59" s="14"/>
+      <c r="A59" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="B59" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="C59" s="37" t="s">
+        <v>62</v>
+      </c>
       <c r="D59" s="18"/>
       <c r="E59" s="17">
         <f t="shared" si="0"/>
@@ -1918,9 +2893,15 @@
       </c>
     </row>
     <row r="60" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A60" s="15"/>
-      <c r="B60" s="15"/>
-      <c r="C60" s="14"/>
+      <c r="A60" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="B60" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="C60" s="37" t="s">
+        <v>65</v>
+      </c>
       <c r="D60" s="18"/>
       <c r="E60" s="17">
         <f t="shared" si="0"/>
@@ -1932,10 +2913,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A61" s="15"/>
-      <c r="B61" s="15"/>
-      <c r="C61" s="14"/>
+    <row r="61" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+      <c r="A61" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B61" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="C61" s="37" t="s">
+        <v>68</v>
+      </c>
       <c r="D61" s="18"/>
       <c r="E61" s="17">
         <f t="shared" si="0"/>
@@ -1948,9 +2935,15 @@
       </c>
     </row>
     <row r="62" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A62" s="15"/>
-      <c r="B62" s="15"/>
-      <c r="C62" s="14"/>
+      <c r="A62" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="B62" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="C62" s="37" t="s">
+        <v>71</v>
+      </c>
       <c r="D62" s="18"/>
       <c r="E62" s="17">
         <f t="shared" si="0"/>
@@ -1962,10 +2955,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A63" s="15"/>
-      <c r="B63" s="15"/>
-      <c r="C63" s="14"/>
+    <row r="63" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+      <c r="A63" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="B63" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="C63" s="37" t="s">
+        <v>167</v>
+      </c>
       <c r="D63" s="18"/>
       <c r="E63" s="17">
         <f t="shared" si="0"/>
@@ -1978,9 +2977,15 @@
       </c>
     </row>
     <row r="64" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A64" s="15"/>
-      <c r="B64" s="15"/>
-      <c r="C64" s="14"/>
+      <c r="A64" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="B64" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="C64" s="37" t="s">
+        <v>77</v>
+      </c>
       <c r="D64" s="18"/>
       <c r="E64" s="17">
         <f t="shared" si="0"/>
@@ -1993,9 +2998,15 @@
       </c>
     </row>
     <row r="65" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A65" s="15"/>
-      <c r="B65" s="15"/>
-      <c r="C65" s="14"/>
+      <c r="A65" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="B65" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="C65" s="37" t="s">
+        <v>80</v>
+      </c>
       <c r="D65" s="18"/>
       <c r="E65" s="17">
         <f t="shared" si="0"/>
@@ -2008,9 +3019,15 @@
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A66" s="15"/>
-      <c r="B66" s="15"/>
-      <c r="C66" s="14"/>
+      <c r="A66" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="B66" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="C66" s="37" t="s">
+        <v>83</v>
+      </c>
       <c r="D66" s="18"/>
       <c r="E66" s="17">
         <f t="shared" si="0"/>
@@ -2023,9 +3040,15 @@
       </c>
     </row>
     <row r="67" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A67" s="15"/>
-      <c r="B67" s="15"/>
-      <c r="C67" s="14"/>
+      <c r="A67" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="B67" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="C67" s="37" t="s">
+        <v>86</v>
+      </c>
       <c r="D67" s="18"/>
       <c r="E67" s="17">
         <f t="shared" si="0"/>
@@ -2037,10 +3060,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A68" s="15"/>
-      <c r="B68" s="15"/>
-      <c r="C68" s="14"/>
+    <row r="68" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+      <c r="A68" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="B68" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="C68" s="37" t="s">
+        <v>89</v>
+      </c>
       <c r="D68" s="18"/>
       <c r="E68" s="17">
         <f t="shared" si="0"/>
@@ -2052,10 +3081,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A69" s="15"/>
-      <c r="B69" s="15"/>
-      <c r="C69" s="14"/>
+    <row r="69" spans="1:7" ht="45" x14ac:dyDescent="0.2">
+      <c r="A69" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="B69" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="C69" s="37" t="s">
+        <v>92</v>
+      </c>
       <c r="D69" s="18"/>
       <c r="E69" s="17">
         <f t="shared" si="0"/>
@@ -2068,9 +3103,15 @@
       </c>
     </row>
     <row r="70" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A70" s="15"/>
-      <c r="B70" s="15"/>
-      <c r="C70" s="14"/>
+      <c r="A70" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="B70" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="C70" s="37" t="s">
+        <v>95</v>
+      </c>
       <c r="D70" s="18"/>
       <c r="E70" s="17">
         <f t="shared" si="0"/>
@@ -2083,9 +3124,15 @@
       </c>
     </row>
     <row r="71" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A71" s="15"/>
-      <c r="B71" s="15"/>
-      <c r="C71" s="14"/>
+      <c r="A71" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="B71" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="C71" s="37" t="s">
+        <v>98</v>
+      </c>
       <c r="D71" s="18"/>
       <c r="E71" s="17">
         <f t="shared" si="0"/>
@@ -2098,9 +3145,15 @@
       </c>
     </row>
     <row r="72" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A72" s="15"/>
-      <c r="B72" s="15"/>
-      <c r="C72" s="14"/>
+      <c r="A72" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="B72" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="C72" s="37" t="s">
+        <v>101</v>
+      </c>
       <c r="D72" s="18"/>
       <c r="E72" s="17">
         <f t="shared" si="0"/>
@@ -2112,10 +3165,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A73" s="15"/>
-      <c r="B73" s="15"/>
-      <c r="C73" s="14"/>
+    <row r="73" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+      <c r="A73" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="B73" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="C73" s="37" t="s">
+        <v>104</v>
+      </c>
       <c r="D73" s="18"/>
       <c r="E73" s="17">
         <f t="shared" si="0"/>
@@ -2127,10 +3186,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A74" s="15"/>
-      <c r="B74" s="15"/>
-      <c r="C74" s="14"/>
+    <row r="74" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+      <c r="A74" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="B74" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="C74" s="37" t="s">
+        <v>107</v>
+      </c>
       <c r="D74" s="18"/>
       <c r="E74" s="17">
         <f t="shared" si="0"/>
@@ -2143,9 +3208,15 @@
       </c>
     </row>
     <row r="75" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A75" s="15"/>
-      <c r="B75" s="15"/>
-      <c r="C75" s="14"/>
+      <c r="A75" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="B75" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="C75" s="37" t="s">
+        <v>134</v>
+      </c>
       <c r="D75" s="18"/>
       <c r="E75" s="17">
         <f t="shared" si="0"/>
@@ -2157,25 +3228,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A76" s="15"/>
-      <c r="B76" s="15"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="18"/>
-      <c r="E76" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F76" s="18"/>
-      <c r="G76" s="17">
+    <row r="76" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A76" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="B76" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="C76" s="36" t="s">
+        <v>194</v>
+      </c>
+      <c r="D76" s="20"/>
+      <c r="E76" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F76" s="20"/>
+      <c r="G76" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A77" s="15"/>
-      <c r="B77" s="15"/>
-      <c r="C77" s="14"/>
+      <c r="A77" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="B77" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="C77" s="37" t="s">
+        <v>197</v>
+      </c>
       <c r="D77" s="18"/>
       <c r="E77" s="17">
         <f t="shared" si="0"/>
@@ -2188,9 +3271,15 @@
       </c>
     </row>
     <row r="78" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A78" s="15"/>
-      <c r="B78" s="15"/>
-      <c r="C78" s="14"/>
+      <c r="A78" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="B78" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="C78" s="37" t="s">
+        <v>200</v>
+      </c>
       <c r="D78" s="18"/>
       <c r="E78" s="17">
         <f t="shared" si="0"/>
@@ -2203,9 +3292,15 @@
       </c>
     </row>
     <row r="79" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A79" s="15"/>
-      <c r="B79" s="15"/>
-      <c r="C79" s="14"/>
+      <c r="A79" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="B79" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="C79" s="37" t="s">
+        <v>203</v>
+      </c>
       <c r="D79" s="18"/>
       <c r="E79" s="17">
         <f t="shared" si="0"/>
@@ -2218,9 +3313,15 @@
       </c>
     </row>
     <row r="80" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A80" s="15"/>
-      <c r="B80" s="15"/>
-      <c r="C80" s="14"/>
+      <c r="A80" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="B80" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="C80" s="37" t="s">
+        <v>206</v>
+      </c>
       <c r="D80" s="18"/>
       <c r="E80" s="17">
         <f t="shared" si="0"/>
@@ -2233,9 +3334,15 @@
       </c>
     </row>
     <row r="81" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A81" s="15"/>
-      <c r="B81" s="15"/>
-      <c r="C81" s="14"/>
+      <c r="A81" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="B81" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="C81" s="37" t="s">
+        <v>209</v>
+      </c>
       <c r="D81" s="18"/>
       <c r="E81" s="17">
         <f t="shared" si="0"/>
@@ -2248,9 +3355,15 @@
       </c>
     </row>
     <row r="82" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A82" s="15"/>
-      <c r="B82" s="15"/>
-      <c r="C82" s="14"/>
+      <c r="A82" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="B82" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="C82" s="37" t="s">
+        <v>212</v>
+      </c>
       <c r="D82" s="18"/>
       <c r="E82" s="17">
         <f t="shared" si="0"/>
@@ -2263,9 +3376,15 @@
       </c>
     </row>
     <row r="83" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A83" s="15"/>
-      <c r="B83" s="15"/>
-      <c r="C83" s="14"/>
+      <c r="A83" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="B83" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="C83" s="37" t="s">
+        <v>215</v>
+      </c>
       <c r="D83" s="18"/>
       <c r="E83" s="17">
         <f t="shared" si="0"/>
@@ -2278,9 +3397,15 @@
       </c>
     </row>
     <row r="84" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A84" s="15"/>
-      <c r="B84" s="15"/>
-      <c r="C84" s="14"/>
+      <c r="A84" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="B84" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="C84" s="37" t="s">
+        <v>218</v>
+      </c>
       <c r="D84" s="18"/>
       <c r="E84" s="17">
         <f t="shared" si="0"/>
@@ -2293,9 +3418,15 @@
       </c>
     </row>
     <row r="85" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A85" s="15"/>
-      <c r="B85" s="15"/>
-      <c r="C85" s="14"/>
+      <c r="A85" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="B85" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="C85" s="37" t="s">
+        <v>221</v>
+      </c>
       <c r="D85" s="18"/>
       <c r="E85" s="17">
         <f t="shared" si="0"/>
@@ -2308,9 +3439,15 @@
       </c>
     </row>
     <row r="86" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A86" s="15"/>
-      <c r="B86" s="15"/>
-      <c r="C86" s="14"/>
+      <c r="A86" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="B86" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="C86" s="37" t="s">
+        <v>224</v>
+      </c>
       <c r="D86" s="18"/>
       <c r="E86" s="17">
         <f t="shared" si="0"/>
@@ -2323,9 +3460,15 @@
       </c>
     </row>
     <row r="87" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A87" s="15"/>
-      <c r="B87" s="15"/>
-      <c r="C87" s="14"/>
+      <c r="A87" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="B87" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="C87" s="37" t="s">
+        <v>227</v>
+      </c>
       <c r="D87" s="18"/>
       <c r="E87" s="17">
         <f t="shared" si="0"/>
@@ -2338,9 +3481,15 @@
       </c>
     </row>
     <row r="88" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A88" s="15"/>
-      <c r="B88" s="15"/>
-      <c r="C88" s="14"/>
+      <c r="A88" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="B88" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="C88" s="37" t="s">
+        <v>230</v>
+      </c>
       <c r="D88" s="18"/>
       <c r="E88" s="17">
         <f t="shared" si="0"/>
@@ -2353,9 +3502,15 @@
       </c>
     </row>
     <row r="89" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A89" s="15"/>
-      <c r="B89" s="15"/>
-      <c r="C89" s="14"/>
+      <c r="A89" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="B89" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="C89" s="37" t="s">
+        <v>233</v>
+      </c>
       <c r="D89" s="18"/>
       <c r="E89" s="17">
         <f t="shared" si="0"/>
@@ -2368,9 +3523,15 @@
       </c>
     </row>
     <row r="90" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A90" s="15"/>
-      <c r="B90" s="15"/>
-      <c r="C90" s="14"/>
+      <c r="A90" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="B90" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="C90" s="37" t="s">
+        <v>236</v>
+      </c>
       <c r="D90" s="18"/>
       <c r="E90" s="17">
         <f t="shared" si="0"/>
@@ -2383,9 +3544,15 @@
       </c>
     </row>
     <row r="91" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A91" s="15"/>
-      <c r="B91" s="15"/>
-      <c r="C91" s="14"/>
+      <c r="A91" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="B91" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="C91" s="37" t="s">
+        <v>239</v>
+      </c>
       <c r="D91" s="18"/>
       <c r="E91" s="17">
         <f t="shared" si="0"/>
@@ -2398,9 +3565,15 @@
       </c>
     </row>
     <row r="92" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A92" s="15"/>
-      <c r="B92" s="15"/>
-      <c r="C92" s="14"/>
+      <c r="A92" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="B92" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="C92" s="37" t="s">
+        <v>242</v>
+      </c>
       <c r="D92" s="18"/>
       <c r="E92" s="17">
         <f t="shared" si="0"/>
@@ -2413,9 +3586,15 @@
       </c>
     </row>
     <row r="93" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A93" s="15"/>
-      <c r="B93" s="15"/>
-      <c r="C93" s="14"/>
+      <c r="A93" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="B93" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="C93" s="37" t="s">
+        <v>245</v>
+      </c>
       <c r="D93" s="18"/>
       <c r="E93" s="17">
         <f t="shared" si="0"/>
@@ -2428,9 +3607,15 @@
       </c>
     </row>
     <row r="94" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A94" s="15"/>
-      <c r="B94" s="15"/>
-      <c r="C94" s="14"/>
+      <c r="A94" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="B94" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="C94" s="37" t="s">
+        <v>248</v>
+      </c>
       <c r="D94" s="18"/>
       <c r="E94" s="17">
         <f t="shared" si="0"/>
@@ -2443,9 +3628,15 @@
       </c>
     </row>
     <row r="95" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A95" s="15"/>
-      <c r="B95" s="15"/>
-      <c r="C95" s="14"/>
+      <c r="A95" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="B95" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="C95" s="37" t="s">
+        <v>251</v>
+      </c>
       <c r="D95" s="18"/>
       <c r="E95" s="17">
         <f t="shared" si="0"/>
@@ -2458,9 +3649,15 @@
       </c>
     </row>
     <row r="96" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A96" s="15"/>
-      <c r="B96" s="15"/>
-      <c r="C96" s="14"/>
+      <c r="A96" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="B96" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="C96" s="37" t="s">
+        <v>254</v>
+      </c>
       <c r="D96" s="18"/>
       <c r="E96" s="17">
         <f t="shared" si="0"/>
@@ -3532,7 +4729,7 @@
       <c r="A168" s="8"/>
       <c r="B168" s="8"/>
       <c r="C168" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G168" s="6"/>
     </row>
@@ -3540,23 +4737,23 @@
       <c r="A169" s="10"/>
       <c r="B169" s="10"/>
       <c r="C169" s="10"/>
-      <c r="D169" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="E169" s="25"/>
-      <c r="F169" s="25"/>
-      <c r="G169" s="25"/>
+      <c r="D169" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="E169" s="28"/>
+      <c r="F169" s="28"/>
+      <c r="G169" s="28"/>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A170" s="11"/>
       <c r="B170" s="11"/>
       <c r="C170" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D170" s="21"/>
-      <c r="E170" s="21"/>
-      <c r="F170" s="21"/>
-      <c r="G170" s="21"/>
+        <v>13</v>
+      </c>
+      <c r="D170" s="24"/>
+      <c r="E170" s="24"/>
+      <c r="F170" s="24"/>
+      <c r="G170" s="24"/>
       <c r="H170" s="11"/>
       <c r="I170" s="11"/>
       <c r="J170" s="11"/>
@@ -3565,12 +4762,12 @@
       <c r="A171" s="9"/>
       <c r="B171" s="9"/>
       <c r="C171" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D171" s="25"/>
-      <c r="E171" s="25"/>
-      <c r="F171" s="25"/>
-      <c r="G171" s="25"/>
+        <v>14</v>
+      </c>
+      <c r="D171" s="28"/>
+      <c r="E171" s="28"/>
+      <c r="F171" s="28"/>
+      <c r="G171" s="28"/>
       <c r="H171" s="13"/>
       <c r="I171" s="13"/>
       <c r="J171" s="13"/>
@@ -3585,37 +4782,37 @@
     </row>
     <row r="177" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C177" s="11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="178" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C178" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="179" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C179" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="180" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C180" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="181" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C181" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="182" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C182" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="184" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C184" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="187" spans="3:3" x14ac:dyDescent="0.2">

--- a/web/EXCEL_TEMPLATE/KHNV/KHNV_DK01A.xlsx
+++ b/web/EXCEL_TEMPLATE/KHNV/KHNV_DK01A.xlsx
@@ -1,25 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24026"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\khnv_01a_thang5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\IMS_REPORTS\IMS_REPORTS\web\EXCEL_TEMPLATE\KHNV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A05635F-CBEA-4704-813B-E0F296286168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11280" xr2:uid="{FEA2E927-87FC-4F8F-B922-B59702A7794E}"/>
+    <workbookView xWindow="936" yWindow="-120" windowWidth="20736" windowHeight="11280"/>
   </bookViews>
   <sheets>
     <sheet name="DK_01A" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">DK_01A!$A$1:$G$171</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">DK_01A!$A$1:$G$149</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">DK_01A!$8:$12</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="193">
   <si>
     <t>Biểu số 01a/NHCS-KH</t>
   </si>
@@ -628,202 +627,13 @@
     <t>XD00063</t>
   </si>
   <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>XD00064</t>
-  </si>
-  <si>
-    <t>THUYẾT MINH MỘT SỐ CHỈ TIÊU (Dự kiến năm kế hoạch)</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>XD00065</t>
-  </si>
-  <si>
-    <t>Số hộ dân cư trú trên địa bàn</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>XD00066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số hộ dân là hộ đồng bào dân tộc thiểu số </t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>XD00067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số hộ nghèo theo chuẩn hộ nghèo (giai đoạn 2021-2025) </t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>XD00068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số hộ nghèo đang còn dư nợ NHCSXH </t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>XD00069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số hộ nghèo đủ điều kiện vay vốn nhưng chưa được vay vốn NHCSXH </t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>XD00070</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số hộ cận nghèo theo chuẩn hộ cận nghèo (giai đoạn 2021-2025) </t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>XD00071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số hộ cận nghèo đang còn dư nợ NHCSXH </t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>XD00072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số hộ cận nghèo đủ điều kiện vay vốn nhưng chưa được vay vốn NHCSXH </t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>XD00073</t>
-  </si>
-  <si>
-    <t>Số hộ mới thoát nghèo (giai đoạn 2019-2021)</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>XD00074</t>
-  </si>
-  <si>
-    <t>Số hộ gia đình sản xuất kinh doanh vùng khó khăn trên địa bàn</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>XD00075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số hộ gia đình SXKD đang còn dư nợ NHCSXH </t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>XD00076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số hộ gia đình SXKD đủ điều kiện vay vốn nhưng chưa được vay vốn NHCSXH </t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>XD00077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số thương nhân hoạt động thương mại tại vùng khó khăn </t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>XD00078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tổng số HSSV theo học các Trường ĐH, CĐ, THCN và dạy nghề </t>
-  </si>
-  <si>
-    <t>79</t>
-  </si>
-  <si>
-    <t>XD00079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số HSSV đang còn dư nợ NHCSXH </t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>XD00080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số lao động có nhu cầu vay vốn giải quyết việc làm </t>
-  </si>
-  <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>XD00081</t>
-  </si>
-  <si>
-    <t>Số lao động được vay vốn giải quyết việc làm trong năm</t>
-  </si>
-  <si>
-    <t>82</t>
-  </si>
-  <si>
-    <t>XD00082</t>
-  </si>
-  <si>
-    <t>Số lao động dự kiến được thu hút từ vay vốn giải quyết việc làm</t>
-  </si>
-  <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>XD00083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tổng số lao động có nhu cầu vay vốn đi lao động có thời hạn ở nước ngoài </t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>XD00084</t>
-  </si>
-  <si>
-    <t>Số công trình NS-VSMT NT dự kiến được xây dựng từ nguồn vốn vay NHCSXH</t>
-  </si>
-  <si>
     <t>THÔN: ... XÃ/PHƯỜNG/THỊ TRẤN: …</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -1068,26 +878,20 @@
     <xf numFmtId="4" fontId="7" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1110,11 +914,17 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1429,462 +1239,462 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37BE2C90-DB6F-4A4B-9FA5-0B2B2544D1FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J187"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:J165"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="6.44140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="17" style="1" customWidth="1"/>
-    <col min="3" max="3" width="80.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="80.109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="2" customWidth="1"/>
-    <col min="8" max="257" width="9.140625" style="2"/>
-    <col min="258" max="258" width="6.42578125" style="2" customWidth="1"/>
-    <col min="259" max="259" width="80.140625" style="2" customWidth="1"/>
-    <col min="260" max="260" width="15.7109375" style="2" customWidth="1"/>
-    <col min="261" max="263" width="14.28515625" style="2" customWidth="1"/>
-    <col min="264" max="513" width="9.140625" style="2"/>
-    <col min="514" max="514" width="6.42578125" style="2" customWidth="1"/>
-    <col min="515" max="515" width="80.140625" style="2" customWidth="1"/>
-    <col min="516" max="516" width="15.7109375" style="2" customWidth="1"/>
-    <col min="517" max="519" width="14.28515625" style="2" customWidth="1"/>
-    <col min="520" max="769" width="9.140625" style="2"/>
-    <col min="770" max="770" width="6.42578125" style="2" customWidth="1"/>
-    <col min="771" max="771" width="80.140625" style="2" customWidth="1"/>
-    <col min="772" max="772" width="15.7109375" style="2" customWidth="1"/>
-    <col min="773" max="775" width="14.28515625" style="2" customWidth="1"/>
-    <col min="776" max="1025" width="9.140625" style="2"/>
-    <col min="1026" max="1026" width="6.42578125" style="2" customWidth="1"/>
-    <col min="1027" max="1027" width="80.140625" style="2" customWidth="1"/>
-    <col min="1028" max="1028" width="15.7109375" style="2" customWidth="1"/>
-    <col min="1029" max="1031" width="14.28515625" style="2" customWidth="1"/>
-    <col min="1032" max="1281" width="9.140625" style="2"/>
-    <col min="1282" max="1282" width="6.42578125" style="2" customWidth="1"/>
-    <col min="1283" max="1283" width="80.140625" style="2" customWidth="1"/>
-    <col min="1284" max="1284" width="15.7109375" style="2" customWidth="1"/>
-    <col min="1285" max="1287" width="14.28515625" style="2" customWidth="1"/>
-    <col min="1288" max="1537" width="9.140625" style="2"/>
-    <col min="1538" max="1538" width="6.42578125" style="2" customWidth="1"/>
-    <col min="1539" max="1539" width="80.140625" style="2" customWidth="1"/>
-    <col min="1540" max="1540" width="15.7109375" style="2" customWidth="1"/>
-    <col min="1541" max="1543" width="14.28515625" style="2" customWidth="1"/>
-    <col min="1544" max="1793" width="9.140625" style="2"/>
-    <col min="1794" max="1794" width="6.42578125" style="2" customWidth="1"/>
-    <col min="1795" max="1795" width="80.140625" style="2" customWidth="1"/>
-    <col min="1796" max="1796" width="15.7109375" style="2" customWidth="1"/>
-    <col min="1797" max="1799" width="14.28515625" style="2" customWidth="1"/>
-    <col min="1800" max="2049" width="9.140625" style="2"/>
-    <col min="2050" max="2050" width="6.42578125" style="2" customWidth="1"/>
-    <col min="2051" max="2051" width="80.140625" style="2" customWidth="1"/>
-    <col min="2052" max="2052" width="15.7109375" style="2" customWidth="1"/>
-    <col min="2053" max="2055" width="14.28515625" style="2" customWidth="1"/>
-    <col min="2056" max="2305" width="9.140625" style="2"/>
-    <col min="2306" max="2306" width="6.42578125" style="2" customWidth="1"/>
-    <col min="2307" max="2307" width="80.140625" style="2" customWidth="1"/>
-    <col min="2308" max="2308" width="15.7109375" style="2" customWidth="1"/>
-    <col min="2309" max="2311" width="14.28515625" style="2" customWidth="1"/>
-    <col min="2312" max="2561" width="9.140625" style="2"/>
-    <col min="2562" max="2562" width="6.42578125" style="2" customWidth="1"/>
-    <col min="2563" max="2563" width="80.140625" style="2" customWidth="1"/>
-    <col min="2564" max="2564" width="15.7109375" style="2" customWidth="1"/>
-    <col min="2565" max="2567" width="14.28515625" style="2" customWidth="1"/>
-    <col min="2568" max="2817" width="9.140625" style="2"/>
-    <col min="2818" max="2818" width="6.42578125" style="2" customWidth="1"/>
-    <col min="2819" max="2819" width="80.140625" style="2" customWidth="1"/>
-    <col min="2820" max="2820" width="15.7109375" style="2" customWidth="1"/>
-    <col min="2821" max="2823" width="14.28515625" style="2" customWidth="1"/>
-    <col min="2824" max="3073" width="9.140625" style="2"/>
-    <col min="3074" max="3074" width="6.42578125" style="2" customWidth="1"/>
-    <col min="3075" max="3075" width="80.140625" style="2" customWidth="1"/>
-    <col min="3076" max="3076" width="15.7109375" style="2" customWidth="1"/>
-    <col min="3077" max="3079" width="14.28515625" style="2" customWidth="1"/>
-    <col min="3080" max="3329" width="9.140625" style="2"/>
-    <col min="3330" max="3330" width="6.42578125" style="2" customWidth="1"/>
-    <col min="3331" max="3331" width="80.140625" style="2" customWidth="1"/>
-    <col min="3332" max="3332" width="15.7109375" style="2" customWidth="1"/>
-    <col min="3333" max="3335" width="14.28515625" style="2" customWidth="1"/>
-    <col min="3336" max="3585" width="9.140625" style="2"/>
-    <col min="3586" max="3586" width="6.42578125" style="2" customWidth="1"/>
-    <col min="3587" max="3587" width="80.140625" style="2" customWidth="1"/>
-    <col min="3588" max="3588" width="15.7109375" style="2" customWidth="1"/>
-    <col min="3589" max="3591" width="14.28515625" style="2" customWidth="1"/>
-    <col min="3592" max="3841" width="9.140625" style="2"/>
-    <col min="3842" max="3842" width="6.42578125" style="2" customWidth="1"/>
-    <col min="3843" max="3843" width="80.140625" style="2" customWidth="1"/>
-    <col min="3844" max="3844" width="15.7109375" style="2" customWidth="1"/>
-    <col min="3845" max="3847" width="14.28515625" style="2" customWidth="1"/>
-    <col min="3848" max="4097" width="9.140625" style="2"/>
-    <col min="4098" max="4098" width="6.42578125" style="2" customWidth="1"/>
-    <col min="4099" max="4099" width="80.140625" style="2" customWidth="1"/>
-    <col min="4100" max="4100" width="15.7109375" style="2" customWidth="1"/>
-    <col min="4101" max="4103" width="14.28515625" style="2" customWidth="1"/>
-    <col min="4104" max="4353" width="9.140625" style="2"/>
-    <col min="4354" max="4354" width="6.42578125" style="2" customWidth="1"/>
-    <col min="4355" max="4355" width="80.140625" style="2" customWidth="1"/>
-    <col min="4356" max="4356" width="15.7109375" style="2" customWidth="1"/>
-    <col min="4357" max="4359" width="14.28515625" style="2" customWidth="1"/>
-    <col min="4360" max="4609" width="9.140625" style="2"/>
-    <col min="4610" max="4610" width="6.42578125" style="2" customWidth="1"/>
-    <col min="4611" max="4611" width="80.140625" style="2" customWidth="1"/>
-    <col min="4612" max="4612" width="15.7109375" style="2" customWidth="1"/>
-    <col min="4613" max="4615" width="14.28515625" style="2" customWidth="1"/>
-    <col min="4616" max="4865" width="9.140625" style="2"/>
-    <col min="4866" max="4866" width="6.42578125" style="2" customWidth="1"/>
-    <col min="4867" max="4867" width="80.140625" style="2" customWidth="1"/>
-    <col min="4868" max="4868" width="15.7109375" style="2" customWidth="1"/>
-    <col min="4869" max="4871" width="14.28515625" style="2" customWidth="1"/>
-    <col min="4872" max="5121" width="9.140625" style="2"/>
-    <col min="5122" max="5122" width="6.42578125" style="2" customWidth="1"/>
-    <col min="5123" max="5123" width="80.140625" style="2" customWidth="1"/>
-    <col min="5124" max="5124" width="15.7109375" style="2" customWidth="1"/>
-    <col min="5125" max="5127" width="14.28515625" style="2" customWidth="1"/>
-    <col min="5128" max="5377" width="9.140625" style="2"/>
-    <col min="5378" max="5378" width="6.42578125" style="2" customWidth="1"/>
-    <col min="5379" max="5379" width="80.140625" style="2" customWidth="1"/>
-    <col min="5380" max="5380" width="15.7109375" style="2" customWidth="1"/>
-    <col min="5381" max="5383" width="14.28515625" style="2" customWidth="1"/>
-    <col min="5384" max="5633" width="9.140625" style="2"/>
-    <col min="5634" max="5634" width="6.42578125" style="2" customWidth="1"/>
-    <col min="5635" max="5635" width="80.140625" style="2" customWidth="1"/>
-    <col min="5636" max="5636" width="15.7109375" style="2" customWidth="1"/>
-    <col min="5637" max="5639" width="14.28515625" style="2" customWidth="1"/>
-    <col min="5640" max="5889" width="9.140625" style="2"/>
-    <col min="5890" max="5890" width="6.42578125" style="2" customWidth="1"/>
-    <col min="5891" max="5891" width="80.140625" style="2" customWidth="1"/>
-    <col min="5892" max="5892" width="15.7109375" style="2" customWidth="1"/>
-    <col min="5893" max="5895" width="14.28515625" style="2" customWidth="1"/>
-    <col min="5896" max="6145" width="9.140625" style="2"/>
-    <col min="6146" max="6146" width="6.42578125" style="2" customWidth="1"/>
-    <col min="6147" max="6147" width="80.140625" style="2" customWidth="1"/>
-    <col min="6148" max="6148" width="15.7109375" style="2" customWidth="1"/>
-    <col min="6149" max="6151" width="14.28515625" style="2" customWidth="1"/>
-    <col min="6152" max="6401" width="9.140625" style="2"/>
-    <col min="6402" max="6402" width="6.42578125" style="2" customWidth="1"/>
-    <col min="6403" max="6403" width="80.140625" style="2" customWidth="1"/>
-    <col min="6404" max="6404" width="15.7109375" style="2" customWidth="1"/>
-    <col min="6405" max="6407" width="14.28515625" style="2" customWidth="1"/>
-    <col min="6408" max="6657" width="9.140625" style="2"/>
-    <col min="6658" max="6658" width="6.42578125" style="2" customWidth="1"/>
-    <col min="6659" max="6659" width="80.140625" style="2" customWidth="1"/>
-    <col min="6660" max="6660" width="15.7109375" style="2" customWidth="1"/>
-    <col min="6661" max="6663" width="14.28515625" style="2" customWidth="1"/>
-    <col min="6664" max="6913" width="9.140625" style="2"/>
-    <col min="6914" max="6914" width="6.42578125" style="2" customWidth="1"/>
-    <col min="6915" max="6915" width="80.140625" style="2" customWidth="1"/>
-    <col min="6916" max="6916" width="15.7109375" style="2" customWidth="1"/>
-    <col min="6917" max="6919" width="14.28515625" style="2" customWidth="1"/>
-    <col min="6920" max="7169" width="9.140625" style="2"/>
-    <col min="7170" max="7170" width="6.42578125" style="2" customWidth="1"/>
-    <col min="7171" max="7171" width="80.140625" style="2" customWidth="1"/>
-    <col min="7172" max="7172" width="15.7109375" style="2" customWidth="1"/>
-    <col min="7173" max="7175" width="14.28515625" style="2" customWidth="1"/>
-    <col min="7176" max="7425" width="9.140625" style="2"/>
-    <col min="7426" max="7426" width="6.42578125" style="2" customWidth="1"/>
-    <col min="7427" max="7427" width="80.140625" style="2" customWidth="1"/>
-    <col min="7428" max="7428" width="15.7109375" style="2" customWidth="1"/>
-    <col min="7429" max="7431" width="14.28515625" style="2" customWidth="1"/>
-    <col min="7432" max="7681" width="9.140625" style="2"/>
-    <col min="7682" max="7682" width="6.42578125" style="2" customWidth="1"/>
-    <col min="7683" max="7683" width="80.140625" style="2" customWidth="1"/>
-    <col min="7684" max="7684" width="15.7109375" style="2" customWidth="1"/>
-    <col min="7685" max="7687" width="14.28515625" style="2" customWidth="1"/>
-    <col min="7688" max="7937" width="9.140625" style="2"/>
-    <col min="7938" max="7938" width="6.42578125" style="2" customWidth="1"/>
-    <col min="7939" max="7939" width="80.140625" style="2" customWidth="1"/>
-    <col min="7940" max="7940" width="15.7109375" style="2" customWidth="1"/>
-    <col min="7941" max="7943" width="14.28515625" style="2" customWidth="1"/>
-    <col min="7944" max="8193" width="9.140625" style="2"/>
-    <col min="8194" max="8194" width="6.42578125" style="2" customWidth="1"/>
-    <col min="8195" max="8195" width="80.140625" style="2" customWidth="1"/>
-    <col min="8196" max="8196" width="15.7109375" style="2" customWidth="1"/>
-    <col min="8197" max="8199" width="14.28515625" style="2" customWidth="1"/>
-    <col min="8200" max="8449" width="9.140625" style="2"/>
-    <col min="8450" max="8450" width="6.42578125" style="2" customWidth="1"/>
-    <col min="8451" max="8451" width="80.140625" style="2" customWidth="1"/>
-    <col min="8452" max="8452" width="15.7109375" style="2" customWidth="1"/>
-    <col min="8453" max="8455" width="14.28515625" style="2" customWidth="1"/>
-    <col min="8456" max="8705" width="9.140625" style="2"/>
-    <col min="8706" max="8706" width="6.42578125" style="2" customWidth="1"/>
-    <col min="8707" max="8707" width="80.140625" style="2" customWidth="1"/>
-    <col min="8708" max="8708" width="15.7109375" style="2" customWidth="1"/>
-    <col min="8709" max="8711" width="14.28515625" style="2" customWidth="1"/>
-    <col min="8712" max="8961" width="9.140625" style="2"/>
-    <col min="8962" max="8962" width="6.42578125" style="2" customWidth="1"/>
-    <col min="8963" max="8963" width="80.140625" style="2" customWidth="1"/>
-    <col min="8964" max="8964" width="15.7109375" style="2" customWidth="1"/>
-    <col min="8965" max="8967" width="14.28515625" style="2" customWidth="1"/>
-    <col min="8968" max="9217" width="9.140625" style="2"/>
-    <col min="9218" max="9218" width="6.42578125" style="2" customWidth="1"/>
-    <col min="9219" max="9219" width="80.140625" style="2" customWidth="1"/>
-    <col min="9220" max="9220" width="15.7109375" style="2" customWidth="1"/>
-    <col min="9221" max="9223" width="14.28515625" style="2" customWidth="1"/>
-    <col min="9224" max="9473" width="9.140625" style="2"/>
-    <col min="9474" max="9474" width="6.42578125" style="2" customWidth="1"/>
-    <col min="9475" max="9475" width="80.140625" style="2" customWidth="1"/>
-    <col min="9476" max="9476" width="15.7109375" style="2" customWidth="1"/>
-    <col min="9477" max="9479" width="14.28515625" style="2" customWidth="1"/>
-    <col min="9480" max="9729" width="9.140625" style="2"/>
-    <col min="9730" max="9730" width="6.42578125" style="2" customWidth="1"/>
-    <col min="9731" max="9731" width="80.140625" style="2" customWidth="1"/>
-    <col min="9732" max="9732" width="15.7109375" style="2" customWidth="1"/>
-    <col min="9733" max="9735" width="14.28515625" style="2" customWidth="1"/>
-    <col min="9736" max="9985" width="9.140625" style="2"/>
-    <col min="9986" max="9986" width="6.42578125" style="2" customWidth="1"/>
-    <col min="9987" max="9987" width="80.140625" style="2" customWidth="1"/>
-    <col min="9988" max="9988" width="15.7109375" style="2" customWidth="1"/>
-    <col min="9989" max="9991" width="14.28515625" style="2" customWidth="1"/>
-    <col min="9992" max="10241" width="9.140625" style="2"/>
-    <col min="10242" max="10242" width="6.42578125" style="2" customWidth="1"/>
-    <col min="10243" max="10243" width="80.140625" style="2" customWidth="1"/>
-    <col min="10244" max="10244" width="15.7109375" style="2" customWidth="1"/>
-    <col min="10245" max="10247" width="14.28515625" style="2" customWidth="1"/>
-    <col min="10248" max="10497" width="9.140625" style="2"/>
-    <col min="10498" max="10498" width="6.42578125" style="2" customWidth="1"/>
-    <col min="10499" max="10499" width="80.140625" style="2" customWidth="1"/>
-    <col min="10500" max="10500" width="15.7109375" style="2" customWidth="1"/>
-    <col min="10501" max="10503" width="14.28515625" style="2" customWidth="1"/>
-    <col min="10504" max="10753" width="9.140625" style="2"/>
-    <col min="10754" max="10754" width="6.42578125" style="2" customWidth="1"/>
-    <col min="10755" max="10755" width="80.140625" style="2" customWidth="1"/>
-    <col min="10756" max="10756" width="15.7109375" style="2" customWidth="1"/>
-    <col min="10757" max="10759" width="14.28515625" style="2" customWidth="1"/>
-    <col min="10760" max="11009" width="9.140625" style="2"/>
-    <col min="11010" max="11010" width="6.42578125" style="2" customWidth="1"/>
-    <col min="11011" max="11011" width="80.140625" style="2" customWidth="1"/>
-    <col min="11012" max="11012" width="15.7109375" style="2" customWidth="1"/>
-    <col min="11013" max="11015" width="14.28515625" style="2" customWidth="1"/>
-    <col min="11016" max="11265" width="9.140625" style="2"/>
-    <col min="11266" max="11266" width="6.42578125" style="2" customWidth="1"/>
-    <col min="11267" max="11267" width="80.140625" style="2" customWidth="1"/>
-    <col min="11268" max="11268" width="15.7109375" style="2" customWidth="1"/>
-    <col min="11269" max="11271" width="14.28515625" style="2" customWidth="1"/>
-    <col min="11272" max="11521" width="9.140625" style="2"/>
-    <col min="11522" max="11522" width="6.42578125" style="2" customWidth="1"/>
-    <col min="11523" max="11523" width="80.140625" style="2" customWidth="1"/>
-    <col min="11524" max="11524" width="15.7109375" style="2" customWidth="1"/>
-    <col min="11525" max="11527" width="14.28515625" style="2" customWidth="1"/>
-    <col min="11528" max="11777" width="9.140625" style="2"/>
-    <col min="11778" max="11778" width="6.42578125" style="2" customWidth="1"/>
-    <col min="11779" max="11779" width="80.140625" style="2" customWidth="1"/>
-    <col min="11780" max="11780" width="15.7109375" style="2" customWidth="1"/>
-    <col min="11781" max="11783" width="14.28515625" style="2" customWidth="1"/>
-    <col min="11784" max="12033" width="9.140625" style="2"/>
-    <col min="12034" max="12034" width="6.42578125" style="2" customWidth="1"/>
-    <col min="12035" max="12035" width="80.140625" style="2" customWidth="1"/>
-    <col min="12036" max="12036" width="15.7109375" style="2" customWidth="1"/>
-    <col min="12037" max="12039" width="14.28515625" style="2" customWidth="1"/>
-    <col min="12040" max="12289" width="9.140625" style="2"/>
-    <col min="12290" max="12290" width="6.42578125" style="2" customWidth="1"/>
-    <col min="12291" max="12291" width="80.140625" style="2" customWidth="1"/>
-    <col min="12292" max="12292" width="15.7109375" style="2" customWidth="1"/>
-    <col min="12293" max="12295" width="14.28515625" style="2" customWidth="1"/>
-    <col min="12296" max="12545" width="9.140625" style="2"/>
-    <col min="12546" max="12546" width="6.42578125" style="2" customWidth="1"/>
-    <col min="12547" max="12547" width="80.140625" style="2" customWidth="1"/>
-    <col min="12548" max="12548" width="15.7109375" style="2" customWidth="1"/>
-    <col min="12549" max="12551" width="14.28515625" style="2" customWidth="1"/>
-    <col min="12552" max="12801" width="9.140625" style="2"/>
-    <col min="12802" max="12802" width="6.42578125" style="2" customWidth="1"/>
-    <col min="12803" max="12803" width="80.140625" style="2" customWidth="1"/>
-    <col min="12804" max="12804" width="15.7109375" style="2" customWidth="1"/>
-    <col min="12805" max="12807" width="14.28515625" style="2" customWidth="1"/>
-    <col min="12808" max="13057" width="9.140625" style="2"/>
-    <col min="13058" max="13058" width="6.42578125" style="2" customWidth="1"/>
-    <col min="13059" max="13059" width="80.140625" style="2" customWidth="1"/>
-    <col min="13060" max="13060" width="15.7109375" style="2" customWidth="1"/>
-    <col min="13061" max="13063" width="14.28515625" style="2" customWidth="1"/>
-    <col min="13064" max="13313" width="9.140625" style="2"/>
-    <col min="13314" max="13314" width="6.42578125" style="2" customWidth="1"/>
-    <col min="13315" max="13315" width="80.140625" style="2" customWidth="1"/>
-    <col min="13316" max="13316" width="15.7109375" style="2" customWidth="1"/>
-    <col min="13317" max="13319" width="14.28515625" style="2" customWidth="1"/>
-    <col min="13320" max="13569" width="9.140625" style="2"/>
-    <col min="13570" max="13570" width="6.42578125" style="2" customWidth="1"/>
-    <col min="13571" max="13571" width="80.140625" style="2" customWidth="1"/>
-    <col min="13572" max="13572" width="15.7109375" style="2" customWidth="1"/>
-    <col min="13573" max="13575" width="14.28515625" style="2" customWidth="1"/>
-    <col min="13576" max="13825" width="9.140625" style="2"/>
-    <col min="13826" max="13826" width="6.42578125" style="2" customWidth="1"/>
-    <col min="13827" max="13827" width="80.140625" style="2" customWidth="1"/>
-    <col min="13828" max="13828" width="15.7109375" style="2" customWidth="1"/>
-    <col min="13829" max="13831" width="14.28515625" style="2" customWidth="1"/>
-    <col min="13832" max="14081" width="9.140625" style="2"/>
-    <col min="14082" max="14082" width="6.42578125" style="2" customWidth="1"/>
-    <col min="14083" max="14083" width="80.140625" style="2" customWidth="1"/>
-    <col min="14084" max="14084" width="15.7109375" style="2" customWidth="1"/>
-    <col min="14085" max="14087" width="14.28515625" style="2" customWidth="1"/>
-    <col min="14088" max="14337" width="9.140625" style="2"/>
-    <col min="14338" max="14338" width="6.42578125" style="2" customWidth="1"/>
-    <col min="14339" max="14339" width="80.140625" style="2" customWidth="1"/>
-    <col min="14340" max="14340" width="15.7109375" style="2" customWidth="1"/>
-    <col min="14341" max="14343" width="14.28515625" style="2" customWidth="1"/>
-    <col min="14344" max="14593" width="9.140625" style="2"/>
-    <col min="14594" max="14594" width="6.42578125" style="2" customWidth="1"/>
-    <col min="14595" max="14595" width="80.140625" style="2" customWidth="1"/>
-    <col min="14596" max="14596" width="15.7109375" style="2" customWidth="1"/>
-    <col min="14597" max="14599" width="14.28515625" style="2" customWidth="1"/>
-    <col min="14600" max="14849" width="9.140625" style="2"/>
-    <col min="14850" max="14850" width="6.42578125" style="2" customWidth="1"/>
-    <col min="14851" max="14851" width="80.140625" style="2" customWidth="1"/>
-    <col min="14852" max="14852" width="15.7109375" style="2" customWidth="1"/>
-    <col min="14853" max="14855" width="14.28515625" style="2" customWidth="1"/>
-    <col min="14856" max="15105" width="9.140625" style="2"/>
-    <col min="15106" max="15106" width="6.42578125" style="2" customWidth="1"/>
-    <col min="15107" max="15107" width="80.140625" style="2" customWidth="1"/>
-    <col min="15108" max="15108" width="15.7109375" style="2" customWidth="1"/>
-    <col min="15109" max="15111" width="14.28515625" style="2" customWidth="1"/>
-    <col min="15112" max="15361" width="9.140625" style="2"/>
-    <col min="15362" max="15362" width="6.42578125" style="2" customWidth="1"/>
-    <col min="15363" max="15363" width="80.140625" style="2" customWidth="1"/>
-    <col min="15364" max="15364" width="15.7109375" style="2" customWidth="1"/>
-    <col min="15365" max="15367" width="14.28515625" style="2" customWidth="1"/>
-    <col min="15368" max="15617" width="9.140625" style="2"/>
-    <col min="15618" max="15618" width="6.42578125" style="2" customWidth="1"/>
-    <col min="15619" max="15619" width="80.140625" style="2" customWidth="1"/>
-    <col min="15620" max="15620" width="15.7109375" style="2" customWidth="1"/>
-    <col min="15621" max="15623" width="14.28515625" style="2" customWidth="1"/>
-    <col min="15624" max="15873" width="9.140625" style="2"/>
-    <col min="15874" max="15874" width="6.42578125" style="2" customWidth="1"/>
-    <col min="15875" max="15875" width="80.140625" style="2" customWidth="1"/>
-    <col min="15876" max="15876" width="15.7109375" style="2" customWidth="1"/>
-    <col min="15877" max="15879" width="14.28515625" style="2" customWidth="1"/>
-    <col min="15880" max="16129" width="9.140625" style="2"/>
-    <col min="16130" max="16130" width="6.42578125" style="2" customWidth="1"/>
-    <col min="16131" max="16131" width="80.140625" style="2" customWidth="1"/>
-    <col min="16132" max="16132" width="15.7109375" style="2" customWidth="1"/>
-    <col min="16133" max="16135" width="14.28515625" style="2" customWidth="1"/>
-    <col min="16136" max="16384" width="9.140625" style="2"/>
+    <col min="5" max="5" width="17.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" style="2" customWidth="1"/>
+    <col min="8" max="257" width="9.109375" style="2"/>
+    <col min="258" max="258" width="6.44140625" style="2" customWidth="1"/>
+    <col min="259" max="259" width="80.109375" style="2" customWidth="1"/>
+    <col min="260" max="260" width="15.6640625" style="2" customWidth="1"/>
+    <col min="261" max="263" width="14.33203125" style="2" customWidth="1"/>
+    <col min="264" max="513" width="9.109375" style="2"/>
+    <col min="514" max="514" width="6.44140625" style="2" customWidth="1"/>
+    <col min="515" max="515" width="80.109375" style="2" customWidth="1"/>
+    <col min="516" max="516" width="15.6640625" style="2" customWidth="1"/>
+    <col min="517" max="519" width="14.33203125" style="2" customWidth="1"/>
+    <col min="520" max="769" width="9.109375" style="2"/>
+    <col min="770" max="770" width="6.44140625" style="2" customWidth="1"/>
+    <col min="771" max="771" width="80.109375" style="2" customWidth="1"/>
+    <col min="772" max="772" width="15.6640625" style="2" customWidth="1"/>
+    <col min="773" max="775" width="14.33203125" style="2" customWidth="1"/>
+    <col min="776" max="1025" width="9.109375" style="2"/>
+    <col min="1026" max="1026" width="6.44140625" style="2" customWidth="1"/>
+    <col min="1027" max="1027" width="80.109375" style="2" customWidth="1"/>
+    <col min="1028" max="1028" width="15.6640625" style="2" customWidth="1"/>
+    <col min="1029" max="1031" width="14.33203125" style="2" customWidth="1"/>
+    <col min="1032" max="1281" width="9.109375" style="2"/>
+    <col min="1282" max="1282" width="6.44140625" style="2" customWidth="1"/>
+    <col min="1283" max="1283" width="80.109375" style="2" customWidth="1"/>
+    <col min="1284" max="1284" width="15.6640625" style="2" customWidth="1"/>
+    <col min="1285" max="1287" width="14.33203125" style="2" customWidth="1"/>
+    <col min="1288" max="1537" width="9.109375" style="2"/>
+    <col min="1538" max="1538" width="6.44140625" style="2" customWidth="1"/>
+    <col min="1539" max="1539" width="80.109375" style="2" customWidth="1"/>
+    <col min="1540" max="1540" width="15.6640625" style="2" customWidth="1"/>
+    <col min="1541" max="1543" width="14.33203125" style="2" customWidth="1"/>
+    <col min="1544" max="1793" width="9.109375" style="2"/>
+    <col min="1794" max="1794" width="6.44140625" style="2" customWidth="1"/>
+    <col min="1795" max="1795" width="80.109375" style="2" customWidth="1"/>
+    <col min="1796" max="1796" width="15.6640625" style="2" customWidth="1"/>
+    <col min="1797" max="1799" width="14.33203125" style="2" customWidth="1"/>
+    <col min="1800" max="2049" width="9.109375" style="2"/>
+    <col min="2050" max="2050" width="6.44140625" style="2" customWidth="1"/>
+    <col min="2051" max="2051" width="80.109375" style="2" customWidth="1"/>
+    <col min="2052" max="2052" width="15.6640625" style="2" customWidth="1"/>
+    <col min="2053" max="2055" width="14.33203125" style="2" customWidth="1"/>
+    <col min="2056" max="2305" width="9.109375" style="2"/>
+    <col min="2306" max="2306" width="6.44140625" style="2" customWidth="1"/>
+    <col min="2307" max="2307" width="80.109375" style="2" customWidth="1"/>
+    <col min="2308" max="2308" width="15.6640625" style="2" customWidth="1"/>
+    <col min="2309" max="2311" width="14.33203125" style="2" customWidth="1"/>
+    <col min="2312" max="2561" width="9.109375" style="2"/>
+    <col min="2562" max="2562" width="6.44140625" style="2" customWidth="1"/>
+    <col min="2563" max="2563" width="80.109375" style="2" customWidth="1"/>
+    <col min="2564" max="2564" width="15.6640625" style="2" customWidth="1"/>
+    <col min="2565" max="2567" width="14.33203125" style="2" customWidth="1"/>
+    <col min="2568" max="2817" width="9.109375" style="2"/>
+    <col min="2818" max="2818" width="6.44140625" style="2" customWidth="1"/>
+    <col min="2819" max="2819" width="80.109375" style="2" customWidth="1"/>
+    <col min="2820" max="2820" width="15.6640625" style="2" customWidth="1"/>
+    <col min="2821" max="2823" width="14.33203125" style="2" customWidth="1"/>
+    <col min="2824" max="3073" width="9.109375" style="2"/>
+    <col min="3074" max="3074" width="6.44140625" style="2" customWidth="1"/>
+    <col min="3075" max="3075" width="80.109375" style="2" customWidth="1"/>
+    <col min="3076" max="3076" width="15.6640625" style="2" customWidth="1"/>
+    <col min="3077" max="3079" width="14.33203125" style="2" customWidth="1"/>
+    <col min="3080" max="3329" width="9.109375" style="2"/>
+    <col min="3330" max="3330" width="6.44140625" style="2" customWidth="1"/>
+    <col min="3331" max="3331" width="80.109375" style="2" customWidth="1"/>
+    <col min="3332" max="3332" width="15.6640625" style="2" customWidth="1"/>
+    <col min="3333" max="3335" width="14.33203125" style="2" customWidth="1"/>
+    <col min="3336" max="3585" width="9.109375" style="2"/>
+    <col min="3586" max="3586" width="6.44140625" style="2" customWidth="1"/>
+    <col min="3587" max="3587" width="80.109375" style="2" customWidth="1"/>
+    <col min="3588" max="3588" width="15.6640625" style="2" customWidth="1"/>
+    <col min="3589" max="3591" width="14.33203125" style="2" customWidth="1"/>
+    <col min="3592" max="3841" width="9.109375" style="2"/>
+    <col min="3842" max="3842" width="6.44140625" style="2" customWidth="1"/>
+    <col min="3843" max="3843" width="80.109375" style="2" customWidth="1"/>
+    <col min="3844" max="3844" width="15.6640625" style="2" customWidth="1"/>
+    <col min="3845" max="3847" width="14.33203125" style="2" customWidth="1"/>
+    <col min="3848" max="4097" width="9.109375" style="2"/>
+    <col min="4098" max="4098" width="6.44140625" style="2" customWidth="1"/>
+    <col min="4099" max="4099" width="80.109375" style="2" customWidth="1"/>
+    <col min="4100" max="4100" width="15.6640625" style="2" customWidth="1"/>
+    <col min="4101" max="4103" width="14.33203125" style="2" customWidth="1"/>
+    <col min="4104" max="4353" width="9.109375" style="2"/>
+    <col min="4354" max="4354" width="6.44140625" style="2" customWidth="1"/>
+    <col min="4355" max="4355" width="80.109375" style="2" customWidth="1"/>
+    <col min="4356" max="4356" width="15.6640625" style="2" customWidth="1"/>
+    <col min="4357" max="4359" width="14.33203125" style="2" customWidth="1"/>
+    <col min="4360" max="4609" width="9.109375" style="2"/>
+    <col min="4610" max="4610" width="6.44140625" style="2" customWidth="1"/>
+    <col min="4611" max="4611" width="80.109375" style="2" customWidth="1"/>
+    <col min="4612" max="4612" width="15.6640625" style="2" customWidth="1"/>
+    <col min="4613" max="4615" width="14.33203125" style="2" customWidth="1"/>
+    <col min="4616" max="4865" width="9.109375" style="2"/>
+    <col min="4866" max="4866" width="6.44140625" style="2" customWidth="1"/>
+    <col min="4867" max="4867" width="80.109375" style="2" customWidth="1"/>
+    <col min="4868" max="4868" width="15.6640625" style="2" customWidth="1"/>
+    <col min="4869" max="4871" width="14.33203125" style="2" customWidth="1"/>
+    <col min="4872" max="5121" width="9.109375" style="2"/>
+    <col min="5122" max="5122" width="6.44140625" style="2" customWidth="1"/>
+    <col min="5123" max="5123" width="80.109375" style="2" customWidth="1"/>
+    <col min="5124" max="5124" width="15.6640625" style="2" customWidth="1"/>
+    <col min="5125" max="5127" width="14.33203125" style="2" customWidth="1"/>
+    <col min="5128" max="5377" width="9.109375" style="2"/>
+    <col min="5378" max="5378" width="6.44140625" style="2" customWidth="1"/>
+    <col min="5379" max="5379" width="80.109375" style="2" customWidth="1"/>
+    <col min="5380" max="5380" width="15.6640625" style="2" customWidth="1"/>
+    <col min="5381" max="5383" width="14.33203125" style="2" customWidth="1"/>
+    <col min="5384" max="5633" width="9.109375" style="2"/>
+    <col min="5634" max="5634" width="6.44140625" style="2" customWidth="1"/>
+    <col min="5635" max="5635" width="80.109375" style="2" customWidth="1"/>
+    <col min="5636" max="5636" width="15.6640625" style="2" customWidth="1"/>
+    <col min="5637" max="5639" width="14.33203125" style="2" customWidth="1"/>
+    <col min="5640" max="5889" width="9.109375" style="2"/>
+    <col min="5890" max="5890" width="6.44140625" style="2" customWidth="1"/>
+    <col min="5891" max="5891" width="80.109375" style="2" customWidth="1"/>
+    <col min="5892" max="5892" width="15.6640625" style="2" customWidth="1"/>
+    <col min="5893" max="5895" width="14.33203125" style="2" customWidth="1"/>
+    <col min="5896" max="6145" width="9.109375" style="2"/>
+    <col min="6146" max="6146" width="6.44140625" style="2" customWidth="1"/>
+    <col min="6147" max="6147" width="80.109375" style="2" customWidth="1"/>
+    <col min="6148" max="6148" width="15.6640625" style="2" customWidth="1"/>
+    <col min="6149" max="6151" width="14.33203125" style="2" customWidth="1"/>
+    <col min="6152" max="6401" width="9.109375" style="2"/>
+    <col min="6402" max="6402" width="6.44140625" style="2" customWidth="1"/>
+    <col min="6403" max="6403" width="80.109375" style="2" customWidth="1"/>
+    <col min="6404" max="6404" width="15.6640625" style="2" customWidth="1"/>
+    <col min="6405" max="6407" width="14.33203125" style="2" customWidth="1"/>
+    <col min="6408" max="6657" width="9.109375" style="2"/>
+    <col min="6658" max="6658" width="6.44140625" style="2" customWidth="1"/>
+    <col min="6659" max="6659" width="80.109375" style="2" customWidth="1"/>
+    <col min="6660" max="6660" width="15.6640625" style="2" customWidth="1"/>
+    <col min="6661" max="6663" width="14.33203125" style="2" customWidth="1"/>
+    <col min="6664" max="6913" width="9.109375" style="2"/>
+    <col min="6914" max="6914" width="6.44140625" style="2" customWidth="1"/>
+    <col min="6915" max="6915" width="80.109375" style="2" customWidth="1"/>
+    <col min="6916" max="6916" width="15.6640625" style="2" customWidth="1"/>
+    <col min="6917" max="6919" width="14.33203125" style="2" customWidth="1"/>
+    <col min="6920" max="7169" width="9.109375" style="2"/>
+    <col min="7170" max="7170" width="6.44140625" style="2" customWidth="1"/>
+    <col min="7171" max="7171" width="80.109375" style="2" customWidth="1"/>
+    <col min="7172" max="7172" width="15.6640625" style="2" customWidth="1"/>
+    <col min="7173" max="7175" width="14.33203125" style="2" customWidth="1"/>
+    <col min="7176" max="7425" width="9.109375" style="2"/>
+    <col min="7426" max="7426" width="6.44140625" style="2" customWidth="1"/>
+    <col min="7427" max="7427" width="80.109375" style="2" customWidth="1"/>
+    <col min="7428" max="7428" width="15.6640625" style="2" customWidth="1"/>
+    <col min="7429" max="7431" width="14.33203125" style="2" customWidth="1"/>
+    <col min="7432" max="7681" width="9.109375" style="2"/>
+    <col min="7682" max="7682" width="6.44140625" style="2" customWidth="1"/>
+    <col min="7683" max="7683" width="80.109375" style="2" customWidth="1"/>
+    <col min="7684" max="7684" width="15.6640625" style="2" customWidth="1"/>
+    <col min="7685" max="7687" width="14.33203125" style="2" customWidth="1"/>
+    <col min="7688" max="7937" width="9.109375" style="2"/>
+    <col min="7938" max="7938" width="6.44140625" style="2" customWidth="1"/>
+    <col min="7939" max="7939" width="80.109375" style="2" customWidth="1"/>
+    <col min="7940" max="7940" width="15.6640625" style="2" customWidth="1"/>
+    <col min="7941" max="7943" width="14.33203125" style="2" customWidth="1"/>
+    <col min="7944" max="8193" width="9.109375" style="2"/>
+    <col min="8194" max="8194" width="6.44140625" style="2" customWidth="1"/>
+    <col min="8195" max="8195" width="80.109375" style="2" customWidth="1"/>
+    <col min="8196" max="8196" width="15.6640625" style="2" customWidth="1"/>
+    <col min="8197" max="8199" width="14.33203125" style="2" customWidth="1"/>
+    <col min="8200" max="8449" width="9.109375" style="2"/>
+    <col min="8450" max="8450" width="6.44140625" style="2" customWidth="1"/>
+    <col min="8451" max="8451" width="80.109375" style="2" customWidth="1"/>
+    <col min="8452" max="8452" width="15.6640625" style="2" customWidth="1"/>
+    <col min="8453" max="8455" width="14.33203125" style="2" customWidth="1"/>
+    <col min="8456" max="8705" width="9.109375" style="2"/>
+    <col min="8706" max="8706" width="6.44140625" style="2" customWidth="1"/>
+    <col min="8707" max="8707" width="80.109375" style="2" customWidth="1"/>
+    <col min="8708" max="8708" width="15.6640625" style="2" customWidth="1"/>
+    <col min="8709" max="8711" width="14.33203125" style="2" customWidth="1"/>
+    <col min="8712" max="8961" width="9.109375" style="2"/>
+    <col min="8962" max="8962" width="6.44140625" style="2" customWidth="1"/>
+    <col min="8963" max="8963" width="80.109375" style="2" customWidth="1"/>
+    <col min="8964" max="8964" width="15.6640625" style="2" customWidth="1"/>
+    <col min="8965" max="8967" width="14.33203125" style="2" customWidth="1"/>
+    <col min="8968" max="9217" width="9.109375" style="2"/>
+    <col min="9218" max="9218" width="6.44140625" style="2" customWidth="1"/>
+    <col min="9219" max="9219" width="80.109375" style="2" customWidth="1"/>
+    <col min="9220" max="9220" width="15.6640625" style="2" customWidth="1"/>
+    <col min="9221" max="9223" width="14.33203125" style="2" customWidth="1"/>
+    <col min="9224" max="9473" width="9.109375" style="2"/>
+    <col min="9474" max="9474" width="6.44140625" style="2" customWidth="1"/>
+    <col min="9475" max="9475" width="80.109375" style="2" customWidth="1"/>
+    <col min="9476" max="9476" width="15.6640625" style="2" customWidth="1"/>
+    <col min="9477" max="9479" width="14.33203125" style="2" customWidth="1"/>
+    <col min="9480" max="9729" width="9.109375" style="2"/>
+    <col min="9730" max="9730" width="6.44140625" style="2" customWidth="1"/>
+    <col min="9731" max="9731" width="80.109375" style="2" customWidth="1"/>
+    <col min="9732" max="9732" width="15.6640625" style="2" customWidth="1"/>
+    <col min="9733" max="9735" width="14.33203125" style="2" customWidth="1"/>
+    <col min="9736" max="9985" width="9.109375" style="2"/>
+    <col min="9986" max="9986" width="6.44140625" style="2" customWidth="1"/>
+    <col min="9987" max="9987" width="80.109375" style="2" customWidth="1"/>
+    <col min="9988" max="9988" width="15.6640625" style="2" customWidth="1"/>
+    <col min="9989" max="9991" width="14.33203125" style="2" customWidth="1"/>
+    <col min="9992" max="10241" width="9.109375" style="2"/>
+    <col min="10242" max="10242" width="6.44140625" style="2" customWidth="1"/>
+    <col min="10243" max="10243" width="80.109375" style="2" customWidth="1"/>
+    <col min="10244" max="10244" width="15.6640625" style="2" customWidth="1"/>
+    <col min="10245" max="10247" width="14.33203125" style="2" customWidth="1"/>
+    <col min="10248" max="10497" width="9.109375" style="2"/>
+    <col min="10498" max="10498" width="6.44140625" style="2" customWidth="1"/>
+    <col min="10499" max="10499" width="80.109375" style="2" customWidth="1"/>
+    <col min="10500" max="10500" width="15.6640625" style="2" customWidth="1"/>
+    <col min="10501" max="10503" width="14.33203125" style="2" customWidth="1"/>
+    <col min="10504" max="10753" width="9.109375" style="2"/>
+    <col min="10754" max="10754" width="6.44140625" style="2" customWidth="1"/>
+    <col min="10755" max="10755" width="80.109375" style="2" customWidth="1"/>
+    <col min="10756" max="10756" width="15.6640625" style="2" customWidth="1"/>
+    <col min="10757" max="10759" width="14.33203125" style="2" customWidth="1"/>
+    <col min="10760" max="11009" width="9.109375" style="2"/>
+    <col min="11010" max="11010" width="6.44140625" style="2" customWidth="1"/>
+    <col min="11011" max="11011" width="80.109375" style="2" customWidth="1"/>
+    <col min="11012" max="11012" width="15.6640625" style="2" customWidth="1"/>
+    <col min="11013" max="11015" width="14.33203125" style="2" customWidth="1"/>
+    <col min="11016" max="11265" width="9.109375" style="2"/>
+    <col min="11266" max="11266" width="6.44140625" style="2" customWidth="1"/>
+    <col min="11267" max="11267" width="80.109375" style="2" customWidth="1"/>
+    <col min="11268" max="11268" width="15.6640625" style="2" customWidth="1"/>
+    <col min="11269" max="11271" width="14.33203125" style="2" customWidth="1"/>
+    <col min="11272" max="11521" width="9.109375" style="2"/>
+    <col min="11522" max="11522" width="6.44140625" style="2" customWidth="1"/>
+    <col min="11523" max="11523" width="80.109375" style="2" customWidth="1"/>
+    <col min="11524" max="11524" width="15.6640625" style="2" customWidth="1"/>
+    <col min="11525" max="11527" width="14.33203125" style="2" customWidth="1"/>
+    <col min="11528" max="11777" width="9.109375" style="2"/>
+    <col min="11778" max="11778" width="6.44140625" style="2" customWidth="1"/>
+    <col min="11779" max="11779" width="80.109375" style="2" customWidth="1"/>
+    <col min="11780" max="11780" width="15.6640625" style="2" customWidth="1"/>
+    <col min="11781" max="11783" width="14.33203125" style="2" customWidth="1"/>
+    <col min="11784" max="12033" width="9.109375" style="2"/>
+    <col min="12034" max="12034" width="6.44140625" style="2" customWidth="1"/>
+    <col min="12035" max="12035" width="80.109375" style="2" customWidth="1"/>
+    <col min="12036" max="12036" width="15.6640625" style="2" customWidth="1"/>
+    <col min="12037" max="12039" width="14.33203125" style="2" customWidth="1"/>
+    <col min="12040" max="12289" width="9.109375" style="2"/>
+    <col min="12290" max="12290" width="6.44140625" style="2" customWidth="1"/>
+    <col min="12291" max="12291" width="80.109375" style="2" customWidth="1"/>
+    <col min="12292" max="12292" width="15.6640625" style="2" customWidth="1"/>
+    <col min="12293" max="12295" width="14.33203125" style="2" customWidth="1"/>
+    <col min="12296" max="12545" width="9.109375" style="2"/>
+    <col min="12546" max="12546" width="6.44140625" style="2" customWidth="1"/>
+    <col min="12547" max="12547" width="80.109375" style="2" customWidth="1"/>
+    <col min="12548" max="12548" width="15.6640625" style="2" customWidth="1"/>
+    <col min="12549" max="12551" width="14.33203125" style="2" customWidth="1"/>
+    <col min="12552" max="12801" width="9.109375" style="2"/>
+    <col min="12802" max="12802" width="6.44140625" style="2" customWidth="1"/>
+    <col min="12803" max="12803" width="80.109375" style="2" customWidth="1"/>
+    <col min="12804" max="12804" width="15.6640625" style="2" customWidth="1"/>
+    <col min="12805" max="12807" width="14.33203125" style="2" customWidth="1"/>
+    <col min="12808" max="13057" width="9.109375" style="2"/>
+    <col min="13058" max="13058" width="6.44140625" style="2" customWidth="1"/>
+    <col min="13059" max="13059" width="80.109375" style="2" customWidth="1"/>
+    <col min="13060" max="13060" width="15.6640625" style="2" customWidth="1"/>
+    <col min="13061" max="13063" width="14.33203125" style="2" customWidth="1"/>
+    <col min="13064" max="13313" width="9.109375" style="2"/>
+    <col min="13314" max="13314" width="6.44140625" style="2" customWidth="1"/>
+    <col min="13315" max="13315" width="80.109375" style="2" customWidth="1"/>
+    <col min="13316" max="13316" width="15.6640625" style="2" customWidth="1"/>
+    <col min="13317" max="13319" width="14.33203125" style="2" customWidth="1"/>
+    <col min="13320" max="13569" width="9.109375" style="2"/>
+    <col min="13570" max="13570" width="6.44140625" style="2" customWidth="1"/>
+    <col min="13571" max="13571" width="80.109375" style="2" customWidth="1"/>
+    <col min="13572" max="13572" width="15.6640625" style="2" customWidth="1"/>
+    <col min="13573" max="13575" width="14.33203125" style="2" customWidth="1"/>
+    <col min="13576" max="13825" width="9.109375" style="2"/>
+    <col min="13826" max="13826" width="6.44140625" style="2" customWidth="1"/>
+    <col min="13827" max="13827" width="80.109375" style="2" customWidth="1"/>
+    <col min="13828" max="13828" width="15.6640625" style="2" customWidth="1"/>
+    <col min="13829" max="13831" width="14.33203125" style="2" customWidth="1"/>
+    <col min="13832" max="14081" width="9.109375" style="2"/>
+    <col min="14082" max="14082" width="6.44140625" style="2" customWidth="1"/>
+    <col min="14083" max="14083" width="80.109375" style="2" customWidth="1"/>
+    <col min="14084" max="14084" width="15.6640625" style="2" customWidth="1"/>
+    <col min="14085" max="14087" width="14.33203125" style="2" customWidth="1"/>
+    <col min="14088" max="14337" width="9.109375" style="2"/>
+    <col min="14338" max="14338" width="6.44140625" style="2" customWidth="1"/>
+    <col min="14339" max="14339" width="80.109375" style="2" customWidth="1"/>
+    <col min="14340" max="14340" width="15.6640625" style="2" customWidth="1"/>
+    <col min="14341" max="14343" width="14.33203125" style="2" customWidth="1"/>
+    <col min="14344" max="14593" width="9.109375" style="2"/>
+    <col min="14594" max="14594" width="6.44140625" style="2" customWidth="1"/>
+    <col min="14595" max="14595" width="80.109375" style="2" customWidth="1"/>
+    <col min="14596" max="14596" width="15.6640625" style="2" customWidth="1"/>
+    <col min="14597" max="14599" width="14.33203125" style="2" customWidth="1"/>
+    <col min="14600" max="14849" width="9.109375" style="2"/>
+    <col min="14850" max="14850" width="6.44140625" style="2" customWidth="1"/>
+    <col min="14851" max="14851" width="80.109375" style="2" customWidth="1"/>
+    <col min="14852" max="14852" width="15.6640625" style="2" customWidth="1"/>
+    <col min="14853" max="14855" width="14.33203125" style="2" customWidth="1"/>
+    <col min="14856" max="15105" width="9.109375" style="2"/>
+    <col min="15106" max="15106" width="6.44140625" style="2" customWidth="1"/>
+    <col min="15107" max="15107" width="80.109375" style="2" customWidth="1"/>
+    <col min="15108" max="15108" width="15.6640625" style="2" customWidth="1"/>
+    <col min="15109" max="15111" width="14.33203125" style="2" customWidth="1"/>
+    <col min="15112" max="15361" width="9.109375" style="2"/>
+    <col min="15362" max="15362" width="6.44140625" style="2" customWidth="1"/>
+    <col min="15363" max="15363" width="80.109375" style="2" customWidth="1"/>
+    <col min="15364" max="15364" width="15.6640625" style="2" customWidth="1"/>
+    <col min="15365" max="15367" width="14.33203125" style="2" customWidth="1"/>
+    <col min="15368" max="15617" width="9.109375" style="2"/>
+    <col min="15618" max="15618" width="6.44140625" style="2" customWidth="1"/>
+    <col min="15619" max="15619" width="80.109375" style="2" customWidth="1"/>
+    <col min="15620" max="15620" width="15.6640625" style="2" customWidth="1"/>
+    <col min="15621" max="15623" width="14.33203125" style="2" customWidth="1"/>
+    <col min="15624" max="15873" width="9.109375" style="2"/>
+    <col min="15874" max="15874" width="6.44140625" style="2" customWidth="1"/>
+    <col min="15875" max="15875" width="80.109375" style="2" customWidth="1"/>
+    <col min="15876" max="15876" width="15.6640625" style="2" customWidth="1"/>
+    <col min="15877" max="15879" width="14.33203125" style="2" customWidth="1"/>
+    <col min="15880" max="16129" width="9.109375" style="2"/>
+    <col min="16130" max="16130" width="6.44140625" style="2" customWidth="1"/>
+    <col min="16131" max="16131" width="80.109375" style="2" customWidth="1"/>
+    <col min="16132" max="16132" width="15.6640625" style="2" customWidth="1"/>
+    <col min="16133" max="16135" width="14.33203125" style="2" customWidth="1"/>
+    <col min="16136" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="F1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="24"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="25"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="25"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G2" s="35"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-    </row>
-    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="27" t="s">
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+    </row>
+    <row r="5" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A5" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-    </row>
-    <row r="6" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A6" s="22" t="s">
-        <v>255</v>
-      </c>
-      <c r="B6" s="22"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+    </row>
+    <row r="6" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A6" s="34" t="s">
+        <v>192</v>
+      </c>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="E7" s="28" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E7" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="23" t="s">
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="23"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="30" t="s">
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="26"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="33" t="s">
+      <c r="F9" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="34"/>
-    </row>
-    <row r="10" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="35" t="s">
+      <c r="G9" s="32"/>
+    </row>
+    <row r="10" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A10" s="26"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="G10" s="35" t="s">
+      <c r="G10" s="33" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="23"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-    </row>
-    <row r="12" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A11" s="26"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+    </row>
+    <row r="12" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>1</v>
       </c>
@@ -1905,14 +1715,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>27</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="C13" s="22" t="s">
         <v>29</v>
       </c>
       <c r="D13" s="20"/>
@@ -1926,35 +1736,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>30</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="36" t="s">
+      <c r="C14" s="22" t="s">
         <v>32</v>
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="21">
-        <f t="shared" ref="E14:E134" si="0">D14+F14</f>
+        <f t="shared" ref="E14:E112" si="0">D14+F14</f>
         <v>0</v>
       </c>
       <c r="F14" s="20"/>
       <c r="G14" s="21">
-        <f t="shared" ref="G14:G134" si="1">IFERROR(F14/D14*100,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" ref="G14:G112" si="1">IFERROR(F14/D14*100,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
         <v>33</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="37" t="s">
+      <c r="C15" s="23" t="s">
         <v>35</v>
       </c>
       <c r="D15" s="16"/>
@@ -1968,14 +1778,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>36</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="37" t="s">
+      <c r="C16" s="23" t="s">
         <v>38</v>
       </c>
       <c r="D16" s="16"/>
@@ -1989,14 +1799,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
         <v>39</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="37" t="s">
+      <c r="C17" s="23" t="s">
         <v>41</v>
       </c>
       <c r="D17" s="16"/>
@@ -2010,14 +1820,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>42</v>
       </c>
       <c r="B18" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="37" t="s">
+      <c r="C18" s="23" t="s">
         <v>44</v>
       </c>
       <c r="D18" s="16"/>
@@ -2031,14 +1841,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
         <v>45</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="37" t="s">
+      <c r="C19" s="23" t="s">
         <v>47</v>
       </c>
       <c r="D19" s="16"/>
@@ -2052,14 +1862,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="45" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>48</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="37" t="s">
+      <c r="C20" s="23" t="s">
         <v>50</v>
       </c>
       <c r="D20" s="16"/>
@@ -2073,14 +1883,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
         <v>51</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="37" t="s">
+      <c r="C21" s="23" t="s">
         <v>53</v>
       </c>
       <c r="D21" s="16"/>
@@ -2094,14 +1904,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>54</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="37" t="s">
+      <c r="C22" s="23" t="s">
         <v>56</v>
       </c>
       <c r="D22" s="16"/>
@@ -2115,14 +1925,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
         <v>57</v>
       </c>
       <c r="B23" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="37" t="s">
+      <c r="C23" s="23" t="s">
         <v>59</v>
       </c>
       <c r="D23" s="16"/>
@@ -2136,14 +1946,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>60</v>
       </c>
       <c r="B24" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="37" t="s">
+      <c r="C24" s="23" t="s">
         <v>62</v>
       </c>
       <c r="D24" s="16"/>
@@ -2157,14 +1967,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
         <v>63</v>
       </c>
       <c r="B25" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="C25" s="37" t="s">
+      <c r="C25" s="23" t="s">
         <v>65</v>
       </c>
       <c r="D25" s="16"/>
@@ -2178,14 +1988,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>66</v>
       </c>
       <c r="B26" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="37" t="s">
+      <c r="C26" s="23" t="s">
         <v>68</v>
       </c>
       <c r="D26" s="16"/>
@@ -2199,14 +2009,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
         <v>69</v>
       </c>
       <c r="B27" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="C27" s="37" t="s">
+      <c r="C27" s="23" t="s">
         <v>71</v>
       </c>
       <c r="D27" s="16"/>
@@ -2220,14 +2030,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
         <v>72</v>
       </c>
       <c r="B28" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C28" s="37" t="s">
+      <c r="C28" s="23" t="s">
         <v>74</v>
       </c>
       <c r="D28" s="16"/>
@@ -2241,14 +2051,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
         <v>75</v>
       </c>
       <c r="B29" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C29" s="37" t="s">
+      <c r="C29" s="23" t="s">
         <v>77</v>
       </c>
       <c r="D29" s="16"/>
@@ -2262,14 +2072,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
         <v>78</v>
       </c>
       <c r="B30" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="C30" s="37" t="s">
+      <c r="C30" s="23" t="s">
         <v>80</v>
       </c>
       <c r="D30" s="16"/>
@@ -2283,14 +2093,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
         <v>81</v>
       </c>
       <c r="B31" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C31" s="37" t="s">
+      <c r="C31" s="23" t="s">
         <v>83</v>
       </c>
       <c r="D31" s="16"/>
@@ -2304,14 +2114,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
         <v>84</v>
       </c>
       <c r="B32" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="C32" s="37" t="s">
+      <c r="C32" s="23" t="s">
         <v>86</v>
       </c>
       <c r="D32" s="16"/>
@@ -2325,14 +2135,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
         <v>87</v>
       </c>
       <c r="B33" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="C33" s="37" t="s">
+      <c r="C33" s="23" t="s">
         <v>89</v>
       </c>
       <c r="D33" s="16"/>
@@ -2346,14 +2156,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="45" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
         <v>90</v>
       </c>
       <c r="B34" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C34" s="37" t="s">
+      <c r="C34" s="23" t="s">
         <v>92</v>
       </c>
       <c r="D34" s="16"/>
@@ -2367,14 +2177,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
         <v>93</v>
       </c>
       <c r="B35" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C35" s="37" t="s">
+      <c r="C35" s="23" t="s">
         <v>95</v>
       </c>
       <c r="D35" s="16"/>
@@ -2388,14 +2198,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
         <v>96</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="C36" s="37" t="s">
+      <c r="C36" s="23" t="s">
         <v>98</v>
       </c>
       <c r="D36" s="16"/>
@@ -2409,14 +2219,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
         <v>99</v>
       </c>
       <c r="B37" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="C37" s="37" t="s">
+      <c r="C37" s="23" t="s">
         <v>101</v>
       </c>
       <c r="D37" s="16"/>
@@ -2430,14 +2240,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
         <v>102</v>
       </c>
       <c r="B38" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C38" s="37" t="s">
+      <c r="C38" s="23" t="s">
         <v>104</v>
       </c>
       <c r="D38" s="16"/>
@@ -2451,14 +2261,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A39" s="15" t="s">
         <v>105</v>
       </c>
       <c r="B39" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="C39" s="37" t="s">
+      <c r="C39" s="23" t="s">
         <v>107</v>
       </c>
       <c r="D39" s="16"/>
@@ -2472,14 +2282,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A40" s="15" t="s">
         <v>108</v>
       </c>
       <c r="B40" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C40" s="37" t="s">
+      <c r="C40" s="23" t="s">
         <v>110</v>
       </c>
       <c r="D40" s="18"/>
@@ -2493,14 +2303,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A41" s="15" t="s">
         <v>111</v>
       </c>
       <c r="B41" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="C41" s="37" t="s">
+      <c r="C41" s="23" t="s">
         <v>113</v>
       </c>
       <c r="D41" s="18"/>
@@ -2514,14 +2324,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A42" s="15" t="s">
         <v>114</v>
       </c>
       <c r="B42" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="C42" s="37" t="s">
+      <c r="C42" s="23" t="s">
         <v>116</v>
       </c>
       <c r="D42" s="18"/>
@@ -2535,14 +2345,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A43" s="15" t="s">
         <v>117</v>
       </c>
       <c r="B43" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C43" s="37" t="s">
+      <c r="C43" s="23" t="s">
         <v>119</v>
       </c>
       <c r="D43" s="18"/>
@@ -2556,14 +2366,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A44" s="15" t="s">
         <v>120</v>
       </c>
       <c r="B44" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="C44" s="37" t="s">
+      <c r="C44" s="23" t="s">
         <v>122</v>
       </c>
       <c r="D44" s="18"/>
@@ -2577,14 +2387,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
         <v>123</v>
       </c>
       <c r="B45" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="C45" s="37" t="s">
+      <c r="C45" s="23" t="s">
         <v>125</v>
       </c>
       <c r="D45" s="18"/>
@@ -2598,14 +2408,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A46" s="15" t="s">
         <v>126</v>
       </c>
       <c r="B46" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="C46" s="37" t="s">
+      <c r="C46" s="23" t="s">
         <v>128</v>
       </c>
       <c r="D46" s="18"/>
@@ -2619,14 +2429,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A47" s="15" t="s">
         <v>129</v>
       </c>
       <c r="B47" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="C47" s="37" t="s">
+      <c r="C47" s="23" t="s">
         <v>131</v>
       </c>
       <c r="D47" s="18"/>
@@ -2640,14 +2450,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A48" s="15" t="s">
         <v>132</v>
       </c>
       <c r="B48" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="C48" s="37" t="s">
+      <c r="C48" s="23" t="s">
         <v>134</v>
       </c>
       <c r="D48" s="18"/>
@@ -2661,14 +2471,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A49" s="19" t="s">
         <v>135</v>
       </c>
       <c r="B49" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="C49" s="36" t="s">
+      <c r="C49" s="22" t="s">
         <v>137</v>
       </c>
       <c r="D49" s="20"/>
@@ -2682,14 +2492,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A50" s="15" t="s">
         <v>138</v>
       </c>
       <c r="B50" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="C50" s="37" t="s">
+      <c r="C50" s="23" t="s">
         <v>35</v>
       </c>
       <c r="D50" s="18"/>
@@ -2703,14 +2513,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A51" s="15" t="s">
         <v>140</v>
       </c>
       <c r="B51" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C51" s="37" t="s">
+      <c r="C51" s="23" t="s">
         <v>38</v>
       </c>
       <c r="D51" s="18"/>
@@ -2724,14 +2534,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A52" s="15" t="s">
         <v>142</v>
       </c>
       <c r="B52" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="C52" s="37" t="s">
+      <c r="C52" s="23" t="s">
         <v>41</v>
       </c>
       <c r="D52" s="18"/>
@@ -2745,14 +2555,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A53" s="15" t="s">
         <v>144</v>
       </c>
       <c r="B53" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="C53" s="37" t="s">
+      <c r="C53" s="23" t="s">
         <v>44</v>
       </c>
       <c r="D53" s="18"/>
@@ -2766,14 +2576,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A54" s="15" t="s">
         <v>146</v>
       </c>
       <c r="B54" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="C54" s="37" t="s">
+      <c r="C54" s="23" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="18"/>
@@ -2787,14 +2597,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="45" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A55" s="15" t="s">
         <v>148</v>
       </c>
       <c r="B55" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="C55" s="37" t="s">
+      <c r="C55" s="23" t="s">
         <v>150</v>
       </c>
       <c r="D55" s="18"/>
@@ -2808,14 +2618,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A56" s="15" t="s">
         <v>151</v>
       </c>
       <c r="B56" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="C56" s="37" t="s">
+      <c r="C56" s="23" t="s">
         <v>53</v>
       </c>
       <c r="D56" s="18"/>
@@ -2829,14 +2639,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A57" s="15" t="s">
         <v>153</v>
       </c>
       <c r="B57" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="C57" s="37" t="s">
+      <c r="C57" s="23" t="s">
         <v>56</v>
       </c>
       <c r="D57" s="18"/>
@@ -2850,14 +2660,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>155</v>
       </c>
       <c r="B58" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="C58" s="37" t="s">
+      <c r="C58" s="23" t="s">
         <v>59</v>
       </c>
       <c r="D58" s="18"/>
@@ -2871,14 +2681,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A59" s="15" t="s">
         <v>157</v>
       </c>
       <c r="B59" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="C59" s="37" t="s">
+      <c r="C59" s="23" t="s">
         <v>62</v>
       </c>
       <c r="D59" s="18"/>
@@ -2892,14 +2702,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A60" s="15" t="s">
         <v>159</v>
       </c>
       <c r="B60" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="C60" s="37" t="s">
+      <c r="C60" s="23" t="s">
         <v>65</v>
       </c>
       <c r="D60" s="18"/>
@@ -2913,14 +2723,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A61" s="15" t="s">
         <v>161</v>
       </c>
       <c r="B61" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="C61" s="37" t="s">
+      <c r="C61" s="23" t="s">
         <v>68</v>
       </c>
       <c r="D61" s="18"/>
@@ -2934,14 +2744,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A62" s="15" t="s">
         <v>163</v>
       </c>
       <c r="B62" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="C62" s="37" t="s">
+      <c r="C62" s="23" t="s">
         <v>71</v>
       </c>
       <c r="D62" s="18"/>
@@ -2955,14 +2765,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A63" s="15" t="s">
         <v>165</v>
       </c>
       <c r="B63" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="C63" s="37" t="s">
+      <c r="C63" s="23" t="s">
         <v>167</v>
       </c>
       <c r="D63" s="18"/>
@@ -2976,14 +2786,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A64" s="15" t="s">
         <v>168</v>
       </c>
       <c r="B64" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="C64" s="37" t="s">
+      <c r="C64" s="23" t="s">
         <v>77</v>
       </c>
       <c r="D64" s="18"/>
@@ -2997,14 +2807,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A65" s="15" t="s">
         <v>170</v>
       </c>
       <c r="B65" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="C65" s="37" t="s">
+      <c r="C65" s="23" t="s">
         <v>80</v>
       </c>
       <c r="D65" s="18"/>
@@ -3018,14 +2828,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A66" s="15" t="s">
         <v>172</v>
       </c>
       <c r="B66" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="C66" s="37" t="s">
+      <c r="C66" s="23" t="s">
         <v>83</v>
       </c>
       <c r="D66" s="18"/>
@@ -3039,14 +2849,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A67" s="15" t="s">
         <v>174</v>
       </c>
       <c r="B67" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="C67" s="37" t="s">
+      <c r="C67" s="23" t="s">
         <v>86</v>
       </c>
       <c r="D67" s="18"/>
@@ -3060,14 +2870,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A68" s="15" t="s">
         <v>176</v>
       </c>
       <c r="B68" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="C68" s="37" t="s">
+      <c r="C68" s="23" t="s">
         <v>89</v>
       </c>
       <c r="D68" s="18"/>
@@ -3081,14 +2891,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="45" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A69" s="15" t="s">
         <v>178</v>
       </c>
       <c r="B69" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="C69" s="37" t="s">
+      <c r="C69" s="23" t="s">
         <v>92</v>
       </c>
       <c r="D69" s="18"/>
@@ -3102,14 +2912,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A70" s="15" t="s">
         <v>180</v>
       </c>
       <c r="B70" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="C70" s="37" t="s">
+      <c r="C70" s="23" t="s">
         <v>95</v>
       </c>
       <c r="D70" s="18"/>
@@ -3123,14 +2933,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A71" s="15" t="s">
         <v>182</v>
       </c>
       <c r="B71" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="C71" s="37" t="s">
+      <c r="C71" s="23" t="s">
         <v>98</v>
       </c>
       <c r="D71" s="18"/>
@@ -3144,14 +2954,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A72" s="15" t="s">
         <v>184</v>
       </c>
       <c r="B72" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="C72" s="37" t="s">
+      <c r="C72" s="23" t="s">
         <v>101</v>
       </c>
       <c r="D72" s="18"/>
@@ -3165,14 +2975,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A73" s="15" t="s">
         <v>186</v>
       </c>
       <c r="B73" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="C73" s="37" t="s">
+      <c r="C73" s="23" t="s">
         <v>104</v>
       </c>
       <c r="D73" s="18"/>
@@ -3186,14 +2996,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A74" s="15" t="s">
         <v>188</v>
       </c>
       <c r="B74" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="C74" s="37" t="s">
+      <c r="C74" s="23" t="s">
         <v>107</v>
       </c>
       <c r="D74" s="18"/>
@@ -3207,14 +3017,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A75" s="15" t="s">
         <v>190</v>
       </c>
       <c r="B75" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="C75" s="37" t="s">
+      <c r="C75" s="23" t="s">
         <v>134</v>
       </c>
       <c r="D75" s="18"/>
@@ -3228,38 +3038,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A76" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="B76" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="C76" s="36" t="s">
-        <v>194</v>
-      </c>
-      <c r="D76" s="20"/>
-      <c r="E76" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F76" s="20"/>
-      <c r="G76" s="21">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A77" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="B77" s="15" t="s">
-        <v>196</v>
-      </c>
-      <c r="C77" s="37" t="s">
-        <v>197</v>
-      </c>
-      <c r="D77" s="18"/>
+    <row r="76" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A76" s="15"/>
+      <c r="B76" s="15"/>
+      <c r="C76" s="14"/>
+      <c r="D76" s="16"/>
+      <c r="E76" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F76" s="18"/>
+      <c r="G76" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A77" s="15"/>
+      <c r="B77" s="15"/>
+      <c r="C77" s="14"/>
+      <c r="D77" s="16"/>
       <c r="E77" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3270,17 +3068,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A78" s="15" t="s">
-        <v>198</v>
-      </c>
-      <c r="B78" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="C78" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="D78" s="18"/>
+    <row r="78" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A78" s="15"/>
+      <c r="B78" s="15"/>
+      <c r="C78" s="14"/>
+      <c r="D78" s="16"/>
       <c r="E78" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3291,17 +3083,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A79" s="15" t="s">
-        <v>201</v>
-      </c>
-      <c r="B79" s="15" t="s">
-        <v>202</v>
-      </c>
-      <c r="C79" s="37" t="s">
-        <v>203</v>
-      </c>
-      <c r="D79" s="18"/>
+    <row r="79" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A79" s="15"/>
+      <c r="B79" s="15"/>
+      <c r="C79" s="14"/>
+      <c r="D79" s="16"/>
       <c r="E79" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3312,17 +3098,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A80" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="B80" s="15" t="s">
-        <v>205</v>
-      </c>
-      <c r="C80" s="37" t="s">
-        <v>206</v>
-      </c>
-      <c r="D80" s="18"/>
+    <row r="80" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A80" s="15"/>
+      <c r="B80" s="15"/>
+      <c r="C80" s="14"/>
+      <c r="D80" s="16"/>
       <c r="E80" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3333,17 +3113,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A81" s="15" t="s">
-        <v>207</v>
-      </c>
-      <c r="B81" s="15" t="s">
-        <v>208</v>
-      </c>
-      <c r="C81" s="37" t="s">
-        <v>209</v>
-      </c>
-      <c r="D81" s="18"/>
+    <row r="81" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A81" s="15"/>
+      <c r="B81" s="15"/>
+      <c r="C81" s="14"/>
+      <c r="D81" s="16"/>
       <c r="E81" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3354,17 +3128,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A82" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="B82" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="C82" s="37" t="s">
-        <v>212</v>
-      </c>
-      <c r="D82" s="18"/>
+    <row r="82" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A82" s="15"/>
+      <c r="B82" s="15"/>
+      <c r="C82" s="14"/>
+      <c r="D82" s="16"/>
       <c r="E82" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3375,17 +3143,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A83" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="B83" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="C83" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="D83" s="18"/>
+    <row r="83" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A83" s="15"/>
+      <c r="B83" s="15"/>
+      <c r="C83" s="14"/>
+      <c r="D83" s="16"/>
       <c r="E83" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3396,17 +3158,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A84" s="15" t="s">
-        <v>216</v>
-      </c>
-      <c r="B84" s="15" t="s">
-        <v>217</v>
-      </c>
-      <c r="C84" s="37" t="s">
-        <v>218</v>
-      </c>
-      <c r="D84" s="18"/>
+    <row r="84" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A84" s="15"/>
+      <c r="B84" s="15"/>
+      <c r="C84" s="14"/>
+      <c r="D84" s="16"/>
       <c r="E84" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3417,17 +3173,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A85" s="15" t="s">
-        <v>219</v>
-      </c>
-      <c r="B85" s="15" t="s">
-        <v>220</v>
-      </c>
-      <c r="C85" s="37" t="s">
-        <v>221</v>
-      </c>
-      <c r="D85" s="18"/>
+    <row r="85" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A85" s="15"/>
+      <c r="B85" s="15"/>
+      <c r="C85" s="14"/>
+      <c r="D85" s="16"/>
       <c r="E85" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3438,17 +3188,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A86" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="B86" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="C86" s="37" t="s">
-        <v>224</v>
-      </c>
-      <c r="D86" s="18"/>
+    <row r="86" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A86" s="15"/>
+      <c r="B86" s="15"/>
+      <c r="C86" s="14"/>
+      <c r="D86" s="16"/>
       <c r="E86" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3459,17 +3203,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A87" s="15" t="s">
-        <v>225</v>
-      </c>
-      <c r="B87" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="C87" s="37" t="s">
-        <v>227</v>
-      </c>
-      <c r="D87" s="18"/>
+    <row r="87" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A87" s="15"/>
+      <c r="B87" s="15"/>
+      <c r="C87" s="14"/>
+      <c r="D87" s="16"/>
       <c r="E87" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3480,17 +3218,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A88" s="15" t="s">
-        <v>228</v>
-      </c>
-      <c r="B88" s="15" t="s">
-        <v>229</v>
-      </c>
-      <c r="C88" s="37" t="s">
-        <v>230</v>
-      </c>
-      <c r="D88" s="18"/>
+    <row r="88" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A88" s="15"/>
+      <c r="B88" s="15"/>
+      <c r="C88" s="14"/>
+      <c r="D88" s="16"/>
       <c r="E88" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3501,17 +3233,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A89" s="15" t="s">
-        <v>231</v>
-      </c>
-      <c r="B89" s="15" t="s">
-        <v>232</v>
-      </c>
-      <c r="C89" s="37" t="s">
-        <v>233</v>
-      </c>
-      <c r="D89" s="18"/>
+    <row r="89" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A89" s="15"/>
+      <c r="B89" s="15"/>
+      <c r="C89" s="14"/>
+      <c r="D89" s="16"/>
       <c r="E89" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3522,17 +3248,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A90" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="B90" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="C90" s="37" t="s">
-        <v>236</v>
-      </c>
-      <c r="D90" s="18"/>
+    <row r="90" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A90" s="15"/>
+      <c r="B90" s="15"/>
+      <c r="C90" s="14"/>
+      <c r="D90" s="16"/>
       <c r="E90" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3543,17 +3263,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A91" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="B91" s="15" t="s">
-        <v>238</v>
-      </c>
-      <c r="C91" s="37" t="s">
-        <v>239</v>
-      </c>
-      <c r="D91" s="18"/>
+    <row r="91" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A91" s="15"/>
+      <c r="B91" s="15"/>
+      <c r="C91" s="14"/>
+      <c r="D91" s="16"/>
       <c r="E91" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3564,17 +3278,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A92" s="15" t="s">
-        <v>240</v>
-      </c>
-      <c r="B92" s="15" t="s">
-        <v>241</v>
-      </c>
-      <c r="C92" s="37" t="s">
-        <v>242</v>
-      </c>
-      <c r="D92" s="18"/>
+    <row r="92" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A92" s="15"/>
+      <c r="B92" s="15"/>
+      <c r="C92" s="14"/>
+      <c r="D92" s="16"/>
       <c r="E92" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3585,17 +3293,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A93" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="B93" s="15" t="s">
-        <v>244</v>
-      </c>
-      <c r="C93" s="37" t="s">
-        <v>245</v>
-      </c>
-      <c r="D93" s="18"/>
+    <row r="93" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A93" s="15"/>
+      <c r="B93" s="15"/>
+      <c r="C93" s="14"/>
+      <c r="D93" s="16"/>
       <c r="E93" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3606,17 +3308,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A94" s="15" t="s">
-        <v>246</v>
-      </c>
-      <c r="B94" s="15" t="s">
-        <v>247</v>
-      </c>
-      <c r="C94" s="37" t="s">
-        <v>248</v>
-      </c>
-      <c r="D94" s="18"/>
+    <row r="94" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A94" s="15"/>
+      <c r="B94" s="15"/>
+      <c r="C94" s="14"/>
+      <c r="D94" s="16"/>
       <c r="E94" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3627,17 +3323,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A95" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="B95" s="15" t="s">
-        <v>250</v>
-      </c>
-      <c r="C95" s="37" t="s">
-        <v>251</v>
-      </c>
-      <c r="D95" s="18"/>
+    <row r="95" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A95" s="15"/>
+      <c r="B95" s="15"/>
+      <c r="C95" s="14"/>
+      <c r="D95" s="16"/>
       <c r="E95" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3648,17 +3338,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A96" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="B96" s="15" t="s">
-        <v>253</v>
-      </c>
-      <c r="C96" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="D96" s="18"/>
+    <row r="96" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A96" s="15"/>
+      <c r="B96" s="15"/>
+      <c r="C96" s="14"/>
+      <c r="D96" s="16"/>
       <c r="E96" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3669,7 +3353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A97" s="15"/>
       <c r="B97" s="15"/>
       <c r="C97" s="14"/>
@@ -3684,7 +3368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A98" s="15"/>
       <c r="B98" s="15"/>
       <c r="C98" s="14"/>
@@ -3699,7 +3383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A99" s="15"/>
       <c r="B99" s="15"/>
       <c r="C99" s="14"/>
@@ -3714,7 +3398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A100" s="15"/>
       <c r="B100" s="15"/>
       <c r="C100" s="14"/>
@@ -3729,7 +3413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A101" s="15"/>
       <c r="B101" s="15"/>
       <c r="C101" s="14"/>
@@ -3744,7 +3428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A102" s="15"/>
       <c r="B102" s="15"/>
       <c r="C102" s="14"/>
@@ -3759,7 +3443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A103" s="15"/>
       <c r="B103" s="15"/>
       <c r="C103" s="14"/>
@@ -3774,7 +3458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A104" s="15"/>
       <c r="B104" s="15"/>
       <c r="C104" s="14"/>
@@ -3789,7 +3473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A105" s="15"/>
       <c r="B105" s="15"/>
       <c r="C105" s="14"/>
@@ -3804,7 +3488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A106" s="15"/>
       <c r="B106" s="15"/>
       <c r="C106" s="14"/>
@@ -3819,7 +3503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A107" s="15"/>
       <c r="B107" s="15"/>
       <c r="C107" s="14"/>
@@ -3834,7 +3518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A108" s="15"/>
       <c r="B108" s="15"/>
       <c r="C108" s="14"/>
@@ -3849,7 +3533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A109" s="15"/>
       <c r="B109" s="15"/>
       <c r="C109" s="14"/>
@@ -3864,7 +3548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A110" s="15"/>
       <c r="B110" s="15"/>
       <c r="C110" s="14"/>
@@ -3879,7 +3563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A111" s="15"/>
       <c r="B111" s="15"/>
       <c r="C111" s="14"/>
@@ -3894,7 +3578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A112" s="15"/>
       <c r="B112" s="15"/>
       <c r="C112" s="14"/>
@@ -3909,352 +3593,352 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A113" s="15"/>
       <c r="B113" s="15"/>
       <c r="C113" s="14"/>
       <c r="D113" s="16"/>
       <c r="E113" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E113:E144" si="2">D113+F113</f>
         <v>0</v>
       </c>
       <c r="F113" s="18"/>
       <c r="G113" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" ref="G113:G144" si="3">IFERROR(F113/D113*100,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A114" s="15"/>
       <c r="B114" s="15"/>
       <c r="C114" s="14"/>
       <c r="D114" s="16"/>
       <c r="E114" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F114" s="18"/>
       <c r="G114" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A115" s="15"/>
       <c r="B115" s="15"/>
       <c r="C115" s="14"/>
       <c r="D115" s="16"/>
       <c r="E115" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F115" s="18"/>
       <c r="G115" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A116" s="15"/>
       <c r="B116" s="15"/>
       <c r="C116" s="14"/>
       <c r="D116" s="16"/>
       <c r="E116" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F116" s="18"/>
       <c r="G116" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A117" s="15"/>
       <c r="B117" s="15"/>
       <c r="C117" s="14"/>
       <c r="D117" s="16"/>
       <c r="E117" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F117" s="18"/>
       <c r="G117" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A118" s="15"/>
       <c r="B118" s="15"/>
       <c r="C118" s="14"/>
       <c r="D118" s="16"/>
       <c r="E118" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F118" s="18"/>
       <c r="G118" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A119" s="15"/>
       <c r="B119" s="15"/>
       <c r="C119" s="14"/>
-      <c r="D119" s="16"/>
+      <c r="D119" s="18"/>
       <c r="E119" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F119" s="18"/>
       <c r="G119" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A120" s="15"/>
       <c r="B120" s="15"/>
       <c r="C120" s="14"/>
-      <c r="D120" s="16"/>
+      <c r="D120" s="18"/>
       <c r="E120" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F120" s="18"/>
       <c r="G120" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A121" s="15"/>
       <c r="B121" s="15"/>
       <c r="C121" s="14"/>
-      <c r="D121" s="16"/>
+      <c r="D121" s="18"/>
       <c r="E121" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F121" s="18"/>
       <c r="G121" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A122" s="15"/>
       <c r="B122" s="15"/>
       <c r="C122" s="14"/>
-      <c r="D122" s="16"/>
+      <c r="D122" s="18"/>
       <c r="E122" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F122" s="18"/>
       <c r="G122" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A123" s="15"/>
       <c r="B123" s="15"/>
       <c r="C123" s="14"/>
-      <c r="D123" s="16"/>
+      <c r="D123" s="18"/>
       <c r="E123" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F123" s="18"/>
       <c r="G123" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A124" s="15"/>
       <c r="B124" s="15"/>
       <c r="C124" s="14"/>
-      <c r="D124" s="16"/>
+      <c r="D124" s="18"/>
       <c r="E124" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F124" s="18"/>
       <c r="G124" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A125" s="15"/>
       <c r="B125" s="15"/>
       <c r="C125" s="14"/>
-      <c r="D125" s="16"/>
+      <c r="D125" s="18"/>
       <c r="E125" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F125" s="18"/>
       <c r="G125" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A126" s="15"/>
       <c r="B126" s="15"/>
       <c r="C126" s="14"/>
-      <c r="D126" s="16"/>
+      <c r="D126" s="18"/>
       <c r="E126" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F126" s="18"/>
       <c r="G126" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A127" s="15"/>
       <c r="B127" s="15"/>
       <c r="C127" s="14"/>
-      <c r="D127" s="16"/>
+      <c r="D127" s="18"/>
       <c r="E127" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F127" s="18"/>
       <c r="G127" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A128" s="15"/>
       <c r="B128" s="15"/>
       <c r="C128" s="14"/>
-      <c r="D128" s="16"/>
+      <c r="D128" s="18"/>
       <c r="E128" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F128" s="18"/>
       <c r="G128" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A129" s="15"/>
       <c r="B129" s="15"/>
       <c r="C129" s="14"/>
-      <c r="D129" s="16"/>
+      <c r="D129" s="18"/>
       <c r="E129" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F129" s="18"/>
       <c r="G129" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A130" s="15"/>
       <c r="B130" s="15"/>
       <c r="C130" s="14"/>
-      <c r="D130" s="16"/>
+      <c r="D130" s="18"/>
       <c r="E130" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F130" s="18"/>
       <c r="G130" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A131" s="15"/>
       <c r="B131" s="15"/>
       <c r="C131" s="14"/>
-      <c r="D131" s="16"/>
+      <c r="D131" s="18"/>
       <c r="E131" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F131" s="18"/>
       <c r="G131" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A132" s="15"/>
       <c r="B132" s="15"/>
       <c r="C132" s="14"/>
       <c r="D132" s="16"/>
       <c r="E132" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F132" s="18"/>
       <c r="G132" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A133" s="15"/>
       <c r="B133" s="15"/>
       <c r="C133" s="14"/>
       <c r="D133" s="16"/>
       <c r="E133" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F133" s="18"/>
       <c r="G133" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A134" s="15"/>
       <c r="B134" s="15"/>
       <c r="C134" s="14"/>
       <c r="D134" s="16"/>
       <c r="E134" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F134" s="18"/>
       <c r="G134" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A135" s="15"/>
       <c r="B135" s="15"/>
       <c r="C135" s="14"/>
       <c r="D135" s="16"/>
       <c r="E135" s="17">
-        <f t="shared" ref="E135:E166" si="2">D135+F135</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F135" s="18"/>
       <c r="G135" s="17">
-        <f t="shared" ref="G135:G166" si="3">IFERROR(F135/D135*100,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A136" s="15"/>
       <c r="B136" s="15"/>
       <c r="C136" s="14"/>
@@ -4269,7 +3953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A137" s="15"/>
       <c r="B137" s="15"/>
       <c r="C137" s="14"/>
@@ -4284,7 +3968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A138" s="15"/>
       <c r="B138" s="15"/>
       <c r="C138" s="14"/>
@@ -4299,7 +3983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A139" s="15"/>
       <c r="B139" s="15"/>
       <c r="C139" s="14"/>
@@ -4314,7 +3998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A140" s="15"/>
       <c r="B140" s="15"/>
       <c r="C140" s="14"/>
@@ -4329,11 +4013,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A141" s="15"/>
       <c r="B141" s="15"/>
       <c r="C141" s="14"/>
-      <c r="D141" s="18"/>
+      <c r="D141" s="16"/>
       <c r="E141" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -4344,11 +4028,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A142" s="15"/>
       <c r="B142" s="15"/>
       <c r="C142" s="14"/>
-      <c r="D142" s="18"/>
+      <c r="D142" s="16"/>
       <c r="E142" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -4359,11 +4043,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A143" s="15"/>
       <c r="B143" s="15"/>
       <c r="C143" s="14"/>
-      <c r="D143" s="18"/>
+      <c r="D143" s="16"/>
       <c r="E143" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -4374,11 +4058,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A144" s="15"/>
       <c r="B144" s="15"/>
       <c r="C144" s="14"/>
-      <c r="D144" s="18"/>
+      <c r="D144" s="16"/>
       <c r="E144" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -4389,440 +4073,117 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A145" s="15"/>
-      <c r="B145" s="15"/>
-      <c r="C145" s="14"/>
-      <c r="D145" s="18"/>
-      <c r="E145" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F145" s="18"/>
-      <c r="G145" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A146" s="15"/>
-      <c r="B146" s="15"/>
-      <c r="C146" s="14"/>
-      <c r="D146" s="18"/>
-      <c r="E146" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F146" s="18"/>
-      <c r="G146" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A147" s="15"/>
-      <c r="B147" s="15"/>
-      <c r="C147" s="14"/>
-      <c r="D147" s="18"/>
-      <c r="E147" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F147" s="18"/>
-      <c r="G147" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A148" s="15"/>
-      <c r="B148" s="15"/>
-      <c r="C148" s="14"/>
-      <c r="D148" s="18"/>
-      <c r="E148" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F148" s="18"/>
-      <c r="G148" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A149" s="15"/>
-      <c r="B149" s="15"/>
-      <c r="C149" s="14"/>
-      <c r="D149" s="18"/>
-      <c r="E149" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F149" s="18"/>
-      <c r="G149" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A150" s="15"/>
-      <c r="B150" s="15"/>
-      <c r="C150" s="14"/>
-      <c r="D150" s="18"/>
-      <c r="E150" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F150" s="18"/>
-      <c r="G150" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A151" s="15"/>
-      <c r="B151" s="15"/>
-      <c r="C151" s="14"/>
-      <c r="D151" s="18"/>
-      <c r="E151" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F151" s="18"/>
-      <c r="G151" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A152" s="15"/>
-      <c r="B152" s="15"/>
-      <c r="C152" s="14"/>
-      <c r="D152" s="18"/>
-      <c r="E152" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F152" s="18"/>
-      <c r="G152" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A153" s="15"/>
-      <c r="B153" s="15"/>
-      <c r="C153" s="14"/>
-      <c r="D153" s="18"/>
-      <c r="E153" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F153" s="18"/>
-      <c r="G153" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A154" s="15"/>
-      <c r="B154" s="15"/>
-      <c r="C154" s="14"/>
-      <c r="D154" s="16"/>
-      <c r="E154" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F154" s="18"/>
-      <c r="G154" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A155" s="15"/>
-      <c r="B155" s="15"/>
-      <c r="C155" s="14"/>
-      <c r="D155" s="16"/>
-      <c r="E155" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F155" s="18"/>
-      <c r="G155" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A156" s="15"/>
-      <c r="B156" s="15"/>
-      <c r="C156" s="14"/>
-      <c r="D156" s="16"/>
-      <c r="E156" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F156" s="18"/>
-      <c r="G156" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A157" s="15"/>
-      <c r="B157" s="15"/>
-      <c r="C157" s="14"/>
-      <c r="D157" s="16"/>
-      <c r="E157" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F157" s="18"/>
-      <c r="G157" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A158" s="15"/>
-      <c r="B158" s="15"/>
-      <c r="C158" s="14"/>
-      <c r="D158" s="16"/>
-      <c r="E158" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F158" s="18"/>
-      <c r="G158" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A159" s="15"/>
-      <c r="B159" s="15"/>
-      <c r="C159" s="14"/>
-      <c r="D159" s="16"/>
-      <c r="E159" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F159" s="18"/>
-      <c r="G159" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A160" s="15"/>
-      <c r="B160" s="15"/>
-      <c r="C160" s="14"/>
-      <c r="D160" s="16"/>
-      <c r="E160" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F160" s="18"/>
-      <c r="G160" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A161" s="15"/>
-      <c r="B161" s="15"/>
-      <c r="C161" s="14"/>
-      <c r="D161" s="16"/>
-      <c r="E161" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F161" s="18"/>
-      <c r="G161" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A162" s="15"/>
-      <c r="B162" s="15"/>
-      <c r="C162" s="14"/>
-      <c r="D162" s="16"/>
-      <c r="E162" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F162" s="18"/>
-      <c r="G162" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A163" s="15"/>
-      <c r="B163" s="15"/>
-      <c r="C163" s="14"/>
-      <c r="D163" s="16"/>
-      <c r="E163" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F163" s="18"/>
-      <c r="G163" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A164" s="15"/>
-      <c r="B164" s="15"/>
-      <c r="C164" s="14"/>
-      <c r="D164" s="16"/>
-      <c r="E164" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F164" s="18"/>
-      <c r="G164" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A165" s="15"/>
-      <c r="B165" s="15"/>
-      <c r="C165" s="14"/>
-      <c r="D165" s="16"/>
-      <c r="E165" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F165" s="18"/>
-      <c r="G165" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A166" s="15"/>
-      <c r="B166" s="15"/>
-      <c r="C166" s="14"/>
-      <c r="D166" s="16"/>
-      <c r="E166" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F166" s="18"/>
-      <c r="G166" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A167" s="8"/>
-      <c r="B167" s="8"/>
-      <c r="C167" s="9"/>
-      <c r="G167" s="6"/>
-    </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A168" s="8"/>
-      <c r="B168" s="8"/>
-      <c r="C168" s="1" t="s">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A145" s="8"/>
+      <c r="B145" s="8"/>
+      <c r="C145" s="9"/>
+      <c r="G145" s="6"/>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A146" s="8"/>
+      <c r="B146" s="8"/>
+      <c r="C146" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G168" s="6"/>
-    </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A169" s="10"/>
-      <c r="B169" s="10"/>
-      <c r="C169" s="10"/>
-      <c r="D169" s="28" t="s">
+      <c r="G146" s="6"/>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A147" s="10"/>
+      <c r="B147" s="10"/>
+      <c r="C147" s="10"/>
+      <c r="D147" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E169" s="28"/>
-      <c r="F169" s="28"/>
-      <c r="G169" s="28"/>
-    </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A170" s="11"/>
-      <c r="B170" s="11"/>
-      <c r="C170" s="12" t="s">
+      <c r="E147" s="24"/>
+      <c r="F147" s="24"/>
+      <c r="G147" s="24"/>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A148" s="11"/>
+      <c r="B148" s="11"/>
+      <c r="C148" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D170" s="24"/>
-      <c r="E170" s="24"/>
-      <c r="F170" s="24"/>
-      <c r="G170" s="24"/>
-      <c r="H170" s="11"/>
-      <c r="I170" s="11"/>
-      <c r="J170" s="11"/>
-    </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A171" s="9"/>
-      <c r="B171" s="9"/>
-      <c r="C171" s="8" t="s">
+      <c r="D148" s="25"/>
+      <c r="E148" s="25"/>
+      <c r="F148" s="25"/>
+      <c r="G148" s="25"/>
+      <c r="H148" s="11"/>
+      <c r="I148" s="11"/>
+      <c r="J148" s="11"/>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A149" s="9"/>
+      <c r="B149" s="9"/>
+      <c r="C149" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D171" s="28"/>
-      <c r="E171" s="28"/>
-      <c r="F171" s="28"/>
-      <c r="G171" s="28"/>
-      <c r="H171" s="13"/>
-      <c r="I171" s="13"/>
-      <c r="J171" s="13"/>
-    </row>
-    <row r="172" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A172" s="2"/>
-      <c r="B172" s="2"/>
-      <c r="C172" s="2"/>
-      <c r="D172" s="2"/>
-      <c r="E172" s="2"/>
-      <c r="F172" s="2"/>
-    </row>
-    <row r="177" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C177" s="11" t="s">
+      <c r="D149" s="24"/>
+      <c r="E149" s="24"/>
+      <c r="F149" s="24"/>
+      <c r="G149" s="24"/>
+      <c r="H149" s="13"/>
+      <c r="I149" s="13"/>
+      <c r="J149" s="13"/>
+    </row>
+    <row r="150" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A150" s="2"/>
+      <c r="B150" s="2"/>
+      <c r="C150" s="2"/>
+      <c r="D150" s="2"/>
+      <c r="E150" s="2"/>
+      <c r="F150" s="2"/>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C155" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="178" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C178" s="1" t="s">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C156" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="179" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C179" s="1" t="s">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C157" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="180" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C180" s="1" t="s">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C158" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="181" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C181" s="1" t="s">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C159" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="182" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C182" s="1" t="s">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C160" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="184" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C184" s="1" t="s">
+    <row r="162" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C162" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="187" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C187" s="11"/>
+    <row r="165" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C165" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="D169:G169"/>
-    <mergeCell ref="D170:G170"/>
-    <mergeCell ref="D171:G171"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="D147:G147"/>
+    <mergeCell ref="D148:G148"/>
+    <mergeCell ref="D149:G149"/>
     <mergeCell ref="E7:H7"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="C8:C11"/>
@@ -4832,13 +4193,6 @@
     <mergeCell ref="F9:G9"/>
     <mergeCell ref="F10:F11"/>
     <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="D4:G4"/>
-    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="3.937007874015748E-2" right="3.937007874015748E-2" top="0.19685039370078741" bottom="3.937007874015748E-2" header="3.937007874015748E-2" footer="3.937007874015748E-2"/>

--- a/web/EXCEL_TEMPLATE/KHNV/KHNV_DK01A.xlsx
+++ b/web/EXCEL_TEMPLATE/KHNV/KHNV_DK01A.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24026"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\IMS_REPORTS\IMS_REPORTS\web\EXCEL_TEMPLATE\KHNV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\KHNV\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD3EEE3-09E2-4A4E-A772-CB5FE54ACB13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="936" yWindow="-120" windowWidth="20736" windowHeight="11280"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DK_01A" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">DK_01A!$A$1:$G$149</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">DK_01A!$A$1:$G$171</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">DK_01A!$8:$12</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="256">
   <si>
     <t>Biểu số 01a/NHCS-KH</t>
   </si>
@@ -210,9 +211,6 @@
     <t>XD00009</t>
   </si>
   <si>
-    <t>Cho vay để ký quỹ đối với người lao động đi làm việc tại Hàn Quốc</t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
@@ -627,14 +625,206 @@
     <t>XD00063</t>
   </si>
   <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>XD00064</t>
+  </si>
+  <si>
+    <t>THUYẾT MINH MỘT SỐ CHỈ TIÊU (Dự kiến năm kế hoạch)</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>XD00065</t>
+  </si>
+  <si>
+    <t>Số hộ dân cư trú trên địa bàn</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>XD00066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số hộ dân là hộ đồng bào dân tộc thiểu số </t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>XD00067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số hộ nghèo theo chuẩn hộ nghèo (giai đoạn 2021-2025) </t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>XD00068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số hộ nghèo đang còn dư nợ NHCSXH </t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>XD00069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số hộ nghèo đủ điều kiện vay vốn nhưng chưa được vay vốn NHCSXH </t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>XD00070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số hộ cận nghèo theo chuẩn hộ cận nghèo (giai đoạn 2021-2025) </t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>XD00071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số hộ cận nghèo đang còn dư nợ NHCSXH </t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>XD00072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số hộ cận nghèo đủ điều kiện vay vốn nhưng chưa được vay vốn NHCSXH </t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>XD00073</t>
+  </si>
+  <si>
+    <t>Số hộ mới thoát nghèo (giai đoạn 2019-2021)</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>XD00074</t>
+  </si>
+  <si>
+    <t>Số hộ gia đình sản xuất kinh doanh vùng khó khăn trên địa bàn</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>XD00075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số hộ gia đình SXKD đang còn dư nợ NHCSXH </t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>XD00076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số hộ gia đình SXKD đủ điều kiện vay vốn nhưng chưa được vay vốn NHCSXH </t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>XD00077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số thương nhân hoạt động thương mại tại vùng khó khăn </t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>XD00078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tổng số HSSV theo học các Trường ĐH, CĐ, THCN và dạy nghề </t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>XD00079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số HSSV đang còn dư nợ NHCSXH </t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>XD00080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số lao động có nhu cầu vay vốn giải quyết việc làm </t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>XD00081</t>
+  </si>
+  <si>
+    <t>Số lao động được vay vốn giải quyết việc làm trong năm</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>XD00082</t>
+  </si>
+  <si>
+    <t>Số lao động dự kiến được thu hút từ vay vốn giải quyết việc làm</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>XD00083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tổng số lao động có nhu cầu vay vốn đi lao động có thời hạn ở nước ngoài </t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>XD00084</t>
+  </si>
+  <si>
+    <t>Số công trình NS-VSMT NT dự kiến được xây dựng từ nguồn vốn vay NHCSXH</t>
+  </si>
+  <si>
     <t>THÔN: ... XÃ/PHƯỜNG/THỊ TRẤN: …</t>
+  </si>
+  <si>
+    <t>Trong đó: Cho vay để ký quỹ đối với người lao động đi làm việc tại Hàn Quốc</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="10" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -690,6 +880,13 @@
       <sz val="11"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="163"/>
     </font>
   </fonts>
   <fills count="3">
@@ -810,7 +1007,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -882,6 +1079,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -986,7 +1186,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1038,7 +1238,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1239,462 +1439,462 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J165"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J187"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="6.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="17" style="1" customWidth="1"/>
-    <col min="3" max="3" width="80.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="80.140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" style="2" customWidth="1"/>
-    <col min="8" max="257" width="9.109375" style="2"/>
-    <col min="258" max="258" width="6.44140625" style="2" customWidth="1"/>
-    <col min="259" max="259" width="80.109375" style="2" customWidth="1"/>
-    <col min="260" max="260" width="15.6640625" style="2" customWidth="1"/>
-    <col min="261" max="263" width="14.33203125" style="2" customWidth="1"/>
-    <col min="264" max="513" width="9.109375" style="2"/>
-    <col min="514" max="514" width="6.44140625" style="2" customWidth="1"/>
-    <col min="515" max="515" width="80.109375" style="2" customWidth="1"/>
-    <col min="516" max="516" width="15.6640625" style="2" customWidth="1"/>
-    <col min="517" max="519" width="14.33203125" style="2" customWidth="1"/>
-    <col min="520" max="769" width="9.109375" style="2"/>
-    <col min="770" max="770" width="6.44140625" style="2" customWidth="1"/>
-    <col min="771" max="771" width="80.109375" style="2" customWidth="1"/>
-    <col min="772" max="772" width="15.6640625" style="2" customWidth="1"/>
-    <col min="773" max="775" width="14.33203125" style="2" customWidth="1"/>
-    <col min="776" max="1025" width="9.109375" style="2"/>
-    <col min="1026" max="1026" width="6.44140625" style="2" customWidth="1"/>
-    <col min="1027" max="1027" width="80.109375" style="2" customWidth="1"/>
-    <col min="1028" max="1028" width="15.6640625" style="2" customWidth="1"/>
-    <col min="1029" max="1031" width="14.33203125" style="2" customWidth="1"/>
-    <col min="1032" max="1281" width="9.109375" style="2"/>
-    <col min="1282" max="1282" width="6.44140625" style="2" customWidth="1"/>
-    <col min="1283" max="1283" width="80.109375" style="2" customWidth="1"/>
-    <col min="1284" max="1284" width="15.6640625" style="2" customWidth="1"/>
-    <col min="1285" max="1287" width="14.33203125" style="2" customWidth="1"/>
-    <col min="1288" max="1537" width="9.109375" style="2"/>
-    <col min="1538" max="1538" width="6.44140625" style="2" customWidth="1"/>
-    <col min="1539" max="1539" width="80.109375" style="2" customWidth="1"/>
-    <col min="1540" max="1540" width="15.6640625" style="2" customWidth="1"/>
-    <col min="1541" max="1543" width="14.33203125" style="2" customWidth="1"/>
-    <col min="1544" max="1793" width="9.109375" style="2"/>
-    <col min="1794" max="1794" width="6.44140625" style="2" customWidth="1"/>
-    <col min="1795" max="1795" width="80.109375" style="2" customWidth="1"/>
-    <col min="1796" max="1796" width="15.6640625" style="2" customWidth="1"/>
-    <col min="1797" max="1799" width="14.33203125" style="2" customWidth="1"/>
-    <col min="1800" max="2049" width="9.109375" style="2"/>
-    <col min="2050" max="2050" width="6.44140625" style="2" customWidth="1"/>
-    <col min="2051" max="2051" width="80.109375" style="2" customWidth="1"/>
-    <col min="2052" max="2052" width="15.6640625" style="2" customWidth="1"/>
-    <col min="2053" max="2055" width="14.33203125" style="2" customWidth="1"/>
-    <col min="2056" max="2305" width="9.109375" style="2"/>
-    <col min="2306" max="2306" width="6.44140625" style="2" customWidth="1"/>
-    <col min="2307" max="2307" width="80.109375" style="2" customWidth="1"/>
-    <col min="2308" max="2308" width="15.6640625" style="2" customWidth="1"/>
-    <col min="2309" max="2311" width="14.33203125" style="2" customWidth="1"/>
-    <col min="2312" max="2561" width="9.109375" style="2"/>
-    <col min="2562" max="2562" width="6.44140625" style="2" customWidth="1"/>
-    <col min="2563" max="2563" width="80.109375" style="2" customWidth="1"/>
-    <col min="2564" max="2564" width="15.6640625" style="2" customWidth="1"/>
-    <col min="2565" max="2567" width="14.33203125" style="2" customWidth="1"/>
-    <col min="2568" max="2817" width="9.109375" style="2"/>
-    <col min="2818" max="2818" width="6.44140625" style="2" customWidth="1"/>
-    <col min="2819" max="2819" width="80.109375" style="2" customWidth="1"/>
-    <col min="2820" max="2820" width="15.6640625" style="2" customWidth="1"/>
-    <col min="2821" max="2823" width="14.33203125" style="2" customWidth="1"/>
-    <col min="2824" max="3073" width="9.109375" style="2"/>
-    <col min="3074" max="3074" width="6.44140625" style="2" customWidth="1"/>
-    <col min="3075" max="3075" width="80.109375" style="2" customWidth="1"/>
-    <col min="3076" max="3076" width="15.6640625" style="2" customWidth="1"/>
-    <col min="3077" max="3079" width="14.33203125" style="2" customWidth="1"/>
-    <col min="3080" max="3329" width="9.109375" style="2"/>
-    <col min="3330" max="3330" width="6.44140625" style="2" customWidth="1"/>
-    <col min="3331" max="3331" width="80.109375" style="2" customWidth="1"/>
-    <col min="3332" max="3332" width="15.6640625" style="2" customWidth="1"/>
-    <col min="3333" max="3335" width="14.33203125" style="2" customWidth="1"/>
-    <col min="3336" max="3585" width="9.109375" style="2"/>
-    <col min="3586" max="3586" width="6.44140625" style="2" customWidth="1"/>
-    <col min="3587" max="3587" width="80.109375" style="2" customWidth="1"/>
-    <col min="3588" max="3588" width="15.6640625" style="2" customWidth="1"/>
-    <col min="3589" max="3591" width="14.33203125" style="2" customWidth="1"/>
-    <col min="3592" max="3841" width="9.109375" style="2"/>
-    <col min="3842" max="3842" width="6.44140625" style="2" customWidth="1"/>
-    <col min="3843" max="3843" width="80.109375" style="2" customWidth="1"/>
-    <col min="3844" max="3844" width="15.6640625" style="2" customWidth="1"/>
-    <col min="3845" max="3847" width="14.33203125" style="2" customWidth="1"/>
-    <col min="3848" max="4097" width="9.109375" style="2"/>
-    <col min="4098" max="4098" width="6.44140625" style="2" customWidth="1"/>
-    <col min="4099" max="4099" width="80.109375" style="2" customWidth="1"/>
-    <col min="4100" max="4100" width="15.6640625" style="2" customWidth="1"/>
-    <col min="4101" max="4103" width="14.33203125" style="2" customWidth="1"/>
-    <col min="4104" max="4353" width="9.109375" style="2"/>
-    <col min="4354" max="4354" width="6.44140625" style="2" customWidth="1"/>
-    <col min="4355" max="4355" width="80.109375" style="2" customWidth="1"/>
-    <col min="4356" max="4356" width="15.6640625" style="2" customWidth="1"/>
-    <col min="4357" max="4359" width="14.33203125" style="2" customWidth="1"/>
-    <col min="4360" max="4609" width="9.109375" style="2"/>
-    <col min="4610" max="4610" width="6.44140625" style="2" customWidth="1"/>
-    <col min="4611" max="4611" width="80.109375" style="2" customWidth="1"/>
-    <col min="4612" max="4612" width="15.6640625" style="2" customWidth="1"/>
-    <col min="4613" max="4615" width="14.33203125" style="2" customWidth="1"/>
-    <col min="4616" max="4865" width="9.109375" style="2"/>
-    <col min="4866" max="4866" width="6.44140625" style="2" customWidth="1"/>
-    <col min="4867" max="4867" width="80.109375" style="2" customWidth="1"/>
-    <col min="4868" max="4868" width="15.6640625" style="2" customWidth="1"/>
-    <col min="4869" max="4871" width="14.33203125" style="2" customWidth="1"/>
-    <col min="4872" max="5121" width="9.109375" style="2"/>
-    <col min="5122" max="5122" width="6.44140625" style="2" customWidth="1"/>
-    <col min="5123" max="5123" width="80.109375" style="2" customWidth="1"/>
-    <col min="5124" max="5124" width="15.6640625" style="2" customWidth="1"/>
-    <col min="5125" max="5127" width="14.33203125" style="2" customWidth="1"/>
-    <col min="5128" max="5377" width="9.109375" style="2"/>
-    <col min="5378" max="5378" width="6.44140625" style="2" customWidth="1"/>
-    <col min="5379" max="5379" width="80.109375" style="2" customWidth="1"/>
-    <col min="5380" max="5380" width="15.6640625" style="2" customWidth="1"/>
-    <col min="5381" max="5383" width="14.33203125" style="2" customWidth="1"/>
-    <col min="5384" max="5633" width="9.109375" style="2"/>
-    <col min="5634" max="5634" width="6.44140625" style="2" customWidth="1"/>
-    <col min="5635" max="5635" width="80.109375" style="2" customWidth="1"/>
-    <col min="5636" max="5636" width="15.6640625" style="2" customWidth="1"/>
-    <col min="5637" max="5639" width="14.33203125" style="2" customWidth="1"/>
-    <col min="5640" max="5889" width="9.109375" style="2"/>
-    <col min="5890" max="5890" width="6.44140625" style="2" customWidth="1"/>
-    <col min="5891" max="5891" width="80.109375" style="2" customWidth="1"/>
-    <col min="5892" max="5892" width="15.6640625" style="2" customWidth="1"/>
-    <col min="5893" max="5895" width="14.33203125" style="2" customWidth="1"/>
-    <col min="5896" max="6145" width="9.109375" style="2"/>
-    <col min="6146" max="6146" width="6.44140625" style="2" customWidth="1"/>
-    <col min="6147" max="6147" width="80.109375" style="2" customWidth="1"/>
-    <col min="6148" max="6148" width="15.6640625" style="2" customWidth="1"/>
-    <col min="6149" max="6151" width="14.33203125" style="2" customWidth="1"/>
-    <col min="6152" max="6401" width="9.109375" style="2"/>
-    <col min="6402" max="6402" width="6.44140625" style="2" customWidth="1"/>
-    <col min="6403" max="6403" width="80.109375" style="2" customWidth="1"/>
-    <col min="6404" max="6404" width="15.6640625" style="2" customWidth="1"/>
-    <col min="6405" max="6407" width="14.33203125" style="2" customWidth="1"/>
-    <col min="6408" max="6657" width="9.109375" style="2"/>
-    <col min="6658" max="6658" width="6.44140625" style="2" customWidth="1"/>
-    <col min="6659" max="6659" width="80.109375" style="2" customWidth="1"/>
-    <col min="6660" max="6660" width="15.6640625" style="2" customWidth="1"/>
-    <col min="6661" max="6663" width="14.33203125" style="2" customWidth="1"/>
-    <col min="6664" max="6913" width="9.109375" style="2"/>
-    <col min="6914" max="6914" width="6.44140625" style="2" customWidth="1"/>
-    <col min="6915" max="6915" width="80.109375" style="2" customWidth="1"/>
-    <col min="6916" max="6916" width="15.6640625" style="2" customWidth="1"/>
-    <col min="6917" max="6919" width="14.33203125" style="2" customWidth="1"/>
-    <col min="6920" max="7169" width="9.109375" style="2"/>
-    <col min="7170" max="7170" width="6.44140625" style="2" customWidth="1"/>
-    <col min="7171" max="7171" width="80.109375" style="2" customWidth="1"/>
-    <col min="7172" max="7172" width="15.6640625" style="2" customWidth="1"/>
-    <col min="7173" max="7175" width="14.33203125" style="2" customWidth="1"/>
-    <col min="7176" max="7425" width="9.109375" style="2"/>
-    <col min="7426" max="7426" width="6.44140625" style="2" customWidth="1"/>
-    <col min="7427" max="7427" width="80.109375" style="2" customWidth="1"/>
-    <col min="7428" max="7428" width="15.6640625" style="2" customWidth="1"/>
-    <col min="7429" max="7431" width="14.33203125" style="2" customWidth="1"/>
-    <col min="7432" max="7681" width="9.109375" style="2"/>
-    <col min="7682" max="7682" width="6.44140625" style="2" customWidth="1"/>
-    <col min="7683" max="7683" width="80.109375" style="2" customWidth="1"/>
-    <col min="7684" max="7684" width="15.6640625" style="2" customWidth="1"/>
-    <col min="7685" max="7687" width="14.33203125" style="2" customWidth="1"/>
-    <col min="7688" max="7937" width="9.109375" style="2"/>
-    <col min="7938" max="7938" width="6.44140625" style="2" customWidth="1"/>
-    <col min="7939" max="7939" width="80.109375" style="2" customWidth="1"/>
-    <col min="7940" max="7940" width="15.6640625" style="2" customWidth="1"/>
-    <col min="7941" max="7943" width="14.33203125" style="2" customWidth="1"/>
-    <col min="7944" max="8193" width="9.109375" style="2"/>
-    <col min="8194" max="8194" width="6.44140625" style="2" customWidth="1"/>
-    <col min="8195" max="8195" width="80.109375" style="2" customWidth="1"/>
-    <col min="8196" max="8196" width="15.6640625" style="2" customWidth="1"/>
-    <col min="8197" max="8199" width="14.33203125" style="2" customWidth="1"/>
-    <col min="8200" max="8449" width="9.109375" style="2"/>
-    <col min="8450" max="8450" width="6.44140625" style="2" customWidth="1"/>
-    <col min="8451" max="8451" width="80.109375" style="2" customWidth="1"/>
-    <col min="8452" max="8452" width="15.6640625" style="2" customWidth="1"/>
-    <col min="8453" max="8455" width="14.33203125" style="2" customWidth="1"/>
-    <col min="8456" max="8705" width="9.109375" style="2"/>
-    <col min="8706" max="8706" width="6.44140625" style="2" customWidth="1"/>
-    <col min="8707" max="8707" width="80.109375" style="2" customWidth="1"/>
-    <col min="8708" max="8708" width="15.6640625" style="2" customWidth="1"/>
-    <col min="8709" max="8711" width="14.33203125" style="2" customWidth="1"/>
-    <col min="8712" max="8961" width="9.109375" style="2"/>
-    <col min="8962" max="8962" width="6.44140625" style="2" customWidth="1"/>
-    <col min="8963" max="8963" width="80.109375" style="2" customWidth="1"/>
-    <col min="8964" max="8964" width="15.6640625" style="2" customWidth="1"/>
-    <col min="8965" max="8967" width="14.33203125" style="2" customWidth="1"/>
-    <col min="8968" max="9217" width="9.109375" style="2"/>
-    <col min="9218" max="9218" width="6.44140625" style="2" customWidth="1"/>
-    <col min="9219" max="9219" width="80.109375" style="2" customWidth="1"/>
-    <col min="9220" max="9220" width="15.6640625" style="2" customWidth="1"/>
-    <col min="9221" max="9223" width="14.33203125" style="2" customWidth="1"/>
-    <col min="9224" max="9473" width="9.109375" style="2"/>
-    <col min="9474" max="9474" width="6.44140625" style="2" customWidth="1"/>
-    <col min="9475" max="9475" width="80.109375" style="2" customWidth="1"/>
-    <col min="9476" max="9476" width="15.6640625" style="2" customWidth="1"/>
-    <col min="9477" max="9479" width="14.33203125" style="2" customWidth="1"/>
-    <col min="9480" max="9729" width="9.109375" style="2"/>
-    <col min="9730" max="9730" width="6.44140625" style="2" customWidth="1"/>
-    <col min="9731" max="9731" width="80.109375" style="2" customWidth="1"/>
-    <col min="9732" max="9732" width="15.6640625" style="2" customWidth="1"/>
-    <col min="9733" max="9735" width="14.33203125" style="2" customWidth="1"/>
-    <col min="9736" max="9985" width="9.109375" style="2"/>
-    <col min="9986" max="9986" width="6.44140625" style="2" customWidth="1"/>
-    <col min="9987" max="9987" width="80.109375" style="2" customWidth="1"/>
-    <col min="9988" max="9988" width="15.6640625" style="2" customWidth="1"/>
-    <col min="9989" max="9991" width="14.33203125" style="2" customWidth="1"/>
-    <col min="9992" max="10241" width="9.109375" style="2"/>
-    <col min="10242" max="10242" width="6.44140625" style="2" customWidth="1"/>
-    <col min="10243" max="10243" width="80.109375" style="2" customWidth="1"/>
-    <col min="10244" max="10244" width="15.6640625" style="2" customWidth="1"/>
-    <col min="10245" max="10247" width="14.33203125" style="2" customWidth="1"/>
-    <col min="10248" max="10497" width="9.109375" style="2"/>
-    <col min="10498" max="10498" width="6.44140625" style="2" customWidth="1"/>
-    <col min="10499" max="10499" width="80.109375" style="2" customWidth="1"/>
-    <col min="10500" max="10500" width="15.6640625" style="2" customWidth="1"/>
-    <col min="10501" max="10503" width="14.33203125" style="2" customWidth="1"/>
-    <col min="10504" max="10753" width="9.109375" style="2"/>
-    <col min="10754" max="10754" width="6.44140625" style="2" customWidth="1"/>
-    <col min="10755" max="10755" width="80.109375" style="2" customWidth="1"/>
-    <col min="10756" max="10756" width="15.6640625" style="2" customWidth="1"/>
-    <col min="10757" max="10759" width="14.33203125" style="2" customWidth="1"/>
-    <col min="10760" max="11009" width="9.109375" style="2"/>
-    <col min="11010" max="11010" width="6.44140625" style="2" customWidth="1"/>
-    <col min="11011" max="11011" width="80.109375" style="2" customWidth="1"/>
-    <col min="11012" max="11012" width="15.6640625" style="2" customWidth="1"/>
-    <col min="11013" max="11015" width="14.33203125" style="2" customWidth="1"/>
-    <col min="11016" max="11265" width="9.109375" style="2"/>
-    <col min="11266" max="11266" width="6.44140625" style="2" customWidth="1"/>
-    <col min="11267" max="11267" width="80.109375" style="2" customWidth="1"/>
-    <col min="11268" max="11268" width="15.6640625" style="2" customWidth="1"/>
-    <col min="11269" max="11271" width="14.33203125" style="2" customWidth="1"/>
-    <col min="11272" max="11521" width="9.109375" style="2"/>
-    <col min="11522" max="11522" width="6.44140625" style="2" customWidth="1"/>
-    <col min="11523" max="11523" width="80.109375" style="2" customWidth="1"/>
-    <col min="11524" max="11524" width="15.6640625" style="2" customWidth="1"/>
-    <col min="11525" max="11527" width="14.33203125" style="2" customWidth="1"/>
-    <col min="11528" max="11777" width="9.109375" style="2"/>
-    <col min="11778" max="11778" width="6.44140625" style="2" customWidth="1"/>
-    <col min="11779" max="11779" width="80.109375" style="2" customWidth="1"/>
-    <col min="11780" max="11780" width="15.6640625" style="2" customWidth="1"/>
-    <col min="11781" max="11783" width="14.33203125" style="2" customWidth="1"/>
-    <col min="11784" max="12033" width="9.109375" style="2"/>
-    <col min="12034" max="12034" width="6.44140625" style="2" customWidth="1"/>
-    <col min="12035" max="12035" width="80.109375" style="2" customWidth="1"/>
-    <col min="12036" max="12036" width="15.6640625" style="2" customWidth="1"/>
-    <col min="12037" max="12039" width="14.33203125" style="2" customWidth="1"/>
-    <col min="12040" max="12289" width="9.109375" style="2"/>
-    <col min="12290" max="12290" width="6.44140625" style="2" customWidth="1"/>
-    <col min="12291" max="12291" width="80.109375" style="2" customWidth="1"/>
-    <col min="12292" max="12292" width="15.6640625" style="2" customWidth="1"/>
-    <col min="12293" max="12295" width="14.33203125" style="2" customWidth="1"/>
-    <col min="12296" max="12545" width="9.109375" style="2"/>
-    <col min="12546" max="12546" width="6.44140625" style="2" customWidth="1"/>
-    <col min="12547" max="12547" width="80.109375" style="2" customWidth="1"/>
-    <col min="12548" max="12548" width="15.6640625" style="2" customWidth="1"/>
-    <col min="12549" max="12551" width="14.33203125" style="2" customWidth="1"/>
-    <col min="12552" max="12801" width="9.109375" style="2"/>
-    <col min="12802" max="12802" width="6.44140625" style="2" customWidth="1"/>
-    <col min="12803" max="12803" width="80.109375" style="2" customWidth="1"/>
-    <col min="12804" max="12804" width="15.6640625" style="2" customWidth="1"/>
-    <col min="12805" max="12807" width="14.33203125" style="2" customWidth="1"/>
-    <col min="12808" max="13057" width="9.109375" style="2"/>
-    <col min="13058" max="13058" width="6.44140625" style="2" customWidth="1"/>
-    <col min="13059" max="13059" width="80.109375" style="2" customWidth="1"/>
-    <col min="13060" max="13060" width="15.6640625" style="2" customWidth="1"/>
-    <col min="13061" max="13063" width="14.33203125" style="2" customWidth="1"/>
-    <col min="13064" max="13313" width="9.109375" style="2"/>
-    <col min="13314" max="13314" width="6.44140625" style="2" customWidth="1"/>
-    <col min="13315" max="13315" width="80.109375" style="2" customWidth="1"/>
-    <col min="13316" max="13316" width="15.6640625" style="2" customWidth="1"/>
-    <col min="13317" max="13319" width="14.33203125" style="2" customWidth="1"/>
-    <col min="13320" max="13569" width="9.109375" style="2"/>
-    <col min="13570" max="13570" width="6.44140625" style="2" customWidth="1"/>
-    <col min="13571" max="13571" width="80.109375" style="2" customWidth="1"/>
-    <col min="13572" max="13572" width="15.6640625" style="2" customWidth="1"/>
-    <col min="13573" max="13575" width="14.33203125" style="2" customWidth="1"/>
-    <col min="13576" max="13825" width="9.109375" style="2"/>
-    <col min="13826" max="13826" width="6.44140625" style="2" customWidth="1"/>
-    <col min="13827" max="13827" width="80.109375" style="2" customWidth="1"/>
-    <col min="13828" max="13828" width="15.6640625" style="2" customWidth="1"/>
-    <col min="13829" max="13831" width="14.33203125" style="2" customWidth="1"/>
-    <col min="13832" max="14081" width="9.109375" style="2"/>
-    <col min="14082" max="14082" width="6.44140625" style="2" customWidth="1"/>
-    <col min="14083" max="14083" width="80.109375" style="2" customWidth="1"/>
-    <col min="14084" max="14084" width="15.6640625" style="2" customWidth="1"/>
-    <col min="14085" max="14087" width="14.33203125" style="2" customWidth="1"/>
-    <col min="14088" max="14337" width="9.109375" style="2"/>
-    <col min="14338" max="14338" width="6.44140625" style="2" customWidth="1"/>
-    <col min="14339" max="14339" width="80.109375" style="2" customWidth="1"/>
-    <col min="14340" max="14340" width="15.6640625" style="2" customWidth="1"/>
-    <col min="14341" max="14343" width="14.33203125" style="2" customWidth="1"/>
-    <col min="14344" max="14593" width="9.109375" style="2"/>
-    <col min="14594" max="14594" width="6.44140625" style="2" customWidth="1"/>
-    <col min="14595" max="14595" width="80.109375" style="2" customWidth="1"/>
-    <col min="14596" max="14596" width="15.6640625" style="2" customWidth="1"/>
-    <col min="14597" max="14599" width="14.33203125" style="2" customWidth="1"/>
-    <col min="14600" max="14849" width="9.109375" style="2"/>
-    <col min="14850" max="14850" width="6.44140625" style="2" customWidth="1"/>
-    <col min="14851" max="14851" width="80.109375" style="2" customWidth="1"/>
-    <col min="14852" max="14852" width="15.6640625" style="2" customWidth="1"/>
-    <col min="14853" max="14855" width="14.33203125" style="2" customWidth="1"/>
-    <col min="14856" max="15105" width="9.109375" style="2"/>
-    <col min="15106" max="15106" width="6.44140625" style="2" customWidth="1"/>
-    <col min="15107" max="15107" width="80.109375" style="2" customWidth="1"/>
-    <col min="15108" max="15108" width="15.6640625" style="2" customWidth="1"/>
-    <col min="15109" max="15111" width="14.33203125" style="2" customWidth="1"/>
-    <col min="15112" max="15361" width="9.109375" style="2"/>
-    <col min="15362" max="15362" width="6.44140625" style="2" customWidth="1"/>
-    <col min="15363" max="15363" width="80.109375" style="2" customWidth="1"/>
-    <col min="15364" max="15364" width="15.6640625" style="2" customWidth="1"/>
-    <col min="15365" max="15367" width="14.33203125" style="2" customWidth="1"/>
-    <col min="15368" max="15617" width="9.109375" style="2"/>
-    <col min="15618" max="15618" width="6.44140625" style="2" customWidth="1"/>
-    <col min="15619" max="15619" width="80.109375" style="2" customWidth="1"/>
-    <col min="15620" max="15620" width="15.6640625" style="2" customWidth="1"/>
-    <col min="15621" max="15623" width="14.33203125" style="2" customWidth="1"/>
-    <col min="15624" max="15873" width="9.109375" style="2"/>
-    <col min="15874" max="15874" width="6.44140625" style="2" customWidth="1"/>
-    <col min="15875" max="15875" width="80.109375" style="2" customWidth="1"/>
-    <col min="15876" max="15876" width="15.6640625" style="2" customWidth="1"/>
-    <col min="15877" max="15879" width="14.33203125" style="2" customWidth="1"/>
-    <col min="15880" max="16129" width="9.109375" style="2"/>
-    <col min="16130" max="16130" width="6.44140625" style="2" customWidth="1"/>
-    <col min="16131" max="16131" width="80.109375" style="2" customWidth="1"/>
-    <col min="16132" max="16132" width="15.6640625" style="2" customWidth="1"/>
-    <col min="16133" max="16135" width="14.33203125" style="2" customWidth="1"/>
-    <col min="16136" max="16384" width="9.109375" style="2"/>
+    <col min="5" max="5" width="17.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="2" customWidth="1"/>
+    <col min="8" max="257" width="9.140625" style="2"/>
+    <col min="258" max="258" width="6.42578125" style="2" customWidth="1"/>
+    <col min="259" max="259" width="80.140625" style="2" customWidth="1"/>
+    <col min="260" max="260" width="15.7109375" style="2" customWidth="1"/>
+    <col min="261" max="263" width="14.28515625" style="2" customWidth="1"/>
+    <col min="264" max="513" width="9.140625" style="2"/>
+    <col min="514" max="514" width="6.42578125" style="2" customWidth="1"/>
+    <col min="515" max="515" width="80.140625" style="2" customWidth="1"/>
+    <col min="516" max="516" width="15.7109375" style="2" customWidth="1"/>
+    <col min="517" max="519" width="14.28515625" style="2" customWidth="1"/>
+    <col min="520" max="769" width="9.140625" style="2"/>
+    <col min="770" max="770" width="6.42578125" style="2" customWidth="1"/>
+    <col min="771" max="771" width="80.140625" style="2" customWidth="1"/>
+    <col min="772" max="772" width="15.7109375" style="2" customWidth="1"/>
+    <col min="773" max="775" width="14.28515625" style="2" customWidth="1"/>
+    <col min="776" max="1025" width="9.140625" style="2"/>
+    <col min="1026" max="1026" width="6.42578125" style="2" customWidth="1"/>
+    <col min="1027" max="1027" width="80.140625" style="2" customWidth="1"/>
+    <col min="1028" max="1028" width="15.7109375" style="2" customWidth="1"/>
+    <col min="1029" max="1031" width="14.28515625" style="2" customWidth="1"/>
+    <col min="1032" max="1281" width="9.140625" style="2"/>
+    <col min="1282" max="1282" width="6.42578125" style="2" customWidth="1"/>
+    <col min="1283" max="1283" width="80.140625" style="2" customWidth="1"/>
+    <col min="1284" max="1284" width="15.7109375" style="2" customWidth="1"/>
+    <col min="1285" max="1287" width="14.28515625" style="2" customWidth="1"/>
+    <col min="1288" max="1537" width="9.140625" style="2"/>
+    <col min="1538" max="1538" width="6.42578125" style="2" customWidth="1"/>
+    <col min="1539" max="1539" width="80.140625" style="2" customWidth="1"/>
+    <col min="1540" max="1540" width="15.7109375" style="2" customWidth="1"/>
+    <col min="1541" max="1543" width="14.28515625" style="2" customWidth="1"/>
+    <col min="1544" max="1793" width="9.140625" style="2"/>
+    <col min="1794" max="1794" width="6.42578125" style="2" customWidth="1"/>
+    <col min="1795" max="1795" width="80.140625" style="2" customWidth="1"/>
+    <col min="1796" max="1796" width="15.7109375" style="2" customWidth="1"/>
+    <col min="1797" max="1799" width="14.28515625" style="2" customWidth="1"/>
+    <col min="1800" max="2049" width="9.140625" style="2"/>
+    <col min="2050" max="2050" width="6.42578125" style="2" customWidth="1"/>
+    <col min="2051" max="2051" width="80.140625" style="2" customWidth="1"/>
+    <col min="2052" max="2052" width="15.7109375" style="2" customWidth="1"/>
+    <col min="2053" max="2055" width="14.28515625" style="2" customWidth="1"/>
+    <col min="2056" max="2305" width="9.140625" style="2"/>
+    <col min="2306" max="2306" width="6.42578125" style="2" customWidth="1"/>
+    <col min="2307" max="2307" width="80.140625" style="2" customWidth="1"/>
+    <col min="2308" max="2308" width="15.7109375" style="2" customWidth="1"/>
+    <col min="2309" max="2311" width="14.28515625" style="2" customWidth="1"/>
+    <col min="2312" max="2561" width="9.140625" style="2"/>
+    <col min="2562" max="2562" width="6.42578125" style="2" customWidth="1"/>
+    <col min="2563" max="2563" width="80.140625" style="2" customWidth="1"/>
+    <col min="2564" max="2564" width="15.7109375" style="2" customWidth="1"/>
+    <col min="2565" max="2567" width="14.28515625" style="2" customWidth="1"/>
+    <col min="2568" max="2817" width="9.140625" style="2"/>
+    <col min="2818" max="2818" width="6.42578125" style="2" customWidth="1"/>
+    <col min="2819" max="2819" width="80.140625" style="2" customWidth="1"/>
+    <col min="2820" max="2820" width="15.7109375" style="2" customWidth="1"/>
+    <col min="2821" max="2823" width="14.28515625" style="2" customWidth="1"/>
+    <col min="2824" max="3073" width="9.140625" style="2"/>
+    <col min="3074" max="3074" width="6.42578125" style="2" customWidth="1"/>
+    <col min="3075" max="3075" width="80.140625" style="2" customWidth="1"/>
+    <col min="3076" max="3076" width="15.7109375" style="2" customWidth="1"/>
+    <col min="3077" max="3079" width="14.28515625" style="2" customWidth="1"/>
+    <col min="3080" max="3329" width="9.140625" style="2"/>
+    <col min="3330" max="3330" width="6.42578125" style="2" customWidth="1"/>
+    <col min="3331" max="3331" width="80.140625" style="2" customWidth="1"/>
+    <col min="3332" max="3332" width="15.7109375" style="2" customWidth="1"/>
+    <col min="3333" max="3335" width="14.28515625" style="2" customWidth="1"/>
+    <col min="3336" max="3585" width="9.140625" style="2"/>
+    <col min="3586" max="3586" width="6.42578125" style="2" customWidth="1"/>
+    <col min="3587" max="3587" width="80.140625" style="2" customWidth="1"/>
+    <col min="3588" max="3588" width="15.7109375" style="2" customWidth="1"/>
+    <col min="3589" max="3591" width="14.28515625" style="2" customWidth="1"/>
+    <col min="3592" max="3841" width="9.140625" style="2"/>
+    <col min="3842" max="3842" width="6.42578125" style="2" customWidth="1"/>
+    <col min="3843" max="3843" width="80.140625" style="2" customWidth="1"/>
+    <col min="3844" max="3844" width="15.7109375" style="2" customWidth="1"/>
+    <col min="3845" max="3847" width="14.28515625" style="2" customWidth="1"/>
+    <col min="3848" max="4097" width="9.140625" style="2"/>
+    <col min="4098" max="4098" width="6.42578125" style="2" customWidth="1"/>
+    <col min="4099" max="4099" width="80.140625" style="2" customWidth="1"/>
+    <col min="4100" max="4100" width="15.7109375" style="2" customWidth="1"/>
+    <col min="4101" max="4103" width="14.28515625" style="2" customWidth="1"/>
+    <col min="4104" max="4353" width="9.140625" style="2"/>
+    <col min="4354" max="4354" width="6.42578125" style="2" customWidth="1"/>
+    <col min="4355" max="4355" width="80.140625" style="2" customWidth="1"/>
+    <col min="4356" max="4356" width="15.7109375" style="2" customWidth="1"/>
+    <col min="4357" max="4359" width="14.28515625" style="2" customWidth="1"/>
+    <col min="4360" max="4609" width="9.140625" style="2"/>
+    <col min="4610" max="4610" width="6.42578125" style="2" customWidth="1"/>
+    <col min="4611" max="4611" width="80.140625" style="2" customWidth="1"/>
+    <col min="4612" max="4612" width="15.7109375" style="2" customWidth="1"/>
+    <col min="4613" max="4615" width="14.28515625" style="2" customWidth="1"/>
+    <col min="4616" max="4865" width="9.140625" style="2"/>
+    <col min="4866" max="4866" width="6.42578125" style="2" customWidth="1"/>
+    <col min="4867" max="4867" width="80.140625" style="2" customWidth="1"/>
+    <col min="4868" max="4868" width="15.7109375" style="2" customWidth="1"/>
+    <col min="4869" max="4871" width="14.28515625" style="2" customWidth="1"/>
+    <col min="4872" max="5121" width="9.140625" style="2"/>
+    <col min="5122" max="5122" width="6.42578125" style="2" customWidth="1"/>
+    <col min="5123" max="5123" width="80.140625" style="2" customWidth="1"/>
+    <col min="5124" max="5124" width="15.7109375" style="2" customWidth="1"/>
+    <col min="5125" max="5127" width="14.28515625" style="2" customWidth="1"/>
+    <col min="5128" max="5377" width="9.140625" style="2"/>
+    <col min="5378" max="5378" width="6.42578125" style="2" customWidth="1"/>
+    <col min="5379" max="5379" width="80.140625" style="2" customWidth="1"/>
+    <col min="5380" max="5380" width="15.7109375" style="2" customWidth="1"/>
+    <col min="5381" max="5383" width="14.28515625" style="2" customWidth="1"/>
+    <col min="5384" max="5633" width="9.140625" style="2"/>
+    <col min="5634" max="5634" width="6.42578125" style="2" customWidth="1"/>
+    <col min="5635" max="5635" width="80.140625" style="2" customWidth="1"/>
+    <col min="5636" max="5636" width="15.7109375" style="2" customWidth="1"/>
+    <col min="5637" max="5639" width="14.28515625" style="2" customWidth="1"/>
+    <col min="5640" max="5889" width="9.140625" style="2"/>
+    <col min="5890" max="5890" width="6.42578125" style="2" customWidth="1"/>
+    <col min="5891" max="5891" width="80.140625" style="2" customWidth="1"/>
+    <col min="5892" max="5892" width="15.7109375" style="2" customWidth="1"/>
+    <col min="5893" max="5895" width="14.28515625" style="2" customWidth="1"/>
+    <col min="5896" max="6145" width="9.140625" style="2"/>
+    <col min="6146" max="6146" width="6.42578125" style="2" customWidth="1"/>
+    <col min="6147" max="6147" width="80.140625" style="2" customWidth="1"/>
+    <col min="6148" max="6148" width="15.7109375" style="2" customWidth="1"/>
+    <col min="6149" max="6151" width="14.28515625" style="2" customWidth="1"/>
+    <col min="6152" max="6401" width="9.140625" style="2"/>
+    <col min="6402" max="6402" width="6.42578125" style="2" customWidth="1"/>
+    <col min="6403" max="6403" width="80.140625" style="2" customWidth="1"/>
+    <col min="6404" max="6404" width="15.7109375" style="2" customWidth="1"/>
+    <col min="6405" max="6407" width="14.28515625" style="2" customWidth="1"/>
+    <col min="6408" max="6657" width="9.140625" style="2"/>
+    <col min="6658" max="6658" width="6.42578125" style="2" customWidth="1"/>
+    <col min="6659" max="6659" width="80.140625" style="2" customWidth="1"/>
+    <col min="6660" max="6660" width="15.7109375" style="2" customWidth="1"/>
+    <col min="6661" max="6663" width="14.28515625" style="2" customWidth="1"/>
+    <col min="6664" max="6913" width="9.140625" style="2"/>
+    <col min="6914" max="6914" width="6.42578125" style="2" customWidth="1"/>
+    <col min="6915" max="6915" width="80.140625" style="2" customWidth="1"/>
+    <col min="6916" max="6916" width="15.7109375" style="2" customWidth="1"/>
+    <col min="6917" max="6919" width="14.28515625" style="2" customWidth="1"/>
+    <col min="6920" max="7169" width="9.140625" style="2"/>
+    <col min="7170" max="7170" width="6.42578125" style="2" customWidth="1"/>
+    <col min="7171" max="7171" width="80.140625" style="2" customWidth="1"/>
+    <col min="7172" max="7172" width="15.7109375" style="2" customWidth="1"/>
+    <col min="7173" max="7175" width="14.28515625" style="2" customWidth="1"/>
+    <col min="7176" max="7425" width="9.140625" style="2"/>
+    <col min="7426" max="7426" width="6.42578125" style="2" customWidth="1"/>
+    <col min="7427" max="7427" width="80.140625" style="2" customWidth="1"/>
+    <col min="7428" max="7428" width="15.7109375" style="2" customWidth="1"/>
+    <col min="7429" max="7431" width="14.28515625" style="2" customWidth="1"/>
+    <col min="7432" max="7681" width="9.140625" style="2"/>
+    <col min="7682" max="7682" width="6.42578125" style="2" customWidth="1"/>
+    <col min="7683" max="7683" width="80.140625" style="2" customWidth="1"/>
+    <col min="7684" max="7684" width="15.7109375" style="2" customWidth="1"/>
+    <col min="7685" max="7687" width="14.28515625" style="2" customWidth="1"/>
+    <col min="7688" max="7937" width="9.140625" style="2"/>
+    <col min="7938" max="7938" width="6.42578125" style="2" customWidth="1"/>
+    <col min="7939" max="7939" width="80.140625" style="2" customWidth="1"/>
+    <col min="7940" max="7940" width="15.7109375" style="2" customWidth="1"/>
+    <col min="7941" max="7943" width="14.28515625" style="2" customWidth="1"/>
+    <col min="7944" max="8193" width="9.140625" style="2"/>
+    <col min="8194" max="8194" width="6.42578125" style="2" customWidth="1"/>
+    <col min="8195" max="8195" width="80.140625" style="2" customWidth="1"/>
+    <col min="8196" max="8196" width="15.7109375" style="2" customWidth="1"/>
+    <col min="8197" max="8199" width="14.28515625" style="2" customWidth="1"/>
+    <col min="8200" max="8449" width="9.140625" style="2"/>
+    <col min="8450" max="8450" width="6.42578125" style="2" customWidth="1"/>
+    <col min="8451" max="8451" width="80.140625" style="2" customWidth="1"/>
+    <col min="8452" max="8452" width="15.7109375" style="2" customWidth="1"/>
+    <col min="8453" max="8455" width="14.28515625" style="2" customWidth="1"/>
+    <col min="8456" max="8705" width="9.140625" style="2"/>
+    <col min="8706" max="8706" width="6.42578125" style="2" customWidth="1"/>
+    <col min="8707" max="8707" width="80.140625" style="2" customWidth="1"/>
+    <col min="8708" max="8708" width="15.7109375" style="2" customWidth="1"/>
+    <col min="8709" max="8711" width="14.28515625" style="2" customWidth="1"/>
+    <col min="8712" max="8961" width="9.140625" style="2"/>
+    <col min="8962" max="8962" width="6.42578125" style="2" customWidth="1"/>
+    <col min="8963" max="8963" width="80.140625" style="2" customWidth="1"/>
+    <col min="8964" max="8964" width="15.7109375" style="2" customWidth="1"/>
+    <col min="8965" max="8967" width="14.28515625" style="2" customWidth="1"/>
+    <col min="8968" max="9217" width="9.140625" style="2"/>
+    <col min="9218" max="9218" width="6.42578125" style="2" customWidth="1"/>
+    <col min="9219" max="9219" width="80.140625" style="2" customWidth="1"/>
+    <col min="9220" max="9220" width="15.7109375" style="2" customWidth="1"/>
+    <col min="9221" max="9223" width="14.28515625" style="2" customWidth="1"/>
+    <col min="9224" max="9473" width="9.140625" style="2"/>
+    <col min="9474" max="9474" width="6.42578125" style="2" customWidth="1"/>
+    <col min="9475" max="9475" width="80.140625" style="2" customWidth="1"/>
+    <col min="9476" max="9476" width="15.7109375" style="2" customWidth="1"/>
+    <col min="9477" max="9479" width="14.28515625" style="2" customWidth="1"/>
+    <col min="9480" max="9729" width="9.140625" style="2"/>
+    <col min="9730" max="9730" width="6.42578125" style="2" customWidth="1"/>
+    <col min="9731" max="9731" width="80.140625" style="2" customWidth="1"/>
+    <col min="9732" max="9732" width="15.7109375" style="2" customWidth="1"/>
+    <col min="9733" max="9735" width="14.28515625" style="2" customWidth="1"/>
+    <col min="9736" max="9985" width="9.140625" style="2"/>
+    <col min="9986" max="9986" width="6.42578125" style="2" customWidth="1"/>
+    <col min="9987" max="9987" width="80.140625" style="2" customWidth="1"/>
+    <col min="9988" max="9988" width="15.7109375" style="2" customWidth="1"/>
+    <col min="9989" max="9991" width="14.28515625" style="2" customWidth="1"/>
+    <col min="9992" max="10241" width="9.140625" style="2"/>
+    <col min="10242" max="10242" width="6.42578125" style="2" customWidth="1"/>
+    <col min="10243" max="10243" width="80.140625" style="2" customWidth="1"/>
+    <col min="10244" max="10244" width="15.7109375" style="2" customWidth="1"/>
+    <col min="10245" max="10247" width="14.28515625" style="2" customWidth="1"/>
+    <col min="10248" max="10497" width="9.140625" style="2"/>
+    <col min="10498" max="10498" width="6.42578125" style="2" customWidth="1"/>
+    <col min="10499" max="10499" width="80.140625" style="2" customWidth="1"/>
+    <col min="10500" max="10500" width="15.7109375" style="2" customWidth="1"/>
+    <col min="10501" max="10503" width="14.28515625" style="2" customWidth="1"/>
+    <col min="10504" max="10753" width="9.140625" style="2"/>
+    <col min="10754" max="10754" width="6.42578125" style="2" customWidth="1"/>
+    <col min="10755" max="10755" width="80.140625" style="2" customWidth="1"/>
+    <col min="10756" max="10756" width="15.7109375" style="2" customWidth="1"/>
+    <col min="10757" max="10759" width="14.28515625" style="2" customWidth="1"/>
+    <col min="10760" max="11009" width="9.140625" style="2"/>
+    <col min="11010" max="11010" width="6.42578125" style="2" customWidth="1"/>
+    <col min="11011" max="11011" width="80.140625" style="2" customWidth="1"/>
+    <col min="11012" max="11012" width="15.7109375" style="2" customWidth="1"/>
+    <col min="11013" max="11015" width="14.28515625" style="2" customWidth="1"/>
+    <col min="11016" max="11265" width="9.140625" style="2"/>
+    <col min="11266" max="11266" width="6.42578125" style="2" customWidth="1"/>
+    <col min="11267" max="11267" width="80.140625" style="2" customWidth="1"/>
+    <col min="11268" max="11268" width="15.7109375" style="2" customWidth="1"/>
+    <col min="11269" max="11271" width="14.28515625" style="2" customWidth="1"/>
+    <col min="11272" max="11521" width="9.140625" style="2"/>
+    <col min="11522" max="11522" width="6.42578125" style="2" customWidth="1"/>
+    <col min="11523" max="11523" width="80.140625" style="2" customWidth="1"/>
+    <col min="11524" max="11524" width="15.7109375" style="2" customWidth="1"/>
+    <col min="11525" max="11527" width="14.28515625" style="2" customWidth="1"/>
+    <col min="11528" max="11777" width="9.140625" style="2"/>
+    <col min="11778" max="11778" width="6.42578125" style="2" customWidth="1"/>
+    <col min="11779" max="11779" width="80.140625" style="2" customWidth="1"/>
+    <col min="11780" max="11780" width="15.7109375" style="2" customWidth="1"/>
+    <col min="11781" max="11783" width="14.28515625" style="2" customWidth="1"/>
+    <col min="11784" max="12033" width="9.140625" style="2"/>
+    <col min="12034" max="12034" width="6.42578125" style="2" customWidth="1"/>
+    <col min="12035" max="12035" width="80.140625" style="2" customWidth="1"/>
+    <col min="12036" max="12036" width="15.7109375" style="2" customWidth="1"/>
+    <col min="12037" max="12039" width="14.28515625" style="2" customWidth="1"/>
+    <col min="12040" max="12289" width="9.140625" style="2"/>
+    <col min="12290" max="12290" width="6.42578125" style="2" customWidth="1"/>
+    <col min="12291" max="12291" width="80.140625" style="2" customWidth="1"/>
+    <col min="12292" max="12292" width="15.7109375" style="2" customWidth="1"/>
+    <col min="12293" max="12295" width="14.28515625" style="2" customWidth="1"/>
+    <col min="12296" max="12545" width="9.140625" style="2"/>
+    <col min="12546" max="12546" width="6.42578125" style="2" customWidth="1"/>
+    <col min="12547" max="12547" width="80.140625" style="2" customWidth="1"/>
+    <col min="12548" max="12548" width="15.7109375" style="2" customWidth="1"/>
+    <col min="12549" max="12551" width="14.28515625" style="2" customWidth="1"/>
+    <col min="12552" max="12801" width="9.140625" style="2"/>
+    <col min="12802" max="12802" width="6.42578125" style="2" customWidth="1"/>
+    <col min="12803" max="12803" width="80.140625" style="2" customWidth="1"/>
+    <col min="12804" max="12804" width="15.7109375" style="2" customWidth="1"/>
+    <col min="12805" max="12807" width="14.28515625" style="2" customWidth="1"/>
+    <col min="12808" max="13057" width="9.140625" style="2"/>
+    <col min="13058" max="13058" width="6.42578125" style="2" customWidth="1"/>
+    <col min="13059" max="13059" width="80.140625" style="2" customWidth="1"/>
+    <col min="13060" max="13060" width="15.7109375" style="2" customWidth="1"/>
+    <col min="13061" max="13063" width="14.28515625" style="2" customWidth="1"/>
+    <col min="13064" max="13313" width="9.140625" style="2"/>
+    <col min="13314" max="13314" width="6.42578125" style="2" customWidth="1"/>
+    <col min="13315" max="13315" width="80.140625" style="2" customWidth="1"/>
+    <col min="13316" max="13316" width="15.7109375" style="2" customWidth="1"/>
+    <col min="13317" max="13319" width="14.28515625" style="2" customWidth="1"/>
+    <col min="13320" max="13569" width="9.140625" style="2"/>
+    <col min="13570" max="13570" width="6.42578125" style="2" customWidth="1"/>
+    <col min="13571" max="13571" width="80.140625" style="2" customWidth="1"/>
+    <col min="13572" max="13572" width="15.7109375" style="2" customWidth="1"/>
+    <col min="13573" max="13575" width="14.28515625" style="2" customWidth="1"/>
+    <col min="13576" max="13825" width="9.140625" style="2"/>
+    <col min="13826" max="13826" width="6.42578125" style="2" customWidth="1"/>
+    <col min="13827" max="13827" width="80.140625" style="2" customWidth="1"/>
+    <col min="13828" max="13828" width="15.7109375" style="2" customWidth="1"/>
+    <col min="13829" max="13831" width="14.28515625" style="2" customWidth="1"/>
+    <col min="13832" max="14081" width="9.140625" style="2"/>
+    <col min="14082" max="14082" width="6.42578125" style="2" customWidth="1"/>
+    <col min="14083" max="14083" width="80.140625" style="2" customWidth="1"/>
+    <col min="14084" max="14084" width="15.7109375" style="2" customWidth="1"/>
+    <col min="14085" max="14087" width="14.28515625" style="2" customWidth="1"/>
+    <col min="14088" max="14337" width="9.140625" style="2"/>
+    <col min="14338" max="14338" width="6.42578125" style="2" customWidth="1"/>
+    <col min="14339" max="14339" width="80.140625" style="2" customWidth="1"/>
+    <col min="14340" max="14340" width="15.7109375" style="2" customWidth="1"/>
+    <col min="14341" max="14343" width="14.28515625" style="2" customWidth="1"/>
+    <col min="14344" max="14593" width="9.140625" style="2"/>
+    <col min="14594" max="14594" width="6.42578125" style="2" customWidth="1"/>
+    <col min="14595" max="14595" width="80.140625" style="2" customWidth="1"/>
+    <col min="14596" max="14596" width="15.7109375" style="2" customWidth="1"/>
+    <col min="14597" max="14599" width="14.28515625" style="2" customWidth="1"/>
+    <col min="14600" max="14849" width="9.140625" style="2"/>
+    <col min="14850" max="14850" width="6.42578125" style="2" customWidth="1"/>
+    <col min="14851" max="14851" width="80.140625" style="2" customWidth="1"/>
+    <col min="14852" max="14852" width="15.7109375" style="2" customWidth="1"/>
+    <col min="14853" max="14855" width="14.28515625" style="2" customWidth="1"/>
+    <col min="14856" max="15105" width="9.140625" style="2"/>
+    <col min="15106" max="15106" width="6.42578125" style="2" customWidth="1"/>
+    <col min="15107" max="15107" width="80.140625" style="2" customWidth="1"/>
+    <col min="15108" max="15108" width="15.7109375" style="2" customWidth="1"/>
+    <col min="15109" max="15111" width="14.28515625" style="2" customWidth="1"/>
+    <col min="15112" max="15361" width="9.140625" style="2"/>
+    <col min="15362" max="15362" width="6.42578125" style="2" customWidth="1"/>
+    <col min="15363" max="15363" width="80.140625" style="2" customWidth="1"/>
+    <col min="15364" max="15364" width="15.7109375" style="2" customWidth="1"/>
+    <col min="15365" max="15367" width="14.28515625" style="2" customWidth="1"/>
+    <col min="15368" max="15617" width="9.140625" style="2"/>
+    <col min="15618" max="15618" width="6.42578125" style="2" customWidth="1"/>
+    <col min="15619" max="15619" width="80.140625" style="2" customWidth="1"/>
+    <col min="15620" max="15620" width="15.7109375" style="2" customWidth="1"/>
+    <col min="15621" max="15623" width="14.28515625" style="2" customWidth="1"/>
+    <col min="15624" max="15873" width="9.140625" style="2"/>
+    <col min="15874" max="15874" width="6.42578125" style="2" customWidth="1"/>
+    <col min="15875" max="15875" width="80.140625" style="2" customWidth="1"/>
+    <col min="15876" max="15876" width="15.7109375" style="2" customWidth="1"/>
+    <col min="15877" max="15879" width="14.28515625" style="2" customWidth="1"/>
+    <col min="15880" max="16129" width="9.140625" style="2"/>
+    <col min="16130" max="16130" width="6.42578125" style="2" customWidth="1"/>
+    <col min="16131" max="16131" width="80.140625" style="2" customWidth="1"/>
+    <col min="16132" max="16132" width="15.7109375" style="2" customWidth="1"/>
+    <col min="16133" max="16135" width="14.28515625" style="2" customWidth="1"/>
+    <col min="16136" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="25"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="F1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="26"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
-      <c r="F2" s="35" t="s">
+      <c r="F2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="35"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G2" s="36"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="36" t="s">
+      <c r="D3" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="36" t="s">
+      <c r="D4" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-    </row>
-    <row r="5" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A5" s="37" t="s">
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+    </row>
+    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-    </row>
-    <row r="6" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A6" s="34" t="s">
-        <v>192</v>
-      </c>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+    </row>
+    <row r="6" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A6" s="35" t="s">
+        <v>254</v>
+      </c>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E7" s="24" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E7" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="26" t="s">
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="26"/>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="28" t="s">
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="31" t="s">
+      <c r="F9" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="32"/>
-    </row>
-    <row r="10" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A10" s="26"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="33" t="s">
+      <c r="G9" s="33"/>
+    </row>
+    <row r="10" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="27"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="G10" s="33" t="s">
+      <c r="G10" s="34" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A11" s="26"/>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-    </row>
-    <row r="12" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+    </row>
+    <row r="12" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>1</v>
       </c>
@@ -1715,7 +1915,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="19" t="s">
         <v>27</v>
       </c>
@@ -1725,18 +1925,24 @@
       <c r="C13" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="20"/>
+      <c r="D13" s="20">
+        <f>D14+D49</f>
+        <v>0</v>
+      </c>
       <c r="E13" s="21">
         <f>D13+F13</f>
         <v>0</v>
       </c>
-      <c r="F13" s="20"/>
+      <c r="F13" s="20">
+        <f>F14+F49</f>
+        <v>0</v>
+      </c>
       <c r="G13" s="21">
         <f>IFERROR(F13/D13*100,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A14" s="19" t="s">
         <v>30</v>
       </c>
@@ -1746,18 +1952,24 @@
       <c r="C14" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="20"/>
+      <c r="D14" s="20">
+        <f>SUM(D15:D40)-D21-D36+D48</f>
+        <v>0</v>
+      </c>
       <c r="E14" s="21">
-        <f t="shared" ref="E14:E112" si="0">D14+F14</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="20"/>
+        <f t="shared" ref="E14:E134" si="0">D14+F14</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="20">
+        <f>SUM(F15:F40)-F21-F36+F48</f>
+        <v>0</v>
+      </c>
       <c r="G14" s="21">
-        <f t="shared" ref="G14:G112" si="1">IFERROR(F14/D14*100,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
+        <f t="shared" ref="G14:G134" si="1">IFERROR(F14/D14*100,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="15" t="s">
         <v>33</v>
       </c>
@@ -1778,7 +1990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="15" t="s">
         <v>36</v>
       </c>
@@ -1799,7 +2011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="15" t="s">
         <v>39</v>
       </c>
@@ -1820,7 +2032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="15" t="s">
         <v>42</v>
       </c>
@@ -1841,7 +2053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="15" t="s">
         <v>45</v>
       </c>
@@ -1862,7 +2074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="45" x14ac:dyDescent="0.2">
       <c r="A20" s="15" t="s">
         <v>48</v>
       </c>
@@ -1883,15 +2095,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="15" t="s">
         <v>51</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="23" t="s">
-        <v>53</v>
+      <c r="C21" s="24" t="s">
+        <v>255</v>
       </c>
       <c r="D21" s="16"/>
       <c r="E21" s="17">
@@ -1904,15 +2116,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="C22" s="23" t="s">
         <v>55</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>56</v>
       </c>
       <c r="D22" s="16"/>
       <c r="E22" s="17">
@@ -1925,15 +2137,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="C23" s="23" t="s">
         <v>58</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>59</v>
       </c>
       <c r="D23" s="16"/>
       <c r="E23" s="17">
@@ -1946,15 +2158,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="C24" s="23" t="s">
         <v>61</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>62</v>
       </c>
       <c r="D24" s="16"/>
       <c r="E24" s="17">
@@ -1967,15 +2179,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="C25" s="23" t="s">
         <v>64</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>65</v>
       </c>
       <c r="D25" s="16"/>
       <c r="E25" s="17">
@@ -1988,15 +2200,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.2">
       <c r="A26" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B26" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="C26" s="23" t="s">
         <v>67</v>
-      </c>
-      <c r="C26" s="23" t="s">
-        <v>68</v>
       </c>
       <c r="D26" s="16"/>
       <c r="E26" s="17">
@@ -2009,15 +2221,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A27" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="C27" s="23" t="s">
         <v>70</v>
-      </c>
-      <c r="C27" s="23" t="s">
-        <v>71</v>
       </c>
       <c r="D27" s="16"/>
       <c r="E27" s="17">
@@ -2030,15 +2242,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.2">
       <c r="A28" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B28" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="C28" s="23" t="s">
         <v>73</v>
-      </c>
-      <c r="C28" s="23" t="s">
-        <v>74</v>
       </c>
       <c r="D28" s="16"/>
       <c r="E28" s="17">
@@ -2051,15 +2263,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A29" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="B29" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="C29" s="23" t="s">
         <v>76</v>
-      </c>
-      <c r="C29" s="23" t="s">
-        <v>77</v>
       </c>
       <c r="D29" s="16"/>
       <c r="E29" s="17">
@@ -2072,15 +2284,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A30" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="B30" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="C30" s="23" t="s">
         <v>79</v>
-      </c>
-      <c r="C30" s="23" t="s">
-        <v>80</v>
       </c>
       <c r="D30" s="16"/>
       <c r="E30" s="17">
@@ -2093,15 +2305,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A31" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="B31" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="C31" s="23" t="s">
         <v>82</v>
-      </c>
-      <c r="C31" s="23" t="s">
-        <v>83</v>
       </c>
       <c r="D31" s="16"/>
       <c r="E31" s="17">
@@ -2114,15 +2326,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A32" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B32" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="C32" s="23" t="s">
         <v>85</v>
-      </c>
-      <c r="C32" s="23" t="s">
-        <v>86</v>
       </c>
       <c r="D32" s="16"/>
       <c r="E32" s="17">
@@ -2135,15 +2347,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="30" x14ac:dyDescent="0.2">
       <c r="A33" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="C33" s="23" t="s">
         <v>88</v>
-      </c>
-      <c r="C33" s="23" t="s">
-        <v>89</v>
       </c>
       <c r="D33" s="16"/>
       <c r="E33" s="17">
@@ -2156,15 +2368,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="45" x14ac:dyDescent="0.2">
       <c r="A34" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B34" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="C34" s="23" t="s">
         <v>91</v>
-      </c>
-      <c r="C34" s="23" t="s">
-        <v>92</v>
       </c>
       <c r="D34" s="16"/>
       <c r="E34" s="17">
@@ -2177,15 +2389,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A35" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B35" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="C35" s="23" t="s">
         <v>94</v>
-      </c>
-      <c r="C35" s="23" t="s">
-        <v>95</v>
       </c>
       <c r="D35" s="16"/>
       <c r="E35" s="17">
@@ -2198,15 +2410,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A36" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B36" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="C36" s="24" t="s">
         <v>97</v>
-      </c>
-      <c r="C36" s="23" t="s">
-        <v>98</v>
       </c>
       <c r="D36" s="16"/>
       <c r="E36" s="17">
@@ -2219,15 +2431,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A37" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="C37" s="23" t="s">
         <v>100</v>
-      </c>
-      <c r="C37" s="23" t="s">
-        <v>101</v>
       </c>
       <c r="D37" s="16"/>
       <c r="E37" s="17">
@@ -2240,15 +2452,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="30" x14ac:dyDescent="0.2">
       <c r="A38" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="B38" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="B38" s="15" t="s">
+      <c r="C38" s="23" t="s">
         <v>103</v>
-      </c>
-      <c r="C38" s="23" t="s">
-        <v>104</v>
       </c>
       <c r="D38" s="16"/>
       <c r="E38" s="17">
@@ -2261,15 +2473,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="30" x14ac:dyDescent="0.2">
       <c r="A39" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B39" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="C39" s="23" t="s">
         <v>106</v>
-      </c>
-      <c r="C39" s="23" t="s">
-        <v>107</v>
       </c>
       <c r="D39" s="16"/>
       <c r="E39" s="17">
@@ -2282,36 +2494,42 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A40" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="B40" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="C40" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="C40" s="23" t="s">
+      <c r="D40" s="18">
+        <f>SUM(D41:D47)</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="18">
+        <f>SUM(F41:F47)</f>
+        <v>0</v>
+      </c>
+      <c r="G40" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A41" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="D40" s="18"/>
-      <c r="E40" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F40" s="18"/>
-      <c r="G40" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A41" s="15" t="s">
+      <c r="B41" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="B41" s="15" t="s">
+      <c r="C41" s="24" t="s">
         <v>112</v>
-      </c>
-      <c r="C41" s="23" t="s">
-        <v>113</v>
       </c>
       <c r="D41" s="18"/>
       <c r="E41" s="17">
@@ -2324,15 +2542,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A42" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B42" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="C42" s="24" t="s">
         <v>115</v>
-      </c>
-      <c r="C42" s="23" t="s">
-        <v>116</v>
       </c>
       <c r="D42" s="18"/>
       <c r="E42" s="17">
@@ -2345,15 +2563,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="B43" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="B43" s="15" t="s">
+      <c r="C43" s="24" t="s">
         <v>118</v>
-      </c>
-      <c r="C43" s="23" t="s">
-        <v>119</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="17">
@@ -2366,15 +2584,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="B44" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="B44" s="15" t="s">
+      <c r="C44" s="24" t="s">
         <v>121</v>
-      </c>
-      <c r="C44" s="23" t="s">
-        <v>122</v>
       </c>
       <c r="D44" s="18"/>
       <c r="E44" s="17">
@@ -2387,15 +2605,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A45" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B45" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="B45" s="15" t="s">
+      <c r="C45" s="24" t="s">
         <v>124</v>
-      </c>
-      <c r="C45" s="23" t="s">
-        <v>125</v>
       </c>
       <c r="D45" s="18"/>
       <c r="E45" s="17">
@@ -2408,15 +2626,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B46" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="B46" s="15" t="s">
+      <c r="C46" s="24" t="s">
         <v>127</v>
-      </c>
-      <c r="C46" s="23" t="s">
-        <v>128</v>
       </c>
       <c r="D46" s="18"/>
       <c r="E46" s="17">
@@ -2429,15 +2647,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A47" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B47" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="B47" s="15" t="s">
+      <c r="C47" s="24" t="s">
         <v>130</v>
-      </c>
-      <c r="C47" s="23" t="s">
-        <v>131</v>
       </c>
       <c r="D47" s="18"/>
       <c r="E47" s="17">
@@ -2450,15 +2668,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A48" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="B48" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="B48" s="15" t="s">
+      <c r="C48" s="23" t="s">
         <v>133</v>
-      </c>
-      <c r="C48" s="23" t="s">
-        <v>134</v>
       </c>
       <c r="D48" s="18"/>
       <c r="E48" s="17">
@@ -2471,33 +2689,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A49" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B49" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="B49" s="19" t="s">
+      <c r="C49" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="C49" s="22" t="s">
+      <c r="D49" s="20">
+        <f>SUM(D50:D75)-D56-D71</f>
+        <v>0</v>
+      </c>
+      <c r="E49" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F49" s="20">
+        <f>SUM(F50:F75)-F56-F71</f>
+        <v>0</v>
+      </c>
+      <c r="G49" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A50" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="D49" s="20"/>
-      <c r="E49" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F49" s="20"/>
-      <c r="G49" s="21">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A50" s="15" t="s">
+      <c r="B50" s="15" t="s">
         <v>138</v>
-      </c>
-      <c r="B50" s="15" t="s">
-        <v>139</v>
       </c>
       <c r="C50" s="23" t="s">
         <v>35</v>
@@ -2513,12 +2737,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A51" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="B51" s="15" t="s">
         <v>140</v>
-      </c>
-      <c r="B51" s="15" t="s">
-        <v>141</v>
       </c>
       <c r="C51" s="23" t="s">
         <v>38</v>
@@ -2534,12 +2758,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A52" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="B52" s="15" t="s">
         <v>142</v>
-      </c>
-      <c r="B52" s="15" t="s">
-        <v>143</v>
       </c>
       <c r="C52" s="23" t="s">
         <v>41</v>
@@ -2555,12 +2779,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A53" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="B53" s="15" t="s">
         <v>144</v>
-      </c>
-      <c r="B53" s="15" t="s">
-        <v>145</v>
       </c>
       <c r="C53" s="23" t="s">
         <v>44</v>
@@ -2576,12 +2800,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A54" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="B54" s="15" t="s">
         <v>146</v>
-      </c>
-      <c r="B54" s="15" t="s">
-        <v>147</v>
       </c>
       <c r="C54" s="23" t="s">
         <v>47</v>
@@ -2597,15 +2821,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" ht="45" x14ac:dyDescent="0.2">
       <c r="A55" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="B55" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="B55" s="15" t="s">
+      <c r="C55" s="23" t="s">
         <v>149</v>
-      </c>
-      <c r="C55" s="23" t="s">
-        <v>150</v>
       </c>
       <c r="D55" s="18"/>
       <c r="E55" s="17">
@@ -2618,15 +2842,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A56" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B56" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="B56" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="C56" s="23" t="s">
-        <v>53</v>
+      <c r="C56" s="24" t="s">
+        <v>255</v>
       </c>
       <c r="D56" s="18"/>
       <c r="E56" s="17">
@@ -2639,15 +2863,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A57" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="B57" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="B57" s="15" t="s">
-        <v>154</v>
-      </c>
       <c r="C57" s="23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D57" s="18"/>
       <c r="E57" s="17">
@@ -2660,15 +2884,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A58" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="B58" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="B58" s="15" t="s">
-        <v>156</v>
-      </c>
       <c r="C58" s="23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D58" s="18"/>
       <c r="E58" s="17">
@@ -2681,15 +2905,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A59" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="B59" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="B59" s="15" t="s">
-        <v>158</v>
-      </c>
       <c r="C59" s="23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D59" s="18"/>
       <c r="E59" s="17">
@@ -2702,15 +2926,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A60" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="B60" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="B60" s="15" t="s">
-        <v>160</v>
-      </c>
       <c r="C60" s="23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D60" s="18"/>
       <c r="E60" s="17">
@@ -2723,15 +2947,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" ht="30" x14ac:dyDescent="0.2">
       <c r="A61" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="B61" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="B61" s="15" t="s">
-        <v>162</v>
-      </c>
       <c r="C61" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D61" s="18"/>
       <c r="E61" s="17">
@@ -2744,15 +2968,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A62" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="B62" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="B62" s="15" t="s">
-        <v>164</v>
-      </c>
       <c r="C62" s="23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D62" s="18"/>
       <c r="E62" s="17">
@@ -2765,15 +2989,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" ht="30" x14ac:dyDescent="0.2">
       <c r="A63" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="B63" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="B63" s="15" t="s">
+      <c r="C63" s="23" t="s">
         <v>166</v>
-      </c>
-      <c r="C63" s="23" t="s">
-        <v>167</v>
       </c>
       <c r="D63" s="18"/>
       <c r="E63" s="17">
@@ -2786,15 +3010,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A64" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="B64" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="B64" s="15" t="s">
-        <v>169</v>
-      </c>
       <c r="C64" s="23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D64" s="18"/>
       <c r="E64" s="17">
@@ -2807,15 +3031,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A65" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="B65" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="B65" s="15" t="s">
-        <v>171</v>
-      </c>
       <c r="C65" s="23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D65" s="18"/>
       <c r="E65" s="17">
@@ -2828,15 +3052,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A66" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="B66" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="B66" s="15" t="s">
-        <v>173</v>
-      </c>
       <c r="C66" s="23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D66" s="18"/>
       <c r="E66" s="17">
@@ -2849,15 +3073,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A67" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="B67" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="B67" s="15" t="s">
-        <v>175</v>
-      </c>
       <c r="C67" s="23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D67" s="18"/>
       <c r="E67" s="17">
@@ -2870,15 +3094,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" ht="30" x14ac:dyDescent="0.2">
       <c r="A68" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="B68" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="B68" s="15" t="s">
-        <v>177</v>
-      </c>
       <c r="C68" s="23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D68" s="18"/>
       <c r="E68" s="17">
@@ -2891,15 +3115,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" ht="45" x14ac:dyDescent="0.2">
       <c r="A69" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="B69" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="B69" s="15" t="s">
-        <v>179</v>
-      </c>
       <c r="C69" s="23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D69" s="18"/>
       <c r="E69" s="17">
@@ -2912,15 +3136,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A70" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="B70" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="B70" s="15" t="s">
-        <v>181</v>
-      </c>
       <c r="C70" s="23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D70" s="18"/>
       <c r="E70" s="17">
@@ -2933,15 +3157,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A71" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="B71" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="B71" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="C71" s="23" t="s">
-        <v>98</v>
+      <c r="C71" s="24" t="s">
+        <v>97</v>
       </c>
       <c r="D71" s="18"/>
       <c r="E71" s="17">
@@ -2954,15 +3178,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A72" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="B72" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="B72" s="15" t="s">
-        <v>185</v>
-      </c>
       <c r="C72" s="23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D72" s="18"/>
       <c r="E72" s="17">
@@ -2975,15 +3199,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" ht="30" x14ac:dyDescent="0.2">
       <c r="A73" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="B73" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="B73" s="15" t="s">
-        <v>187</v>
-      </c>
       <c r="C73" s="23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D73" s="18"/>
       <c r="E73" s="17">
@@ -2996,15 +3220,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" ht="30" x14ac:dyDescent="0.2">
       <c r="A74" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="B74" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="B74" s="15" t="s">
-        <v>189</v>
-      </c>
       <c r="C74" s="23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D74" s="18"/>
       <c r="E74" s="17">
@@ -3017,15 +3241,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A75" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="B75" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="B75" s="15" t="s">
-        <v>191</v>
-      </c>
       <c r="C75" s="23" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D75" s="18"/>
       <c r="E75" s="17">
@@ -3038,26 +3262,38 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A76" s="15"/>
-      <c r="B76" s="15"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="16"/>
-      <c r="E76" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F76" s="18"/>
-      <c r="G76" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A77" s="15"/>
-      <c r="B77" s="15"/>
-      <c r="C77" s="14"/>
-      <c r="D77" s="16"/>
+    <row r="76" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A76" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="B76" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="C76" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="D76" s="20"/>
+      <c r="E76" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F76" s="20"/>
+      <c r="G76" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A77" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="B77" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C77" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="D77" s="18"/>
       <c r="E77" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3068,11 +3304,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A78" s="15"/>
-      <c r="B78" s="15"/>
-      <c r="C78" s="14"/>
-      <c r="D78" s="16"/>
+    <row r="78" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A78" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="B78" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="C78" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="D78" s="18"/>
       <c r="E78" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3083,11 +3325,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A79" s="15"/>
-      <c r="B79" s="15"/>
-      <c r="C79" s="14"/>
-      <c r="D79" s="16"/>
+    <row r="79" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A79" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="B79" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="C79" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="D79" s="18"/>
       <c r="E79" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3098,11 +3346,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A80" s="15"/>
-      <c r="B80" s="15"/>
-      <c r="C80" s="14"/>
-      <c r="D80" s="16"/>
+    <row r="80" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A80" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="B80" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="C80" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="D80" s="18"/>
       <c r="E80" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3113,11 +3367,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A81" s="15"/>
-      <c r="B81" s="15"/>
-      <c r="C81" s="14"/>
-      <c r="D81" s="16"/>
+    <row r="81" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A81" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="B81" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="C81" s="23" t="s">
+        <v>208</v>
+      </c>
+      <c r="D81" s="18"/>
       <c r="E81" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3128,11 +3388,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A82" s="15"/>
-      <c r="B82" s="15"/>
-      <c r="C82" s="14"/>
-      <c r="D82" s="16"/>
+    <row r="82" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A82" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="B82" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="C82" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="D82" s="18"/>
       <c r="E82" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3143,11 +3409,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A83" s="15"/>
-      <c r="B83" s="15"/>
-      <c r="C83" s="14"/>
-      <c r="D83" s="16"/>
+    <row r="83" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A83" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="B83" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="C83" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="D83" s="18"/>
       <c r="E83" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3158,11 +3430,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A84" s="15"/>
-      <c r="B84" s="15"/>
-      <c r="C84" s="14"/>
-      <c r="D84" s="16"/>
+    <row r="84" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A84" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="B84" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="C84" s="23" t="s">
+        <v>217</v>
+      </c>
+      <c r="D84" s="18"/>
       <c r="E84" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3173,11 +3451,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A85" s="15"/>
-      <c r="B85" s="15"/>
-      <c r="C85" s="14"/>
-      <c r="D85" s="16"/>
+    <row r="85" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A85" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="B85" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="C85" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="D85" s="18"/>
       <c r="E85" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3188,11 +3472,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A86" s="15"/>
-      <c r="B86" s="15"/>
-      <c r="C86" s="14"/>
-      <c r="D86" s="16"/>
+    <row r="86" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A86" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="B86" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="C86" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="D86" s="18"/>
       <c r="E86" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3203,11 +3493,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A87" s="15"/>
-      <c r="B87" s="15"/>
-      <c r="C87" s="14"/>
-      <c r="D87" s="16"/>
+    <row r="87" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A87" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="B87" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="C87" s="23" t="s">
+        <v>226</v>
+      </c>
+      <c r="D87" s="18"/>
       <c r="E87" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3218,11 +3514,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A88" s="15"/>
-      <c r="B88" s="15"/>
-      <c r="C88" s="14"/>
-      <c r="D88" s="16"/>
+    <row r="88" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A88" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="B88" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="C88" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="D88" s="18"/>
       <c r="E88" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3233,11 +3535,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A89" s="15"/>
-      <c r="B89" s="15"/>
-      <c r="C89" s="14"/>
-      <c r="D89" s="16"/>
+    <row r="89" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A89" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="B89" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="C89" s="23" t="s">
+        <v>232</v>
+      </c>
+      <c r="D89" s="18"/>
       <c r="E89" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3248,11 +3556,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A90" s="15"/>
-      <c r="B90" s="15"/>
-      <c r="C90" s="14"/>
-      <c r="D90" s="16"/>
+    <row r="90" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A90" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="B90" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="C90" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="D90" s="18"/>
       <c r="E90" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3263,11 +3577,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A91" s="15"/>
-      <c r="B91" s="15"/>
-      <c r="C91" s="14"/>
-      <c r="D91" s="16"/>
+    <row r="91" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A91" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="B91" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="C91" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="D91" s="18"/>
       <c r="E91" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3278,11 +3598,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A92" s="15"/>
-      <c r="B92" s="15"/>
-      <c r="C92" s="14"/>
-      <c r="D92" s="16"/>
+    <row r="92" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A92" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="B92" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="C92" s="23" t="s">
+        <v>241</v>
+      </c>
+      <c r="D92" s="18"/>
       <c r="E92" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3293,11 +3619,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A93" s="15"/>
-      <c r="B93" s="15"/>
-      <c r="C93" s="14"/>
-      <c r="D93" s="16"/>
+    <row r="93" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A93" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="B93" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="C93" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="D93" s="18"/>
       <c r="E93" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3308,11 +3640,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A94" s="15"/>
-      <c r="B94" s="15"/>
-      <c r="C94" s="14"/>
-      <c r="D94" s="16"/>
+    <row r="94" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A94" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="B94" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="C94" s="23" t="s">
+        <v>247</v>
+      </c>
+      <c r="D94" s="18"/>
       <c r="E94" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3323,11 +3661,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A95" s="15"/>
-      <c r="B95" s="15"/>
-      <c r="C95" s="14"/>
-      <c r="D95" s="16"/>
+    <row r="95" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A95" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="B95" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="C95" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="D95" s="18"/>
       <c r="E95" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3338,11 +3682,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A96" s="15"/>
-      <c r="B96" s="15"/>
-      <c r="C96" s="14"/>
-      <c r="D96" s="16"/>
+    <row r="96" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A96" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="B96" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="C96" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="D96" s="18"/>
       <c r="E96" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3353,7 +3703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A97" s="15"/>
       <c r="B97" s="15"/>
       <c r="C97" s="14"/>
@@ -3368,7 +3718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A98" s="15"/>
       <c r="B98" s="15"/>
       <c r="C98" s="14"/>
@@ -3383,7 +3733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A99" s="15"/>
       <c r="B99" s="15"/>
       <c r="C99" s="14"/>
@@ -3398,7 +3748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A100" s="15"/>
       <c r="B100" s="15"/>
       <c r="C100" s="14"/>
@@ -3413,7 +3763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A101" s="15"/>
       <c r="B101" s="15"/>
       <c r="C101" s="14"/>
@@ -3428,7 +3778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A102" s="15"/>
       <c r="B102" s="15"/>
       <c r="C102" s="14"/>
@@ -3443,7 +3793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A103" s="15"/>
       <c r="B103" s="15"/>
       <c r="C103" s="14"/>
@@ -3458,7 +3808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A104" s="15"/>
       <c r="B104" s="15"/>
       <c r="C104" s="14"/>
@@ -3473,7 +3823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A105" s="15"/>
       <c r="B105" s="15"/>
       <c r="C105" s="14"/>
@@ -3488,7 +3838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A106" s="15"/>
       <c r="B106" s="15"/>
       <c r="C106" s="14"/>
@@ -3503,7 +3853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A107" s="15"/>
       <c r="B107" s="15"/>
       <c r="C107" s="14"/>
@@ -3518,7 +3868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A108" s="15"/>
       <c r="B108" s="15"/>
       <c r="C108" s="14"/>
@@ -3533,7 +3883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A109" s="15"/>
       <c r="B109" s="15"/>
       <c r="C109" s="14"/>
@@ -3548,7 +3898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A110" s="15"/>
       <c r="B110" s="15"/>
       <c r="C110" s="14"/>
@@ -3563,7 +3913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A111" s="15"/>
       <c r="B111" s="15"/>
       <c r="C111" s="14"/>
@@ -3578,7 +3928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A112" s="15"/>
       <c r="B112" s="15"/>
       <c r="C112" s="14"/>
@@ -3593,352 +3943,352 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A113" s="15"/>
       <c r="B113" s="15"/>
       <c r="C113" s="14"/>
       <c r="D113" s="16"/>
       <c r="E113" s="17">
-        <f t="shared" ref="E113:E144" si="2">D113+F113</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F113" s="18"/>
       <c r="G113" s="17">
-        <f t="shared" ref="G113:G144" si="3">IFERROR(F113/D113*100,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A114" s="15"/>
       <c r="B114" s="15"/>
       <c r="C114" s="14"/>
       <c r="D114" s="16"/>
       <c r="E114" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F114" s="18"/>
       <c r="G114" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A115" s="15"/>
       <c r="B115" s="15"/>
       <c r="C115" s="14"/>
       <c r="D115" s="16"/>
       <c r="E115" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F115" s="18"/>
       <c r="G115" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A116" s="15"/>
       <c r="B116" s="15"/>
       <c r="C116" s="14"/>
       <c r="D116" s="16"/>
       <c r="E116" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F116" s="18"/>
       <c r="G116" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A117" s="15"/>
       <c r="B117" s="15"/>
       <c r="C117" s="14"/>
       <c r="D117" s="16"/>
       <c r="E117" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F117" s="18"/>
       <c r="G117" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A118" s="15"/>
       <c r="B118" s="15"/>
       <c r="C118" s="14"/>
       <c r="D118" s="16"/>
       <c r="E118" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F118" s="18"/>
       <c r="G118" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A119" s="15"/>
       <c r="B119" s="15"/>
       <c r="C119" s="14"/>
-      <c r="D119" s="18"/>
+      <c r="D119" s="16"/>
       <c r="E119" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F119" s="18"/>
       <c r="G119" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A120" s="15"/>
       <c r="B120" s="15"/>
       <c r="C120" s="14"/>
-      <c r="D120" s="18"/>
+      <c r="D120" s="16"/>
       <c r="E120" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F120" s="18"/>
       <c r="G120" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A121" s="15"/>
       <c r="B121" s="15"/>
       <c r="C121" s="14"/>
-      <c r="D121" s="18"/>
+      <c r="D121" s="16"/>
       <c r="E121" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F121" s="18"/>
       <c r="G121" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A122" s="15"/>
       <c r="B122" s="15"/>
       <c r="C122" s="14"/>
-      <c r="D122" s="18"/>
+      <c r="D122" s="16"/>
       <c r="E122" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F122" s="18"/>
       <c r="G122" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A123" s="15"/>
       <c r="B123" s="15"/>
       <c r="C123" s="14"/>
-      <c r="D123" s="18"/>
+      <c r="D123" s="16"/>
       <c r="E123" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F123" s="18"/>
       <c r="G123" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A124" s="15"/>
       <c r="B124" s="15"/>
       <c r="C124" s="14"/>
-      <c r="D124" s="18"/>
+      <c r="D124" s="16"/>
       <c r="E124" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F124" s="18"/>
       <c r="G124" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A125" s="15"/>
       <c r="B125" s="15"/>
       <c r="C125" s="14"/>
-      <c r="D125" s="18"/>
+      <c r="D125" s="16"/>
       <c r="E125" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F125" s="18"/>
       <c r="G125" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A126" s="15"/>
       <c r="B126" s="15"/>
       <c r="C126" s="14"/>
-      <c r="D126" s="18"/>
+      <c r="D126" s="16"/>
       <c r="E126" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F126" s="18"/>
       <c r="G126" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A127" s="15"/>
       <c r="B127" s="15"/>
       <c r="C127" s="14"/>
-      <c r="D127" s="18"/>
+      <c r="D127" s="16"/>
       <c r="E127" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F127" s="18"/>
       <c r="G127" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A128" s="15"/>
       <c r="B128" s="15"/>
       <c r="C128" s="14"/>
-      <c r="D128" s="18"/>
+      <c r="D128" s="16"/>
       <c r="E128" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F128" s="18"/>
       <c r="G128" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A129" s="15"/>
       <c r="B129" s="15"/>
       <c r="C129" s="14"/>
-      <c r="D129" s="18"/>
+      <c r="D129" s="16"/>
       <c r="E129" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F129" s="18"/>
       <c r="G129" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A130" s="15"/>
       <c r="B130" s="15"/>
       <c r="C130" s="14"/>
-      <c r="D130" s="18"/>
+      <c r="D130" s="16"/>
       <c r="E130" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F130" s="18"/>
       <c r="G130" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A131" s="15"/>
       <c r="B131" s="15"/>
       <c r="C131" s="14"/>
-      <c r="D131" s="18"/>
+      <c r="D131" s="16"/>
       <c r="E131" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F131" s="18"/>
       <c r="G131" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A132" s="15"/>
       <c r="B132" s="15"/>
       <c r="C132" s="14"/>
       <c r="D132" s="16"/>
       <c r="E132" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F132" s="18"/>
       <c r="G132" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A133" s="15"/>
       <c r="B133" s="15"/>
       <c r="C133" s="14"/>
       <c r="D133" s="16"/>
       <c r="E133" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F133" s="18"/>
       <c r="G133" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A134" s="15"/>
       <c r="B134" s="15"/>
       <c r="C134" s="14"/>
       <c r="D134" s="16"/>
       <c r="E134" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F134" s="18"/>
       <c r="G134" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A135" s="15"/>
       <c r="B135" s="15"/>
       <c r="C135" s="14"/>
       <c r="D135" s="16"/>
       <c r="E135" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="E135:E166" si="2">D135+F135</f>
         <v>0</v>
       </c>
       <c r="F135" s="18"/>
       <c r="G135" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+        <f t="shared" ref="G135:G166" si="3">IFERROR(F135/D135*100,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A136" s="15"/>
       <c r="B136" s="15"/>
       <c r="C136" s="14"/>
@@ -3953,7 +4303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A137" s="15"/>
       <c r="B137" s="15"/>
       <c r="C137" s="14"/>
@@ -3968,7 +4318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A138" s="15"/>
       <c r="B138" s="15"/>
       <c r="C138" s="14"/>
@@ -3983,7 +4333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A139" s="15"/>
       <c r="B139" s="15"/>
       <c r="C139" s="14"/>
@@ -3998,7 +4348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A140" s="15"/>
       <c r="B140" s="15"/>
       <c r="C140" s="14"/>
@@ -4013,11 +4363,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A141" s="15"/>
       <c r="B141" s="15"/>
       <c r="C141" s="14"/>
-      <c r="D141" s="16"/>
+      <c r="D141" s="18"/>
       <c r="E141" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -4028,11 +4378,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A142" s="15"/>
       <c r="B142" s="15"/>
       <c r="C142" s="14"/>
-      <c r="D142" s="16"/>
+      <c r="D142" s="18"/>
       <c r="E142" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -4043,11 +4393,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A143" s="15"/>
       <c r="B143" s="15"/>
       <c r="C143" s="14"/>
-      <c r="D143" s="16"/>
+      <c r="D143" s="18"/>
       <c r="E143" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -4058,11 +4408,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A144" s="15"/>
       <c r="B144" s="15"/>
       <c r="C144" s="14"/>
-      <c r="D144" s="16"/>
+      <c r="D144" s="18"/>
       <c r="E144" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -4073,104 +4423,434 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A145" s="8"/>
-      <c r="B145" s="8"/>
-      <c r="C145" s="9"/>
-      <c r="G145" s="6"/>
-    </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A146" s="8"/>
-      <c r="B146" s="8"/>
-      <c r="C146" s="1" t="s">
+    <row r="145" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A145" s="15"/>
+      <c r="B145" s="15"/>
+      <c r="C145" s="14"/>
+      <c r="D145" s="18"/>
+      <c r="E145" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F145" s="18"/>
+      <c r="G145" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A146" s="15"/>
+      <c r="B146" s="15"/>
+      <c r="C146" s="14"/>
+      <c r="D146" s="18"/>
+      <c r="E146" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F146" s="18"/>
+      <c r="G146" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A147" s="15"/>
+      <c r="B147" s="15"/>
+      <c r="C147" s="14"/>
+      <c r="D147" s="18"/>
+      <c r="E147" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F147" s="18"/>
+      <c r="G147" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A148" s="15"/>
+      <c r="B148" s="15"/>
+      <c r="C148" s="14"/>
+      <c r="D148" s="18"/>
+      <c r="E148" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F148" s="18"/>
+      <c r="G148" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A149" s="15"/>
+      <c r="B149" s="15"/>
+      <c r="C149" s="14"/>
+      <c r="D149" s="18"/>
+      <c r="E149" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F149" s="18"/>
+      <c r="G149" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A150" s="15"/>
+      <c r="B150" s="15"/>
+      <c r="C150" s="14"/>
+      <c r="D150" s="18"/>
+      <c r="E150" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F150" s="18"/>
+      <c r="G150" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A151" s="15"/>
+      <c r="B151" s="15"/>
+      <c r="C151" s="14"/>
+      <c r="D151" s="18"/>
+      <c r="E151" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F151" s="18"/>
+      <c r="G151" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A152" s="15"/>
+      <c r="B152" s="15"/>
+      <c r="C152" s="14"/>
+      <c r="D152" s="18"/>
+      <c r="E152" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F152" s="18"/>
+      <c r="G152" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A153" s="15"/>
+      <c r="B153" s="15"/>
+      <c r="C153" s="14"/>
+      <c r="D153" s="18"/>
+      <c r="E153" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F153" s="18"/>
+      <c r="G153" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A154" s="15"/>
+      <c r="B154" s="15"/>
+      <c r="C154" s="14"/>
+      <c r="D154" s="16"/>
+      <c r="E154" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F154" s="18"/>
+      <c r="G154" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A155" s="15"/>
+      <c r="B155" s="15"/>
+      <c r="C155" s="14"/>
+      <c r="D155" s="16"/>
+      <c r="E155" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F155" s="18"/>
+      <c r="G155" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A156" s="15"/>
+      <c r="B156" s="15"/>
+      <c r="C156" s="14"/>
+      <c r="D156" s="16"/>
+      <c r="E156" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F156" s="18"/>
+      <c r="G156" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A157" s="15"/>
+      <c r="B157" s="15"/>
+      <c r="C157" s="14"/>
+      <c r="D157" s="16"/>
+      <c r="E157" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F157" s="18"/>
+      <c r="G157" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A158" s="15"/>
+      <c r="B158" s="15"/>
+      <c r="C158" s="14"/>
+      <c r="D158" s="16"/>
+      <c r="E158" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F158" s="18"/>
+      <c r="G158" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A159" s="15"/>
+      <c r="B159" s="15"/>
+      <c r="C159" s="14"/>
+      <c r="D159" s="16"/>
+      <c r="E159" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F159" s="18"/>
+      <c r="G159" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A160" s="15"/>
+      <c r="B160" s="15"/>
+      <c r="C160" s="14"/>
+      <c r="D160" s="16"/>
+      <c r="E160" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F160" s="18"/>
+      <c r="G160" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+      <c r="A161" s="15"/>
+      <c r="B161" s="15"/>
+      <c r="C161" s="14"/>
+      <c r="D161" s="16"/>
+      <c r="E161" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F161" s="18"/>
+      <c r="G161" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+      <c r="A162" s="15"/>
+      <c r="B162" s="15"/>
+      <c r="C162" s="14"/>
+      <c r="D162" s="16"/>
+      <c r="E162" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F162" s="18"/>
+      <c r="G162" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+      <c r="A163" s="15"/>
+      <c r="B163" s="15"/>
+      <c r="C163" s="14"/>
+      <c r="D163" s="16"/>
+      <c r="E163" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F163" s="18"/>
+      <c r="G163" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+      <c r="A164" s="15"/>
+      <c r="B164" s="15"/>
+      <c r="C164" s="14"/>
+      <c r="D164" s="16"/>
+      <c r="E164" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F164" s="18"/>
+      <c r="G164" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+      <c r="A165" s="15"/>
+      <c r="B165" s="15"/>
+      <c r="C165" s="14"/>
+      <c r="D165" s="16"/>
+      <c r="E165" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F165" s="18"/>
+      <c r="G165" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+      <c r="A166" s="15"/>
+      <c r="B166" s="15"/>
+      <c r="C166" s="14"/>
+      <c r="D166" s="16"/>
+      <c r="E166" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F166" s="18"/>
+      <c r="G166" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A167" s="8"/>
+      <c r="B167" s="8"/>
+      <c r="C167" s="9"/>
+      <c r="G167" s="6"/>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A168" s="8"/>
+      <c r="B168" s="8"/>
+      <c r="C168" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G146" s="6"/>
-    </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A147" s="10"/>
-      <c r="B147" s="10"/>
-      <c r="C147" s="10"/>
-      <c r="D147" s="24" t="s">
+      <c r="G168" s="6"/>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A169" s="10"/>
+      <c r="B169" s="10"/>
+      <c r="C169" s="10"/>
+      <c r="D169" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="E147" s="24"/>
-      <c r="F147" s="24"/>
-      <c r="G147" s="24"/>
-    </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A148" s="11"/>
-      <c r="B148" s="11"/>
-      <c r="C148" s="12" t="s">
+      <c r="E169" s="25"/>
+      <c r="F169" s="25"/>
+      <c r="G169" s="25"/>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A170" s="11"/>
+      <c r="B170" s="11"/>
+      <c r="C170" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D148" s="25"/>
-      <c r="E148" s="25"/>
-      <c r="F148" s="25"/>
-      <c r="G148" s="25"/>
-      <c r="H148" s="11"/>
-      <c r="I148" s="11"/>
-      <c r="J148" s="11"/>
-    </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A149" s="9"/>
-      <c r="B149" s="9"/>
-      <c r="C149" s="8" t="s">
+      <c r="D170" s="26"/>
+      <c r="E170" s="26"/>
+      <c r="F170" s="26"/>
+      <c r="G170" s="26"/>
+      <c r="H170" s="11"/>
+      <c r="I170" s="11"/>
+      <c r="J170" s="11"/>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A171" s="9"/>
+      <c r="B171" s="9"/>
+      <c r="C171" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D149" s="24"/>
-      <c r="E149" s="24"/>
-      <c r="F149" s="24"/>
-      <c r="G149" s="24"/>
-      <c r="H149" s="13"/>
-      <c r="I149" s="13"/>
-      <c r="J149" s="13"/>
-    </row>
-    <row r="150" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A150" s="2"/>
-      <c r="B150" s="2"/>
-      <c r="C150" s="2"/>
-      <c r="D150" s="2"/>
-      <c r="E150" s="2"/>
-      <c r="F150" s="2"/>
-    </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C155" s="11" t="s">
+      <c r="D171" s="25"/>
+      <c r="E171" s="25"/>
+      <c r="F171" s="25"/>
+      <c r="G171" s="25"/>
+      <c r="H171" s="13"/>
+      <c r="I171" s="13"/>
+      <c r="J171" s="13"/>
+    </row>
+    <row r="172" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A172" s="2"/>
+      <c r="B172" s="2"/>
+      <c r="C172" s="2"/>
+      <c r="D172" s="2"/>
+      <c r="E172" s="2"/>
+      <c r="F172" s="2"/>
+    </row>
+    <row r="177" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C177" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C156" s="1" t="s">
+    <row r="178" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C178" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C157" s="1" t="s">
+    <row r="179" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C179" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C158" s="1" t="s">
+    <row r="180" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C180" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C159" s="1" t="s">
+    <row r="181" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C181" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C160" s="1" t="s">
+    <row r="182" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C182" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="162" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C162" s="1" t="s">
+    <row r="184" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C184" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="165" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C165" s="11"/>
+    <row r="187" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C187" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -4181,9 +4861,9 @@
     <mergeCell ref="D3:G3"/>
     <mergeCell ref="D4:G4"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="D147:G147"/>
-    <mergeCell ref="D148:G148"/>
-    <mergeCell ref="D149:G149"/>
+    <mergeCell ref="D169:G169"/>
+    <mergeCell ref="D170:G170"/>
+    <mergeCell ref="D171:G171"/>
     <mergeCell ref="E7:H7"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="C8:C11"/>

--- a/web/EXCEL_TEMPLATE/KHNV/KHNV_DK01A.xlsx
+++ b/web/EXCEL_TEMPLATE/KHNV/KHNV_DK01A.xlsx
@@ -1,25 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24026"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\KHNV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cap nhat CN\IMS_REPORT KHNV - New\EXCEL_TEMPLATE\KHNV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD3EEE3-09E2-4A4E-A772-CB5FE54ACB13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3048" yWindow="-120" windowWidth="20736" windowHeight="11280"/>
   </bookViews>
   <sheets>
     <sheet name="DK_01A" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">DK_01A!$A$1:$G$171</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">DK_01A!$A$1:$G$152</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">DK_01A!$8:$12</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="173">
   <si>
     <t>Biểu số 01a/NHCS-KH</t>
   </si>
@@ -469,362 +468,113 @@
     <t>XD00038</t>
   </si>
   <si>
-    <t>39</t>
-  </si>
-  <si>
     <t>XD00039</t>
   </si>
   <si>
-    <t>40</t>
-  </si>
-  <si>
     <t>XD00040</t>
   </si>
   <si>
-    <t>41</t>
-  </si>
-  <si>
     <t>XD00041</t>
   </si>
   <si>
-    <t>42</t>
-  </si>
-  <si>
     <t>XD00042</t>
   </si>
   <si>
-    <t>43</t>
-  </si>
-  <si>
     <t>XD00043</t>
   </si>
   <si>
     <t>Cho vay người lao động đi làm việc ở nước ngoài theo Quyết định số 365/QĐ-NHNN, Quyết định số 1465/QĐ-TTg, Quyết định số 63/2015/QĐ-TTg và Nghị định số 61/2015/NĐ-CP</t>
   </si>
   <si>
-    <t>44</t>
-  </si>
-  <si>
     <t>XD00044</t>
   </si>
   <si>
-    <t>45</t>
-  </si>
-  <si>
     <t>XD00045</t>
   </si>
   <si>
-    <t>46</t>
-  </si>
-  <si>
     <t>XD00046</t>
   </si>
   <si>
-    <t>47</t>
-  </si>
-  <si>
     <t>XD00047</t>
   </si>
   <si>
-    <t>48</t>
-  </si>
-  <si>
     <t>XD00048</t>
   </si>
   <si>
-    <t>49</t>
-  </si>
-  <si>
     <t>XD00049</t>
   </si>
   <si>
-    <t>50</t>
-  </si>
-  <si>
     <t>XD00050</t>
   </si>
   <si>
-    <t>51</t>
-  </si>
-  <si>
     <t>XD00051</t>
   </si>
   <si>
     <t>Cho vay đồng bào DTTS vùng ĐBSCL theo QĐ 29/2013/QĐ-TTg (QĐ 74/2008/QĐ-TTg)</t>
   </si>
   <si>
-    <t>52</t>
-  </si>
-  <si>
     <t>XD00052</t>
   </si>
   <si>
-    <t>53</t>
-  </si>
-  <si>
     <t>XD00053</t>
   </si>
   <si>
-    <t>54</t>
-  </si>
-  <si>
     <t>XD00054</t>
   </si>
   <si>
-    <t>55</t>
-  </si>
-  <si>
     <t>XD00055</t>
   </si>
   <si>
-    <t>56</t>
-  </si>
-  <si>
     <t>XD00056</t>
   </si>
   <si>
-    <t>57</t>
-  </si>
-  <si>
     <t>XD00057</t>
   </si>
   <si>
-    <t>58</t>
-  </si>
-  <si>
     <t>XD00058</t>
   </si>
   <si>
-    <t>59</t>
-  </si>
-  <si>
     <t>XD00059</t>
   </si>
   <si>
-    <t>60</t>
-  </si>
-  <si>
     <t>XD00060</t>
   </si>
   <si>
-    <t>61</t>
-  </si>
-  <si>
     <t>XD00061</t>
   </si>
   <si>
-    <t>62</t>
-  </si>
-  <si>
     <t>XD00062</t>
   </si>
   <si>
-    <t>63</t>
-  </si>
-  <si>
     <t>XD00063</t>
   </si>
   <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>XD00064</t>
-  </si>
-  <si>
-    <t>THUYẾT MINH MỘT SỐ CHỈ TIÊU (Dự kiến năm kế hoạch)</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>XD00065</t>
-  </si>
-  <si>
-    <t>Số hộ dân cư trú trên địa bàn</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>XD00066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số hộ dân là hộ đồng bào dân tộc thiểu số </t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>XD00067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số hộ nghèo theo chuẩn hộ nghèo (giai đoạn 2021-2025) </t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>XD00068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số hộ nghèo đang còn dư nợ NHCSXH </t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>XD00069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số hộ nghèo đủ điều kiện vay vốn nhưng chưa được vay vốn NHCSXH </t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>XD00070</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số hộ cận nghèo theo chuẩn hộ cận nghèo (giai đoạn 2021-2025) </t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>XD00071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số hộ cận nghèo đang còn dư nợ NHCSXH </t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>XD00072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số hộ cận nghèo đủ điều kiện vay vốn nhưng chưa được vay vốn NHCSXH </t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>XD00073</t>
-  </si>
-  <si>
-    <t>Số hộ mới thoát nghèo (giai đoạn 2019-2021)</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>XD00074</t>
-  </si>
-  <si>
-    <t>Số hộ gia đình sản xuất kinh doanh vùng khó khăn trên địa bàn</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>XD00075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số hộ gia đình SXKD đang còn dư nợ NHCSXH </t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>XD00076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số hộ gia đình SXKD đủ điều kiện vay vốn nhưng chưa được vay vốn NHCSXH </t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>XD00077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số thương nhân hoạt động thương mại tại vùng khó khăn </t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>XD00078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tổng số HSSV theo học các Trường ĐH, CĐ, THCN và dạy nghề </t>
-  </si>
-  <si>
-    <t>79</t>
-  </si>
-  <si>
-    <t>XD00079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số HSSV đang còn dư nợ NHCSXH </t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>XD00080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số lao động có nhu cầu vay vốn giải quyết việc làm </t>
-  </si>
-  <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>XD00081</t>
-  </si>
-  <si>
-    <t>Số lao động được vay vốn giải quyết việc làm trong năm</t>
-  </si>
-  <si>
-    <t>82</t>
-  </si>
-  <si>
-    <t>XD00082</t>
-  </si>
-  <si>
-    <t>Số lao động dự kiến được thu hút từ vay vốn giải quyết việc làm</t>
-  </si>
-  <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>XD00083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tổng số lao động có nhu cầu vay vốn đi lao động có thời hạn ở nước ngoài </t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>XD00084</t>
-  </si>
-  <si>
-    <t>Số công trình NS-VSMT NT dự kiến được xây dựng từ nguồn vốn vay NHCSXH</t>
-  </si>
-  <si>
     <t>THÔN: ... XÃ/PHƯỜNG/THỊ TRẤN: …</t>
   </si>
   <si>
     <t>Trong đó: Cho vay để ký quỹ đối với người lao động đi làm việc tại Hàn Quốc</t>
+  </si>
+  <si>
+    <t>Cho vay để ký quỹ đối với người lao động đi làm việc tại Hàn Quốc</t>
+  </si>
+  <si>
+    <t>Cho vay trả lương ngừng việc theo QĐ15</t>
+  </si>
+  <si>
+    <t>Cho vay hỗ trợ người sử dụng lao động vay vốn trả lương theo QĐ 23/2021/QĐ-TTg</t>
+  </si>
+  <si>
+    <t>XD00085</t>
+  </si>
+  <si>
+    <t>XD00086</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -887,6 +637,16 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="163"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1007,7 +767,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1084,14 +844,32 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1112,18 +890,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1439,462 +1205,462 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J187"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:J168"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="6.44140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="17" style="1" customWidth="1"/>
-    <col min="3" max="3" width="80.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="80.109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="2" customWidth="1"/>
-    <col min="8" max="257" width="9.140625" style="2"/>
-    <col min="258" max="258" width="6.42578125" style="2" customWidth="1"/>
-    <col min="259" max="259" width="80.140625" style="2" customWidth="1"/>
-    <col min="260" max="260" width="15.7109375" style="2" customWidth="1"/>
-    <col min="261" max="263" width="14.28515625" style="2" customWidth="1"/>
-    <col min="264" max="513" width="9.140625" style="2"/>
-    <col min="514" max="514" width="6.42578125" style="2" customWidth="1"/>
-    <col min="515" max="515" width="80.140625" style="2" customWidth="1"/>
-    <col min="516" max="516" width="15.7109375" style="2" customWidth="1"/>
-    <col min="517" max="519" width="14.28515625" style="2" customWidth="1"/>
-    <col min="520" max="769" width="9.140625" style="2"/>
-    <col min="770" max="770" width="6.42578125" style="2" customWidth="1"/>
-    <col min="771" max="771" width="80.140625" style="2" customWidth="1"/>
-    <col min="772" max="772" width="15.7109375" style="2" customWidth="1"/>
-    <col min="773" max="775" width="14.28515625" style="2" customWidth="1"/>
-    <col min="776" max="1025" width="9.140625" style="2"/>
-    <col min="1026" max="1026" width="6.42578125" style="2" customWidth="1"/>
-    <col min="1027" max="1027" width="80.140625" style="2" customWidth="1"/>
-    <col min="1028" max="1028" width="15.7109375" style="2" customWidth="1"/>
-    <col min="1029" max="1031" width="14.28515625" style="2" customWidth="1"/>
-    <col min="1032" max="1281" width="9.140625" style="2"/>
-    <col min="1282" max="1282" width="6.42578125" style="2" customWidth="1"/>
-    <col min="1283" max="1283" width="80.140625" style="2" customWidth="1"/>
-    <col min="1284" max="1284" width="15.7109375" style="2" customWidth="1"/>
-    <col min="1285" max="1287" width="14.28515625" style="2" customWidth="1"/>
-    <col min="1288" max="1537" width="9.140625" style="2"/>
-    <col min="1538" max="1538" width="6.42578125" style="2" customWidth="1"/>
-    <col min="1539" max="1539" width="80.140625" style="2" customWidth="1"/>
-    <col min="1540" max="1540" width="15.7109375" style="2" customWidth="1"/>
-    <col min="1541" max="1543" width="14.28515625" style="2" customWidth="1"/>
-    <col min="1544" max="1793" width="9.140625" style="2"/>
-    <col min="1794" max="1794" width="6.42578125" style="2" customWidth="1"/>
-    <col min="1795" max="1795" width="80.140625" style="2" customWidth="1"/>
-    <col min="1796" max="1796" width="15.7109375" style="2" customWidth="1"/>
-    <col min="1797" max="1799" width="14.28515625" style="2" customWidth="1"/>
-    <col min="1800" max="2049" width="9.140625" style="2"/>
-    <col min="2050" max="2050" width="6.42578125" style="2" customWidth="1"/>
-    <col min="2051" max="2051" width="80.140625" style="2" customWidth="1"/>
-    <col min="2052" max="2052" width="15.7109375" style="2" customWidth="1"/>
-    <col min="2053" max="2055" width="14.28515625" style="2" customWidth="1"/>
-    <col min="2056" max="2305" width="9.140625" style="2"/>
-    <col min="2306" max="2306" width="6.42578125" style="2" customWidth="1"/>
-    <col min="2307" max="2307" width="80.140625" style="2" customWidth="1"/>
-    <col min="2308" max="2308" width="15.7109375" style="2" customWidth="1"/>
-    <col min="2309" max="2311" width="14.28515625" style="2" customWidth="1"/>
-    <col min="2312" max="2561" width="9.140625" style="2"/>
-    <col min="2562" max="2562" width="6.42578125" style="2" customWidth="1"/>
-    <col min="2563" max="2563" width="80.140625" style="2" customWidth="1"/>
-    <col min="2564" max="2564" width="15.7109375" style="2" customWidth="1"/>
-    <col min="2565" max="2567" width="14.28515625" style="2" customWidth="1"/>
-    <col min="2568" max="2817" width="9.140625" style="2"/>
-    <col min="2818" max="2818" width="6.42578125" style="2" customWidth="1"/>
-    <col min="2819" max="2819" width="80.140625" style="2" customWidth="1"/>
-    <col min="2820" max="2820" width="15.7109375" style="2" customWidth="1"/>
-    <col min="2821" max="2823" width="14.28515625" style="2" customWidth="1"/>
-    <col min="2824" max="3073" width="9.140625" style="2"/>
-    <col min="3074" max="3074" width="6.42578125" style="2" customWidth="1"/>
-    <col min="3075" max="3075" width="80.140625" style="2" customWidth="1"/>
-    <col min="3076" max="3076" width="15.7109375" style="2" customWidth="1"/>
-    <col min="3077" max="3079" width="14.28515625" style="2" customWidth="1"/>
-    <col min="3080" max="3329" width="9.140625" style="2"/>
-    <col min="3330" max="3330" width="6.42578125" style="2" customWidth="1"/>
-    <col min="3331" max="3331" width="80.140625" style="2" customWidth="1"/>
-    <col min="3332" max="3332" width="15.7109375" style="2" customWidth="1"/>
-    <col min="3333" max="3335" width="14.28515625" style="2" customWidth="1"/>
-    <col min="3336" max="3585" width="9.140625" style="2"/>
-    <col min="3586" max="3586" width="6.42578125" style="2" customWidth="1"/>
-    <col min="3587" max="3587" width="80.140625" style="2" customWidth="1"/>
-    <col min="3588" max="3588" width="15.7109375" style="2" customWidth="1"/>
-    <col min="3589" max="3591" width="14.28515625" style="2" customWidth="1"/>
-    <col min="3592" max="3841" width="9.140625" style="2"/>
-    <col min="3842" max="3842" width="6.42578125" style="2" customWidth="1"/>
-    <col min="3843" max="3843" width="80.140625" style="2" customWidth="1"/>
-    <col min="3844" max="3844" width="15.7109375" style="2" customWidth="1"/>
-    <col min="3845" max="3847" width="14.28515625" style="2" customWidth="1"/>
-    <col min="3848" max="4097" width="9.140625" style="2"/>
-    <col min="4098" max="4098" width="6.42578125" style="2" customWidth="1"/>
-    <col min="4099" max="4099" width="80.140625" style="2" customWidth="1"/>
-    <col min="4100" max="4100" width="15.7109375" style="2" customWidth="1"/>
-    <col min="4101" max="4103" width="14.28515625" style="2" customWidth="1"/>
-    <col min="4104" max="4353" width="9.140625" style="2"/>
-    <col min="4354" max="4354" width="6.42578125" style="2" customWidth="1"/>
-    <col min="4355" max="4355" width="80.140625" style="2" customWidth="1"/>
-    <col min="4356" max="4356" width="15.7109375" style="2" customWidth="1"/>
-    <col min="4357" max="4359" width="14.28515625" style="2" customWidth="1"/>
-    <col min="4360" max="4609" width="9.140625" style="2"/>
-    <col min="4610" max="4610" width="6.42578125" style="2" customWidth="1"/>
-    <col min="4611" max="4611" width="80.140625" style="2" customWidth="1"/>
-    <col min="4612" max="4612" width="15.7109375" style="2" customWidth="1"/>
-    <col min="4613" max="4615" width="14.28515625" style="2" customWidth="1"/>
-    <col min="4616" max="4865" width="9.140625" style="2"/>
-    <col min="4866" max="4866" width="6.42578125" style="2" customWidth="1"/>
-    <col min="4867" max="4867" width="80.140625" style="2" customWidth="1"/>
-    <col min="4868" max="4868" width="15.7109375" style="2" customWidth="1"/>
-    <col min="4869" max="4871" width="14.28515625" style="2" customWidth="1"/>
-    <col min="4872" max="5121" width="9.140625" style="2"/>
-    <col min="5122" max="5122" width="6.42578125" style="2" customWidth="1"/>
-    <col min="5123" max="5123" width="80.140625" style="2" customWidth="1"/>
-    <col min="5124" max="5124" width="15.7109375" style="2" customWidth="1"/>
-    <col min="5125" max="5127" width="14.28515625" style="2" customWidth="1"/>
-    <col min="5128" max="5377" width="9.140625" style="2"/>
-    <col min="5378" max="5378" width="6.42578125" style="2" customWidth="1"/>
-    <col min="5379" max="5379" width="80.140625" style="2" customWidth="1"/>
-    <col min="5380" max="5380" width="15.7109375" style="2" customWidth="1"/>
-    <col min="5381" max="5383" width="14.28515625" style="2" customWidth="1"/>
-    <col min="5384" max="5633" width="9.140625" style="2"/>
-    <col min="5634" max="5634" width="6.42578125" style="2" customWidth="1"/>
-    <col min="5635" max="5635" width="80.140625" style="2" customWidth="1"/>
-    <col min="5636" max="5636" width="15.7109375" style="2" customWidth="1"/>
-    <col min="5637" max="5639" width="14.28515625" style="2" customWidth="1"/>
-    <col min="5640" max="5889" width="9.140625" style="2"/>
-    <col min="5890" max="5890" width="6.42578125" style="2" customWidth="1"/>
-    <col min="5891" max="5891" width="80.140625" style="2" customWidth="1"/>
-    <col min="5892" max="5892" width="15.7109375" style="2" customWidth="1"/>
-    <col min="5893" max="5895" width="14.28515625" style="2" customWidth="1"/>
-    <col min="5896" max="6145" width="9.140625" style="2"/>
-    <col min="6146" max="6146" width="6.42578125" style="2" customWidth="1"/>
-    <col min="6147" max="6147" width="80.140625" style="2" customWidth="1"/>
-    <col min="6148" max="6148" width="15.7109375" style="2" customWidth="1"/>
-    <col min="6149" max="6151" width="14.28515625" style="2" customWidth="1"/>
-    <col min="6152" max="6401" width="9.140625" style="2"/>
-    <col min="6402" max="6402" width="6.42578125" style="2" customWidth="1"/>
-    <col min="6403" max="6403" width="80.140625" style="2" customWidth="1"/>
-    <col min="6404" max="6404" width="15.7109375" style="2" customWidth="1"/>
-    <col min="6405" max="6407" width="14.28515625" style="2" customWidth="1"/>
-    <col min="6408" max="6657" width="9.140625" style="2"/>
-    <col min="6658" max="6658" width="6.42578125" style="2" customWidth="1"/>
-    <col min="6659" max="6659" width="80.140625" style="2" customWidth="1"/>
-    <col min="6660" max="6660" width="15.7109375" style="2" customWidth="1"/>
-    <col min="6661" max="6663" width="14.28515625" style="2" customWidth="1"/>
-    <col min="6664" max="6913" width="9.140625" style="2"/>
-    <col min="6914" max="6914" width="6.42578125" style="2" customWidth="1"/>
-    <col min="6915" max="6915" width="80.140625" style="2" customWidth="1"/>
-    <col min="6916" max="6916" width="15.7109375" style="2" customWidth="1"/>
-    <col min="6917" max="6919" width="14.28515625" style="2" customWidth="1"/>
-    <col min="6920" max="7169" width="9.140625" style="2"/>
-    <col min="7170" max="7170" width="6.42578125" style="2" customWidth="1"/>
-    <col min="7171" max="7171" width="80.140625" style="2" customWidth="1"/>
-    <col min="7172" max="7172" width="15.7109375" style="2" customWidth="1"/>
-    <col min="7173" max="7175" width="14.28515625" style="2" customWidth="1"/>
-    <col min="7176" max="7425" width="9.140625" style="2"/>
-    <col min="7426" max="7426" width="6.42578125" style="2" customWidth="1"/>
-    <col min="7427" max="7427" width="80.140625" style="2" customWidth="1"/>
-    <col min="7428" max="7428" width="15.7109375" style="2" customWidth="1"/>
-    <col min="7429" max="7431" width="14.28515625" style="2" customWidth="1"/>
-    <col min="7432" max="7681" width="9.140625" style="2"/>
-    <col min="7682" max="7682" width="6.42578125" style="2" customWidth="1"/>
-    <col min="7683" max="7683" width="80.140625" style="2" customWidth="1"/>
-    <col min="7684" max="7684" width="15.7109375" style="2" customWidth="1"/>
-    <col min="7685" max="7687" width="14.28515625" style="2" customWidth="1"/>
-    <col min="7688" max="7937" width="9.140625" style="2"/>
-    <col min="7938" max="7938" width="6.42578125" style="2" customWidth="1"/>
-    <col min="7939" max="7939" width="80.140625" style="2" customWidth="1"/>
-    <col min="7940" max="7940" width="15.7109375" style="2" customWidth="1"/>
-    <col min="7941" max="7943" width="14.28515625" style="2" customWidth="1"/>
-    <col min="7944" max="8193" width="9.140625" style="2"/>
-    <col min="8194" max="8194" width="6.42578125" style="2" customWidth="1"/>
-    <col min="8195" max="8195" width="80.140625" style="2" customWidth="1"/>
-    <col min="8196" max="8196" width="15.7109375" style="2" customWidth="1"/>
-    <col min="8197" max="8199" width="14.28515625" style="2" customWidth="1"/>
-    <col min="8200" max="8449" width="9.140625" style="2"/>
-    <col min="8450" max="8450" width="6.42578125" style="2" customWidth="1"/>
-    <col min="8451" max="8451" width="80.140625" style="2" customWidth="1"/>
-    <col min="8452" max="8452" width="15.7109375" style="2" customWidth="1"/>
-    <col min="8453" max="8455" width="14.28515625" style="2" customWidth="1"/>
-    <col min="8456" max="8705" width="9.140625" style="2"/>
-    <col min="8706" max="8706" width="6.42578125" style="2" customWidth="1"/>
-    <col min="8707" max="8707" width="80.140625" style="2" customWidth="1"/>
-    <col min="8708" max="8708" width="15.7109375" style="2" customWidth="1"/>
-    <col min="8709" max="8711" width="14.28515625" style="2" customWidth="1"/>
-    <col min="8712" max="8961" width="9.140625" style="2"/>
-    <col min="8962" max="8962" width="6.42578125" style="2" customWidth="1"/>
-    <col min="8963" max="8963" width="80.140625" style="2" customWidth="1"/>
-    <col min="8964" max="8964" width="15.7109375" style="2" customWidth="1"/>
-    <col min="8965" max="8967" width="14.28515625" style="2" customWidth="1"/>
-    <col min="8968" max="9217" width="9.140625" style="2"/>
-    <col min="9218" max="9218" width="6.42578125" style="2" customWidth="1"/>
-    <col min="9219" max="9219" width="80.140625" style="2" customWidth="1"/>
-    <col min="9220" max="9220" width="15.7109375" style="2" customWidth="1"/>
-    <col min="9221" max="9223" width="14.28515625" style="2" customWidth="1"/>
-    <col min="9224" max="9473" width="9.140625" style="2"/>
-    <col min="9474" max="9474" width="6.42578125" style="2" customWidth="1"/>
-    <col min="9475" max="9475" width="80.140625" style="2" customWidth="1"/>
-    <col min="9476" max="9476" width="15.7109375" style="2" customWidth="1"/>
-    <col min="9477" max="9479" width="14.28515625" style="2" customWidth="1"/>
-    <col min="9480" max="9729" width="9.140625" style="2"/>
-    <col min="9730" max="9730" width="6.42578125" style="2" customWidth="1"/>
-    <col min="9731" max="9731" width="80.140625" style="2" customWidth="1"/>
-    <col min="9732" max="9732" width="15.7109375" style="2" customWidth="1"/>
-    <col min="9733" max="9735" width="14.28515625" style="2" customWidth="1"/>
-    <col min="9736" max="9985" width="9.140625" style="2"/>
-    <col min="9986" max="9986" width="6.42578125" style="2" customWidth="1"/>
-    <col min="9987" max="9987" width="80.140625" style="2" customWidth="1"/>
-    <col min="9988" max="9988" width="15.7109375" style="2" customWidth="1"/>
-    <col min="9989" max="9991" width="14.28515625" style="2" customWidth="1"/>
-    <col min="9992" max="10241" width="9.140625" style="2"/>
-    <col min="10242" max="10242" width="6.42578125" style="2" customWidth="1"/>
-    <col min="10243" max="10243" width="80.140625" style="2" customWidth="1"/>
-    <col min="10244" max="10244" width="15.7109375" style="2" customWidth="1"/>
-    <col min="10245" max="10247" width="14.28515625" style="2" customWidth="1"/>
-    <col min="10248" max="10497" width="9.140625" style="2"/>
-    <col min="10498" max="10498" width="6.42578125" style="2" customWidth="1"/>
-    <col min="10499" max="10499" width="80.140625" style="2" customWidth="1"/>
-    <col min="10500" max="10500" width="15.7109375" style="2" customWidth="1"/>
-    <col min="10501" max="10503" width="14.28515625" style="2" customWidth="1"/>
-    <col min="10504" max="10753" width="9.140625" style="2"/>
-    <col min="10754" max="10754" width="6.42578125" style="2" customWidth="1"/>
-    <col min="10755" max="10755" width="80.140625" style="2" customWidth="1"/>
-    <col min="10756" max="10756" width="15.7109375" style="2" customWidth="1"/>
-    <col min="10757" max="10759" width="14.28515625" style="2" customWidth="1"/>
-    <col min="10760" max="11009" width="9.140625" style="2"/>
-    <col min="11010" max="11010" width="6.42578125" style="2" customWidth="1"/>
-    <col min="11011" max="11011" width="80.140625" style="2" customWidth="1"/>
-    <col min="11012" max="11012" width="15.7109375" style="2" customWidth="1"/>
-    <col min="11013" max="11015" width="14.28515625" style="2" customWidth="1"/>
-    <col min="11016" max="11265" width="9.140625" style="2"/>
-    <col min="11266" max="11266" width="6.42578125" style="2" customWidth="1"/>
-    <col min="11267" max="11267" width="80.140625" style="2" customWidth="1"/>
-    <col min="11268" max="11268" width="15.7109375" style="2" customWidth="1"/>
-    <col min="11269" max="11271" width="14.28515625" style="2" customWidth="1"/>
-    <col min="11272" max="11521" width="9.140625" style="2"/>
-    <col min="11522" max="11522" width="6.42578125" style="2" customWidth="1"/>
-    <col min="11523" max="11523" width="80.140625" style="2" customWidth="1"/>
-    <col min="11524" max="11524" width="15.7109375" style="2" customWidth="1"/>
-    <col min="11525" max="11527" width="14.28515625" style="2" customWidth="1"/>
-    <col min="11528" max="11777" width="9.140625" style="2"/>
-    <col min="11778" max="11778" width="6.42578125" style="2" customWidth="1"/>
-    <col min="11779" max="11779" width="80.140625" style="2" customWidth="1"/>
-    <col min="11780" max="11780" width="15.7109375" style="2" customWidth="1"/>
-    <col min="11781" max="11783" width="14.28515625" style="2" customWidth="1"/>
-    <col min="11784" max="12033" width="9.140625" style="2"/>
-    <col min="12034" max="12034" width="6.42578125" style="2" customWidth="1"/>
-    <col min="12035" max="12035" width="80.140625" style="2" customWidth="1"/>
-    <col min="12036" max="12036" width="15.7109375" style="2" customWidth="1"/>
-    <col min="12037" max="12039" width="14.28515625" style="2" customWidth="1"/>
-    <col min="12040" max="12289" width="9.140625" style="2"/>
-    <col min="12290" max="12290" width="6.42578125" style="2" customWidth="1"/>
-    <col min="12291" max="12291" width="80.140625" style="2" customWidth="1"/>
-    <col min="12292" max="12292" width="15.7109375" style="2" customWidth="1"/>
-    <col min="12293" max="12295" width="14.28515625" style="2" customWidth="1"/>
-    <col min="12296" max="12545" width="9.140625" style="2"/>
-    <col min="12546" max="12546" width="6.42578125" style="2" customWidth="1"/>
-    <col min="12547" max="12547" width="80.140625" style="2" customWidth="1"/>
-    <col min="12548" max="12548" width="15.7109375" style="2" customWidth="1"/>
-    <col min="12549" max="12551" width="14.28515625" style="2" customWidth="1"/>
-    <col min="12552" max="12801" width="9.140625" style="2"/>
-    <col min="12802" max="12802" width="6.42578125" style="2" customWidth="1"/>
-    <col min="12803" max="12803" width="80.140625" style="2" customWidth="1"/>
-    <col min="12804" max="12804" width="15.7109375" style="2" customWidth="1"/>
-    <col min="12805" max="12807" width="14.28515625" style="2" customWidth="1"/>
-    <col min="12808" max="13057" width="9.140625" style="2"/>
-    <col min="13058" max="13058" width="6.42578125" style="2" customWidth="1"/>
-    <col min="13059" max="13059" width="80.140625" style="2" customWidth="1"/>
-    <col min="13060" max="13060" width="15.7109375" style="2" customWidth="1"/>
-    <col min="13061" max="13063" width="14.28515625" style="2" customWidth="1"/>
-    <col min="13064" max="13313" width="9.140625" style="2"/>
-    <col min="13314" max="13314" width="6.42578125" style="2" customWidth="1"/>
-    <col min="13315" max="13315" width="80.140625" style="2" customWidth="1"/>
-    <col min="13316" max="13316" width="15.7109375" style="2" customWidth="1"/>
-    <col min="13317" max="13319" width="14.28515625" style="2" customWidth="1"/>
-    <col min="13320" max="13569" width="9.140625" style="2"/>
-    <col min="13570" max="13570" width="6.42578125" style="2" customWidth="1"/>
-    <col min="13571" max="13571" width="80.140625" style="2" customWidth="1"/>
-    <col min="13572" max="13572" width="15.7109375" style="2" customWidth="1"/>
-    <col min="13573" max="13575" width="14.28515625" style="2" customWidth="1"/>
-    <col min="13576" max="13825" width="9.140625" style="2"/>
-    <col min="13826" max="13826" width="6.42578125" style="2" customWidth="1"/>
-    <col min="13827" max="13827" width="80.140625" style="2" customWidth="1"/>
-    <col min="13828" max="13828" width="15.7109375" style="2" customWidth="1"/>
-    <col min="13829" max="13831" width="14.28515625" style="2" customWidth="1"/>
-    <col min="13832" max="14081" width="9.140625" style="2"/>
-    <col min="14082" max="14082" width="6.42578125" style="2" customWidth="1"/>
-    <col min="14083" max="14083" width="80.140625" style="2" customWidth="1"/>
-    <col min="14084" max="14084" width="15.7109375" style="2" customWidth="1"/>
-    <col min="14085" max="14087" width="14.28515625" style="2" customWidth="1"/>
-    <col min="14088" max="14337" width="9.140625" style="2"/>
-    <col min="14338" max="14338" width="6.42578125" style="2" customWidth="1"/>
-    <col min="14339" max="14339" width="80.140625" style="2" customWidth="1"/>
-    <col min="14340" max="14340" width="15.7109375" style="2" customWidth="1"/>
-    <col min="14341" max="14343" width="14.28515625" style="2" customWidth="1"/>
-    <col min="14344" max="14593" width="9.140625" style="2"/>
-    <col min="14594" max="14594" width="6.42578125" style="2" customWidth="1"/>
-    <col min="14595" max="14595" width="80.140625" style="2" customWidth="1"/>
-    <col min="14596" max="14596" width="15.7109375" style="2" customWidth="1"/>
-    <col min="14597" max="14599" width="14.28515625" style="2" customWidth="1"/>
-    <col min="14600" max="14849" width="9.140625" style="2"/>
-    <col min="14850" max="14850" width="6.42578125" style="2" customWidth="1"/>
-    <col min="14851" max="14851" width="80.140625" style="2" customWidth="1"/>
-    <col min="14852" max="14852" width="15.7109375" style="2" customWidth="1"/>
-    <col min="14853" max="14855" width="14.28515625" style="2" customWidth="1"/>
-    <col min="14856" max="15105" width="9.140625" style="2"/>
-    <col min="15106" max="15106" width="6.42578125" style="2" customWidth="1"/>
-    <col min="15107" max="15107" width="80.140625" style="2" customWidth="1"/>
-    <col min="15108" max="15108" width="15.7109375" style="2" customWidth="1"/>
-    <col min="15109" max="15111" width="14.28515625" style="2" customWidth="1"/>
-    <col min="15112" max="15361" width="9.140625" style="2"/>
-    <col min="15362" max="15362" width="6.42578125" style="2" customWidth="1"/>
-    <col min="15363" max="15363" width="80.140625" style="2" customWidth="1"/>
-    <col min="15364" max="15364" width="15.7109375" style="2" customWidth="1"/>
-    <col min="15365" max="15367" width="14.28515625" style="2" customWidth="1"/>
-    <col min="15368" max="15617" width="9.140625" style="2"/>
-    <col min="15618" max="15618" width="6.42578125" style="2" customWidth="1"/>
-    <col min="15619" max="15619" width="80.140625" style="2" customWidth="1"/>
-    <col min="15620" max="15620" width="15.7109375" style="2" customWidth="1"/>
-    <col min="15621" max="15623" width="14.28515625" style="2" customWidth="1"/>
-    <col min="15624" max="15873" width="9.140625" style="2"/>
-    <col min="15874" max="15874" width="6.42578125" style="2" customWidth="1"/>
-    <col min="15875" max="15875" width="80.140625" style="2" customWidth="1"/>
-    <col min="15876" max="15876" width="15.7109375" style="2" customWidth="1"/>
-    <col min="15877" max="15879" width="14.28515625" style="2" customWidth="1"/>
-    <col min="15880" max="16129" width="9.140625" style="2"/>
-    <col min="16130" max="16130" width="6.42578125" style="2" customWidth="1"/>
-    <col min="16131" max="16131" width="80.140625" style="2" customWidth="1"/>
-    <col min="16132" max="16132" width="15.7109375" style="2" customWidth="1"/>
-    <col min="16133" max="16135" width="14.28515625" style="2" customWidth="1"/>
-    <col min="16136" max="16384" width="9.140625" style="2"/>
+    <col min="5" max="5" width="17.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" style="2" customWidth="1"/>
+    <col min="8" max="257" width="9.109375" style="2"/>
+    <col min="258" max="258" width="6.44140625" style="2" customWidth="1"/>
+    <col min="259" max="259" width="80.109375" style="2" customWidth="1"/>
+    <col min="260" max="260" width="15.6640625" style="2" customWidth="1"/>
+    <col min="261" max="263" width="14.33203125" style="2" customWidth="1"/>
+    <col min="264" max="513" width="9.109375" style="2"/>
+    <col min="514" max="514" width="6.44140625" style="2" customWidth="1"/>
+    <col min="515" max="515" width="80.109375" style="2" customWidth="1"/>
+    <col min="516" max="516" width="15.6640625" style="2" customWidth="1"/>
+    <col min="517" max="519" width="14.33203125" style="2" customWidth="1"/>
+    <col min="520" max="769" width="9.109375" style="2"/>
+    <col min="770" max="770" width="6.44140625" style="2" customWidth="1"/>
+    <col min="771" max="771" width="80.109375" style="2" customWidth="1"/>
+    <col min="772" max="772" width="15.6640625" style="2" customWidth="1"/>
+    <col min="773" max="775" width="14.33203125" style="2" customWidth="1"/>
+    <col min="776" max="1025" width="9.109375" style="2"/>
+    <col min="1026" max="1026" width="6.44140625" style="2" customWidth="1"/>
+    <col min="1027" max="1027" width="80.109375" style="2" customWidth="1"/>
+    <col min="1028" max="1028" width="15.6640625" style="2" customWidth="1"/>
+    <col min="1029" max="1031" width="14.33203125" style="2" customWidth="1"/>
+    <col min="1032" max="1281" width="9.109375" style="2"/>
+    <col min="1282" max="1282" width="6.44140625" style="2" customWidth="1"/>
+    <col min="1283" max="1283" width="80.109375" style="2" customWidth="1"/>
+    <col min="1284" max="1284" width="15.6640625" style="2" customWidth="1"/>
+    <col min="1285" max="1287" width="14.33203125" style="2" customWidth="1"/>
+    <col min="1288" max="1537" width="9.109375" style="2"/>
+    <col min="1538" max="1538" width="6.44140625" style="2" customWidth="1"/>
+    <col min="1539" max="1539" width="80.109375" style="2" customWidth="1"/>
+    <col min="1540" max="1540" width="15.6640625" style="2" customWidth="1"/>
+    <col min="1541" max="1543" width="14.33203125" style="2" customWidth="1"/>
+    <col min="1544" max="1793" width="9.109375" style="2"/>
+    <col min="1794" max="1794" width="6.44140625" style="2" customWidth="1"/>
+    <col min="1795" max="1795" width="80.109375" style="2" customWidth="1"/>
+    <col min="1796" max="1796" width="15.6640625" style="2" customWidth="1"/>
+    <col min="1797" max="1799" width="14.33203125" style="2" customWidth="1"/>
+    <col min="1800" max="2049" width="9.109375" style="2"/>
+    <col min="2050" max="2050" width="6.44140625" style="2" customWidth="1"/>
+    <col min="2051" max="2051" width="80.109375" style="2" customWidth="1"/>
+    <col min="2052" max="2052" width="15.6640625" style="2" customWidth="1"/>
+    <col min="2053" max="2055" width="14.33203125" style="2" customWidth="1"/>
+    <col min="2056" max="2305" width="9.109375" style="2"/>
+    <col min="2306" max="2306" width="6.44140625" style="2" customWidth="1"/>
+    <col min="2307" max="2307" width="80.109375" style="2" customWidth="1"/>
+    <col min="2308" max="2308" width="15.6640625" style="2" customWidth="1"/>
+    <col min="2309" max="2311" width="14.33203125" style="2" customWidth="1"/>
+    <col min="2312" max="2561" width="9.109375" style="2"/>
+    <col min="2562" max="2562" width="6.44140625" style="2" customWidth="1"/>
+    <col min="2563" max="2563" width="80.109375" style="2" customWidth="1"/>
+    <col min="2564" max="2564" width="15.6640625" style="2" customWidth="1"/>
+    <col min="2565" max="2567" width="14.33203125" style="2" customWidth="1"/>
+    <col min="2568" max="2817" width="9.109375" style="2"/>
+    <col min="2818" max="2818" width="6.44140625" style="2" customWidth="1"/>
+    <col min="2819" max="2819" width="80.109375" style="2" customWidth="1"/>
+    <col min="2820" max="2820" width="15.6640625" style="2" customWidth="1"/>
+    <col min="2821" max="2823" width="14.33203125" style="2" customWidth="1"/>
+    <col min="2824" max="3073" width="9.109375" style="2"/>
+    <col min="3074" max="3074" width="6.44140625" style="2" customWidth="1"/>
+    <col min="3075" max="3075" width="80.109375" style="2" customWidth="1"/>
+    <col min="3076" max="3076" width="15.6640625" style="2" customWidth="1"/>
+    <col min="3077" max="3079" width="14.33203125" style="2" customWidth="1"/>
+    <col min="3080" max="3329" width="9.109375" style="2"/>
+    <col min="3330" max="3330" width="6.44140625" style="2" customWidth="1"/>
+    <col min="3331" max="3331" width="80.109375" style="2" customWidth="1"/>
+    <col min="3332" max="3332" width="15.6640625" style="2" customWidth="1"/>
+    <col min="3333" max="3335" width="14.33203125" style="2" customWidth="1"/>
+    <col min="3336" max="3585" width="9.109375" style="2"/>
+    <col min="3586" max="3586" width="6.44140625" style="2" customWidth="1"/>
+    <col min="3587" max="3587" width="80.109375" style="2" customWidth="1"/>
+    <col min="3588" max="3588" width="15.6640625" style="2" customWidth="1"/>
+    <col min="3589" max="3591" width="14.33203125" style="2" customWidth="1"/>
+    <col min="3592" max="3841" width="9.109375" style="2"/>
+    <col min="3842" max="3842" width="6.44140625" style="2" customWidth="1"/>
+    <col min="3843" max="3843" width="80.109375" style="2" customWidth="1"/>
+    <col min="3844" max="3844" width="15.6640625" style="2" customWidth="1"/>
+    <col min="3845" max="3847" width="14.33203125" style="2" customWidth="1"/>
+    <col min="3848" max="4097" width="9.109375" style="2"/>
+    <col min="4098" max="4098" width="6.44140625" style="2" customWidth="1"/>
+    <col min="4099" max="4099" width="80.109375" style="2" customWidth="1"/>
+    <col min="4100" max="4100" width="15.6640625" style="2" customWidth="1"/>
+    <col min="4101" max="4103" width="14.33203125" style="2" customWidth="1"/>
+    <col min="4104" max="4353" width="9.109375" style="2"/>
+    <col min="4354" max="4354" width="6.44140625" style="2" customWidth="1"/>
+    <col min="4355" max="4355" width="80.109375" style="2" customWidth="1"/>
+    <col min="4356" max="4356" width="15.6640625" style="2" customWidth="1"/>
+    <col min="4357" max="4359" width="14.33203125" style="2" customWidth="1"/>
+    <col min="4360" max="4609" width="9.109375" style="2"/>
+    <col min="4610" max="4610" width="6.44140625" style="2" customWidth="1"/>
+    <col min="4611" max="4611" width="80.109375" style="2" customWidth="1"/>
+    <col min="4612" max="4612" width="15.6640625" style="2" customWidth="1"/>
+    <col min="4613" max="4615" width="14.33203125" style="2" customWidth="1"/>
+    <col min="4616" max="4865" width="9.109375" style="2"/>
+    <col min="4866" max="4866" width="6.44140625" style="2" customWidth="1"/>
+    <col min="4867" max="4867" width="80.109375" style="2" customWidth="1"/>
+    <col min="4868" max="4868" width="15.6640625" style="2" customWidth="1"/>
+    <col min="4869" max="4871" width="14.33203125" style="2" customWidth="1"/>
+    <col min="4872" max="5121" width="9.109375" style="2"/>
+    <col min="5122" max="5122" width="6.44140625" style="2" customWidth="1"/>
+    <col min="5123" max="5123" width="80.109375" style="2" customWidth="1"/>
+    <col min="5124" max="5124" width="15.6640625" style="2" customWidth="1"/>
+    <col min="5125" max="5127" width="14.33203125" style="2" customWidth="1"/>
+    <col min="5128" max="5377" width="9.109375" style="2"/>
+    <col min="5378" max="5378" width="6.44140625" style="2" customWidth="1"/>
+    <col min="5379" max="5379" width="80.109375" style="2" customWidth="1"/>
+    <col min="5380" max="5380" width="15.6640625" style="2" customWidth="1"/>
+    <col min="5381" max="5383" width="14.33203125" style="2" customWidth="1"/>
+    <col min="5384" max="5633" width="9.109375" style="2"/>
+    <col min="5634" max="5634" width="6.44140625" style="2" customWidth="1"/>
+    <col min="5635" max="5635" width="80.109375" style="2" customWidth="1"/>
+    <col min="5636" max="5636" width="15.6640625" style="2" customWidth="1"/>
+    <col min="5637" max="5639" width="14.33203125" style="2" customWidth="1"/>
+    <col min="5640" max="5889" width="9.109375" style="2"/>
+    <col min="5890" max="5890" width="6.44140625" style="2" customWidth="1"/>
+    <col min="5891" max="5891" width="80.109375" style="2" customWidth="1"/>
+    <col min="5892" max="5892" width="15.6640625" style="2" customWidth="1"/>
+    <col min="5893" max="5895" width="14.33203125" style="2" customWidth="1"/>
+    <col min="5896" max="6145" width="9.109375" style="2"/>
+    <col min="6146" max="6146" width="6.44140625" style="2" customWidth="1"/>
+    <col min="6147" max="6147" width="80.109375" style="2" customWidth="1"/>
+    <col min="6148" max="6148" width="15.6640625" style="2" customWidth="1"/>
+    <col min="6149" max="6151" width="14.33203125" style="2" customWidth="1"/>
+    <col min="6152" max="6401" width="9.109375" style="2"/>
+    <col min="6402" max="6402" width="6.44140625" style="2" customWidth="1"/>
+    <col min="6403" max="6403" width="80.109375" style="2" customWidth="1"/>
+    <col min="6404" max="6404" width="15.6640625" style="2" customWidth="1"/>
+    <col min="6405" max="6407" width="14.33203125" style="2" customWidth="1"/>
+    <col min="6408" max="6657" width="9.109375" style="2"/>
+    <col min="6658" max="6658" width="6.44140625" style="2" customWidth="1"/>
+    <col min="6659" max="6659" width="80.109375" style="2" customWidth="1"/>
+    <col min="6660" max="6660" width="15.6640625" style="2" customWidth="1"/>
+    <col min="6661" max="6663" width="14.33203125" style="2" customWidth="1"/>
+    <col min="6664" max="6913" width="9.109375" style="2"/>
+    <col min="6914" max="6914" width="6.44140625" style="2" customWidth="1"/>
+    <col min="6915" max="6915" width="80.109375" style="2" customWidth="1"/>
+    <col min="6916" max="6916" width="15.6640625" style="2" customWidth="1"/>
+    <col min="6917" max="6919" width="14.33203125" style="2" customWidth="1"/>
+    <col min="6920" max="7169" width="9.109375" style="2"/>
+    <col min="7170" max="7170" width="6.44140625" style="2" customWidth="1"/>
+    <col min="7171" max="7171" width="80.109375" style="2" customWidth="1"/>
+    <col min="7172" max="7172" width="15.6640625" style="2" customWidth="1"/>
+    <col min="7173" max="7175" width="14.33203125" style="2" customWidth="1"/>
+    <col min="7176" max="7425" width="9.109375" style="2"/>
+    <col min="7426" max="7426" width="6.44140625" style="2" customWidth="1"/>
+    <col min="7427" max="7427" width="80.109375" style="2" customWidth="1"/>
+    <col min="7428" max="7428" width="15.6640625" style="2" customWidth="1"/>
+    <col min="7429" max="7431" width="14.33203125" style="2" customWidth="1"/>
+    <col min="7432" max="7681" width="9.109375" style="2"/>
+    <col min="7682" max="7682" width="6.44140625" style="2" customWidth="1"/>
+    <col min="7683" max="7683" width="80.109375" style="2" customWidth="1"/>
+    <col min="7684" max="7684" width="15.6640625" style="2" customWidth="1"/>
+    <col min="7685" max="7687" width="14.33203125" style="2" customWidth="1"/>
+    <col min="7688" max="7937" width="9.109375" style="2"/>
+    <col min="7938" max="7938" width="6.44140625" style="2" customWidth="1"/>
+    <col min="7939" max="7939" width="80.109375" style="2" customWidth="1"/>
+    <col min="7940" max="7940" width="15.6640625" style="2" customWidth="1"/>
+    <col min="7941" max="7943" width="14.33203125" style="2" customWidth="1"/>
+    <col min="7944" max="8193" width="9.109375" style="2"/>
+    <col min="8194" max="8194" width="6.44140625" style="2" customWidth="1"/>
+    <col min="8195" max="8195" width="80.109375" style="2" customWidth="1"/>
+    <col min="8196" max="8196" width="15.6640625" style="2" customWidth="1"/>
+    <col min="8197" max="8199" width="14.33203125" style="2" customWidth="1"/>
+    <col min="8200" max="8449" width="9.109375" style="2"/>
+    <col min="8450" max="8450" width="6.44140625" style="2" customWidth="1"/>
+    <col min="8451" max="8451" width="80.109375" style="2" customWidth="1"/>
+    <col min="8452" max="8452" width="15.6640625" style="2" customWidth="1"/>
+    <col min="8453" max="8455" width="14.33203125" style="2" customWidth="1"/>
+    <col min="8456" max="8705" width="9.109375" style="2"/>
+    <col min="8706" max="8706" width="6.44140625" style="2" customWidth="1"/>
+    <col min="8707" max="8707" width="80.109375" style="2" customWidth="1"/>
+    <col min="8708" max="8708" width="15.6640625" style="2" customWidth="1"/>
+    <col min="8709" max="8711" width="14.33203125" style="2" customWidth="1"/>
+    <col min="8712" max="8961" width="9.109375" style="2"/>
+    <col min="8962" max="8962" width="6.44140625" style="2" customWidth="1"/>
+    <col min="8963" max="8963" width="80.109375" style="2" customWidth="1"/>
+    <col min="8964" max="8964" width="15.6640625" style="2" customWidth="1"/>
+    <col min="8965" max="8967" width="14.33203125" style="2" customWidth="1"/>
+    <col min="8968" max="9217" width="9.109375" style="2"/>
+    <col min="9218" max="9218" width="6.44140625" style="2" customWidth="1"/>
+    <col min="9219" max="9219" width="80.109375" style="2" customWidth="1"/>
+    <col min="9220" max="9220" width="15.6640625" style="2" customWidth="1"/>
+    <col min="9221" max="9223" width="14.33203125" style="2" customWidth="1"/>
+    <col min="9224" max="9473" width="9.109375" style="2"/>
+    <col min="9474" max="9474" width="6.44140625" style="2" customWidth="1"/>
+    <col min="9475" max="9475" width="80.109375" style="2" customWidth="1"/>
+    <col min="9476" max="9476" width="15.6640625" style="2" customWidth="1"/>
+    <col min="9477" max="9479" width="14.33203125" style="2" customWidth="1"/>
+    <col min="9480" max="9729" width="9.109375" style="2"/>
+    <col min="9730" max="9730" width="6.44140625" style="2" customWidth="1"/>
+    <col min="9731" max="9731" width="80.109375" style="2" customWidth="1"/>
+    <col min="9732" max="9732" width="15.6640625" style="2" customWidth="1"/>
+    <col min="9733" max="9735" width="14.33203125" style="2" customWidth="1"/>
+    <col min="9736" max="9985" width="9.109375" style="2"/>
+    <col min="9986" max="9986" width="6.44140625" style="2" customWidth="1"/>
+    <col min="9987" max="9987" width="80.109375" style="2" customWidth="1"/>
+    <col min="9988" max="9988" width="15.6640625" style="2" customWidth="1"/>
+    <col min="9989" max="9991" width="14.33203125" style="2" customWidth="1"/>
+    <col min="9992" max="10241" width="9.109375" style="2"/>
+    <col min="10242" max="10242" width="6.44140625" style="2" customWidth="1"/>
+    <col min="10243" max="10243" width="80.109375" style="2" customWidth="1"/>
+    <col min="10244" max="10244" width="15.6640625" style="2" customWidth="1"/>
+    <col min="10245" max="10247" width="14.33203125" style="2" customWidth="1"/>
+    <col min="10248" max="10497" width="9.109375" style="2"/>
+    <col min="10498" max="10498" width="6.44140625" style="2" customWidth="1"/>
+    <col min="10499" max="10499" width="80.109375" style="2" customWidth="1"/>
+    <col min="10500" max="10500" width="15.6640625" style="2" customWidth="1"/>
+    <col min="10501" max="10503" width="14.33203125" style="2" customWidth="1"/>
+    <col min="10504" max="10753" width="9.109375" style="2"/>
+    <col min="10754" max="10754" width="6.44140625" style="2" customWidth="1"/>
+    <col min="10755" max="10755" width="80.109375" style="2" customWidth="1"/>
+    <col min="10756" max="10756" width="15.6640625" style="2" customWidth="1"/>
+    <col min="10757" max="10759" width="14.33203125" style="2" customWidth="1"/>
+    <col min="10760" max="11009" width="9.109375" style="2"/>
+    <col min="11010" max="11010" width="6.44140625" style="2" customWidth="1"/>
+    <col min="11011" max="11011" width="80.109375" style="2" customWidth="1"/>
+    <col min="11012" max="11012" width="15.6640625" style="2" customWidth="1"/>
+    <col min="11013" max="11015" width="14.33203125" style="2" customWidth="1"/>
+    <col min="11016" max="11265" width="9.109375" style="2"/>
+    <col min="11266" max="11266" width="6.44140625" style="2" customWidth="1"/>
+    <col min="11267" max="11267" width="80.109375" style="2" customWidth="1"/>
+    <col min="11268" max="11268" width="15.6640625" style="2" customWidth="1"/>
+    <col min="11269" max="11271" width="14.33203125" style="2" customWidth="1"/>
+    <col min="11272" max="11521" width="9.109375" style="2"/>
+    <col min="11522" max="11522" width="6.44140625" style="2" customWidth="1"/>
+    <col min="11523" max="11523" width="80.109375" style="2" customWidth="1"/>
+    <col min="11524" max="11524" width="15.6640625" style="2" customWidth="1"/>
+    <col min="11525" max="11527" width="14.33203125" style="2" customWidth="1"/>
+    <col min="11528" max="11777" width="9.109375" style="2"/>
+    <col min="11778" max="11778" width="6.44140625" style="2" customWidth="1"/>
+    <col min="11779" max="11779" width="80.109375" style="2" customWidth="1"/>
+    <col min="11780" max="11780" width="15.6640625" style="2" customWidth="1"/>
+    <col min="11781" max="11783" width="14.33203125" style="2" customWidth="1"/>
+    <col min="11784" max="12033" width="9.109375" style="2"/>
+    <col min="12034" max="12034" width="6.44140625" style="2" customWidth="1"/>
+    <col min="12035" max="12035" width="80.109375" style="2" customWidth="1"/>
+    <col min="12036" max="12036" width="15.6640625" style="2" customWidth="1"/>
+    <col min="12037" max="12039" width="14.33203125" style="2" customWidth="1"/>
+    <col min="12040" max="12289" width="9.109375" style="2"/>
+    <col min="12290" max="12290" width="6.44140625" style="2" customWidth="1"/>
+    <col min="12291" max="12291" width="80.109375" style="2" customWidth="1"/>
+    <col min="12292" max="12292" width="15.6640625" style="2" customWidth="1"/>
+    <col min="12293" max="12295" width="14.33203125" style="2" customWidth="1"/>
+    <col min="12296" max="12545" width="9.109375" style="2"/>
+    <col min="12546" max="12546" width="6.44140625" style="2" customWidth="1"/>
+    <col min="12547" max="12547" width="80.109375" style="2" customWidth="1"/>
+    <col min="12548" max="12548" width="15.6640625" style="2" customWidth="1"/>
+    <col min="12549" max="12551" width="14.33203125" style="2" customWidth="1"/>
+    <col min="12552" max="12801" width="9.109375" style="2"/>
+    <col min="12802" max="12802" width="6.44140625" style="2" customWidth="1"/>
+    <col min="12803" max="12803" width="80.109375" style="2" customWidth="1"/>
+    <col min="12804" max="12804" width="15.6640625" style="2" customWidth="1"/>
+    <col min="12805" max="12807" width="14.33203125" style="2" customWidth="1"/>
+    <col min="12808" max="13057" width="9.109375" style="2"/>
+    <col min="13058" max="13058" width="6.44140625" style="2" customWidth="1"/>
+    <col min="13059" max="13059" width="80.109375" style="2" customWidth="1"/>
+    <col min="13060" max="13060" width="15.6640625" style="2" customWidth="1"/>
+    <col min="13061" max="13063" width="14.33203125" style="2" customWidth="1"/>
+    <col min="13064" max="13313" width="9.109375" style="2"/>
+    <col min="13314" max="13314" width="6.44140625" style="2" customWidth="1"/>
+    <col min="13315" max="13315" width="80.109375" style="2" customWidth="1"/>
+    <col min="13316" max="13316" width="15.6640625" style="2" customWidth="1"/>
+    <col min="13317" max="13319" width="14.33203125" style="2" customWidth="1"/>
+    <col min="13320" max="13569" width="9.109375" style="2"/>
+    <col min="13570" max="13570" width="6.44140625" style="2" customWidth="1"/>
+    <col min="13571" max="13571" width="80.109375" style="2" customWidth="1"/>
+    <col min="13572" max="13572" width="15.6640625" style="2" customWidth="1"/>
+    <col min="13573" max="13575" width="14.33203125" style="2" customWidth="1"/>
+    <col min="13576" max="13825" width="9.109375" style="2"/>
+    <col min="13826" max="13826" width="6.44140625" style="2" customWidth="1"/>
+    <col min="13827" max="13827" width="80.109375" style="2" customWidth="1"/>
+    <col min="13828" max="13828" width="15.6640625" style="2" customWidth="1"/>
+    <col min="13829" max="13831" width="14.33203125" style="2" customWidth="1"/>
+    <col min="13832" max="14081" width="9.109375" style="2"/>
+    <col min="14082" max="14082" width="6.44140625" style="2" customWidth="1"/>
+    <col min="14083" max="14083" width="80.109375" style="2" customWidth="1"/>
+    <col min="14084" max="14084" width="15.6640625" style="2" customWidth="1"/>
+    <col min="14085" max="14087" width="14.33203125" style="2" customWidth="1"/>
+    <col min="14088" max="14337" width="9.109375" style="2"/>
+    <col min="14338" max="14338" width="6.44140625" style="2" customWidth="1"/>
+    <col min="14339" max="14339" width="80.109375" style="2" customWidth="1"/>
+    <col min="14340" max="14340" width="15.6640625" style="2" customWidth="1"/>
+    <col min="14341" max="14343" width="14.33203125" style="2" customWidth="1"/>
+    <col min="14344" max="14593" width="9.109375" style="2"/>
+    <col min="14594" max="14594" width="6.44140625" style="2" customWidth="1"/>
+    <col min="14595" max="14595" width="80.109375" style="2" customWidth="1"/>
+    <col min="14596" max="14596" width="15.6640625" style="2" customWidth="1"/>
+    <col min="14597" max="14599" width="14.33203125" style="2" customWidth="1"/>
+    <col min="14600" max="14849" width="9.109375" style="2"/>
+    <col min="14850" max="14850" width="6.44140625" style="2" customWidth="1"/>
+    <col min="14851" max="14851" width="80.109375" style="2" customWidth="1"/>
+    <col min="14852" max="14852" width="15.6640625" style="2" customWidth="1"/>
+    <col min="14853" max="14855" width="14.33203125" style="2" customWidth="1"/>
+    <col min="14856" max="15105" width="9.109375" style="2"/>
+    <col min="15106" max="15106" width="6.44140625" style="2" customWidth="1"/>
+    <col min="15107" max="15107" width="80.109375" style="2" customWidth="1"/>
+    <col min="15108" max="15108" width="15.6640625" style="2" customWidth="1"/>
+    <col min="15109" max="15111" width="14.33203125" style="2" customWidth="1"/>
+    <col min="15112" max="15361" width="9.109375" style="2"/>
+    <col min="15362" max="15362" width="6.44140625" style="2" customWidth="1"/>
+    <col min="15363" max="15363" width="80.109375" style="2" customWidth="1"/>
+    <col min="15364" max="15364" width="15.6640625" style="2" customWidth="1"/>
+    <col min="15365" max="15367" width="14.33203125" style="2" customWidth="1"/>
+    <col min="15368" max="15617" width="9.109375" style="2"/>
+    <col min="15618" max="15618" width="6.44140625" style="2" customWidth="1"/>
+    <col min="15619" max="15619" width="80.109375" style="2" customWidth="1"/>
+    <col min="15620" max="15620" width="15.6640625" style="2" customWidth="1"/>
+    <col min="15621" max="15623" width="14.33203125" style="2" customWidth="1"/>
+    <col min="15624" max="15873" width="9.109375" style="2"/>
+    <col min="15874" max="15874" width="6.44140625" style="2" customWidth="1"/>
+    <col min="15875" max="15875" width="80.109375" style="2" customWidth="1"/>
+    <col min="15876" max="15876" width="15.6640625" style="2" customWidth="1"/>
+    <col min="15877" max="15879" width="14.33203125" style="2" customWidth="1"/>
+    <col min="15880" max="16129" width="9.109375" style="2"/>
+    <col min="16130" max="16130" width="6.44140625" style="2" customWidth="1"/>
+    <col min="16131" max="16131" width="80.109375" style="2" customWidth="1"/>
+    <col min="16132" max="16132" width="15.6640625" style="2" customWidth="1"/>
+    <col min="16133" max="16135" width="14.33203125" style="2" customWidth="1"/>
+    <col min="16136" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="F1" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="26"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="29"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
-      <c r="F2" s="36" t="s">
+      <c r="F2" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="36"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G2" s="30"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="37" t="s">
+      <c r="D3" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="37" t="s">
+      <c r="D4" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-    </row>
-    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="38" t="s">
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+    </row>
+    <row r="5" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A5" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-    </row>
-    <row r="6" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A6" s="35" t="s">
-        <v>254</v>
-      </c>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
+      <c r="B5" s="32"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+    </row>
+    <row r="6" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A6" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="E7" s="25" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E7" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="27" t="s">
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="28" t="s">
+      <c r="E8" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="27"/>
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="29" t="s">
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="28"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="32" t="s">
+      <c r="F9" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="33"/>
-    </row>
-    <row r="10" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="27"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="34" t="s">
+      <c r="G9" s="39"/>
+    </row>
+    <row r="10" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A10" s="28"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="G10" s="34" t="s">
+      <c r="G10" s="40" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="27"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-    </row>
-    <row r="12" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A11" s="28"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+    </row>
+    <row r="12" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>1</v>
       </c>
@@ -1915,7 +1681,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>27</v>
       </c>
@@ -1926,7 +1692,7 @@
         <v>29</v>
       </c>
       <c r="D13" s="20">
-        <f>D14+D49</f>
+        <f>D14+D51</f>
         <v>0</v>
       </c>
       <c r="E13" s="21">
@@ -1934,7 +1700,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="20">
-        <f>F14+F49</f>
+        <f>F14+F51</f>
         <v>0</v>
       </c>
       <c r="G13" s="21">
@@ -1942,7 +1708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>30</v>
       </c>
@@ -1957,7 +1723,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="21">
-        <f t="shared" ref="E14:E134" si="0">D14+F14</f>
+        <f t="shared" ref="E14:E115" si="0">D14+F14</f>
         <v>0</v>
       </c>
       <c r="F14" s="20">
@@ -1965,15 +1731,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="21">
-        <f t="shared" ref="G14:G134" si="1">IFERROR(F14/D14*100,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" ref="G14:G115" si="1">IFERROR(F14/D14*100,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="25" t="s">
         <v>34</v>
       </c>
       <c r="C15" s="23" t="s">
@@ -1990,11 +1756,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="25" t="s">
         <v>37</v>
       </c>
       <c r="C16" s="23" t="s">
@@ -2011,11 +1777,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="25" t="s">
         <v>40</v>
       </c>
       <c r="C17" s="23" t="s">
@@ -2032,11 +1798,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="25" t="s">
         <v>43</v>
       </c>
       <c r="C18" s="23" t="s">
@@ -2053,11 +1819,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="25" t="s">
         <v>46</v>
       </c>
       <c r="C19" s="23" t="s">
@@ -2074,11 +1840,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="45" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="25" t="s">
         <v>49</v>
       </c>
       <c r="C20" s="23" t="s">
@@ -2095,15 +1861,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="25" t="s">
         <v>52</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>255</v>
+        <v>168</v>
       </c>
       <c r="D21" s="16"/>
       <c r="E21" s="17">
@@ -2116,11 +1882,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="25" t="s">
         <v>54</v>
       </c>
       <c r="C22" s="23" t="s">
@@ -2137,11 +1903,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="25" t="s">
         <v>57</v>
       </c>
       <c r="C23" s="23" t="s">
@@ -2158,11 +1924,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="25" t="s">
         <v>60</v>
       </c>
       <c r="C24" s="23" t="s">
@@ -2179,11 +1945,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="25" t="s">
         <v>63</v>
       </c>
       <c r="C25" s="23" t="s">
@@ -2200,11 +1966,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="25" t="s">
         <v>66</v>
       </c>
       <c r="C26" s="23" t="s">
@@ -2221,11 +1987,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="25" t="s">
         <v>69</v>
       </c>
       <c r="C27" s="23" t="s">
@@ -2242,11 +2008,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="25" t="s">
         <v>72</v>
       </c>
       <c r="C28" s="23" t="s">
@@ -2263,11 +2029,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="25" t="s">
         <v>75</v>
       </c>
       <c r="C29" s="23" t="s">
@@ -2284,11 +2050,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="25" t="s">
         <v>78</v>
       </c>
       <c r="C30" s="23" t="s">
@@ -2305,11 +2071,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="25" t="s">
         <v>81</v>
       </c>
       <c r="C31" s="23" t="s">
@@ -2326,11 +2092,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="25" t="s">
         <v>84</v>
       </c>
       <c r="C32" s="23" t="s">
@@ -2347,11 +2113,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="25" t="s">
         <v>87</v>
       </c>
       <c r="C33" s="23" t="s">
@@ -2368,11 +2134,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="45" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="25" t="s">
         <v>90</v>
       </c>
       <c r="C34" s="23" t="s">
@@ -2389,11 +2155,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="25" t="s">
         <v>93</v>
       </c>
       <c r="C35" s="23" t="s">
@@ -2410,11 +2176,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="B36" s="25" t="s">
         <v>96</v>
       </c>
       <c r="C36" s="24" t="s">
@@ -2431,15 +2197,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="B37" s="15" t="s">
-        <v>99</v>
+      <c r="B37" s="25" t="s">
+        <v>171</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>100</v>
+        <v>169</v>
       </c>
       <c r="D37" s="16"/>
       <c r="E37" s="17">
@@ -2452,15 +2218,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="B38" s="15" t="s">
-        <v>102</v>
+      <c r="B38" s="25" t="s">
+        <v>172</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>103</v>
+        <v>170</v>
       </c>
       <c r="D38" s="16"/>
       <c r="E38" s="17">
@@ -2473,15 +2239,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A39" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="B39" s="15" t="s">
-        <v>105</v>
+      <c r="B39" s="25" t="s">
+        <v>99</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D39" s="16"/>
       <c r="E39" s="17">
@@ -2494,42 +2260,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A40" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="B40" s="15" t="s">
-        <v>108</v>
+      <c r="B40" s="25" t="s">
+        <v>102</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="D40" s="18">
-        <f>SUM(D41:D47)</f>
-        <v>0</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="D40" s="18"/>
       <c r="E40" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F40" s="18">
-        <f>SUM(F41:F47)</f>
-        <v>0</v>
-      </c>
+      <c r="F40" s="18"/>
       <c r="G40" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A41" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B41" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="C41" s="24" t="s">
-        <v>112</v>
+      <c r="B41" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="C41" s="23" t="s">
+        <v>106</v>
       </c>
       <c r="D41" s="18"/>
       <c r="E41" s="17">
@@ -2542,36 +2302,42 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A42" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="B42" s="15" t="s">
-        <v>114</v>
+      <c r="B42" s="25" t="s">
+        <v>108</v>
       </c>
       <c r="C42" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="D42" s="18"/>
+        <v>109</v>
+      </c>
+      <c r="D42" s="18">
+        <f>SUM(D43:D49)</f>
+        <v>0</v>
+      </c>
       <c r="E42" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F42" s="18"/>
+      <c r="F42" s="18">
+        <f>SUM(F43:F49)</f>
+        <v>0</v>
+      </c>
       <c r="G42" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A43" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="B43" s="15" t="s">
-        <v>117</v>
+      <c r="B43" s="25" t="s">
+        <v>111</v>
       </c>
       <c r="C43" s="24" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="17">
@@ -2584,15 +2350,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A44" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="B44" s="15" t="s">
-        <v>120</v>
+      <c r="B44" s="25" t="s">
+        <v>114</v>
       </c>
       <c r="C44" s="24" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D44" s="18"/>
       <c r="E44" s="17">
@@ -2605,15 +2371,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="B45" s="15" t="s">
-        <v>123</v>
+      <c r="B45" s="25" t="s">
+        <v>117</v>
       </c>
       <c r="C45" s="24" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D45" s="18"/>
       <c r="E45" s="17">
@@ -2626,15 +2392,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A46" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="B46" s="15" t="s">
-        <v>126</v>
+      <c r="B46" s="25" t="s">
+        <v>120</v>
       </c>
       <c r="C46" s="24" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D46" s="18"/>
       <c r="E46" s="17">
@@ -2647,15 +2413,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A47" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="B47" s="15" t="s">
-        <v>129</v>
+      <c r="B47" s="25" t="s">
+        <v>123</v>
       </c>
       <c r="C47" s="24" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D47" s="18"/>
       <c r="E47" s="17">
@@ -2668,15 +2434,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A48" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="B48" s="15" t="s">
-        <v>132</v>
+      <c r="B48" s="25" t="s">
+        <v>126</v>
       </c>
       <c r="C48" s="23" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D48" s="18"/>
       <c r="E48" s="17">
@@ -2689,42 +2455,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A49" s="19" t="s">
+    <row r="49" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A49" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="B49" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="C49" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="D49" s="20">
-        <f>SUM(D50:D75)-D56-D71</f>
-        <v>0</v>
-      </c>
-      <c r="E49" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F49" s="20">
-        <f>SUM(F50:F75)-F56-F71</f>
-        <v>0</v>
-      </c>
-      <c r="G49" s="21">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B49" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="C49" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="D49" s="18"/>
+      <c r="E49" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F49" s="18"/>
+      <c r="G49" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A50" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="B50" s="15" t="s">
-        <v>138</v>
+      <c r="B50" s="25" t="s">
+        <v>132</v>
       </c>
       <c r="C50" s="23" t="s">
-        <v>35</v>
+        <v>133</v>
       </c>
       <c r="D50" s="18"/>
       <c r="E50" s="17">
@@ -2737,36 +2497,42 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A51" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="B51" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="C51" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="D51" s="18"/>
-      <c r="E51" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F51" s="18"/>
-      <c r="G51" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A52" s="15" t="s">
-        <v>141</v>
+    <row r="51" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A51" s="19">
+        <v>39</v>
+      </c>
+      <c r="B51" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="C51" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="D51" s="20">
+        <f>SUM(D52:D77)-D58-D73</f>
+        <v>0</v>
+      </c>
+      <c r="E51" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F51" s="20">
+        <f>SUM(F52:F77)-F58-F73</f>
+        <v>0</v>
+      </c>
+      <c r="G51" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A52" s="15">
+        <v>40</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C52" s="23" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D52" s="18"/>
       <c r="E52" s="17">
@@ -2779,15 +2545,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A53" s="15" t="s">
-        <v>143</v>
+    <row r="53" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A53" s="15">
+        <v>41</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C53" s="23" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D53" s="18"/>
       <c r="E53" s="17">
@@ -2800,15 +2566,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A54" s="15" t="s">
-        <v>145</v>
+    <row r="54" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A54" s="15">
+        <v>42</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C54" s="23" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D54" s="18"/>
       <c r="E54" s="17">
@@ -2821,15 +2587,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="45" x14ac:dyDescent="0.2">
-      <c r="A55" s="15" t="s">
-        <v>147</v>
+    <row r="55" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A55" s="15">
+        <v>43</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C55" s="23" t="s">
-        <v>149</v>
+        <v>44</v>
       </c>
       <c r="D55" s="18"/>
       <c r="E55" s="17">
@@ -2842,15 +2608,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A56" s="15" t="s">
-        <v>150</v>
+    <row r="56" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A56" s="15">
+        <v>44</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="C56" s="24" t="s">
-        <v>255</v>
+        <v>142</v>
+      </c>
+      <c r="C56" s="23" t="s">
+        <v>47</v>
       </c>
       <c r="D56" s="18"/>
       <c r="E56" s="17">
@@ -2863,15 +2629,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A57" s="15" t="s">
-        <v>152</v>
+    <row r="57" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A57" s="15">
+        <v>45</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C57" s="23" t="s">
-        <v>55</v>
+        <v>144</v>
       </c>
       <c r="D57" s="18"/>
       <c r="E57" s="17">
@@ -2884,15 +2650,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A58" s="15" t="s">
-        <v>154</v>
+    <row r="58" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A58" s="15">
+        <v>46</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="C58" s="23" t="s">
-        <v>58</v>
+        <v>145</v>
+      </c>
+      <c r="C58" s="24" t="s">
+        <v>167</v>
       </c>
       <c r="D58" s="18"/>
       <c r="E58" s="17">
@@ -2905,15 +2671,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A59" s="15" t="s">
-        <v>156</v>
+    <row r="59" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A59" s="15">
+        <v>47</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="C59" s="23" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D59" s="18"/>
       <c r="E59" s="17">
@@ -2926,15 +2692,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A60" s="15" t="s">
-        <v>158</v>
+    <row r="60" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A60" s="15">
+        <v>48</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="C60" s="23" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D60" s="18"/>
       <c r="E60" s="17">
@@ -2947,15 +2713,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A61" s="15" t="s">
-        <v>160</v>
+    <row r="61" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A61" s="15">
+        <v>49</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="C61" s="23" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D61" s="18"/>
       <c r="E61" s="17">
@@ -2968,15 +2734,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A62" s="15" t="s">
-        <v>162</v>
+    <row r="62" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A62" s="15">
+        <v>50</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="C62" s="23" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D62" s="18"/>
       <c r="E62" s="17">
@@ -2989,15 +2755,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A63" s="15" t="s">
-        <v>164</v>
+    <row r="63" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A63" s="15">
+        <v>51</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="C63" s="23" t="s">
-        <v>166</v>
+        <v>67</v>
       </c>
       <c r="D63" s="18"/>
       <c r="E63" s="17">
@@ -3010,15 +2776,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A64" s="15" t="s">
-        <v>167</v>
+    <row r="64" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A64" s="15">
+        <v>52</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="C64" s="23" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D64" s="18"/>
       <c r="E64" s="17">
@@ -3031,15 +2797,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A65" s="15" t="s">
-        <v>169</v>
+    <row r="65" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A65" s="15">
+        <v>53</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="C65" s="23" t="s">
-        <v>79</v>
+        <v>153</v>
       </c>
       <c r="D65" s="18"/>
       <c r="E65" s="17">
@@ -3052,15 +2818,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A66" s="15" t="s">
-        <v>171</v>
+    <row r="66" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A66" s="15">
+        <v>54</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="C66" s="23" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D66" s="18"/>
       <c r="E66" s="17">
@@ -3073,15 +2839,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A67" s="15" t="s">
-        <v>173</v>
+    <row r="67" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A67" s="15">
+        <v>55</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="C67" s="23" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D67" s="18"/>
       <c r="E67" s="17">
@@ -3094,15 +2860,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A68" s="15" t="s">
-        <v>175</v>
+    <row r="68" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A68" s="15">
+        <v>56</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="C68" s="23" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D68" s="18"/>
       <c r="E68" s="17">
@@ -3115,15 +2881,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="45" x14ac:dyDescent="0.2">
-      <c r="A69" s="15" t="s">
-        <v>177</v>
+    <row r="69" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A69" s="15">
+        <v>57</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="C69" s="23" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D69" s="18"/>
       <c r="E69" s="17">
@@ -3136,15 +2902,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A70" s="15" t="s">
-        <v>179</v>
+    <row r="70" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A70" s="15">
+        <v>58</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="C70" s="23" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D70" s="18"/>
       <c r="E70" s="17">
@@ -3157,15 +2923,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A71" s="15" t="s">
-        <v>181</v>
+    <row r="71" spans="1:7" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A71" s="15">
+        <v>59</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="C71" s="24" t="s">
-        <v>97</v>
+        <v>159</v>
+      </c>
+      <c r="C71" s="23" t="s">
+        <v>91</v>
       </c>
       <c r="D71" s="18"/>
       <c r="E71" s="17">
@@ -3178,15 +2944,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A72" s="15" t="s">
-        <v>183</v>
+    <row r="72" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A72" s="15">
+        <v>60</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="C72" s="23" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D72" s="18"/>
       <c r="E72" s="17">
@@ -3199,15 +2965,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A73" s="15" t="s">
-        <v>185</v>
+    <row r="73" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A73" s="15">
+        <v>61</v>
       </c>
       <c r="B73" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="C73" s="23" t="s">
-        <v>103</v>
+        <v>161</v>
+      </c>
+      <c r="C73" s="24" t="s">
+        <v>97</v>
       </c>
       <c r="D73" s="18"/>
       <c r="E73" s="17">
@@ -3220,15 +2986,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A74" s="15" t="s">
-        <v>187</v>
+    <row r="74" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A74" s="15">
+        <v>62</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="C74" s="23" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D74" s="18"/>
       <c r="E74" s="17">
@@ -3241,15 +3007,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A75" s="15" t="s">
-        <v>189</v>
+    <row r="75" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A75" s="15">
+        <v>63</v>
       </c>
       <c r="B75" s="15" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="C75" s="23" t="s">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="D75" s="18"/>
       <c r="E75" s="17">
@@ -3262,36 +3028,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A76" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="B76" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="C76" s="22" t="s">
-        <v>193</v>
-      </c>
-      <c r="D76" s="20"/>
-      <c r="E76" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F76" s="20"/>
-      <c r="G76" s="21">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A77" s="15" t="s">
-        <v>194</v>
+    <row r="76" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A76" s="15">
+        <v>64</v>
+      </c>
+      <c r="B76" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="C76" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="D76" s="18"/>
+      <c r="E76" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F76" s="18"/>
+      <c r="G76" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A77" s="15">
+        <v>65</v>
       </c>
       <c r="B77" s="15" t="s">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="C77" s="23" t="s">
-        <v>196</v>
+        <v>133</v>
       </c>
       <c r="D77" s="18"/>
       <c r="E77" s="17">
@@ -3304,17 +3070,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A78" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B78" s="15" t="s">
-        <v>198</v>
-      </c>
-      <c r="C78" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="D78" s="18"/>
+    <row r="78" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A78" s="15"/>
+      <c r="B78" s="15"/>
+      <c r="C78" s="14"/>
+      <c r="D78" s="16"/>
       <c r="E78" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3325,17 +3085,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A79" s="15" t="s">
-        <v>200</v>
-      </c>
-      <c r="B79" s="15" t="s">
-        <v>201</v>
-      </c>
-      <c r="C79" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="D79" s="18"/>
+    <row r="79" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A79" s="15"/>
+      <c r="B79" s="15"/>
+      <c r="C79" s="14"/>
+      <c r="D79" s="16"/>
       <c r="E79" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3346,17 +3100,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A80" s="15" t="s">
-        <v>203</v>
-      </c>
-      <c r="B80" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="C80" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="D80" s="18"/>
+    <row r="80" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A80" s="15"/>
+      <c r="B80" s="15"/>
+      <c r="C80" s="14"/>
+      <c r="D80" s="16"/>
       <c r="E80" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3367,17 +3115,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A81" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="B81" s="15" t="s">
-        <v>207</v>
-      </c>
-      <c r="C81" s="23" t="s">
-        <v>208</v>
-      </c>
-      <c r="D81" s="18"/>
+    <row r="81" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A81" s="15"/>
+      <c r="B81" s="15"/>
+      <c r="C81" s="14"/>
+      <c r="D81" s="16"/>
       <c r="E81" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3388,17 +3130,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A82" s="15" t="s">
-        <v>209</v>
-      </c>
-      <c r="B82" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="C82" s="23" t="s">
-        <v>211</v>
-      </c>
-      <c r="D82" s="18"/>
+    <row r="82" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A82" s="15"/>
+      <c r="B82" s="15"/>
+      <c r="C82" s="14"/>
+      <c r="D82" s="16"/>
       <c r="E82" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3409,17 +3145,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A83" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="B83" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="C83" s="23" t="s">
-        <v>214</v>
-      </c>
-      <c r="D83" s="18"/>
+    <row r="83" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A83" s="15"/>
+      <c r="B83" s="15"/>
+      <c r="C83" s="14"/>
+      <c r="D83" s="16"/>
       <c r="E83" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3430,17 +3160,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A84" s="15" t="s">
-        <v>215</v>
-      </c>
-      <c r="B84" s="15" t="s">
-        <v>216</v>
-      </c>
-      <c r="C84" s="23" t="s">
-        <v>217</v>
-      </c>
-      <c r="D84" s="18"/>
+    <row r="84" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A84" s="15"/>
+      <c r="B84" s="15"/>
+      <c r="C84" s="14"/>
+      <c r="D84" s="16"/>
       <c r="E84" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3451,17 +3175,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A85" s="15" t="s">
-        <v>218</v>
-      </c>
-      <c r="B85" s="15" t="s">
-        <v>219</v>
-      </c>
-      <c r="C85" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="D85" s="18"/>
+    <row r="85" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A85" s="15"/>
+      <c r="B85" s="15"/>
+      <c r="C85" s="14"/>
+      <c r="D85" s="16"/>
       <c r="E85" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3472,17 +3190,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A86" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="B86" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="C86" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="D86" s="18"/>
+    <row r="86" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A86" s="15"/>
+      <c r="B86" s="15"/>
+      <c r="C86" s="14"/>
+      <c r="D86" s="16"/>
       <c r="E86" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3493,17 +3205,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A87" s="15" t="s">
-        <v>224</v>
-      </c>
-      <c r="B87" s="15" t="s">
-        <v>225</v>
-      </c>
-      <c r="C87" s="23" t="s">
-        <v>226</v>
-      </c>
-      <c r="D87" s="18"/>
+    <row r="87" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A87" s="15"/>
+      <c r="B87" s="15"/>
+      <c r="C87" s="14"/>
+      <c r="D87" s="16"/>
       <c r="E87" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3514,17 +3220,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A88" s="15" t="s">
-        <v>227</v>
-      </c>
-      <c r="B88" s="15" t="s">
-        <v>228</v>
-      </c>
-      <c r="C88" s="23" t="s">
-        <v>229</v>
-      </c>
-      <c r="D88" s="18"/>
+    <row r="88" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A88" s="15"/>
+      <c r="B88" s="15"/>
+      <c r="C88" s="14"/>
+      <c r="D88" s="16"/>
       <c r="E88" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3535,17 +3235,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A89" s="15" t="s">
-        <v>230</v>
-      </c>
-      <c r="B89" s="15" t="s">
-        <v>231</v>
-      </c>
-      <c r="C89" s="23" t="s">
-        <v>232</v>
-      </c>
-      <c r="D89" s="18"/>
+    <row r="89" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A89" s="15"/>
+      <c r="B89" s="15"/>
+      <c r="C89" s="14"/>
+      <c r="D89" s="16"/>
       <c r="E89" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3556,17 +3250,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A90" s="15" t="s">
-        <v>233</v>
-      </c>
-      <c r="B90" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="C90" s="23" t="s">
-        <v>235</v>
-      </c>
-      <c r="D90" s="18"/>
+    <row r="90" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A90" s="15"/>
+      <c r="B90" s="15"/>
+      <c r="C90" s="14"/>
+      <c r="D90" s="16"/>
       <c r="E90" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3577,17 +3265,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A91" s="15" t="s">
-        <v>236</v>
-      </c>
-      <c r="B91" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="C91" s="23" t="s">
-        <v>238</v>
-      </c>
-      <c r="D91" s="18"/>
+    <row r="91" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A91" s="15"/>
+      <c r="B91" s="15"/>
+      <c r="C91" s="14"/>
+      <c r="D91" s="16"/>
       <c r="E91" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3598,17 +3280,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A92" s="15" t="s">
-        <v>239</v>
-      </c>
-      <c r="B92" s="15" t="s">
-        <v>240</v>
-      </c>
-      <c r="C92" s="23" t="s">
-        <v>241</v>
-      </c>
-      <c r="D92" s="18"/>
+    <row r="92" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A92" s="15"/>
+      <c r="B92" s="15"/>
+      <c r="C92" s="14"/>
+      <c r="D92" s="16"/>
       <c r="E92" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3619,17 +3295,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A93" s="15" t="s">
-        <v>242</v>
-      </c>
-      <c r="B93" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="C93" s="23" t="s">
-        <v>244</v>
-      </c>
-      <c r="D93" s="18"/>
+    <row r="93" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A93" s="15"/>
+      <c r="B93" s="15"/>
+      <c r="C93" s="14"/>
+      <c r="D93" s="16"/>
       <c r="E93" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3640,17 +3310,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A94" s="15" t="s">
-        <v>245</v>
-      </c>
-      <c r="B94" s="15" t="s">
-        <v>246</v>
-      </c>
-      <c r="C94" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="D94" s="18"/>
+    <row r="94" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A94" s="15"/>
+      <c r="B94" s="15"/>
+      <c r="C94" s="14"/>
+      <c r="D94" s="16"/>
       <c r="E94" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3661,17 +3325,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A95" s="15" t="s">
-        <v>248</v>
-      </c>
-      <c r="B95" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="C95" s="23" t="s">
-        <v>250</v>
-      </c>
-      <c r="D95" s="18"/>
+    <row r="95" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A95" s="15"/>
+      <c r="B95" s="15"/>
+      <c r="C95" s="14"/>
+      <c r="D95" s="16"/>
       <c r="E95" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3682,17 +3340,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A96" s="15" t="s">
-        <v>251</v>
-      </c>
-      <c r="B96" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="C96" s="23" t="s">
-        <v>253</v>
-      </c>
-      <c r="D96" s="18"/>
+    <row r="96" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A96" s="15"/>
+      <c r="B96" s="15"/>
+      <c r="C96" s="14"/>
+      <c r="D96" s="16"/>
       <c r="E96" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3703,7 +3355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A97" s="15"/>
       <c r="B97" s="15"/>
       <c r="C97" s="14"/>
@@ -3718,7 +3370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A98" s="15"/>
       <c r="B98" s="15"/>
       <c r="C98" s="14"/>
@@ -3733,7 +3385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A99" s="15"/>
       <c r="B99" s="15"/>
       <c r="C99" s="14"/>
@@ -3748,7 +3400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A100" s="15"/>
       <c r="B100" s="15"/>
       <c r="C100" s="14"/>
@@ -3763,7 +3415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A101" s="15"/>
       <c r="B101" s="15"/>
       <c r="C101" s="14"/>
@@ -3778,7 +3430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A102" s="15"/>
       <c r="B102" s="15"/>
       <c r="C102" s="14"/>
@@ -3793,7 +3445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A103" s="15"/>
       <c r="B103" s="15"/>
       <c r="C103" s="14"/>
@@ -3808,7 +3460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A104" s="15"/>
       <c r="B104" s="15"/>
       <c r="C104" s="14"/>
@@ -3823,7 +3475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A105" s="15"/>
       <c r="B105" s="15"/>
       <c r="C105" s="14"/>
@@ -3838,7 +3490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A106" s="15"/>
       <c r="B106" s="15"/>
       <c r="C106" s="14"/>
@@ -3853,7 +3505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A107" s="15"/>
       <c r="B107" s="15"/>
       <c r="C107" s="14"/>
@@ -3868,7 +3520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A108" s="15"/>
       <c r="B108" s="15"/>
       <c r="C108" s="14"/>
@@ -3883,7 +3535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A109" s="15"/>
       <c r="B109" s="15"/>
       <c r="C109" s="14"/>
@@ -3898,7 +3550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A110" s="15"/>
       <c r="B110" s="15"/>
       <c r="C110" s="14"/>
@@ -3913,7 +3565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A111" s="15"/>
       <c r="B111" s="15"/>
       <c r="C111" s="14"/>
@@ -3928,7 +3580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A112" s="15"/>
       <c r="B112" s="15"/>
       <c r="C112" s="14"/>
@@ -3943,7 +3595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A113" s="15"/>
       <c r="B113" s="15"/>
       <c r="C113" s="14"/>
@@ -3958,7 +3610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A114" s="15"/>
       <c r="B114" s="15"/>
       <c r="C114" s="14"/>
@@ -3973,7 +3625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A115" s="15"/>
       <c r="B115" s="15"/>
       <c r="C115" s="14"/>
@@ -3988,307 +3640,307 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A116" s="15"/>
       <c r="B116" s="15"/>
       <c r="C116" s="14"/>
       <c r="D116" s="16"/>
       <c r="E116" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E116:E147" si="2">D116+F116</f>
         <v>0</v>
       </c>
       <c r="F116" s="18"/>
       <c r="G116" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" ref="G116:G147" si="3">IFERROR(F116/D116*100,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A117" s="15"/>
       <c r="B117" s="15"/>
       <c r="C117" s="14"/>
       <c r="D117" s="16"/>
       <c r="E117" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F117" s="18"/>
       <c r="G117" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A118" s="15"/>
       <c r="B118" s="15"/>
       <c r="C118" s="14"/>
       <c r="D118" s="16"/>
       <c r="E118" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F118" s="18"/>
       <c r="G118" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A119" s="15"/>
       <c r="B119" s="15"/>
       <c r="C119" s="14"/>
       <c r="D119" s="16"/>
       <c r="E119" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F119" s="18"/>
       <c r="G119" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A120" s="15"/>
       <c r="B120" s="15"/>
       <c r="C120" s="14"/>
       <c r="D120" s="16"/>
       <c r="E120" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F120" s="18"/>
       <c r="G120" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A121" s="15"/>
       <c r="B121" s="15"/>
       <c r="C121" s="14"/>
       <c r="D121" s="16"/>
       <c r="E121" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F121" s="18"/>
       <c r="G121" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A122" s="15"/>
       <c r="B122" s="15"/>
       <c r="C122" s="14"/>
-      <c r="D122" s="16"/>
+      <c r="D122" s="18"/>
       <c r="E122" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F122" s="18"/>
       <c r="G122" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A123" s="15"/>
       <c r="B123" s="15"/>
       <c r="C123" s="14"/>
-      <c r="D123" s="16"/>
+      <c r="D123" s="18"/>
       <c r="E123" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F123" s="18"/>
       <c r="G123" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A124" s="15"/>
       <c r="B124" s="15"/>
       <c r="C124" s="14"/>
-      <c r="D124" s="16"/>
+      <c r="D124" s="18"/>
       <c r="E124" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F124" s="18"/>
       <c r="G124" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A125" s="15"/>
       <c r="B125" s="15"/>
       <c r="C125" s="14"/>
-      <c r="D125" s="16"/>
+      <c r="D125" s="18"/>
       <c r="E125" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F125" s="18"/>
       <c r="G125" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A126" s="15"/>
       <c r="B126" s="15"/>
       <c r="C126" s="14"/>
-      <c r="D126" s="16"/>
+      <c r="D126" s="18"/>
       <c r="E126" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F126" s="18"/>
       <c r="G126" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A127" s="15"/>
       <c r="B127" s="15"/>
       <c r="C127" s="14"/>
-      <c r="D127" s="16"/>
+      <c r="D127" s="18"/>
       <c r="E127" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F127" s="18"/>
       <c r="G127" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A128" s="15"/>
       <c r="B128" s="15"/>
       <c r="C128" s="14"/>
-      <c r="D128" s="16"/>
+      <c r="D128" s="18"/>
       <c r="E128" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F128" s="18"/>
       <c r="G128" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A129" s="15"/>
       <c r="B129" s="15"/>
       <c r="C129" s="14"/>
-      <c r="D129" s="16"/>
+      <c r="D129" s="18"/>
       <c r="E129" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F129" s="18"/>
       <c r="G129" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A130" s="15"/>
       <c r="B130" s="15"/>
       <c r="C130" s="14"/>
-      <c r="D130" s="16"/>
+      <c r="D130" s="18"/>
       <c r="E130" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F130" s="18"/>
       <c r="G130" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A131" s="15"/>
       <c r="B131" s="15"/>
       <c r="C131" s="14"/>
-      <c r="D131" s="16"/>
+      <c r="D131" s="18"/>
       <c r="E131" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F131" s="18"/>
       <c r="G131" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A132" s="15"/>
       <c r="B132" s="15"/>
       <c r="C132" s="14"/>
-      <c r="D132" s="16"/>
+      <c r="D132" s="18"/>
       <c r="E132" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F132" s="18"/>
       <c r="G132" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A133" s="15"/>
       <c r="B133" s="15"/>
       <c r="C133" s="14"/>
-      <c r="D133" s="16"/>
+      <c r="D133" s="18"/>
       <c r="E133" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F133" s="18"/>
       <c r="G133" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A134" s="15"/>
       <c r="B134" s="15"/>
       <c r="C134" s="14"/>
-      <c r="D134" s="16"/>
+      <c r="D134" s="18"/>
       <c r="E134" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F134" s="18"/>
       <c r="G134" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A135" s="15"/>
       <c r="B135" s="15"/>
       <c r="C135" s="14"/>
       <c r="D135" s="16"/>
       <c r="E135" s="17">
-        <f t="shared" ref="E135:E166" si="2">D135+F135</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F135" s="18"/>
       <c r="G135" s="17">
-        <f t="shared" ref="G135:G166" si="3">IFERROR(F135/D135*100,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A136" s="15"/>
       <c r="B136" s="15"/>
       <c r="C136" s="14"/>
@@ -4303,7 +3955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A137" s="15"/>
       <c r="B137" s="15"/>
       <c r="C137" s="14"/>
@@ -4318,7 +3970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A138" s="15"/>
       <c r="B138" s="15"/>
       <c r="C138" s="14"/>
@@ -4333,7 +3985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A139" s="15"/>
       <c r="B139" s="15"/>
       <c r="C139" s="14"/>
@@ -4348,7 +4000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A140" s="15"/>
       <c r="B140" s="15"/>
       <c r="C140" s="14"/>
@@ -4363,11 +4015,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A141" s="15"/>
       <c r="B141" s="15"/>
       <c r="C141" s="14"/>
-      <c r="D141" s="18"/>
+      <c r="D141" s="16"/>
       <c r="E141" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -4378,11 +4030,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A142" s="15"/>
       <c r="B142" s="15"/>
       <c r="C142" s="14"/>
-      <c r="D142" s="18"/>
+      <c r="D142" s="16"/>
       <c r="E142" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -4393,11 +4045,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A143" s="15"/>
       <c r="B143" s="15"/>
       <c r="C143" s="14"/>
-      <c r="D143" s="18"/>
+      <c r="D143" s="16"/>
       <c r="E143" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -4408,11 +4060,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A144" s="15"/>
       <c r="B144" s="15"/>
       <c r="C144" s="14"/>
-      <c r="D144" s="18"/>
+      <c r="D144" s="16"/>
       <c r="E144" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -4423,11 +4075,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A145" s="15"/>
       <c r="B145" s="15"/>
       <c r="C145" s="14"/>
-      <c r="D145" s="18"/>
+      <c r="D145" s="16"/>
       <c r="E145" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -4438,11 +4090,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A146" s="15"/>
       <c r="B146" s="15"/>
       <c r="C146" s="14"/>
-      <c r="D146" s="18"/>
+      <c r="D146" s="16"/>
       <c r="E146" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -4453,11 +4105,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A147" s="15"/>
       <c r="B147" s="15"/>
       <c r="C147" s="14"/>
-      <c r="D147" s="18"/>
+      <c r="D147" s="16"/>
       <c r="E147" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -4468,402 +4120,110 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A148" s="15"/>
-      <c r="B148" s="15"/>
-      <c r="C148" s="14"/>
-      <c r="D148" s="18"/>
-      <c r="E148" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F148" s="18"/>
-      <c r="G148" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A149" s="15"/>
-      <c r="B149" s="15"/>
-      <c r="C149" s="14"/>
-      <c r="D149" s="18"/>
-      <c r="E149" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F149" s="18"/>
-      <c r="G149" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A150" s="15"/>
-      <c r="B150" s="15"/>
-      <c r="C150" s="14"/>
-      <c r="D150" s="18"/>
-      <c r="E150" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F150" s="18"/>
-      <c r="G150" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A151" s="15"/>
-      <c r="B151" s="15"/>
-      <c r="C151" s="14"/>
-      <c r="D151" s="18"/>
-      <c r="E151" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F151" s="18"/>
-      <c r="G151" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A152" s="15"/>
-      <c r="B152" s="15"/>
-      <c r="C152" s="14"/>
-      <c r="D152" s="18"/>
-      <c r="E152" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F152" s="18"/>
-      <c r="G152" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A153" s="15"/>
-      <c r="B153" s="15"/>
-      <c r="C153" s="14"/>
-      <c r="D153" s="18"/>
-      <c r="E153" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F153" s="18"/>
-      <c r="G153" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A154" s="15"/>
-      <c r="B154" s="15"/>
-      <c r="C154" s="14"/>
-      <c r="D154" s="16"/>
-      <c r="E154" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F154" s="18"/>
-      <c r="G154" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A155" s="15"/>
-      <c r="B155" s="15"/>
-      <c r="C155" s="14"/>
-      <c r="D155" s="16"/>
-      <c r="E155" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F155" s="18"/>
-      <c r="G155" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A156" s="15"/>
-      <c r="B156" s="15"/>
-      <c r="C156" s="14"/>
-      <c r="D156" s="16"/>
-      <c r="E156" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F156" s="18"/>
-      <c r="G156" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A157" s="15"/>
-      <c r="B157" s="15"/>
-      <c r="C157" s="14"/>
-      <c r="D157" s="16"/>
-      <c r="E157" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F157" s="18"/>
-      <c r="G157" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A158" s="15"/>
-      <c r="B158" s="15"/>
-      <c r="C158" s="14"/>
-      <c r="D158" s="16"/>
-      <c r="E158" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F158" s="18"/>
-      <c r="G158" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A159" s="15"/>
-      <c r="B159" s="15"/>
-      <c r="C159" s="14"/>
-      <c r="D159" s="16"/>
-      <c r="E159" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F159" s="18"/>
-      <c r="G159" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A160" s="15"/>
-      <c r="B160" s="15"/>
-      <c r="C160" s="14"/>
-      <c r="D160" s="16"/>
-      <c r="E160" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F160" s="18"/>
-      <c r="G160" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A161" s="15"/>
-      <c r="B161" s="15"/>
-      <c r="C161" s="14"/>
-      <c r="D161" s="16"/>
-      <c r="E161" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F161" s="18"/>
-      <c r="G161" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A162" s="15"/>
-      <c r="B162" s="15"/>
-      <c r="C162" s="14"/>
-      <c r="D162" s="16"/>
-      <c r="E162" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F162" s="18"/>
-      <c r="G162" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A163" s="15"/>
-      <c r="B163" s="15"/>
-      <c r="C163" s="14"/>
-      <c r="D163" s="16"/>
-      <c r="E163" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F163" s="18"/>
-      <c r="G163" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A164" s="15"/>
-      <c r="B164" s="15"/>
-      <c r="C164" s="14"/>
-      <c r="D164" s="16"/>
-      <c r="E164" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F164" s="18"/>
-      <c r="G164" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A165" s="15"/>
-      <c r="B165" s="15"/>
-      <c r="C165" s="14"/>
-      <c r="D165" s="16"/>
-      <c r="E165" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F165" s="18"/>
-      <c r="G165" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A166" s="15"/>
-      <c r="B166" s="15"/>
-      <c r="C166" s="14"/>
-      <c r="D166" s="16"/>
-      <c r="E166" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F166" s="18"/>
-      <c r="G166" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A167" s="8"/>
-      <c r="B167" s="8"/>
-      <c r="C167" s="9"/>
-      <c r="G167" s="6"/>
-    </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A168" s="8"/>
-      <c r="B168" s="8"/>
-      <c r="C168" s="1" t="s">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A148" s="8"/>
+      <c r="B148" s="8"/>
+      <c r="C148" s="9"/>
+      <c r="G148" s="6"/>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A149" s="8"/>
+      <c r="B149" s="8"/>
+      <c r="C149" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G168" s="6"/>
-    </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A169" s="10"/>
-      <c r="B169" s="10"/>
-      <c r="C169" s="10"/>
-      <c r="D169" s="25" t="s">
+      <c r="G149" s="6"/>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A150" s="10"/>
+      <c r="B150" s="10"/>
+      <c r="C150" s="10"/>
+      <c r="D150" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="E169" s="25"/>
-      <c r="F169" s="25"/>
-      <c r="G169" s="25"/>
-    </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A170" s="11"/>
-      <c r="B170" s="11"/>
-      <c r="C170" s="12" t="s">
+      <c r="E150" s="33"/>
+      <c r="F150" s="33"/>
+      <c r="G150" s="33"/>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A151" s="11"/>
+      <c r="B151" s="11"/>
+      <c r="C151" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D170" s="26"/>
-      <c r="E170" s="26"/>
-      <c r="F170" s="26"/>
-      <c r="G170" s="26"/>
-      <c r="H170" s="11"/>
-      <c r="I170" s="11"/>
-      <c r="J170" s="11"/>
-    </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A171" s="9"/>
-      <c r="B171" s="9"/>
-      <c r="C171" s="8" t="s">
+      <c r="D151" s="29"/>
+      <c r="E151" s="29"/>
+      <c r="F151" s="29"/>
+      <c r="G151" s="29"/>
+      <c r="H151" s="11"/>
+      <c r="I151" s="11"/>
+      <c r="J151" s="11"/>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A152" s="9"/>
+      <c r="B152" s="9"/>
+      <c r="C152" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D171" s="25"/>
-      <c r="E171" s="25"/>
-      <c r="F171" s="25"/>
-      <c r="G171" s="25"/>
-      <c r="H171" s="13"/>
-      <c r="I171" s="13"/>
-      <c r="J171" s="13"/>
-    </row>
-    <row r="172" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A172" s="2"/>
-      <c r="B172" s="2"/>
-      <c r="C172" s="2"/>
-      <c r="D172" s="2"/>
-      <c r="E172" s="2"/>
-      <c r="F172" s="2"/>
-    </row>
-    <row r="177" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C177" s="11" t="s">
+      <c r="D152" s="33"/>
+      <c r="E152" s="33"/>
+      <c r="F152" s="33"/>
+      <c r="G152" s="33"/>
+      <c r="H152" s="13"/>
+      <c r="I152" s="13"/>
+      <c r="J152" s="13"/>
+    </row>
+    <row r="153" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A153" s="2"/>
+      <c r="B153" s="2"/>
+      <c r="C153" s="2"/>
+      <c r="D153" s="2"/>
+      <c r="E153" s="2"/>
+      <c r="F153" s="2"/>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C158" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="178" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C178" s="1" t="s">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C159" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="179" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C179" s="1" t="s">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C160" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="180" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C180" s="1" t="s">
+    <row r="161" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C161" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="181" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C181" s="1" t="s">
+    <row r="162" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C162" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="182" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C182" s="1" t="s">
+    <row r="163" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C163" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="184" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C184" s="1" t="s">
+    <row r="165" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C165" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="187" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C187" s="11"/>
+    <row r="168" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C168" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="D4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="D169:G169"/>
-    <mergeCell ref="D170:G170"/>
-    <mergeCell ref="D171:G171"/>
+    <mergeCell ref="D150:G150"/>
+    <mergeCell ref="D151:G151"/>
+    <mergeCell ref="D152:G152"/>
     <mergeCell ref="E7:H7"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="C8:C11"/>
@@ -4873,10 +4233,17 @@
     <mergeCell ref="F9:G9"/>
     <mergeCell ref="F10:F11"/>
     <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="3.937007874015748E-2" right="3.937007874015748E-2" top="0.19685039370078741" bottom="3.937007874015748E-2" header="3.937007874015748E-2" footer="3.937007874015748E-2"/>
-  <pageSetup paperSize="9" scale="63" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="56" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
--- a/web/EXCEL_TEMPLATE/KHNV/KHNV_DK01A.xlsx
+++ b/web/EXCEL_TEMPLATE/KHNV/KHNV_DK01A.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cap nhat CN\IMS_REPORT KHNV - New\EXCEL_TEMPLATE\KHNV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSHOP\CV NAM 2024\TTBC\KHNV\Chỉnh sửa Kế hoạch tín dụng 2025\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69AD824D-422E-4DAA-BD21-11AFD56DC24F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3048" yWindow="-120" windowWidth="20736" windowHeight="11280"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DK_01A" sheetId="1" r:id="rId1"/>
@@ -18,7 +19,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">DK_01A!$A$1:$G$152</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">DK_01A!$8:$12</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -573,7 +574,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -767,7 +768,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -818,12 +819,8 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="4" fontId="9" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="9" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -832,7 +829,7 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="4" fontId="7" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="7" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -850,26 +847,14 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -890,6 +875,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1205,408 +1202,408 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J168"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="6.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="17" style="1" customWidth="1"/>
-    <col min="3" max="3" width="80.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="80.140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" style="2" customWidth="1"/>
-    <col min="8" max="257" width="9.109375" style="2"/>
-    <col min="258" max="258" width="6.44140625" style="2" customWidth="1"/>
-    <col min="259" max="259" width="80.109375" style="2" customWidth="1"/>
-    <col min="260" max="260" width="15.6640625" style="2" customWidth="1"/>
-    <col min="261" max="263" width="14.33203125" style="2" customWidth="1"/>
-    <col min="264" max="513" width="9.109375" style="2"/>
-    <col min="514" max="514" width="6.44140625" style="2" customWidth="1"/>
-    <col min="515" max="515" width="80.109375" style="2" customWidth="1"/>
-    <col min="516" max="516" width="15.6640625" style="2" customWidth="1"/>
-    <col min="517" max="519" width="14.33203125" style="2" customWidth="1"/>
-    <col min="520" max="769" width="9.109375" style="2"/>
-    <col min="770" max="770" width="6.44140625" style="2" customWidth="1"/>
-    <col min="771" max="771" width="80.109375" style="2" customWidth="1"/>
-    <col min="772" max="772" width="15.6640625" style="2" customWidth="1"/>
-    <col min="773" max="775" width="14.33203125" style="2" customWidth="1"/>
-    <col min="776" max="1025" width="9.109375" style="2"/>
-    <col min="1026" max="1026" width="6.44140625" style="2" customWidth="1"/>
-    <col min="1027" max="1027" width="80.109375" style="2" customWidth="1"/>
-    <col min="1028" max="1028" width="15.6640625" style="2" customWidth="1"/>
-    <col min="1029" max="1031" width="14.33203125" style="2" customWidth="1"/>
-    <col min="1032" max="1281" width="9.109375" style="2"/>
-    <col min="1282" max="1282" width="6.44140625" style="2" customWidth="1"/>
-    <col min="1283" max="1283" width="80.109375" style="2" customWidth="1"/>
-    <col min="1284" max="1284" width="15.6640625" style="2" customWidth="1"/>
-    <col min="1285" max="1287" width="14.33203125" style="2" customWidth="1"/>
-    <col min="1288" max="1537" width="9.109375" style="2"/>
-    <col min="1538" max="1538" width="6.44140625" style="2" customWidth="1"/>
-    <col min="1539" max="1539" width="80.109375" style="2" customWidth="1"/>
-    <col min="1540" max="1540" width="15.6640625" style="2" customWidth="1"/>
-    <col min="1541" max="1543" width="14.33203125" style="2" customWidth="1"/>
-    <col min="1544" max="1793" width="9.109375" style="2"/>
-    <col min="1794" max="1794" width="6.44140625" style="2" customWidth="1"/>
-    <col min="1795" max="1795" width="80.109375" style="2" customWidth="1"/>
-    <col min="1796" max="1796" width="15.6640625" style="2" customWidth="1"/>
-    <col min="1797" max="1799" width="14.33203125" style="2" customWidth="1"/>
-    <col min="1800" max="2049" width="9.109375" style="2"/>
-    <col min="2050" max="2050" width="6.44140625" style="2" customWidth="1"/>
-    <col min="2051" max="2051" width="80.109375" style="2" customWidth="1"/>
-    <col min="2052" max="2052" width="15.6640625" style="2" customWidth="1"/>
-    <col min="2053" max="2055" width="14.33203125" style="2" customWidth="1"/>
-    <col min="2056" max="2305" width="9.109375" style="2"/>
-    <col min="2306" max="2306" width="6.44140625" style="2" customWidth="1"/>
-    <col min="2307" max="2307" width="80.109375" style="2" customWidth="1"/>
-    <col min="2308" max="2308" width="15.6640625" style="2" customWidth="1"/>
-    <col min="2309" max="2311" width="14.33203125" style="2" customWidth="1"/>
-    <col min="2312" max="2561" width="9.109375" style="2"/>
-    <col min="2562" max="2562" width="6.44140625" style="2" customWidth="1"/>
-    <col min="2563" max="2563" width="80.109375" style="2" customWidth="1"/>
-    <col min="2564" max="2564" width="15.6640625" style="2" customWidth="1"/>
-    <col min="2565" max="2567" width="14.33203125" style="2" customWidth="1"/>
-    <col min="2568" max="2817" width="9.109375" style="2"/>
-    <col min="2818" max="2818" width="6.44140625" style="2" customWidth="1"/>
-    <col min="2819" max="2819" width="80.109375" style="2" customWidth="1"/>
-    <col min="2820" max="2820" width="15.6640625" style="2" customWidth="1"/>
-    <col min="2821" max="2823" width="14.33203125" style="2" customWidth="1"/>
-    <col min="2824" max="3073" width="9.109375" style="2"/>
-    <col min="3074" max="3074" width="6.44140625" style="2" customWidth="1"/>
-    <col min="3075" max="3075" width="80.109375" style="2" customWidth="1"/>
-    <col min="3076" max="3076" width="15.6640625" style="2" customWidth="1"/>
-    <col min="3077" max="3079" width="14.33203125" style="2" customWidth="1"/>
-    <col min="3080" max="3329" width="9.109375" style="2"/>
-    <col min="3330" max="3330" width="6.44140625" style="2" customWidth="1"/>
-    <col min="3331" max="3331" width="80.109375" style="2" customWidth="1"/>
-    <col min="3332" max="3332" width="15.6640625" style="2" customWidth="1"/>
-    <col min="3333" max="3335" width="14.33203125" style="2" customWidth="1"/>
-    <col min="3336" max="3585" width="9.109375" style="2"/>
-    <col min="3586" max="3586" width="6.44140625" style="2" customWidth="1"/>
-    <col min="3587" max="3587" width="80.109375" style="2" customWidth="1"/>
-    <col min="3588" max="3588" width="15.6640625" style="2" customWidth="1"/>
-    <col min="3589" max="3591" width="14.33203125" style="2" customWidth="1"/>
-    <col min="3592" max="3841" width="9.109375" style="2"/>
-    <col min="3842" max="3842" width="6.44140625" style="2" customWidth="1"/>
-    <col min="3843" max="3843" width="80.109375" style="2" customWidth="1"/>
-    <col min="3844" max="3844" width="15.6640625" style="2" customWidth="1"/>
-    <col min="3845" max="3847" width="14.33203125" style="2" customWidth="1"/>
-    <col min="3848" max="4097" width="9.109375" style="2"/>
-    <col min="4098" max="4098" width="6.44140625" style="2" customWidth="1"/>
-    <col min="4099" max="4099" width="80.109375" style="2" customWidth="1"/>
-    <col min="4100" max="4100" width="15.6640625" style="2" customWidth="1"/>
-    <col min="4101" max="4103" width="14.33203125" style="2" customWidth="1"/>
-    <col min="4104" max="4353" width="9.109375" style="2"/>
-    <col min="4354" max="4354" width="6.44140625" style="2" customWidth="1"/>
-    <col min="4355" max="4355" width="80.109375" style="2" customWidth="1"/>
-    <col min="4356" max="4356" width="15.6640625" style="2" customWidth="1"/>
-    <col min="4357" max="4359" width="14.33203125" style="2" customWidth="1"/>
-    <col min="4360" max="4609" width="9.109375" style="2"/>
-    <col min="4610" max="4610" width="6.44140625" style="2" customWidth="1"/>
-    <col min="4611" max="4611" width="80.109375" style="2" customWidth="1"/>
-    <col min="4612" max="4612" width="15.6640625" style="2" customWidth="1"/>
-    <col min="4613" max="4615" width="14.33203125" style="2" customWidth="1"/>
-    <col min="4616" max="4865" width="9.109375" style="2"/>
-    <col min="4866" max="4866" width="6.44140625" style="2" customWidth="1"/>
-    <col min="4867" max="4867" width="80.109375" style="2" customWidth="1"/>
-    <col min="4868" max="4868" width="15.6640625" style="2" customWidth="1"/>
-    <col min="4869" max="4871" width="14.33203125" style="2" customWidth="1"/>
-    <col min="4872" max="5121" width="9.109375" style="2"/>
-    <col min="5122" max="5122" width="6.44140625" style="2" customWidth="1"/>
-    <col min="5123" max="5123" width="80.109375" style="2" customWidth="1"/>
-    <col min="5124" max="5124" width="15.6640625" style="2" customWidth="1"/>
-    <col min="5125" max="5127" width="14.33203125" style="2" customWidth="1"/>
-    <col min="5128" max="5377" width="9.109375" style="2"/>
-    <col min="5378" max="5378" width="6.44140625" style="2" customWidth="1"/>
-    <col min="5379" max="5379" width="80.109375" style="2" customWidth="1"/>
-    <col min="5380" max="5380" width="15.6640625" style="2" customWidth="1"/>
-    <col min="5381" max="5383" width="14.33203125" style="2" customWidth="1"/>
-    <col min="5384" max="5633" width="9.109375" style="2"/>
-    <col min="5634" max="5634" width="6.44140625" style="2" customWidth="1"/>
-    <col min="5635" max="5635" width="80.109375" style="2" customWidth="1"/>
-    <col min="5636" max="5636" width="15.6640625" style="2" customWidth="1"/>
-    <col min="5637" max="5639" width="14.33203125" style="2" customWidth="1"/>
-    <col min="5640" max="5889" width="9.109375" style="2"/>
-    <col min="5890" max="5890" width="6.44140625" style="2" customWidth="1"/>
-    <col min="5891" max="5891" width="80.109375" style="2" customWidth="1"/>
-    <col min="5892" max="5892" width="15.6640625" style="2" customWidth="1"/>
-    <col min="5893" max="5895" width="14.33203125" style="2" customWidth="1"/>
-    <col min="5896" max="6145" width="9.109375" style="2"/>
-    <col min="6146" max="6146" width="6.44140625" style="2" customWidth="1"/>
-    <col min="6147" max="6147" width="80.109375" style="2" customWidth="1"/>
-    <col min="6148" max="6148" width="15.6640625" style="2" customWidth="1"/>
-    <col min="6149" max="6151" width="14.33203125" style="2" customWidth="1"/>
-    <col min="6152" max="6401" width="9.109375" style="2"/>
-    <col min="6402" max="6402" width="6.44140625" style="2" customWidth="1"/>
-    <col min="6403" max="6403" width="80.109375" style="2" customWidth="1"/>
-    <col min="6404" max="6404" width="15.6640625" style="2" customWidth="1"/>
-    <col min="6405" max="6407" width="14.33203125" style="2" customWidth="1"/>
-    <col min="6408" max="6657" width="9.109375" style="2"/>
-    <col min="6658" max="6658" width="6.44140625" style="2" customWidth="1"/>
-    <col min="6659" max="6659" width="80.109375" style="2" customWidth="1"/>
-    <col min="6660" max="6660" width="15.6640625" style="2" customWidth="1"/>
-    <col min="6661" max="6663" width="14.33203125" style="2" customWidth="1"/>
-    <col min="6664" max="6913" width="9.109375" style="2"/>
-    <col min="6914" max="6914" width="6.44140625" style="2" customWidth="1"/>
-    <col min="6915" max="6915" width="80.109375" style="2" customWidth="1"/>
-    <col min="6916" max="6916" width="15.6640625" style="2" customWidth="1"/>
-    <col min="6917" max="6919" width="14.33203125" style="2" customWidth="1"/>
-    <col min="6920" max="7169" width="9.109375" style="2"/>
-    <col min="7170" max="7170" width="6.44140625" style="2" customWidth="1"/>
-    <col min="7171" max="7171" width="80.109375" style="2" customWidth="1"/>
-    <col min="7172" max="7172" width="15.6640625" style="2" customWidth="1"/>
-    <col min="7173" max="7175" width="14.33203125" style="2" customWidth="1"/>
-    <col min="7176" max="7425" width="9.109375" style="2"/>
-    <col min="7426" max="7426" width="6.44140625" style="2" customWidth="1"/>
-    <col min="7427" max="7427" width="80.109375" style="2" customWidth="1"/>
-    <col min="7428" max="7428" width="15.6640625" style="2" customWidth="1"/>
-    <col min="7429" max="7431" width="14.33203125" style="2" customWidth="1"/>
-    <col min="7432" max="7681" width="9.109375" style="2"/>
-    <col min="7682" max="7682" width="6.44140625" style="2" customWidth="1"/>
-    <col min="7683" max="7683" width="80.109375" style="2" customWidth="1"/>
-    <col min="7684" max="7684" width="15.6640625" style="2" customWidth="1"/>
-    <col min="7685" max="7687" width="14.33203125" style="2" customWidth="1"/>
-    <col min="7688" max="7937" width="9.109375" style="2"/>
-    <col min="7938" max="7938" width="6.44140625" style="2" customWidth="1"/>
-    <col min="7939" max="7939" width="80.109375" style="2" customWidth="1"/>
-    <col min="7940" max="7940" width="15.6640625" style="2" customWidth="1"/>
-    <col min="7941" max="7943" width="14.33203125" style="2" customWidth="1"/>
-    <col min="7944" max="8193" width="9.109375" style="2"/>
-    <col min="8194" max="8194" width="6.44140625" style="2" customWidth="1"/>
-    <col min="8195" max="8195" width="80.109375" style="2" customWidth="1"/>
-    <col min="8196" max="8196" width="15.6640625" style="2" customWidth="1"/>
-    <col min="8197" max="8199" width="14.33203125" style="2" customWidth="1"/>
-    <col min="8200" max="8449" width="9.109375" style="2"/>
-    <col min="8450" max="8450" width="6.44140625" style="2" customWidth="1"/>
-    <col min="8451" max="8451" width="80.109375" style="2" customWidth="1"/>
-    <col min="8452" max="8452" width="15.6640625" style="2" customWidth="1"/>
-    <col min="8453" max="8455" width="14.33203125" style="2" customWidth="1"/>
-    <col min="8456" max="8705" width="9.109375" style="2"/>
-    <col min="8706" max="8706" width="6.44140625" style="2" customWidth="1"/>
-    <col min="8707" max="8707" width="80.109375" style="2" customWidth="1"/>
-    <col min="8708" max="8708" width="15.6640625" style="2" customWidth="1"/>
-    <col min="8709" max="8711" width="14.33203125" style="2" customWidth="1"/>
-    <col min="8712" max="8961" width="9.109375" style="2"/>
-    <col min="8962" max="8962" width="6.44140625" style="2" customWidth="1"/>
-    <col min="8963" max="8963" width="80.109375" style="2" customWidth="1"/>
-    <col min="8964" max="8964" width="15.6640625" style="2" customWidth="1"/>
-    <col min="8965" max="8967" width="14.33203125" style="2" customWidth="1"/>
-    <col min="8968" max="9217" width="9.109375" style="2"/>
-    <col min="9218" max="9218" width="6.44140625" style="2" customWidth="1"/>
-    <col min="9219" max="9219" width="80.109375" style="2" customWidth="1"/>
-    <col min="9220" max="9220" width="15.6640625" style="2" customWidth="1"/>
-    <col min="9221" max="9223" width="14.33203125" style="2" customWidth="1"/>
-    <col min="9224" max="9473" width="9.109375" style="2"/>
-    <col min="9474" max="9474" width="6.44140625" style="2" customWidth="1"/>
-    <col min="9475" max="9475" width="80.109375" style="2" customWidth="1"/>
-    <col min="9476" max="9476" width="15.6640625" style="2" customWidth="1"/>
-    <col min="9477" max="9479" width="14.33203125" style="2" customWidth="1"/>
-    <col min="9480" max="9729" width="9.109375" style="2"/>
-    <col min="9730" max="9730" width="6.44140625" style="2" customWidth="1"/>
-    <col min="9731" max="9731" width="80.109375" style="2" customWidth="1"/>
-    <col min="9732" max="9732" width="15.6640625" style="2" customWidth="1"/>
-    <col min="9733" max="9735" width="14.33203125" style="2" customWidth="1"/>
-    <col min="9736" max="9985" width="9.109375" style="2"/>
-    <col min="9986" max="9986" width="6.44140625" style="2" customWidth="1"/>
-    <col min="9987" max="9987" width="80.109375" style="2" customWidth="1"/>
-    <col min="9988" max="9988" width="15.6640625" style="2" customWidth="1"/>
-    <col min="9989" max="9991" width="14.33203125" style="2" customWidth="1"/>
-    <col min="9992" max="10241" width="9.109375" style="2"/>
-    <col min="10242" max="10242" width="6.44140625" style="2" customWidth="1"/>
-    <col min="10243" max="10243" width="80.109375" style="2" customWidth="1"/>
-    <col min="10244" max="10244" width="15.6640625" style="2" customWidth="1"/>
-    <col min="10245" max="10247" width="14.33203125" style="2" customWidth="1"/>
-    <col min="10248" max="10497" width="9.109375" style="2"/>
-    <col min="10498" max="10498" width="6.44140625" style="2" customWidth="1"/>
-    <col min="10499" max="10499" width="80.109375" style="2" customWidth="1"/>
-    <col min="10500" max="10500" width="15.6640625" style="2" customWidth="1"/>
-    <col min="10501" max="10503" width="14.33203125" style="2" customWidth="1"/>
-    <col min="10504" max="10753" width="9.109375" style="2"/>
-    <col min="10754" max="10754" width="6.44140625" style="2" customWidth="1"/>
-    <col min="10755" max="10755" width="80.109375" style="2" customWidth="1"/>
-    <col min="10756" max="10756" width="15.6640625" style="2" customWidth="1"/>
-    <col min="10757" max="10759" width="14.33203125" style="2" customWidth="1"/>
-    <col min="10760" max="11009" width="9.109375" style="2"/>
-    <col min="11010" max="11010" width="6.44140625" style="2" customWidth="1"/>
-    <col min="11011" max="11011" width="80.109375" style="2" customWidth="1"/>
-    <col min="11012" max="11012" width="15.6640625" style="2" customWidth="1"/>
-    <col min="11013" max="11015" width="14.33203125" style="2" customWidth="1"/>
-    <col min="11016" max="11265" width="9.109375" style="2"/>
-    <col min="11266" max="11266" width="6.44140625" style="2" customWidth="1"/>
-    <col min="11267" max="11267" width="80.109375" style="2" customWidth="1"/>
-    <col min="11268" max="11268" width="15.6640625" style="2" customWidth="1"/>
-    <col min="11269" max="11271" width="14.33203125" style="2" customWidth="1"/>
-    <col min="11272" max="11521" width="9.109375" style="2"/>
-    <col min="11522" max="11522" width="6.44140625" style="2" customWidth="1"/>
-    <col min="11523" max="11523" width="80.109375" style="2" customWidth="1"/>
-    <col min="11524" max="11524" width="15.6640625" style="2" customWidth="1"/>
-    <col min="11525" max="11527" width="14.33203125" style="2" customWidth="1"/>
-    <col min="11528" max="11777" width="9.109375" style="2"/>
-    <col min="11778" max="11778" width="6.44140625" style="2" customWidth="1"/>
-    <col min="11779" max="11779" width="80.109375" style="2" customWidth="1"/>
-    <col min="11780" max="11780" width="15.6640625" style="2" customWidth="1"/>
-    <col min="11781" max="11783" width="14.33203125" style="2" customWidth="1"/>
-    <col min="11784" max="12033" width="9.109375" style="2"/>
-    <col min="12034" max="12034" width="6.44140625" style="2" customWidth="1"/>
-    <col min="12035" max="12035" width="80.109375" style="2" customWidth="1"/>
-    <col min="12036" max="12036" width="15.6640625" style="2" customWidth="1"/>
-    <col min="12037" max="12039" width="14.33203125" style="2" customWidth="1"/>
-    <col min="12040" max="12289" width="9.109375" style="2"/>
-    <col min="12290" max="12290" width="6.44140625" style="2" customWidth="1"/>
-    <col min="12291" max="12291" width="80.109375" style="2" customWidth="1"/>
-    <col min="12292" max="12292" width="15.6640625" style="2" customWidth="1"/>
-    <col min="12293" max="12295" width="14.33203125" style="2" customWidth="1"/>
-    <col min="12296" max="12545" width="9.109375" style="2"/>
-    <col min="12546" max="12546" width="6.44140625" style="2" customWidth="1"/>
-    <col min="12547" max="12547" width="80.109375" style="2" customWidth="1"/>
-    <col min="12548" max="12548" width="15.6640625" style="2" customWidth="1"/>
-    <col min="12549" max="12551" width="14.33203125" style="2" customWidth="1"/>
-    <col min="12552" max="12801" width="9.109375" style="2"/>
-    <col min="12802" max="12802" width="6.44140625" style="2" customWidth="1"/>
-    <col min="12803" max="12803" width="80.109375" style="2" customWidth="1"/>
-    <col min="12804" max="12804" width="15.6640625" style="2" customWidth="1"/>
-    <col min="12805" max="12807" width="14.33203125" style="2" customWidth="1"/>
-    <col min="12808" max="13057" width="9.109375" style="2"/>
-    <col min="13058" max="13058" width="6.44140625" style="2" customWidth="1"/>
-    <col min="13059" max="13059" width="80.109375" style="2" customWidth="1"/>
-    <col min="13060" max="13060" width="15.6640625" style="2" customWidth="1"/>
-    <col min="13061" max="13063" width="14.33203125" style="2" customWidth="1"/>
-    <col min="13064" max="13313" width="9.109375" style="2"/>
-    <col min="13314" max="13314" width="6.44140625" style="2" customWidth="1"/>
-    <col min="13315" max="13315" width="80.109375" style="2" customWidth="1"/>
-    <col min="13316" max="13316" width="15.6640625" style="2" customWidth="1"/>
-    <col min="13317" max="13319" width="14.33203125" style="2" customWidth="1"/>
-    <col min="13320" max="13569" width="9.109375" style="2"/>
-    <col min="13570" max="13570" width="6.44140625" style="2" customWidth="1"/>
-    <col min="13571" max="13571" width="80.109375" style="2" customWidth="1"/>
-    <col min="13572" max="13572" width="15.6640625" style="2" customWidth="1"/>
-    <col min="13573" max="13575" width="14.33203125" style="2" customWidth="1"/>
-    <col min="13576" max="13825" width="9.109375" style="2"/>
-    <col min="13826" max="13826" width="6.44140625" style="2" customWidth="1"/>
-    <col min="13827" max="13827" width="80.109375" style="2" customWidth="1"/>
-    <col min="13828" max="13828" width="15.6640625" style="2" customWidth="1"/>
-    <col min="13829" max="13831" width="14.33203125" style="2" customWidth="1"/>
-    <col min="13832" max="14081" width="9.109375" style="2"/>
-    <col min="14082" max="14082" width="6.44140625" style="2" customWidth="1"/>
-    <col min="14083" max="14083" width="80.109375" style="2" customWidth="1"/>
-    <col min="14084" max="14084" width="15.6640625" style="2" customWidth="1"/>
-    <col min="14085" max="14087" width="14.33203125" style="2" customWidth="1"/>
-    <col min="14088" max="14337" width="9.109375" style="2"/>
-    <col min="14338" max="14338" width="6.44140625" style="2" customWidth="1"/>
-    <col min="14339" max="14339" width="80.109375" style="2" customWidth="1"/>
-    <col min="14340" max="14340" width="15.6640625" style="2" customWidth="1"/>
-    <col min="14341" max="14343" width="14.33203125" style="2" customWidth="1"/>
-    <col min="14344" max="14593" width="9.109375" style="2"/>
-    <col min="14594" max="14594" width="6.44140625" style="2" customWidth="1"/>
-    <col min="14595" max="14595" width="80.109375" style="2" customWidth="1"/>
-    <col min="14596" max="14596" width="15.6640625" style="2" customWidth="1"/>
-    <col min="14597" max="14599" width="14.33203125" style="2" customWidth="1"/>
-    <col min="14600" max="14849" width="9.109375" style="2"/>
-    <col min="14850" max="14850" width="6.44140625" style="2" customWidth="1"/>
-    <col min="14851" max="14851" width="80.109375" style="2" customWidth="1"/>
-    <col min="14852" max="14852" width="15.6640625" style="2" customWidth="1"/>
-    <col min="14853" max="14855" width="14.33203125" style="2" customWidth="1"/>
-    <col min="14856" max="15105" width="9.109375" style="2"/>
-    <col min="15106" max="15106" width="6.44140625" style="2" customWidth="1"/>
-    <col min="15107" max="15107" width="80.109375" style="2" customWidth="1"/>
-    <col min="15108" max="15108" width="15.6640625" style="2" customWidth="1"/>
-    <col min="15109" max="15111" width="14.33203125" style="2" customWidth="1"/>
-    <col min="15112" max="15361" width="9.109375" style="2"/>
-    <col min="15362" max="15362" width="6.44140625" style="2" customWidth="1"/>
-    <col min="15363" max="15363" width="80.109375" style="2" customWidth="1"/>
-    <col min="15364" max="15364" width="15.6640625" style="2" customWidth="1"/>
-    <col min="15365" max="15367" width="14.33203125" style="2" customWidth="1"/>
-    <col min="15368" max="15617" width="9.109375" style="2"/>
-    <col min="15618" max="15618" width="6.44140625" style="2" customWidth="1"/>
-    <col min="15619" max="15619" width="80.109375" style="2" customWidth="1"/>
-    <col min="15620" max="15620" width="15.6640625" style="2" customWidth="1"/>
-    <col min="15621" max="15623" width="14.33203125" style="2" customWidth="1"/>
-    <col min="15624" max="15873" width="9.109375" style="2"/>
-    <col min="15874" max="15874" width="6.44140625" style="2" customWidth="1"/>
-    <col min="15875" max="15875" width="80.109375" style="2" customWidth="1"/>
-    <col min="15876" max="15876" width="15.6640625" style="2" customWidth="1"/>
-    <col min="15877" max="15879" width="14.33203125" style="2" customWidth="1"/>
-    <col min="15880" max="16129" width="9.109375" style="2"/>
-    <col min="16130" max="16130" width="6.44140625" style="2" customWidth="1"/>
-    <col min="16131" max="16131" width="80.109375" style="2" customWidth="1"/>
-    <col min="16132" max="16132" width="15.6640625" style="2" customWidth="1"/>
-    <col min="16133" max="16135" width="14.33203125" style="2" customWidth="1"/>
-    <col min="16136" max="16384" width="9.109375" style="2"/>
+    <col min="5" max="5" width="17.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="2" customWidth="1"/>
+    <col min="8" max="257" width="9.140625" style="2"/>
+    <col min="258" max="258" width="6.42578125" style="2" customWidth="1"/>
+    <col min="259" max="259" width="80.140625" style="2" customWidth="1"/>
+    <col min="260" max="260" width="15.7109375" style="2" customWidth="1"/>
+    <col min="261" max="263" width="14.28515625" style="2" customWidth="1"/>
+    <col min="264" max="513" width="9.140625" style="2"/>
+    <col min="514" max="514" width="6.42578125" style="2" customWidth="1"/>
+    <col min="515" max="515" width="80.140625" style="2" customWidth="1"/>
+    <col min="516" max="516" width="15.7109375" style="2" customWidth="1"/>
+    <col min="517" max="519" width="14.28515625" style="2" customWidth="1"/>
+    <col min="520" max="769" width="9.140625" style="2"/>
+    <col min="770" max="770" width="6.42578125" style="2" customWidth="1"/>
+    <col min="771" max="771" width="80.140625" style="2" customWidth="1"/>
+    <col min="772" max="772" width="15.7109375" style="2" customWidth="1"/>
+    <col min="773" max="775" width="14.28515625" style="2" customWidth="1"/>
+    <col min="776" max="1025" width="9.140625" style="2"/>
+    <col min="1026" max="1026" width="6.42578125" style="2" customWidth="1"/>
+    <col min="1027" max="1027" width="80.140625" style="2" customWidth="1"/>
+    <col min="1028" max="1028" width="15.7109375" style="2" customWidth="1"/>
+    <col min="1029" max="1031" width="14.28515625" style="2" customWidth="1"/>
+    <col min="1032" max="1281" width="9.140625" style="2"/>
+    <col min="1282" max="1282" width="6.42578125" style="2" customWidth="1"/>
+    <col min="1283" max="1283" width="80.140625" style="2" customWidth="1"/>
+    <col min="1284" max="1284" width="15.7109375" style="2" customWidth="1"/>
+    <col min="1285" max="1287" width="14.28515625" style="2" customWidth="1"/>
+    <col min="1288" max="1537" width="9.140625" style="2"/>
+    <col min="1538" max="1538" width="6.42578125" style="2" customWidth="1"/>
+    <col min="1539" max="1539" width="80.140625" style="2" customWidth="1"/>
+    <col min="1540" max="1540" width="15.7109375" style="2" customWidth="1"/>
+    <col min="1541" max="1543" width="14.28515625" style="2" customWidth="1"/>
+    <col min="1544" max="1793" width="9.140625" style="2"/>
+    <col min="1794" max="1794" width="6.42578125" style="2" customWidth="1"/>
+    <col min="1795" max="1795" width="80.140625" style="2" customWidth="1"/>
+    <col min="1796" max="1796" width="15.7109375" style="2" customWidth="1"/>
+    <col min="1797" max="1799" width="14.28515625" style="2" customWidth="1"/>
+    <col min="1800" max="2049" width="9.140625" style="2"/>
+    <col min="2050" max="2050" width="6.42578125" style="2" customWidth="1"/>
+    <col min="2051" max="2051" width="80.140625" style="2" customWidth="1"/>
+    <col min="2052" max="2052" width="15.7109375" style="2" customWidth="1"/>
+    <col min="2053" max="2055" width="14.28515625" style="2" customWidth="1"/>
+    <col min="2056" max="2305" width="9.140625" style="2"/>
+    <col min="2306" max="2306" width="6.42578125" style="2" customWidth="1"/>
+    <col min="2307" max="2307" width="80.140625" style="2" customWidth="1"/>
+    <col min="2308" max="2308" width="15.7109375" style="2" customWidth="1"/>
+    <col min="2309" max="2311" width="14.28515625" style="2" customWidth="1"/>
+    <col min="2312" max="2561" width="9.140625" style="2"/>
+    <col min="2562" max="2562" width="6.42578125" style="2" customWidth="1"/>
+    <col min="2563" max="2563" width="80.140625" style="2" customWidth="1"/>
+    <col min="2564" max="2564" width="15.7109375" style="2" customWidth="1"/>
+    <col min="2565" max="2567" width="14.28515625" style="2" customWidth="1"/>
+    <col min="2568" max="2817" width="9.140625" style="2"/>
+    <col min="2818" max="2818" width="6.42578125" style="2" customWidth="1"/>
+    <col min="2819" max="2819" width="80.140625" style="2" customWidth="1"/>
+    <col min="2820" max="2820" width="15.7109375" style="2" customWidth="1"/>
+    <col min="2821" max="2823" width="14.28515625" style="2" customWidth="1"/>
+    <col min="2824" max="3073" width="9.140625" style="2"/>
+    <col min="3074" max="3074" width="6.42578125" style="2" customWidth="1"/>
+    <col min="3075" max="3075" width="80.140625" style="2" customWidth="1"/>
+    <col min="3076" max="3076" width="15.7109375" style="2" customWidth="1"/>
+    <col min="3077" max="3079" width="14.28515625" style="2" customWidth="1"/>
+    <col min="3080" max="3329" width="9.140625" style="2"/>
+    <col min="3330" max="3330" width="6.42578125" style="2" customWidth="1"/>
+    <col min="3331" max="3331" width="80.140625" style="2" customWidth="1"/>
+    <col min="3332" max="3332" width="15.7109375" style="2" customWidth="1"/>
+    <col min="3333" max="3335" width="14.28515625" style="2" customWidth="1"/>
+    <col min="3336" max="3585" width="9.140625" style="2"/>
+    <col min="3586" max="3586" width="6.42578125" style="2" customWidth="1"/>
+    <col min="3587" max="3587" width="80.140625" style="2" customWidth="1"/>
+    <col min="3588" max="3588" width="15.7109375" style="2" customWidth="1"/>
+    <col min="3589" max="3591" width="14.28515625" style="2" customWidth="1"/>
+    <col min="3592" max="3841" width="9.140625" style="2"/>
+    <col min="3842" max="3842" width="6.42578125" style="2" customWidth="1"/>
+    <col min="3843" max="3843" width="80.140625" style="2" customWidth="1"/>
+    <col min="3844" max="3844" width="15.7109375" style="2" customWidth="1"/>
+    <col min="3845" max="3847" width="14.28515625" style="2" customWidth="1"/>
+    <col min="3848" max="4097" width="9.140625" style="2"/>
+    <col min="4098" max="4098" width="6.42578125" style="2" customWidth="1"/>
+    <col min="4099" max="4099" width="80.140625" style="2" customWidth="1"/>
+    <col min="4100" max="4100" width="15.7109375" style="2" customWidth="1"/>
+    <col min="4101" max="4103" width="14.28515625" style="2" customWidth="1"/>
+    <col min="4104" max="4353" width="9.140625" style="2"/>
+    <col min="4354" max="4354" width="6.42578125" style="2" customWidth="1"/>
+    <col min="4355" max="4355" width="80.140625" style="2" customWidth="1"/>
+    <col min="4356" max="4356" width="15.7109375" style="2" customWidth="1"/>
+    <col min="4357" max="4359" width="14.28515625" style="2" customWidth="1"/>
+    <col min="4360" max="4609" width="9.140625" style="2"/>
+    <col min="4610" max="4610" width="6.42578125" style="2" customWidth="1"/>
+    <col min="4611" max="4611" width="80.140625" style="2" customWidth="1"/>
+    <col min="4612" max="4612" width="15.7109375" style="2" customWidth="1"/>
+    <col min="4613" max="4615" width="14.28515625" style="2" customWidth="1"/>
+    <col min="4616" max="4865" width="9.140625" style="2"/>
+    <col min="4866" max="4866" width="6.42578125" style="2" customWidth="1"/>
+    <col min="4867" max="4867" width="80.140625" style="2" customWidth="1"/>
+    <col min="4868" max="4868" width="15.7109375" style="2" customWidth="1"/>
+    <col min="4869" max="4871" width="14.28515625" style="2" customWidth="1"/>
+    <col min="4872" max="5121" width="9.140625" style="2"/>
+    <col min="5122" max="5122" width="6.42578125" style="2" customWidth="1"/>
+    <col min="5123" max="5123" width="80.140625" style="2" customWidth="1"/>
+    <col min="5124" max="5124" width="15.7109375" style="2" customWidth="1"/>
+    <col min="5125" max="5127" width="14.28515625" style="2" customWidth="1"/>
+    <col min="5128" max="5377" width="9.140625" style="2"/>
+    <col min="5378" max="5378" width="6.42578125" style="2" customWidth="1"/>
+    <col min="5379" max="5379" width="80.140625" style="2" customWidth="1"/>
+    <col min="5380" max="5380" width="15.7109375" style="2" customWidth="1"/>
+    <col min="5381" max="5383" width="14.28515625" style="2" customWidth="1"/>
+    <col min="5384" max="5633" width="9.140625" style="2"/>
+    <col min="5634" max="5634" width="6.42578125" style="2" customWidth="1"/>
+    <col min="5635" max="5635" width="80.140625" style="2" customWidth="1"/>
+    <col min="5636" max="5636" width="15.7109375" style="2" customWidth="1"/>
+    <col min="5637" max="5639" width="14.28515625" style="2" customWidth="1"/>
+    <col min="5640" max="5889" width="9.140625" style="2"/>
+    <col min="5890" max="5890" width="6.42578125" style="2" customWidth="1"/>
+    <col min="5891" max="5891" width="80.140625" style="2" customWidth="1"/>
+    <col min="5892" max="5892" width="15.7109375" style="2" customWidth="1"/>
+    <col min="5893" max="5895" width="14.28515625" style="2" customWidth="1"/>
+    <col min="5896" max="6145" width="9.140625" style="2"/>
+    <col min="6146" max="6146" width="6.42578125" style="2" customWidth="1"/>
+    <col min="6147" max="6147" width="80.140625" style="2" customWidth="1"/>
+    <col min="6148" max="6148" width="15.7109375" style="2" customWidth="1"/>
+    <col min="6149" max="6151" width="14.28515625" style="2" customWidth="1"/>
+    <col min="6152" max="6401" width="9.140625" style="2"/>
+    <col min="6402" max="6402" width="6.42578125" style="2" customWidth="1"/>
+    <col min="6403" max="6403" width="80.140625" style="2" customWidth="1"/>
+    <col min="6404" max="6404" width="15.7109375" style="2" customWidth="1"/>
+    <col min="6405" max="6407" width="14.28515625" style="2" customWidth="1"/>
+    <col min="6408" max="6657" width="9.140625" style="2"/>
+    <col min="6658" max="6658" width="6.42578125" style="2" customWidth="1"/>
+    <col min="6659" max="6659" width="80.140625" style="2" customWidth="1"/>
+    <col min="6660" max="6660" width="15.7109375" style="2" customWidth="1"/>
+    <col min="6661" max="6663" width="14.28515625" style="2" customWidth="1"/>
+    <col min="6664" max="6913" width="9.140625" style="2"/>
+    <col min="6914" max="6914" width="6.42578125" style="2" customWidth="1"/>
+    <col min="6915" max="6915" width="80.140625" style="2" customWidth="1"/>
+    <col min="6916" max="6916" width="15.7109375" style="2" customWidth="1"/>
+    <col min="6917" max="6919" width="14.28515625" style="2" customWidth="1"/>
+    <col min="6920" max="7169" width="9.140625" style="2"/>
+    <col min="7170" max="7170" width="6.42578125" style="2" customWidth="1"/>
+    <col min="7171" max="7171" width="80.140625" style="2" customWidth="1"/>
+    <col min="7172" max="7172" width="15.7109375" style="2" customWidth="1"/>
+    <col min="7173" max="7175" width="14.28515625" style="2" customWidth="1"/>
+    <col min="7176" max="7425" width="9.140625" style="2"/>
+    <col min="7426" max="7426" width="6.42578125" style="2" customWidth="1"/>
+    <col min="7427" max="7427" width="80.140625" style="2" customWidth="1"/>
+    <col min="7428" max="7428" width="15.7109375" style="2" customWidth="1"/>
+    <col min="7429" max="7431" width="14.28515625" style="2" customWidth="1"/>
+    <col min="7432" max="7681" width="9.140625" style="2"/>
+    <col min="7682" max="7682" width="6.42578125" style="2" customWidth="1"/>
+    <col min="7683" max="7683" width="80.140625" style="2" customWidth="1"/>
+    <col min="7684" max="7684" width="15.7109375" style="2" customWidth="1"/>
+    <col min="7685" max="7687" width="14.28515625" style="2" customWidth="1"/>
+    <col min="7688" max="7937" width="9.140625" style="2"/>
+    <col min="7938" max="7938" width="6.42578125" style="2" customWidth="1"/>
+    <col min="7939" max="7939" width="80.140625" style="2" customWidth="1"/>
+    <col min="7940" max="7940" width="15.7109375" style="2" customWidth="1"/>
+    <col min="7941" max="7943" width="14.28515625" style="2" customWidth="1"/>
+    <col min="7944" max="8193" width="9.140625" style="2"/>
+    <col min="8194" max="8194" width="6.42578125" style="2" customWidth="1"/>
+    <col min="8195" max="8195" width="80.140625" style="2" customWidth="1"/>
+    <col min="8196" max="8196" width="15.7109375" style="2" customWidth="1"/>
+    <col min="8197" max="8199" width="14.28515625" style="2" customWidth="1"/>
+    <col min="8200" max="8449" width="9.140625" style="2"/>
+    <col min="8450" max="8450" width="6.42578125" style="2" customWidth="1"/>
+    <col min="8451" max="8451" width="80.140625" style="2" customWidth="1"/>
+    <col min="8452" max="8452" width="15.7109375" style="2" customWidth="1"/>
+    <col min="8453" max="8455" width="14.28515625" style="2" customWidth="1"/>
+    <col min="8456" max="8705" width="9.140625" style="2"/>
+    <col min="8706" max="8706" width="6.42578125" style="2" customWidth="1"/>
+    <col min="8707" max="8707" width="80.140625" style="2" customWidth="1"/>
+    <col min="8708" max="8708" width="15.7109375" style="2" customWidth="1"/>
+    <col min="8709" max="8711" width="14.28515625" style="2" customWidth="1"/>
+    <col min="8712" max="8961" width="9.140625" style="2"/>
+    <col min="8962" max="8962" width="6.42578125" style="2" customWidth="1"/>
+    <col min="8963" max="8963" width="80.140625" style="2" customWidth="1"/>
+    <col min="8964" max="8964" width="15.7109375" style="2" customWidth="1"/>
+    <col min="8965" max="8967" width="14.28515625" style="2" customWidth="1"/>
+    <col min="8968" max="9217" width="9.140625" style="2"/>
+    <col min="9218" max="9218" width="6.42578125" style="2" customWidth="1"/>
+    <col min="9219" max="9219" width="80.140625" style="2" customWidth="1"/>
+    <col min="9220" max="9220" width="15.7109375" style="2" customWidth="1"/>
+    <col min="9221" max="9223" width="14.28515625" style="2" customWidth="1"/>
+    <col min="9224" max="9473" width="9.140625" style="2"/>
+    <col min="9474" max="9474" width="6.42578125" style="2" customWidth="1"/>
+    <col min="9475" max="9475" width="80.140625" style="2" customWidth="1"/>
+    <col min="9476" max="9476" width="15.7109375" style="2" customWidth="1"/>
+    <col min="9477" max="9479" width="14.28515625" style="2" customWidth="1"/>
+    <col min="9480" max="9729" width="9.140625" style="2"/>
+    <col min="9730" max="9730" width="6.42578125" style="2" customWidth="1"/>
+    <col min="9731" max="9731" width="80.140625" style="2" customWidth="1"/>
+    <col min="9732" max="9732" width="15.7109375" style="2" customWidth="1"/>
+    <col min="9733" max="9735" width="14.28515625" style="2" customWidth="1"/>
+    <col min="9736" max="9985" width="9.140625" style="2"/>
+    <col min="9986" max="9986" width="6.42578125" style="2" customWidth="1"/>
+    <col min="9987" max="9987" width="80.140625" style="2" customWidth="1"/>
+    <col min="9988" max="9988" width="15.7109375" style="2" customWidth="1"/>
+    <col min="9989" max="9991" width="14.28515625" style="2" customWidth="1"/>
+    <col min="9992" max="10241" width="9.140625" style="2"/>
+    <col min="10242" max="10242" width="6.42578125" style="2" customWidth="1"/>
+    <col min="10243" max="10243" width="80.140625" style="2" customWidth="1"/>
+    <col min="10244" max="10244" width="15.7109375" style="2" customWidth="1"/>
+    <col min="10245" max="10247" width="14.28515625" style="2" customWidth="1"/>
+    <col min="10248" max="10497" width="9.140625" style="2"/>
+    <col min="10498" max="10498" width="6.42578125" style="2" customWidth="1"/>
+    <col min="10499" max="10499" width="80.140625" style="2" customWidth="1"/>
+    <col min="10500" max="10500" width="15.7109375" style="2" customWidth="1"/>
+    <col min="10501" max="10503" width="14.28515625" style="2" customWidth="1"/>
+    <col min="10504" max="10753" width="9.140625" style="2"/>
+    <col min="10754" max="10754" width="6.42578125" style="2" customWidth="1"/>
+    <col min="10755" max="10755" width="80.140625" style="2" customWidth="1"/>
+    <col min="10756" max="10756" width="15.7109375" style="2" customWidth="1"/>
+    <col min="10757" max="10759" width="14.28515625" style="2" customWidth="1"/>
+    <col min="10760" max="11009" width="9.140625" style="2"/>
+    <col min="11010" max="11010" width="6.42578125" style="2" customWidth="1"/>
+    <col min="11011" max="11011" width="80.140625" style="2" customWidth="1"/>
+    <col min="11012" max="11012" width="15.7109375" style="2" customWidth="1"/>
+    <col min="11013" max="11015" width="14.28515625" style="2" customWidth="1"/>
+    <col min="11016" max="11265" width="9.140625" style="2"/>
+    <col min="11266" max="11266" width="6.42578125" style="2" customWidth="1"/>
+    <col min="11267" max="11267" width="80.140625" style="2" customWidth="1"/>
+    <col min="11268" max="11268" width="15.7109375" style="2" customWidth="1"/>
+    <col min="11269" max="11271" width="14.28515625" style="2" customWidth="1"/>
+    <col min="11272" max="11521" width="9.140625" style="2"/>
+    <col min="11522" max="11522" width="6.42578125" style="2" customWidth="1"/>
+    <col min="11523" max="11523" width="80.140625" style="2" customWidth="1"/>
+    <col min="11524" max="11524" width="15.7109375" style="2" customWidth="1"/>
+    <col min="11525" max="11527" width="14.28515625" style="2" customWidth="1"/>
+    <col min="11528" max="11777" width="9.140625" style="2"/>
+    <col min="11778" max="11778" width="6.42578125" style="2" customWidth="1"/>
+    <col min="11779" max="11779" width="80.140625" style="2" customWidth="1"/>
+    <col min="11780" max="11780" width="15.7109375" style="2" customWidth="1"/>
+    <col min="11781" max="11783" width="14.28515625" style="2" customWidth="1"/>
+    <col min="11784" max="12033" width="9.140625" style="2"/>
+    <col min="12034" max="12034" width="6.42578125" style="2" customWidth="1"/>
+    <col min="12035" max="12035" width="80.140625" style="2" customWidth="1"/>
+    <col min="12036" max="12036" width="15.7109375" style="2" customWidth="1"/>
+    <col min="12037" max="12039" width="14.28515625" style="2" customWidth="1"/>
+    <col min="12040" max="12289" width="9.140625" style="2"/>
+    <col min="12290" max="12290" width="6.42578125" style="2" customWidth="1"/>
+    <col min="12291" max="12291" width="80.140625" style="2" customWidth="1"/>
+    <col min="12292" max="12292" width="15.7109375" style="2" customWidth="1"/>
+    <col min="12293" max="12295" width="14.28515625" style="2" customWidth="1"/>
+    <col min="12296" max="12545" width="9.140625" style="2"/>
+    <col min="12546" max="12546" width="6.42578125" style="2" customWidth="1"/>
+    <col min="12547" max="12547" width="80.140625" style="2" customWidth="1"/>
+    <col min="12548" max="12548" width="15.7109375" style="2" customWidth="1"/>
+    <col min="12549" max="12551" width="14.28515625" style="2" customWidth="1"/>
+    <col min="12552" max="12801" width="9.140625" style="2"/>
+    <col min="12802" max="12802" width="6.42578125" style="2" customWidth="1"/>
+    <col min="12803" max="12803" width="80.140625" style="2" customWidth="1"/>
+    <col min="12804" max="12804" width="15.7109375" style="2" customWidth="1"/>
+    <col min="12805" max="12807" width="14.28515625" style="2" customWidth="1"/>
+    <col min="12808" max="13057" width="9.140625" style="2"/>
+    <col min="13058" max="13058" width="6.42578125" style="2" customWidth="1"/>
+    <col min="13059" max="13059" width="80.140625" style="2" customWidth="1"/>
+    <col min="13060" max="13060" width="15.7109375" style="2" customWidth="1"/>
+    <col min="13061" max="13063" width="14.28515625" style="2" customWidth="1"/>
+    <col min="13064" max="13313" width="9.140625" style="2"/>
+    <col min="13314" max="13314" width="6.42578125" style="2" customWidth="1"/>
+    <col min="13315" max="13315" width="80.140625" style="2" customWidth="1"/>
+    <col min="13316" max="13316" width="15.7109375" style="2" customWidth="1"/>
+    <col min="13317" max="13319" width="14.28515625" style="2" customWidth="1"/>
+    <col min="13320" max="13569" width="9.140625" style="2"/>
+    <col min="13570" max="13570" width="6.42578125" style="2" customWidth="1"/>
+    <col min="13571" max="13571" width="80.140625" style="2" customWidth="1"/>
+    <col min="13572" max="13572" width="15.7109375" style="2" customWidth="1"/>
+    <col min="13573" max="13575" width="14.28515625" style="2" customWidth="1"/>
+    <col min="13576" max="13825" width="9.140625" style="2"/>
+    <col min="13826" max="13826" width="6.42578125" style="2" customWidth="1"/>
+    <col min="13827" max="13827" width="80.140625" style="2" customWidth="1"/>
+    <col min="13828" max="13828" width="15.7109375" style="2" customWidth="1"/>
+    <col min="13829" max="13831" width="14.28515625" style="2" customWidth="1"/>
+    <col min="13832" max="14081" width="9.140625" style="2"/>
+    <col min="14082" max="14082" width="6.42578125" style="2" customWidth="1"/>
+    <col min="14083" max="14083" width="80.140625" style="2" customWidth="1"/>
+    <col min="14084" max="14084" width="15.7109375" style="2" customWidth="1"/>
+    <col min="14085" max="14087" width="14.28515625" style="2" customWidth="1"/>
+    <col min="14088" max="14337" width="9.140625" style="2"/>
+    <col min="14338" max="14338" width="6.42578125" style="2" customWidth="1"/>
+    <col min="14339" max="14339" width="80.140625" style="2" customWidth="1"/>
+    <col min="14340" max="14340" width="15.7109375" style="2" customWidth="1"/>
+    <col min="14341" max="14343" width="14.28515625" style="2" customWidth="1"/>
+    <col min="14344" max="14593" width="9.140625" style="2"/>
+    <col min="14594" max="14594" width="6.42578125" style="2" customWidth="1"/>
+    <col min="14595" max="14595" width="80.140625" style="2" customWidth="1"/>
+    <col min="14596" max="14596" width="15.7109375" style="2" customWidth="1"/>
+    <col min="14597" max="14599" width="14.28515625" style="2" customWidth="1"/>
+    <col min="14600" max="14849" width="9.140625" style="2"/>
+    <col min="14850" max="14850" width="6.42578125" style="2" customWidth="1"/>
+    <col min="14851" max="14851" width="80.140625" style="2" customWidth="1"/>
+    <col min="14852" max="14852" width="15.7109375" style="2" customWidth="1"/>
+    <col min="14853" max="14855" width="14.28515625" style="2" customWidth="1"/>
+    <col min="14856" max="15105" width="9.140625" style="2"/>
+    <col min="15106" max="15106" width="6.42578125" style="2" customWidth="1"/>
+    <col min="15107" max="15107" width="80.140625" style="2" customWidth="1"/>
+    <col min="15108" max="15108" width="15.7109375" style="2" customWidth="1"/>
+    <col min="15109" max="15111" width="14.28515625" style="2" customWidth="1"/>
+    <col min="15112" max="15361" width="9.140625" style="2"/>
+    <col min="15362" max="15362" width="6.42578125" style="2" customWidth="1"/>
+    <col min="15363" max="15363" width="80.140625" style="2" customWidth="1"/>
+    <col min="15364" max="15364" width="15.7109375" style="2" customWidth="1"/>
+    <col min="15365" max="15367" width="14.28515625" style="2" customWidth="1"/>
+    <col min="15368" max="15617" width="9.140625" style="2"/>
+    <col min="15618" max="15618" width="6.42578125" style="2" customWidth="1"/>
+    <col min="15619" max="15619" width="80.140625" style="2" customWidth="1"/>
+    <col min="15620" max="15620" width="15.7109375" style="2" customWidth="1"/>
+    <col min="15621" max="15623" width="14.28515625" style="2" customWidth="1"/>
+    <col min="15624" max="15873" width="9.140625" style="2"/>
+    <col min="15874" max="15874" width="6.42578125" style="2" customWidth="1"/>
+    <col min="15875" max="15875" width="80.140625" style="2" customWidth="1"/>
+    <col min="15876" max="15876" width="15.7109375" style="2" customWidth="1"/>
+    <col min="15877" max="15879" width="14.28515625" style="2" customWidth="1"/>
+    <col min="15880" max="16129" width="9.140625" style="2"/>
+    <col min="16130" max="16130" width="6.42578125" style="2" customWidth="1"/>
+    <col min="16131" max="16131" width="80.140625" style="2" customWidth="1"/>
+    <col min="16132" max="16132" width="15.7109375" style="2" customWidth="1"/>
+    <col min="16133" max="16135" width="14.28515625" style="2" customWidth="1"/>
+    <col min="16136" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="29"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="F1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="27"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="30"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G2" s="37"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-    </row>
-    <row r="5" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A5" s="32" t="s">
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+    </row>
+    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="32"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-    </row>
-    <row r="6" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A6" s="27" t="s">
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+    </row>
+    <row r="6" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A6" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E7" s="33" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E7" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="28" t="s">
         <v>5</v>
       </c>
@@ -1619,48 +1616,48 @@
       <c r="D8" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="34" t="s">
+      <c r="E8" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="28"/>
       <c r="B9" s="28"/>
       <c r="C9" s="28"/>
       <c r="D9" s="28"/>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="38" t="s">
+      <c r="F9" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="39"/>
-    </row>
-    <row r="10" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="G9" s="34"/>
+    </row>
+    <row r="10" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="28"/>
       <c r="B10" s="28"/>
       <c r="C10" s="28"/>
       <c r="D10" s="28"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="40" t="s">
+      <c r="E10" s="31"/>
+      <c r="F10" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="G10" s="40" t="s">
+      <c r="G10" s="35" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="28"/>
       <c r="B11" s="28"/>
       <c r="C11" s="28"/>
       <c r="D11" s="28"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
-    </row>
-    <row r="12" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="E11" s="32"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+    </row>
+    <row r="12" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>1</v>
       </c>
@@ -1681,68 +1678,68 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+    <row r="13" spans="1:10" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="19">
         <f>D14+D51</f>
         <v>0</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="20">
         <f>D13+F13</f>
         <v>0</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="19">
         <f>F14+F51</f>
         <v>0</v>
       </c>
-      <c r="G13" s="21">
+      <c r="G13" s="20">
         <f>IFERROR(F13/D13*100,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
+    <row r="14" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A14" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="19">
         <f>SUM(D15:D40)-D21-D36+D48</f>
         <v>0</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="20">
         <f t="shared" ref="E14:E115" si="0">D14+F14</f>
         <v>0</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="19">
         <f>SUM(F15:F40)-F21-F36+F48</f>
         <v>0</v>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="20">
         <f t="shared" ref="G14:G115" si="1">IFERROR(F14/D14*100,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="C15" s="22" t="s">
         <v>35</v>
       </c>
       <c r="D15" s="16"/>
@@ -1750,20 +1747,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F15" s="18"/>
+      <c r="F15" s="16"/>
       <c r="G15" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="22" t="s">
         <v>38</v>
       </c>
       <c r="D16" s="16"/>
@@ -1771,20 +1768,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F16" s="18"/>
+      <c r="F16" s="16"/>
       <c r="G16" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="23" t="s">
+      <c r="C17" s="22" t="s">
         <v>41</v>
       </c>
       <c r="D17" s="16"/>
@@ -1792,20 +1789,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F17" s="18"/>
+      <c r="F17" s="16"/>
       <c r="G17" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="23" t="s">
+      <c r="C18" s="22" t="s">
         <v>44</v>
       </c>
       <c r="D18" s="16"/>
@@ -1813,20 +1810,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F18" s="18"/>
+      <c r="F18" s="16"/>
       <c r="G18" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="23" t="s">
+      <c r="C19" s="22" t="s">
         <v>47</v>
       </c>
       <c r="D19" s="16"/>
@@ -1834,20 +1831,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F19" s="18"/>
+      <c r="F19" s="16"/>
       <c r="G19" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="45" x14ac:dyDescent="0.2">
       <c r="A20" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="25" t="s">
+      <c r="B20" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="22" t="s">
         <v>50</v>
       </c>
       <c r="D20" s="16"/>
@@ -1855,20 +1852,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F20" s="18"/>
+      <c r="F20" s="16"/>
       <c r="G20" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="25" t="s">
+      <c r="B21" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C21" s="23" t="s">
         <v>168</v>
       </c>
       <c r="D21" s="16"/>
@@ -1876,20 +1873,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F21" s="18"/>
+      <c r="F21" s="16"/>
       <c r="G21" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="B22" s="25" t="s">
+      <c r="B22" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="22" t="s">
         <v>55</v>
       </c>
       <c r="D22" s="16"/>
@@ -1897,20 +1894,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F22" s="18"/>
+      <c r="F22" s="16"/>
       <c r="G22" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="25" t="s">
+      <c r="B23" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="23" t="s">
+      <c r="C23" s="22" t="s">
         <v>58</v>
       </c>
       <c r="D23" s="16"/>
@@ -1918,20 +1915,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F23" s="18"/>
+      <c r="F23" s="16"/>
       <c r="G23" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="B24" s="25" t="s">
+      <c r="B24" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="22" t="s">
         <v>61</v>
       </c>
       <c r="D24" s="16"/>
@@ -1939,20 +1936,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F24" s="18"/>
+      <c r="F24" s="16"/>
       <c r="G24" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="25" t="s">
+      <c r="B25" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="23" t="s">
+      <c r="C25" s="22" t="s">
         <v>64</v>
       </c>
       <c r="D25" s="16"/>
@@ -1960,20 +1957,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F25" s="18"/>
+      <c r="F25" s="16"/>
       <c r="G25" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.2">
       <c r="A26" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="B26" s="25" t="s">
+      <c r="B26" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="C26" s="23" t="s">
+      <c r="C26" s="22" t="s">
         <v>67</v>
       </c>
       <c r="D26" s="16"/>
@@ -1981,20 +1978,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F26" s="18"/>
+      <c r="F26" s="16"/>
       <c r="G26" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A27" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="B27" s="25" t="s">
+      <c r="B27" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="22" t="s">
         <v>70</v>
       </c>
       <c r="D27" s="16"/>
@@ -2002,20 +1999,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F27" s="18"/>
+      <c r="F27" s="16"/>
       <c r="G27" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.2">
       <c r="A28" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="B28" s="25" t="s">
+      <c r="B28" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="22" t="s">
         <v>73</v>
       </c>
       <c r="D28" s="16"/>
@@ -2023,20 +2020,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F28" s="18"/>
+      <c r="F28" s="16"/>
       <c r="G28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A29" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="B29" s="25" t="s">
+      <c r="B29" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="C29" s="23" t="s">
+      <c r="C29" s="22" t="s">
         <v>76</v>
       </c>
       <c r="D29" s="16"/>
@@ -2044,20 +2041,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F29" s="18"/>
+      <c r="F29" s="16"/>
       <c r="G29" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A30" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="B30" s="25" t="s">
+      <c r="B30" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="C30" s="23" t="s">
+      <c r="C30" s="22" t="s">
         <v>79</v>
       </c>
       <c r="D30" s="16"/>
@@ -2065,20 +2062,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F30" s="18"/>
+      <c r="F30" s="16"/>
       <c r="G30" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A31" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="B31" s="25" t="s">
+      <c r="B31" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="C31" s="23" t="s">
+      <c r="C31" s="22" t="s">
         <v>82</v>
       </c>
       <c r="D31" s="16"/>
@@ -2086,20 +2083,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F31" s="18"/>
+      <c r="F31" s="16"/>
       <c r="G31" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A32" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="B32" s="25" t="s">
+      <c r="B32" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="C32" s="23" t="s">
+      <c r="C32" s="22" t="s">
         <v>85</v>
       </c>
       <c r="D32" s="16"/>
@@ -2107,20 +2104,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F32" s="18"/>
+      <c r="F32" s="16"/>
       <c r="G32" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="30" x14ac:dyDescent="0.2">
       <c r="A33" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="B33" s="25" t="s">
+      <c r="B33" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C33" s="22" t="s">
         <v>88</v>
       </c>
       <c r="D33" s="16"/>
@@ -2128,20 +2125,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F33" s="18"/>
+      <c r="F33" s="16"/>
       <c r="G33" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="45" x14ac:dyDescent="0.2">
       <c r="A34" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B34" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="C34" s="23" t="s">
+      <c r="C34" s="22" t="s">
         <v>91</v>
       </c>
       <c r="D34" s="16"/>
@@ -2149,20 +2146,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F34" s="18"/>
+      <c r="F34" s="16"/>
       <c r="G34" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A35" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="B35" s="25" t="s">
+      <c r="B35" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="C35" s="23" t="s">
+      <c r="C35" s="22" t="s">
         <v>94</v>
       </c>
       <c r="D35" s="16"/>
@@ -2170,20 +2167,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F35" s="18"/>
+      <c r="F35" s="16"/>
       <c r="G35" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A36" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="B36" s="25" t="s">
+      <c r="B36" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="C36" s="24" t="s">
+      <c r="C36" s="23" t="s">
         <v>97</v>
       </c>
       <c r="D36" s="16"/>
@@ -2191,20 +2188,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F36" s="18"/>
+      <c r="F36" s="16"/>
       <c r="G36" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A37" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="B37" s="25" t="s">
+      <c r="B37" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="C37" s="23" t="s">
+      <c r="C37" s="22" t="s">
         <v>169</v>
       </c>
       <c r="D37" s="16"/>
@@ -2212,20 +2209,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F37" s="18"/>
+      <c r="F37" s="16"/>
       <c r="G37" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A38" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="B38" s="25" t="s">
+      <c r="B38" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="C38" s="23" t="s">
+      <c r="C38" s="22" t="s">
         <v>170</v>
       </c>
       <c r="D38" s="16"/>
@@ -2233,20 +2230,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F38" s="18"/>
+      <c r="F38" s="16"/>
       <c r="G38" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A39" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="B39" s="25" t="s">
+      <c r="B39" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="C39" s="23" t="s">
+      <c r="C39" s="22" t="s">
         <v>100</v>
       </c>
       <c r="D39" s="16"/>
@@ -2254,65 +2251,65 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F39" s="18"/>
+      <c r="F39" s="16"/>
       <c r="G39" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="30" x14ac:dyDescent="0.2">
       <c r="A40" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="B40" s="25" t="s">
+      <c r="B40" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="C40" s="23" t="s">
+      <c r="C40" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="D40" s="18"/>
+      <c r="D40" s="16"/>
       <c r="E40" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F40" s="18"/>
+      <c r="F40" s="16"/>
       <c r="G40" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="30" x14ac:dyDescent="0.2">
       <c r="A41" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B41" s="25" t="s">
+      <c r="B41" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C41" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="D41" s="18"/>
+      <c r="D41" s="16"/>
       <c r="E41" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F41" s="18"/>
+      <c r="F41" s="16"/>
       <c r="G41" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A42" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="B42" s="25" t="s">
+      <c r="B42" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="C42" s="24" t="s">
+      <c r="C42" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="D42" s="18">
+      <c r="D42" s="16">
         <f>SUM(D43:D49)</f>
         <v>0</v>
       </c>
@@ -2320,7 +2317,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F42" s="18">
+      <c r="F42" s="16">
         <f>SUM(F43:F49)</f>
         <v>0</v>
       </c>
@@ -2329,748 +2326,748 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="B43" s="25" t="s">
+      <c r="B43" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="C43" s="24" t="s">
+      <c r="C43" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="D43" s="18"/>
+      <c r="D43" s="16"/>
       <c r="E43" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F43" s="18"/>
+      <c r="F43" s="16"/>
       <c r="G43" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="B44" s="25" t="s">
+      <c r="B44" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="C44" s="24" t="s">
+      <c r="C44" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="D44" s="18"/>
+      <c r="D44" s="16"/>
       <c r="E44" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F44" s="18"/>
+      <c r="F44" s="16"/>
       <c r="G44" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A45" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="B45" s="25" t="s">
+      <c r="B45" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="C45" s="24" t="s">
+      <c r="C45" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="D45" s="18"/>
+      <c r="D45" s="16"/>
       <c r="E45" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F45" s="18"/>
+      <c r="F45" s="16"/>
       <c r="G45" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="B46" s="25" t="s">
+      <c r="B46" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="C46" s="24" t="s">
+      <c r="C46" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="D46" s="18"/>
+      <c r="D46" s="16"/>
       <c r="E46" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F46" s="18"/>
+      <c r="F46" s="16"/>
       <c r="G46" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A47" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="B47" s="25" t="s">
+      <c r="B47" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="C47" s="24" t="s">
+      <c r="C47" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="D47" s="18"/>
+      <c r="D47" s="16"/>
       <c r="E47" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F47" s="18"/>
+      <c r="F47" s="16"/>
       <c r="G47" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A48" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="B48" s="25" t="s">
+      <c r="B48" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="C48" s="23" t="s">
+      <c r="C48" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="D48" s="18"/>
+      <c r="D48" s="16"/>
       <c r="E48" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F48" s="18"/>
+      <c r="F48" s="16"/>
       <c r="G48" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A49" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="B49" s="25" t="s">
+      <c r="B49" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="C49" s="26" t="s">
+      <c r="C49" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="D49" s="18"/>
+      <c r="D49" s="16"/>
       <c r="E49" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F49" s="18"/>
+      <c r="F49" s="16"/>
       <c r="G49" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A50" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="B50" s="25" t="s">
+      <c r="B50" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="C50" s="23" t="s">
+      <c r="C50" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="D50" s="18"/>
+      <c r="D50" s="16"/>
       <c r="E50" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F50" s="18"/>
+      <c r="F50" s="16"/>
       <c r="G50" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A51" s="19">
+    <row r="51" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A51" s="18">
         <v>39</v>
       </c>
-      <c r="B51" s="19" t="s">
+      <c r="B51" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="C51" s="22" t="s">
+      <c r="C51" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="D51" s="20">
+      <c r="D51" s="19">
         <f>SUM(D52:D77)-D58-D73</f>
         <v>0</v>
       </c>
-      <c r="E51" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F51" s="20">
+      <c r="E51" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F51" s="19">
         <f>SUM(F52:F77)-F58-F73</f>
         <v>0</v>
       </c>
-      <c r="G51" s="21">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="G51" s="20">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A52" s="15">
         <v>40</v>
       </c>
       <c r="B52" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="C52" s="23" t="s">
+      <c r="C52" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="D52" s="18"/>
+      <c r="D52" s="16"/>
       <c r="E52" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F52" s="18"/>
+      <c r="F52" s="16"/>
       <c r="G52" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A53" s="15">
         <v>41</v>
       </c>
       <c r="B53" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="C53" s="23" t="s">
+      <c r="C53" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="D53" s="18"/>
+      <c r="D53" s="16"/>
       <c r="E53" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F53" s="18"/>
+      <c r="F53" s="16"/>
       <c r="G53" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A54" s="15">
         <v>42</v>
       </c>
       <c r="B54" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="C54" s="23" t="s">
+      <c r="C54" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="D54" s="18"/>
+      <c r="D54" s="16"/>
       <c r="E54" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F54" s="18"/>
+      <c r="F54" s="16"/>
       <c r="G54" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A55" s="15">
         <v>43</v>
       </c>
       <c r="B55" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C55" s="23" t="s">
+      <c r="C55" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="D55" s="18"/>
+      <c r="D55" s="16"/>
       <c r="E55" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F55" s="18"/>
+      <c r="F55" s="16"/>
       <c r="G55" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A56" s="15">
         <v>44</v>
       </c>
       <c r="B56" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="C56" s="23" t="s">
+      <c r="C56" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="D56" s="18"/>
+      <c r="D56" s="16"/>
       <c r="E56" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F56" s="18"/>
+      <c r="F56" s="16"/>
       <c r="G56" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" ht="45" x14ac:dyDescent="0.2">
       <c r="A57" s="15">
         <v>45</v>
       </c>
       <c r="B57" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="C57" s="23" t="s">
+      <c r="C57" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="D57" s="18"/>
+      <c r="D57" s="16"/>
       <c r="E57" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F57" s="18"/>
+      <c r="F57" s="16"/>
       <c r="G57" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A58" s="15">
         <v>46</v>
       </c>
       <c r="B58" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="C58" s="24" t="s">
+      <c r="C58" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="D58" s="18"/>
+      <c r="D58" s="16"/>
       <c r="E58" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F58" s="18"/>
+      <c r="F58" s="16"/>
       <c r="G58" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A59" s="15">
         <v>47</v>
       </c>
       <c r="B59" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="C59" s="23" t="s">
+      <c r="C59" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="D59" s="18"/>
+      <c r="D59" s="16"/>
       <c r="E59" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F59" s="18"/>
+      <c r="F59" s="16"/>
       <c r="G59" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A60" s="15">
         <v>48</v>
       </c>
       <c r="B60" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="C60" s="23" t="s">
+      <c r="C60" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="D60" s="18"/>
+      <c r="D60" s="16"/>
       <c r="E60" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F60" s="18"/>
+      <c r="F60" s="16"/>
       <c r="G60" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A61" s="15">
         <v>49</v>
       </c>
       <c r="B61" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="C61" s="23" t="s">
+      <c r="C61" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="D61" s="18"/>
+      <c r="D61" s="16"/>
       <c r="E61" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F61" s="18"/>
+      <c r="F61" s="16"/>
       <c r="G61" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A62" s="15">
         <v>50</v>
       </c>
       <c r="B62" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="C62" s="23" t="s">
+      <c r="C62" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="D62" s="18"/>
+      <c r="D62" s="16"/>
       <c r="E62" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F62" s="18"/>
+      <c r="F62" s="16"/>
       <c r="G62" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" ht="30" x14ac:dyDescent="0.2">
       <c r="A63" s="15">
         <v>51</v>
       </c>
       <c r="B63" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="C63" s="23" t="s">
+      <c r="C63" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="D63" s="18"/>
+      <c r="D63" s="16"/>
       <c r="E63" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F63" s="18"/>
+      <c r="F63" s="16"/>
       <c r="G63" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A64" s="15">
         <v>52</v>
       </c>
       <c r="B64" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="C64" s="23" t="s">
+      <c r="C64" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="D64" s="18"/>
+      <c r="D64" s="16"/>
       <c r="E64" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F64" s="18"/>
+      <c r="F64" s="16"/>
       <c r="G64" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" ht="30" x14ac:dyDescent="0.2">
       <c r="A65" s="15">
         <v>53</v>
       </c>
       <c r="B65" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="C65" s="23" t="s">
+      <c r="C65" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="D65" s="18"/>
+      <c r="D65" s="16"/>
       <c r="E65" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F65" s="18"/>
+      <c r="F65" s="16"/>
       <c r="G65" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A66" s="15">
         <v>54</v>
       </c>
       <c r="B66" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="C66" s="23" t="s">
+      <c r="C66" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="D66" s="18"/>
+      <c r="D66" s="16"/>
       <c r="E66" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F66" s="18"/>
+      <c r="F66" s="16"/>
       <c r="G66" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A67" s="15">
         <v>55</v>
       </c>
       <c r="B67" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="C67" s="23" t="s">
+      <c r="C67" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="D67" s="18"/>
+      <c r="D67" s="16"/>
       <c r="E67" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F67" s="18"/>
+      <c r="F67" s="16"/>
       <c r="G67" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A68" s="15">
         <v>56</v>
       </c>
       <c r="B68" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="C68" s="23" t="s">
+      <c r="C68" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="D68" s="18"/>
+      <c r="D68" s="16"/>
       <c r="E68" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F68" s="18"/>
+      <c r="F68" s="16"/>
       <c r="G68" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A69" s="15">
         <v>57</v>
       </c>
       <c r="B69" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="C69" s="23" t="s">
+      <c r="C69" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="D69" s="18"/>
+      <c r="D69" s="16"/>
       <c r="E69" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F69" s="18"/>
+      <c r="F69" s="16"/>
       <c r="G69" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" ht="30" x14ac:dyDescent="0.2">
       <c r="A70" s="15">
         <v>58</v>
       </c>
       <c r="B70" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="C70" s="23" t="s">
+      <c r="C70" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="D70" s="18"/>
+      <c r="D70" s="16"/>
       <c r="E70" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F70" s="18"/>
+      <c r="F70" s="16"/>
       <c r="G70" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" ht="45" x14ac:dyDescent="0.2">
       <c r="A71" s="15">
         <v>59</v>
       </c>
       <c r="B71" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="C71" s="23" t="s">
+      <c r="C71" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="D71" s="18"/>
+      <c r="D71" s="16"/>
       <c r="E71" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F71" s="18"/>
+      <c r="F71" s="16"/>
       <c r="G71" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A72" s="15">
         <v>60</v>
       </c>
       <c r="B72" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="C72" s="23" t="s">
+      <c r="C72" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="D72" s="18"/>
+      <c r="D72" s="16"/>
       <c r="E72" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F72" s="18"/>
+      <c r="F72" s="16"/>
       <c r="G72" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A73" s="15">
         <v>61</v>
       </c>
       <c r="B73" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="C73" s="24" t="s">
+      <c r="C73" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="D73" s="18"/>
+      <c r="D73" s="16"/>
       <c r="E73" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F73" s="18"/>
+      <c r="F73" s="16"/>
       <c r="G73" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A74" s="15">
         <v>62</v>
       </c>
       <c r="B74" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="C74" s="23" t="s">
+      <c r="C74" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="D74" s="18"/>
+      <c r="D74" s="16"/>
       <c r="E74" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F74" s="18"/>
+      <c r="F74" s="16"/>
       <c r="G74" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" ht="30" x14ac:dyDescent="0.2">
       <c r="A75" s="15">
         <v>63</v>
       </c>
       <c r="B75" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="C75" s="23" t="s">
+      <c r="C75" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="D75" s="18"/>
+      <c r="D75" s="16"/>
       <c r="E75" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F75" s="18"/>
+      <c r="F75" s="16"/>
       <c r="G75" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" ht="30" x14ac:dyDescent="0.2">
       <c r="A76" s="15">
         <v>64</v>
       </c>
       <c r="B76" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="C76" s="23" t="s">
+      <c r="C76" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="D76" s="18"/>
+      <c r="D76" s="16"/>
       <c r="E76" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F76" s="18"/>
+      <c r="F76" s="16"/>
       <c r="G76" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A77" s="15">
         <v>65</v>
       </c>
       <c r="B77" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="C77" s="23" t="s">
+      <c r="C77" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="D77" s="18"/>
+      <c r="D77" s="16"/>
       <c r="E77" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F77" s="18"/>
+      <c r="F77" s="16"/>
       <c r="G77" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A78" s="15"/>
       <c r="B78" s="15"/>
       <c r="C78" s="14"/>
@@ -3079,13 +3076,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F78" s="18"/>
+      <c r="F78" s="16"/>
       <c r="G78" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A79" s="15"/>
       <c r="B79" s="15"/>
       <c r="C79" s="14"/>
@@ -3094,13 +3091,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F79" s="18"/>
+      <c r="F79" s="16"/>
       <c r="G79" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A80" s="15"/>
       <c r="B80" s="15"/>
       <c r="C80" s="14"/>
@@ -3109,13 +3106,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F80" s="18"/>
+      <c r="F80" s="16"/>
       <c r="G80" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A81" s="15"/>
       <c r="B81" s="15"/>
       <c r="C81" s="14"/>
@@ -3124,13 +3121,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F81" s="18"/>
+      <c r="F81" s="16"/>
       <c r="G81" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A82" s="15"/>
       <c r="B82" s="15"/>
       <c r="C82" s="14"/>
@@ -3139,13 +3136,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F82" s="18"/>
+      <c r="F82" s="16"/>
       <c r="G82" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A83" s="15"/>
       <c r="B83" s="15"/>
       <c r="C83" s="14"/>
@@ -3154,13 +3151,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F83" s="18"/>
+      <c r="F83" s="16"/>
       <c r="G83" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A84" s="15"/>
       <c r="B84" s="15"/>
       <c r="C84" s="14"/>
@@ -3169,13 +3166,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F84" s="18"/>
+      <c r="F84" s="16"/>
       <c r="G84" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:7" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A85" s="15"/>
       <c r="B85" s="15"/>
       <c r="C85" s="14"/>
@@ -3184,13 +3181,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F85" s="18"/>
+      <c r="F85" s="16"/>
       <c r="G85" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A86" s="15"/>
       <c r="B86" s="15"/>
       <c r="C86" s="14"/>
@@ -3199,13 +3196,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F86" s="18"/>
+      <c r="F86" s="16"/>
       <c r="G86" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A87" s="15"/>
       <c r="B87" s="15"/>
       <c r="C87" s="14"/>
@@ -3214,13 +3211,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F87" s="18"/>
+      <c r="F87" s="16"/>
       <c r="G87" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A88" s="15"/>
       <c r="B88" s="15"/>
       <c r="C88" s="14"/>
@@ -3229,13 +3226,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F88" s="18"/>
+      <c r="F88" s="16"/>
       <c r="G88" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A89" s="15"/>
       <c r="B89" s="15"/>
       <c r="C89" s="14"/>
@@ -3244,13 +3241,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F89" s="18"/>
+      <c r="F89" s="16"/>
       <c r="G89" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A90" s="15"/>
       <c r="B90" s="15"/>
       <c r="C90" s="14"/>
@@ -3259,13 +3256,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F90" s="18"/>
+      <c r="F90" s="16"/>
       <c r="G90" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A91" s="15"/>
       <c r="B91" s="15"/>
       <c r="C91" s="14"/>
@@ -3274,13 +3271,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F91" s="18"/>
+      <c r="F91" s="16"/>
       <c r="G91" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A92" s="15"/>
       <c r="B92" s="15"/>
       <c r="C92" s="14"/>
@@ -3289,13 +3286,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F92" s="18"/>
+      <c r="F92" s="16"/>
       <c r="G92" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A93" s="15"/>
       <c r="B93" s="15"/>
       <c r="C93" s="14"/>
@@ -3304,13 +3301,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F93" s="18"/>
+      <c r="F93" s="16"/>
       <c r="G93" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A94" s="15"/>
       <c r="B94" s="15"/>
       <c r="C94" s="14"/>
@@ -3319,13 +3316,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F94" s="18"/>
+      <c r="F94" s="16"/>
       <c r="G94" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A95" s="15"/>
       <c r="B95" s="15"/>
       <c r="C95" s="14"/>
@@ -3334,13 +3331,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F95" s="18"/>
+      <c r="F95" s="16"/>
       <c r="G95" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A96" s="15"/>
       <c r="B96" s="15"/>
       <c r="C96" s="14"/>
@@ -3349,13 +3346,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F96" s="18"/>
+      <c r="F96" s="16"/>
       <c r="G96" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A97" s="15"/>
       <c r="B97" s="15"/>
       <c r="C97" s="14"/>
@@ -3364,13 +3361,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F97" s="18"/>
+      <c r="F97" s="16"/>
       <c r="G97" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A98" s="15"/>
       <c r="B98" s="15"/>
       <c r="C98" s="14"/>
@@ -3379,13 +3376,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F98" s="18"/>
+      <c r="F98" s="16"/>
       <c r="G98" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A99" s="15"/>
       <c r="B99" s="15"/>
       <c r="C99" s="14"/>
@@ -3394,13 +3391,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F99" s="18"/>
+      <c r="F99" s="16"/>
       <c r="G99" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A100" s="15"/>
       <c r="B100" s="15"/>
       <c r="C100" s="14"/>
@@ -3409,13 +3406,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F100" s="18"/>
+      <c r="F100" s="16"/>
       <c r="G100" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A101" s="15"/>
       <c r="B101" s="15"/>
       <c r="C101" s="14"/>
@@ -3424,13 +3421,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F101" s="18"/>
+      <c r="F101" s="16"/>
       <c r="G101" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A102" s="15"/>
       <c r="B102" s="15"/>
       <c r="C102" s="14"/>
@@ -3439,13 +3436,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F102" s="18"/>
+      <c r="F102" s="16"/>
       <c r="G102" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A103" s="15"/>
       <c r="B103" s="15"/>
       <c r="C103" s="14"/>
@@ -3454,13 +3451,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F103" s="18"/>
+      <c r="F103" s="16"/>
       <c r="G103" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A104" s="15"/>
       <c r="B104" s="15"/>
       <c r="C104" s="14"/>
@@ -3469,13 +3466,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F104" s="18"/>
+      <c r="F104" s="16"/>
       <c r="G104" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A105" s="15"/>
       <c r="B105" s="15"/>
       <c r="C105" s="14"/>
@@ -3484,13 +3481,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F105" s="18"/>
+      <c r="F105" s="16"/>
       <c r="G105" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A106" s="15"/>
       <c r="B106" s="15"/>
       <c r="C106" s="14"/>
@@ -3499,13 +3496,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F106" s="18"/>
+      <c r="F106" s="16"/>
       <c r="G106" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A107" s="15"/>
       <c r="B107" s="15"/>
       <c r="C107" s="14"/>
@@ -3514,13 +3511,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F107" s="18"/>
+      <c r="F107" s="16"/>
       <c r="G107" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A108" s="15"/>
       <c r="B108" s="15"/>
       <c r="C108" s="14"/>
@@ -3529,13 +3526,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F108" s="18"/>
+      <c r="F108" s="16"/>
       <c r="G108" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A109" s="15"/>
       <c r="B109" s="15"/>
       <c r="C109" s="14"/>
@@ -3544,13 +3541,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F109" s="18"/>
+      <c r="F109" s="16"/>
       <c r="G109" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A110" s="15"/>
       <c r="B110" s="15"/>
       <c r="C110" s="14"/>
@@ -3559,13 +3556,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F110" s="18"/>
+      <c r="F110" s="16"/>
       <c r="G110" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A111" s="15"/>
       <c r="B111" s="15"/>
       <c r="C111" s="14"/>
@@ -3574,13 +3571,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F111" s="18"/>
+      <c r="F111" s="16"/>
       <c r="G111" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A112" s="15"/>
       <c r="B112" s="15"/>
       <c r="C112" s="14"/>
@@ -3589,13 +3586,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F112" s="18"/>
+      <c r="F112" s="16"/>
       <c r="G112" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A113" s="15"/>
       <c r="B113" s="15"/>
       <c r="C113" s="14"/>
@@ -3604,13 +3601,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F113" s="18"/>
+      <c r="F113" s="16"/>
       <c r="G113" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A114" s="15"/>
       <c r="B114" s="15"/>
       <c r="C114" s="14"/>
@@ -3619,13 +3616,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F114" s="18"/>
+      <c r="F114" s="16"/>
       <c r="G114" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A115" s="15"/>
       <c r="B115" s="15"/>
       <c r="C115" s="14"/>
@@ -3634,13 +3631,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F115" s="18"/>
+      <c r="F115" s="16"/>
       <c r="G115" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A116" s="15"/>
       <c r="B116" s="15"/>
       <c r="C116" s="14"/>
@@ -3649,13 +3646,13 @@
         <f t="shared" ref="E116:E147" si="2">D116+F116</f>
         <v>0</v>
       </c>
-      <c r="F116" s="18"/>
+      <c r="F116" s="16"/>
       <c r="G116" s="17">
         <f t="shared" ref="G116:G147" si="3">IFERROR(F116/D116*100,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A117" s="15"/>
       <c r="B117" s="15"/>
       <c r="C117" s="14"/>
@@ -3664,13 +3661,13 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F117" s="18"/>
+      <c r="F117" s="16"/>
       <c r="G117" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A118" s="15"/>
       <c r="B118" s="15"/>
       <c r="C118" s="14"/>
@@ -3679,13 +3676,13 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F118" s="18"/>
+      <c r="F118" s="16"/>
       <c r="G118" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A119" s="15"/>
       <c r="B119" s="15"/>
       <c r="C119" s="14"/>
@@ -3694,13 +3691,13 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F119" s="18"/>
+      <c r="F119" s="16"/>
       <c r="G119" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A120" s="15"/>
       <c r="B120" s="15"/>
       <c r="C120" s="14"/>
@@ -3709,13 +3706,13 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F120" s="18"/>
+      <c r="F120" s="16"/>
       <c r="G120" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A121" s="15"/>
       <c r="B121" s="15"/>
       <c r="C121" s="14"/>
@@ -3724,208 +3721,208 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F121" s="18"/>
+      <c r="F121" s="16"/>
       <c r="G121" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A122" s="15"/>
       <c r="B122" s="15"/>
       <c r="C122" s="14"/>
-      <c r="D122" s="18"/>
+      <c r="D122" s="16"/>
       <c r="E122" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F122" s="18"/>
+      <c r="F122" s="16"/>
       <c r="G122" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A123" s="15"/>
       <c r="B123" s="15"/>
       <c r="C123" s="14"/>
-      <c r="D123" s="18"/>
+      <c r="D123" s="16"/>
       <c r="E123" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F123" s="18"/>
+      <c r="F123" s="16"/>
       <c r="G123" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A124" s="15"/>
       <c r="B124" s="15"/>
       <c r="C124" s="14"/>
-      <c r="D124" s="18"/>
+      <c r="D124" s="16"/>
       <c r="E124" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F124" s="18"/>
+      <c r="F124" s="16"/>
       <c r="G124" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A125" s="15"/>
       <c r="B125" s="15"/>
       <c r="C125" s="14"/>
-      <c r="D125" s="18"/>
+      <c r="D125" s="16"/>
       <c r="E125" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F125" s="18"/>
+      <c r="F125" s="16"/>
       <c r="G125" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A126" s="15"/>
       <c r="B126" s="15"/>
       <c r="C126" s="14"/>
-      <c r="D126" s="18"/>
+      <c r="D126" s="16"/>
       <c r="E126" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F126" s="18"/>
+      <c r="F126" s="16"/>
       <c r="G126" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A127" s="15"/>
       <c r="B127" s="15"/>
       <c r="C127" s="14"/>
-      <c r="D127" s="18"/>
+      <c r="D127" s="16"/>
       <c r="E127" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F127" s="18"/>
+      <c r="F127" s="16"/>
       <c r="G127" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A128" s="15"/>
       <c r="B128" s="15"/>
       <c r="C128" s="14"/>
-      <c r="D128" s="18"/>
+      <c r="D128" s="16"/>
       <c r="E128" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F128" s="18"/>
+      <c r="F128" s="16"/>
       <c r="G128" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A129" s="15"/>
       <c r="B129" s="15"/>
       <c r="C129" s="14"/>
-      <c r="D129" s="18"/>
+      <c r="D129" s="16"/>
       <c r="E129" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F129" s="18"/>
+      <c r="F129" s="16"/>
       <c r="G129" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A130" s="15"/>
       <c r="B130" s="15"/>
       <c r="C130" s="14"/>
-      <c r="D130" s="18"/>
+      <c r="D130" s="16"/>
       <c r="E130" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F130" s="18"/>
+      <c r="F130" s="16"/>
       <c r="G130" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A131" s="15"/>
       <c r="B131" s="15"/>
       <c r="C131" s="14"/>
-      <c r="D131" s="18"/>
+      <c r="D131" s="16"/>
       <c r="E131" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F131" s="18"/>
+      <c r="F131" s="16"/>
       <c r="G131" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A132" s="15"/>
       <c r="B132" s="15"/>
       <c r="C132" s="14"/>
-      <c r="D132" s="18"/>
+      <c r="D132" s="16"/>
       <c r="E132" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F132" s="18"/>
+      <c r="F132" s="16"/>
       <c r="G132" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A133" s="15"/>
       <c r="B133" s="15"/>
       <c r="C133" s="14"/>
-      <c r="D133" s="18"/>
+      <c r="D133" s="16"/>
       <c r="E133" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F133" s="18"/>
+      <c r="F133" s="16"/>
       <c r="G133" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A134" s="15"/>
       <c r="B134" s="15"/>
       <c r="C134" s="14"/>
-      <c r="D134" s="18"/>
+      <c r="D134" s="16"/>
       <c r="E134" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F134" s="18"/>
+      <c r="F134" s="16"/>
       <c r="G134" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:7" s="6" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A135" s="15"/>
       <c r="B135" s="15"/>
       <c r="C135" s="14"/>
@@ -3934,13 +3931,13 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F135" s="18"/>
+      <c r="F135" s="16"/>
       <c r="G135" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A136" s="15"/>
       <c r="B136" s="15"/>
       <c r="C136" s="14"/>
@@ -3949,13 +3946,13 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F136" s="18"/>
+      <c r="F136" s="16"/>
       <c r="G136" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A137" s="15"/>
       <c r="B137" s="15"/>
       <c r="C137" s="14"/>
@@ -3964,13 +3961,13 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F137" s="18"/>
+      <c r="F137" s="16"/>
       <c r="G137" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A138" s="15"/>
       <c r="B138" s="15"/>
       <c r="C138" s="14"/>
@@ -3979,13 +3976,13 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F138" s="18"/>
+      <c r="F138" s="16"/>
       <c r="G138" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A139" s="15"/>
       <c r="B139" s="15"/>
       <c r="C139" s="14"/>
@@ -3994,13 +3991,13 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F139" s="18"/>
+      <c r="F139" s="16"/>
       <c r="G139" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A140" s="15"/>
       <c r="B140" s="15"/>
       <c r="C140" s="14"/>
@@ -4009,13 +4006,13 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F140" s="18"/>
+      <c r="F140" s="16"/>
       <c r="G140" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A141" s="15"/>
       <c r="B141" s="15"/>
       <c r="C141" s="14"/>
@@ -4024,13 +4021,13 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F141" s="18"/>
+      <c r="F141" s="16"/>
       <c r="G141" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A142" s="15"/>
       <c r="B142" s="15"/>
       <c r="C142" s="14"/>
@@ -4039,13 +4036,13 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F142" s="18"/>
+      <c r="F142" s="16"/>
       <c r="G142" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A143" s="15"/>
       <c r="B143" s="15"/>
       <c r="C143" s="14"/>
@@ -4054,13 +4051,13 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F143" s="18"/>
+      <c r="F143" s="16"/>
       <c r="G143" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A144" s="15"/>
       <c r="B144" s="15"/>
       <c r="C144" s="14"/>
@@ -4069,13 +4066,13 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F144" s="18"/>
+      <c r="F144" s="16"/>
       <c r="G144" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A145" s="15"/>
       <c r="B145" s="15"/>
       <c r="C145" s="14"/>
@@ -4084,13 +4081,13 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F145" s="18"/>
+      <c r="F145" s="16"/>
       <c r="G145" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A146" s="15"/>
       <c r="B146" s="15"/>
       <c r="C146" s="14"/>
@@ -4099,13 +4096,13 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F146" s="18"/>
+      <c r="F146" s="16"/>
       <c r="G146" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A147" s="15"/>
       <c r="B147" s="15"/>
       <c r="C147" s="14"/>
@@ -4114,19 +4111,19 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F147" s="18"/>
+      <c r="F147" s="16"/>
       <c r="G147" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A148" s="8"/>
       <c r="B148" s="8"/>
       <c r="C148" s="9"/>
       <c r="G148" s="6"/>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A149" s="8"/>
       <c r="B149" s="8"/>
       <c r="C149" s="1" t="s">
@@ -4134,46 +4131,46 @@
       </c>
       <c r="G149" s="6"/>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A150" s="10"/>
       <c r="B150" s="10"/>
       <c r="C150" s="10"/>
-      <c r="D150" s="33" t="s">
+      <c r="D150" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="E150" s="33"/>
-      <c r="F150" s="33"/>
-      <c r="G150" s="33"/>
-    </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E150" s="26"/>
+      <c r="F150" s="26"/>
+      <c r="G150" s="26"/>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A151" s="11"/>
       <c r="B151" s="11"/>
       <c r="C151" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D151" s="29"/>
-      <c r="E151" s="29"/>
-      <c r="F151" s="29"/>
-      <c r="G151" s="29"/>
+      <c r="D151" s="27"/>
+      <c r="E151" s="27"/>
+      <c r="F151" s="27"/>
+      <c r="G151" s="27"/>
       <c r="H151" s="11"/>
       <c r="I151" s="11"/>
       <c r="J151" s="11"/>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A152" s="9"/>
       <c r="B152" s="9"/>
       <c r="C152" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D152" s="33"/>
-      <c r="E152" s="33"/>
-      <c r="F152" s="33"/>
-      <c r="G152" s="33"/>
+      <c r="D152" s="26"/>
+      <c r="E152" s="26"/>
+      <c r="F152" s="26"/>
+      <c r="G152" s="26"/>
       <c r="H152" s="13"/>
       <c r="I152" s="13"/>
       <c r="J152" s="13"/>
     </row>
-    <row r="153" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -4181,46 +4178,53 @@
       <c r="E153" s="2"/>
       <c r="F153" s="2"/>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C158" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C159" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C160" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="161" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C161" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="162" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C162" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="163" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C163" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="165" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C165" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="168" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C168" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="A5:G5"/>
     <mergeCell ref="D150:G150"/>
     <mergeCell ref="D151:G151"/>
     <mergeCell ref="D152:G152"/>
@@ -4233,13 +4237,6 @@
     <mergeCell ref="F9:G9"/>
     <mergeCell ref="F10:F11"/>
     <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="D4:G4"/>
-    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="3.937007874015748E-2" right="3.937007874015748E-2" top="0.19685039370078741" bottom="3.937007874015748E-2" header="3.937007874015748E-2" footer="3.937007874015748E-2"/>
